--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$521</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ504"/>
+  <dimension ref="A1:AJ521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9919,11 +9919,11 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA113" t="n">
         <v>-1.11</v>
@@ -9934,6 +9934,15 @@
       <c r="AC113" t="n">
         <v>2.64</v>
       </c>
+      <c r="AD113" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>-3.19</v>
+      </c>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -9942,7 +9951,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -9994,11 +10003,11 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA114" t="n">
         <v>-2.05</v>
@@ -10009,6 +10018,15 @@
       <c r="AC114" t="n">
         <v>-6.48</v>
       </c>
+      <c r="AD114" t="n">
+        <v>-13.31</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>-14.68</v>
+      </c>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -10017,7 +10035,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10069,11 +10087,11 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z115" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA115" t="n">
         <v>-9.960000000000001</v>
@@ -10084,6 +10102,15 @@
       <c r="AC115" t="n">
         <v>-4.46</v>
       </c>
+      <c r="AD115" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>-15.2</v>
+      </c>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -10092,7 +10119,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10144,11 +10171,11 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA116" t="n">
         <v>8.92</v>
@@ -10159,6 +10186,15 @@
       <c r="AC116" t="n">
         <v>13.47</v>
       </c>
+      <c r="AD116" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>-4.74</v>
+      </c>
       <c r="AG116" t="b">
         <v>1</v>
       </c>
@@ -10167,7 +10203,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -10219,11 +10255,11 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z117" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA117" t="n">
         <v>-1.6</v>
@@ -10234,6 +10270,15 @@
       <c r="AC117" t="n">
         <v>6.5</v>
       </c>
+      <c r="AD117" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>-5.01</v>
+      </c>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -10242,7 +10287,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -10294,11 +10339,11 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z118" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA118" t="n">
         <v>-12.29</v>
@@ -10309,6 +10354,15 @@
       <c r="AC118" t="n">
         <v>-5.51</v>
       </c>
+      <c r="AD118" t="n">
+        <v>-9.32</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>-20.55</v>
+      </c>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -10317,7 +10371,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10369,11 +10423,11 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z119" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA119" t="n">
         <v>-14.49</v>
@@ -10384,6 +10438,15 @@
       <c r="AC119" t="n">
         <v>-13.46</v>
       </c>
+      <c r="AD119" t="n">
+        <v>-15.83</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>-17.95</v>
+      </c>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -10392,7 +10455,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10444,11 +10507,11 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA120" t="n">
         <v>-4.39</v>
@@ -10459,6 +10522,15 @@
       <c r="AC120" t="n">
         <v>-1.34</v>
       </c>
+      <c r="AD120" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>-10.31</v>
+      </c>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -10467,7 +10539,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10519,11 +10591,11 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z121" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA121" t="n">
         <v>8.210000000000001</v>
@@ -10534,6 +10606,15 @@
       <c r="AC121" t="n">
         <v>0.65</v>
       </c>
+      <c r="AD121" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>-2.59</v>
+      </c>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -10542,7 +10623,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -10594,11 +10675,11 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA122" t="n">
         <v>17.92</v>
@@ -10609,6 +10690,15 @@
       <c r="AC122" t="n">
         <v>6.22</v>
       </c>
+      <c r="AD122" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.18</v>
+      </c>
       <c r="AG122" t="b">
         <v>1</v>
       </c>
@@ -10617,7 +10707,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -10669,11 +10759,11 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA123" t="n">
         <v>-1.27</v>
@@ -10684,6 +10774,15 @@
       <c r="AC123" t="n">
         <v>17.68</v>
       </c>
+      <c r="AD123" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>-4.3</v>
+      </c>
       <c r="AG123" t="b">
         <v>1</v>
       </c>
@@ -10692,7 +10791,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -10744,11 +10843,11 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA124" t="n">
         <v>-8.640000000000001</v>
@@ -10759,6 +10858,15 @@
       <c r="AC124" t="n">
         <v>2.78</v>
       </c>
+      <c r="AD124" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>-9.52</v>
+      </c>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -10767,7 +10875,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10819,11 +10927,11 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA125" t="n">
         <v>-1.75</v>
@@ -10834,6 +10942,15 @@
       <c r="AC125" t="n">
         <v>10.63</v>
       </c>
+      <c r="AD125" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>-3.9</v>
+      </c>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -10842,7 +10959,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -10894,11 +11011,11 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z126" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA126" t="n">
         <v>-9.369999999999999</v>
@@ -10909,6 +11026,15 @@
       <c r="AC126" t="n">
         <v>8.57</v>
       </c>
+      <c r="AD126" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>-13.02</v>
+      </c>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -10917,7 +11043,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -10969,11 +11095,11 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA127" t="n">
         <v>-6.15</v>
@@ -10984,6 +11110,15 @@
       <c r="AC127" t="n">
         <v>5.35</v>
       </c>
+      <c r="AD127" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>-7.75</v>
+      </c>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -10992,7 +11127,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -11044,11 +11179,11 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA128" t="n">
         <v>-8.289999999999999</v>
@@ -11059,6 +11194,15 @@
       <c r="AC128" t="n">
         <v>1.45</v>
       </c>
+      <c r="AD128" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>-11.03</v>
+      </c>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -11067,7 +11211,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -11119,11 +11263,11 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z129" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA129" t="n">
         <v>-68.09</v>
@@ -11134,6 +11278,15 @@
       <c r="AC129" t="n">
         <v>-62.39</v>
       </c>
+      <c r="AD129" t="n">
+        <v>-65.70999999999999</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>-56.57</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>-68.98</v>
+      </c>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -11142,7 +11295,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -11247,7 +11400,7 @@
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -11371,7 +11524,7 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -11495,7 +11648,7 @@
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -11619,7 +11772,7 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -11743,7 +11896,7 @@
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -11867,7 +12020,7 @@
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -11991,7 +12144,7 @@
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -12112,7 +12265,7 @@
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -12236,7 +12389,7 @@
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -12360,7 +12513,7 @@
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -12484,7 +12637,7 @@
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -12608,7 +12761,7 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -12732,7 +12885,7 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -12856,7 +13009,7 @@
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -12980,7 +13133,7 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -13104,7 +13257,7 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -13228,7 +13381,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -13352,7 +13505,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -13476,7 +13629,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -13600,7 +13753,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -13724,7 +13877,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -13848,7 +14001,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -13972,7 +14125,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -14096,7 +14249,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -14220,7 +14373,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -14344,7 +14497,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -14468,7 +14621,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -14592,7 +14745,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -14716,7 +14869,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -14840,7 +14993,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -14964,7 +15117,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -15088,7 +15241,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -15212,7 +15365,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -15336,7 +15489,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -15460,7 +15613,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -15584,7 +15737,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -15708,7 +15861,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -15832,7 +15985,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -16067,7 +16220,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -16191,7 +16344,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -16315,7 +16468,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -16439,7 +16592,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -16563,7 +16716,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -16687,7 +16840,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -16811,7 +16964,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -16935,7 +17088,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -17059,7 +17212,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -17183,7 +17336,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -17418,7 +17571,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -17542,13 +17695,16 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
       </c>
       <c r="AB181" t="n">
         <v>-2.55</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>-4.58</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -17663,13 +17819,16 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
       </c>
       <c r="AB182" t="n">
         <v>-3.73</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>-8.890000000000001</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -17784,13 +17943,16 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
       </c>
       <c r="AB183" t="n">
         <v>-6.99</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>-5.39</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -17905,13 +18067,16 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
       </c>
       <c r="AB184" t="n">
         <v>23.68</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>11.33</v>
       </c>
       <c r="AG184" t="b">
         <v>1</v>
@@ -18026,13 +18191,16 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
       </c>
       <c r="AB185" t="n">
         <v>-8.17</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>-10.93</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -18147,13 +18315,16 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
       </c>
       <c r="AB186" t="n">
         <v>-60.48</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>-63.97</v>
       </c>
       <c r="AG186" t="b">
         <v>0</v>
@@ -18268,7 +18439,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -18389,7 +18560,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -18510,7 +18681,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -18631,7 +18802,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -18752,7 +18923,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -18873,7 +19044,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -18994,7 +19165,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -19115,7 +19286,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19236,7 +19407,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19357,7 +19528,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -19478,7 +19649,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -19821,7 +19992,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -19942,7 +20113,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -20063,7 +20234,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -20184,7 +20355,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -20196,7 +20367,7 @@
         <v>0</v>
       </c>
       <c r="AH203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI203" t="inlineStr">
         <is>
@@ -20305,7 +20476,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -20426,7 +20597,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -20547,7 +20718,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -20668,7 +20839,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -20680,7 +20851,7 @@
         <v>0</v>
       </c>
       <c r="AH207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
@@ -20789,7 +20960,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -20910,7 +21081,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21031,7 +21202,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21152,7 +21323,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -21273,7 +21444,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -21505,7 +21676,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -21626,7 +21797,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -21747,7 +21918,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -21868,7 +22039,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -21989,7 +22160,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22110,7 +22281,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -22231,7 +22402,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -22352,7 +22523,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -22473,7 +22644,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -22594,7 +22765,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -22715,7 +22886,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -22727,7 +22898,7 @@
         <v>0</v>
       </c>
       <c r="AH224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
@@ -22836,7 +23007,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -22957,7 +23128,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23078,7 +23249,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -23199,7 +23370,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -23320,7 +23491,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -23441,7 +23612,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -23562,7 +23733,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -23794,7 +23965,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24137,7 +24308,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -24258,7 +24429,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -24379,7 +24550,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -24500,7 +24671,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -24621,7 +24792,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -24742,7 +24913,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -24863,7 +25034,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -24984,7 +25155,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -25105,7 +25276,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -25226,7 +25397,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -25347,7 +25518,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -25359,7 +25530,7 @@
         <v>0</v>
       </c>
       <c r="AH246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
@@ -25468,7 +25639,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -25589,7 +25760,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -25710,7 +25881,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -25831,7 +26002,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -25952,7 +26123,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -26073,7 +26244,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -26194,7 +26365,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -26315,7 +26486,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -26327,7 +26498,7 @@
         <v>0</v>
       </c>
       <c r="AH254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
@@ -26436,7 +26607,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -26779,7 +26950,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -27122,7 +27293,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -27243,7 +27414,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -27364,7 +27535,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -27485,7 +27656,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -27717,7 +27888,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -27838,7 +28009,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -27959,7 +28130,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -28080,16 +28251,19 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
       </c>
+      <c r="AB269" t="n">
+        <v>-4.98</v>
+      </c>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
       <c r="AH269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI269" t="inlineStr">
         <is>
@@ -28198,16 +28372,19 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
       </c>
+      <c r="AB270" t="n">
+        <v>-4.39</v>
+      </c>
       <c r="AG270" t="b">
         <v>0</v>
       </c>
       <c r="AH270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI270" t="inlineStr">
         <is>
@@ -28316,16 +28493,19 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
       </c>
+      <c r="AB271" t="n">
+        <v>-5.61</v>
+      </c>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
       <c r="AH271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI271" t="inlineStr">
         <is>
@@ -28434,10 +28614,13 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>-9.02</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -28552,10 +28735,13 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>10.47</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -28670,10 +28856,13 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>-11.07</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -28788,10 +28977,13 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>-6.07</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -28906,10 +29098,13 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>-0.32</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -29024,10 +29219,13 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>-6.51</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -29142,10 +29340,13 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>-12.45</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
@@ -29260,10 +29461,13 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>-2.9</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -29378,10 +29582,13 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>-1.77</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -29496,10 +29703,13 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>-1.03</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -29614,10 +29824,13 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>-12.89</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -29732,10 +29945,13 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>1.75</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -29850,10 +30066,13 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>1.5</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -29968,10 +30187,13 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>-0.88</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -30086,10 +30308,13 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>6.94</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -30204,10 +30429,13 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>1.81</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -30322,10 +30550,13 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>14.62</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -30440,10 +30671,13 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>16.6</v>
       </c>
       <c r="AG289" t="b">
         <v>1</v>
@@ -30558,10 +30792,13 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>12.97</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -30676,10 +30913,13 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>-21.63</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -30794,10 +31034,13 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>-3.36</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -30912,10 +31155,13 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>2.72</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -31363,10 +31609,13 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>4.92</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -31481,10 +31730,13 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>-11.9</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -31599,10 +31851,13 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>-68.01000000000001</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -31828,7 +32083,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -31837,7 +32092,7 @@
         <v>0</v>
       </c>
       <c r="AH301" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI301" t="inlineStr">
         <is>
@@ -31946,7 +32201,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -32064,7 +32319,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -32182,7 +32437,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -32300,7 +32555,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -32418,7 +32673,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -32536,7 +32791,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -32654,7 +32909,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -32772,7 +33027,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -32890,7 +33145,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -33008,7 +33263,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -33126,7 +33381,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -33244,7 +33499,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -33362,7 +33617,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -33480,7 +33735,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -33598,7 +33853,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -33716,7 +33971,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -33834,7 +34089,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -33952,7 +34207,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -34070,7 +34325,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -34188,7 +34443,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -34306,7 +34561,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -34424,7 +34679,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -34542,7 +34797,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -34882,7 +35137,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -35000,7 +35255,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -35118,7 +35373,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -35458,7 +35713,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -35576,7 +35831,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -35585,7 +35840,7 @@
         <v>0</v>
       </c>
       <c r="AH333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI333" t="inlineStr">
         <is>
@@ -35694,7 +35949,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -35812,7 +36067,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -35930,7 +36185,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -35939,7 +36194,7 @@
         <v>0</v>
       </c>
       <c r="AH336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI336" t="inlineStr">
         <is>
@@ -36048,7 +36303,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -36166,7 +36421,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -36284,7 +36539,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -36402,7 +36657,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -36520,7 +36775,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -36638,7 +36893,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -36756,7 +37011,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -36874,7 +37129,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -36992,7 +37247,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -37110,7 +37365,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -37228,7 +37483,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -37346,7 +37601,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -37464,7 +37719,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -37582,7 +37837,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -37700,7 +37955,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -37818,7 +38073,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -37936,7 +38191,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -38498,7 +38753,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -38616,7 +38871,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -38734,7 +38989,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -38852,7 +39107,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -38970,7 +39225,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -39088,7 +39343,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -39206,7 +39461,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -39215,7 +39470,7 @@
         <v>0</v>
       </c>
       <c r="AH364" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI364" t="inlineStr">
         <is>
@@ -39324,7 +39579,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -39442,7 +39697,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -39560,7 +39815,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -39678,7 +39933,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -39796,7 +40051,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -39914,7 +40169,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -40032,7 +40287,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -40150,7 +40405,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -40268,7 +40523,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -40386,7 +40641,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -40504,7 +40759,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -40622,7 +40877,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -40740,7 +40995,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -41080,7 +41335,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -41198,7 +41453,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -41427,7 +41682,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -41545,7 +41800,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -41663,7 +41918,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -41781,7 +42036,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -41899,7 +42154,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -41908,7 +42163,7 @@
         <v>0</v>
       </c>
       <c r="AH387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI387" t="inlineStr">
         <is>
@@ -42017,7 +42272,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -42135,7 +42390,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -42250,7 +42505,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -42368,7 +42623,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -42486,7 +42741,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -42604,7 +42859,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -42722,7 +42977,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -42840,7 +43095,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -42958,7 +43213,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -43076,7 +43331,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -43194,7 +43449,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -43312,7 +43567,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -43430,7 +43685,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -43548,7 +43803,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -43666,7 +43921,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -43784,7 +44039,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -43902,7 +44157,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -44020,7 +44275,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -44138,7 +44393,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -44256,7 +44511,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -44374,7 +44629,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -44492,7 +44747,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -44943,7 +45198,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -45061,7 +45316,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -45179,13 +45434,16 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA415" t="n">
+        <v>-5.56</v>
       </c>
       <c r="AG415" t="b">
         <v>0</v>
       </c>
       <c r="AH415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI415" t="inlineStr">
         <is>
@@ -45294,7 +45552,10 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA416" t="n">
+        <v>1.52</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -45409,13 +45670,16 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA417" t="n">
+        <v>-5.98</v>
       </c>
       <c r="AG417" t="b">
         <v>0</v>
       </c>
       <c r="AH417" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI417" t="inlineStr">
         <is>
@@ -45524,13 +45788,16 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA418" t="n">
+        <v>-5.68</v>
       </c>
       <c r="AG418" t="b">
         <v>0</v>
       </c>
       <c r="AH418" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI418" t="inlineStr">
         <is>
@@ -45639,7 +45906,10 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA419" t="n">
+        <v>-7.92</v>
       </c>
       <c r="AG419" t="b">
         <v>0</v>
@@ -45754,7 +46024,10 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>-6.51</v>
       </c>
       <c r="AG420" t="b">
         <v>0</v>
@@ -45869,7 +46142,10 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA421" t="n">
+        <v>-4.32</v>
       </c>
       <c r="AG421" t="b">
         <v>0</v>
@@ -45984,13 +46260,16 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA422" t="n">
+        <v>-4.21</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
       </c>
       <c r="AH422" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI422" t="inlineStr">
         <is>
@@ -46099,7 +46378,10 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA423" t="n">
+        <v>-4.2</v>
       </c>
       <c r="AG423" t="b">
         <v>0</v>
@@ -46214,7 +46496,10 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA424" t="n">
+        <v>-1.31</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
@@ -46329,7 +46614,10 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA425" t="n">
+        <v>3.01</v>
       </c>
       <c r="AG425" t="b">
         <v>0</v>
@@ -46444,7 +46732,10 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA426" t="n">
+        <v>-1.75</v>
       </c>
       <c r="AG426" t="b">
         <v>0</v>
@@ -46559,7 +46850,10 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA427" t="n">
+        <v>5.01</v>
       </c>
       <c r="AG427" t="b">
         <v>0</v>
@@ -46674,7 +46968,10 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA428" t="n">
+        <v>6.43</v>
       </c>
       <c r="AG428" t="b">
         <v>0</v>
@@ -46789,7 +47086,10 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA429" t="n">
+        <v>5.96</v>
       </c>
       <c r="AG429" t="b">
         <v>0</v>
@@ -46904,7 +47204,10 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA430" t="n">
+        <v>5.16</v>
       </c>
       <c r="AG430" t="b">
         <v>0</v>
@@ -47019,7 +47322,10 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA431" t="n">
+        <v>6.84</v>
       </c>
       <c r="AG431" t="b">
         <v>0</v>
@@ -47134,7 +47440,10 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA432" t="n">
+        <v>-3.22</v>
       </c>
       <c r="AG432" t="b">
         <v>0</v>
@@ -47249,7 +47558,10 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA433" t="n">
+        <v>3.45</v>
       </c>
       <c r="AG433" t="b">
         <v>0</v>
@@ -47364,7 +47676,10 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>3.85</v>
       </c>
       <c r="AG434" t="b">
         <v>0</v>
@@ -47701,7 +48016,10 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>7.83</v>
       </c>
       <c r="AG437" t="b">
         <v>0</v>
@@ -47927,7 +48245,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG439" t="b">
         <v>0</v>
@@ -48042,7 +48360,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG440" t="b">
         <v>0</v>
@@ -48157,7 +48475,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG441" t="b">
         <v>0</v>
@@ -48272,7 +48590,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG442" t="b">
         <v>0</v>
@@ -48387,7 +48705,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG443" t="b">
         <v>0</v>
@@ -48502,13 +48820,13 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG444" t="b">
         <v>0</v>
       </c>
       <c r="AH444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI444" t="inlineStr">
         <is>
@@ -48617,13 +48935,13 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
       <c r="AH445" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI445" t="inlineStr">
         <is>
@@ -48732,7 +49050,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG446" t="b">
         <v>0</v>
@@ -48847,7 +49165,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG447" t="b">
         <v>0</v>
@@ -48962,7 +49280,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG448" t="b">
         <v>0</v>
@@ -49077,7 +49395,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG449" t="b">
         <v>0</v>
@@ -49192,7 +49510,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG450" t="b">
         <v>0</v>
@@ -49307,7 +49625,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG451" t="b">
         <v>0</v>
@@ -49422,7 +49740,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG452" t="b">
         <v>0</v>
@@ -49537,7 +49855,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG453" t="b">
         <v>0</v>
@@ -49652,7 +49970,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG454" t="b">
         <v>0</v>
@@ -49767,7 +50085,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG455" t="b">
         <v>0</v>
@@ -49882,13 +50200,13 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG456" t="b">
         <v>0</v>
       </c>
       <c r="AH456" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI456" t="inlineStr">
         <is>
@@ -49997,7 +50315,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG457" t="b">
         <v>0</v>
@@ -50112,7 +50430,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG458" t="b">
         <v>0</v>
@@ -50449,7 +50767,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG461" t="b">
         <v>0</v>
@@ -50564,7 +50882,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG462" t="b">
         <v>0</v>
@@ -50679,7 +50997,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -50794,13 +51112,13 @@
         </is>
       </c>
       <c r="Z464" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG464" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH464" t="b">
         <v>1</v>
-      </c>
-      <c r="AG464" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH464" t="b">
-        <v>0</v>
       </c>
       <c r="AI464" t="inlineStr">
         <is>
@@ -50909,13 +51227,13 @@
         </is>
       </c>
       <c r="Z465" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG465" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH465" t="b">
         <v>1</v>
-      </c>
-      <c r="AG465" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH465" t="b">
-        <v>0</v>
       </c>
       <c r="AI465" t="inlineStr">
         <is>
@@ -51024,13 +51342,13 @@
         </is>
       </c>
       <c r="Z466" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG466" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH466" t="b">
         <v>1</v>
-      </c>
-      <c r="AG466" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH466" t="b">
-        <v>0</v>
       </c>
       <c r="AI466" t="inlineStr">
         <is>
@@ -51139,7 +51457,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -51254,7 +51572,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
@@ -51369,7 +51687,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG469" t="b">
         <v>0</v>
@@ -51484,7 +51802,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -51599,7 +51917,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -51714,7 +52032,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -51829,7 +52147,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -51944,7 +52262,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -52059,7 +52377,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -52174,7 +52492,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
@@ -52289,13 +52607,13 @@
         </is>
       </c>
       <c r="Z477" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG477" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH477" t="b">
         <v>1</v>
-      </c>
-      <c r="AG477" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH477" t="b">
-        <v>0</v>
       </c>
       <c r="AI477" t="inlineStr">
         <is>
@@ -52404,7 +52722,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG478" t="b">
         <v>0</v>
@@ -52852,7 +53170,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG482" t="b">
         <v>0</v>
@@ -52967,7 +53285,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG483" t="b">
         <v>0</v>
@@ -53082,7 +53400,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -53197,7 +53515,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -53312,7 +53630,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG486" t="b">
         <v>0</v>
@@ -53427,7 +53745,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG487" t="b">
         <v>0</v>
@@ -53542,7 +53860,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -53657,7 +53975,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -53772,7 +54090,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -53887,7 +54205,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -54002,7 +54320,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -54117,7 +54435,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -54232,7 +54550,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -54347,7 +54665,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -54462,7 +54780,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -54577,7 +54895,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -54692,7 +55010,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -54807,7 +55125,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG499" t="b">
         <v>0</v>
@@ -54922,7 +55240,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -55037,7 +55355,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG501" t="b">
         <v>0</v>
@@ -55152,7 +55470,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -55267,7 +55585,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG503" t="b">
         <v>0</v>
@@ -55382,7 +55700,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -55391,13 +55709,1968 @@
         <v>0</v>
       </c>
       <c r="AI504" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="F505" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I505" t="b">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>10</v>
+      </c>
+      <c r="K505" t="n">
+        <v>156.75</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M505" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N505" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P505" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S505" t="n">
+        <v>7</v>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V505" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="W505" t="n">
+        <v>171</v>
+      </c>
+      <c r="X505" t="n">
+        <v>132.525</v>
+      </c>
+      <c r="Y505" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z505" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG505" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH505" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI505" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="F506" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I506" t="b">
+        <v>0</v>
+      </c>
+      <c r="J506" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="K506" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M506" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N506" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P506" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>77.06999999999999</v>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S506" t="n">
+        <v>7</v>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V506" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="W506" t="n">
+        <v>21.3168</v>
+      </c>
+      <c r="X506" t="n">
+        <v>17.0655</v>
+      </c>
+      <c r="Y506" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z506" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG506" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH506" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI506" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>78.31</v>
+      </c>
+      <c r="F507" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I507" t="b">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>10</v>
+      </c>
+      <c r="K507" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M507" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N507" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P507" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>76.45999999999999</v>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S507" t="n">
+        <v>7</v>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V507" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="W507" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="X507" t="n">
+        <v>43.059</v>
+      </c>
+      <c r="Y507" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z507" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG507" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH507" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI507" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="F508" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I508" t="b">
+        <v>0</v>
+      </c>
+      <c r="J508" t="n">
+        <v>10</v>
+      </c>
+      <c r="K508" t="n">
+        <v>169.4</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M508" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N508" t="n">
+        <v>5</v>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P508" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>67.43000000000001</v>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S508" t="n">
+        <v>7</v>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V508" t="n">
+        <v>154</v>
+      </c>
+      <c r="W508" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="X508" t="n">
+        <v>143.22</v>
+      </c>
+      <c r="Y508" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z508" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG508" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH508" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI508" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>83.81999999999999</v>
+      </c>
+      <c r="F509" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I509" t="b">
+        <v>0</v>
+      </c>
+      <c r="J509" t="n">
+        <v>10</v>
+      </c>
+      <c r="K509" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M509" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N509" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P509" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>79.06999999999999</v>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S509" t="n">
+        <v>7</v>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V509" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="W509" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="X509" t="n">
+        <v>36.084</v>
+      </c>
+      <c r="Y509" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z509" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG509" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH509" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI509" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="F510" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I510" t="b">
+        <v>0</v>
+      </c>
+      <c r="J510" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K510" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M510" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N510" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P510" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>81.45999999999999</v>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S510" t="n">
+        <v>7</v>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V510" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="W510" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="X510" t="n">
+        <v>43.1055</v>
+      </c>
+      <c r="Y510" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z510" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG510" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH510" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI510" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F511" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I511" t="b">
+        <v>0</v>
+      </c>
+      <c r="J511" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="K511" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M511" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N511" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P511" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S511" t="n">
+        <v>7</v>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V511" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="W511" t="n">
+        <v>61.6586</v>
+      </c>
+      <c r="X511" t="n">
+        <v>48.825</v>
+      </c>
+      <c r="Y511" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z511" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG511" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH511" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI511" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="F512" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I512" t="b">
+        <v>0</v>
+      </c>
+      <c r="J512" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K512" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M512" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N512" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P512" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S512" t="n">
+        <v>7</v>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V512" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="W512" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="X512" t="n">
+        <v>40.5015</v>
+      </c>
+      <c r="Y512" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z512" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG512" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH512" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI512" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="F513" t="n">
+        <v>55.98</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I513" t="b">
+        <v>0</v>
+      </c>
+      <c r="J513" t="n">
+        <v>10</v>
+      </c>
+      <c r="K513" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M513" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N513" t="n">
+        <v>5</v>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P513" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S513" t="n">
+        <v>7</v>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V513" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="W513" t="n">
+        <v>52.8845</v>
+      </c>
+      <c r="X513" t="n">
+        <v>41.664</v>
+      </c>
+      <c r="Y513" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z513" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG513" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH513" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI513" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>79.29000000000001</v>
+      </c>
+      <c r="F514" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I514" t="b">
+        <v>0</v>
+      </c>
+      <c r="J514" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="K514" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M514" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N514" t="n">
+        <v>3</v>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P514" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S514" t="n">
+        <v>7</v>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V514" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="W514" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="X514" t="n">
+        <v>37.0605</v>
+      </c>
+      <c r="Y514" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z514" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG514" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH514" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI514" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>聯詠</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F515" t="n">
+        <v>54</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I515" t="b">
+        <v>0</v>
+      </c>
+      <c r="J515" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="K515" t="n">
+        <v>610</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M515" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N515" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P515" t="n">
+        <v>541</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S515" t="n">
+        <v>7</v>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V515" t="n">
+        <v>556</v>
+      </c>
+      <c r="W515" t="n">
+        <v>643.3067</v>
+      </c>
+      <c r="X515" t="n">
+        <v>517.08</v>
+      </c>
+      <c r="Y515" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z515" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG515" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH515" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI515" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="F516" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I516" t="b">
+        <v>0</v>
+      </c>
+      <c r="J516" t="n">
+        <v>10</v>
+      </c>
+      <c r="K516" t="n">
+        <v>561</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M516" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N516" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P516" t="n">
+        <v>496</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S516" t="n">
+        <v>7</v>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V516" t="n">
+        <v>510</v>
+      </c>
+      <c r="W516" t="n">
+        <v>587.7032</v>
+      </c>
+      <c r="X516" t="n">
+        <v>474.3</v>
+      </c>
+      <c r="Y516" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z516" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG516" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH516" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI516" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="F517" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I517" t="b">
+        <v>0</v>
+      </c>
+      <c r="J517" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="K517" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M517" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N517" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P517" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S517" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V517" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="W517" t="n">
+        <v>135.3084</v>
+      </c>
+      <c r="X517" t="n">
+        <v>114.1893</v>
+      </c>
+      <c r="Y517" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z517" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG517" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH517" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI517" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="F518" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I518" t="b">
+        <v>0</v>
+      </c>
+      <c r="J518" t="n">
+        <v>10</v>
+      </c>
+      <c r="K518" t="n">
+        <v>7040</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M518" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N518" t="n">
+        <v>5</v>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P518" t="n">
+        <v>6127.5</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S518" t="n">
+        <v>7</v>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V518" t="n">
+        <v>6400</v>
+      </c>
+      <c r="W518" t="n">
+        <v>7680</v>
+      </c>
+      <c r="X518" t="n">
+        <v>5952</v>
+      </c>
+      <c r="Y518" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z518" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG518" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH518" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI518" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>73.55</v>
+      </c>
+      <c r="F519" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I519" t="b">
+        <v>0</v>
+      </c>
+      <c r="J519" t="n">
+        <v>10</v>
+      </c>
+      <c r="K519" t="n">
+        <v>457.6</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M519" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N519" t="n">
+        <v>5</v>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P519" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q519" t="n">
+        <v>61.64</v>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S519" t="n">
+        <v>7</v>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V519" t="n">
+        <v>416</v>
+      </c>
+      <c r="W519" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="X519" t="n">
+        <v>386.88</v>
+      </c>
+      <c r="Y519" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z519" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG519" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH519" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI519" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="F520" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I520" t="b">
+        <v>0</v>
+      </c>
+      <c r="J520" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="K520" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M520" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N520" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P520" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="Q520" t="n">
+        <v>61.41</v>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S520" t="n">
+        <v>5.7008</v>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V520" t="n">
+        <v>106</v>
+      </c>
+      <c r="W520" t="n">
+        <v>116.5572</v>
+      </c>
+      <c r="X520" t="n">
+        <v>99.9571</v>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z520" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG520" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH520" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI520" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="F521" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I521" t="b">
+        <v>0</v>
+      </c>
+      <c r="J521" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K521" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M521" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N521" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P521" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="Q521" t="n">
+        <v>74.93000000000001</v>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S521" t="n">
+        <v>7</v>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V521" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="W521" t="n">
+        <v>31.0717</v>
+      </c>
+      <c r="X521" t="n">
+        <v>25.5285</v>
+      </c>
+      <c r="Y521" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z521" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG521" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH521" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI521" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ504"/>
+  <autoFilter ref="A1:AJ521"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -55490,25 +57763,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4857</v>
+        <v>0.4836</v>
       </c>
       <c r="D4" t="n">
-        <v>2.01</v>
+        <v>1.23</v>
       </c>
       <c r="E4" t="n">
-        <v>13.12</v>
+        <v>12.29</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3048</v>
+        <v>0.2869</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4762</v>
+        <v>0.4918</v>
       </c>
     </row>
   </sheetData>
@@ -55624,25 +57897,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4857</v>
+        <v>0.4836</v>
       </c>
       <c r="D6" t="n">
-        <v>2.01</v>
+        <v>1.23</v>
       </c>
       <c r="E6" t="n">
-        <v>13.12</v>
+        <v>12.29</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3048</v>
+        <v>0.2869</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4762</v>
+        <v>0.4918</v>
       </c>
     </row>
   </sheetData>
@@ -55683,7 +57956,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 14:27:05</t>
+          <t>2026-09-14 14:24:08</t>
         </is>
       </c>
     </row>
@@ -55730,7 +58003,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7">
@@ -55740,7 +58013,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$521</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$536</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ521"/>
+  <dimension ref="A1:AJ536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11396,11 +11396,11 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z130" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA130" t="n">
         <v>0.42</v>
@@ -11411,6 +11411,15 @@
       <c r="AC130" t="n">
         <v>1.96</v>
       </c>
+      <c r="AD130" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>-2.8</v>
+      </c>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -11419,7 +11428,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -11520,11 +11529,11 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA131" t="n">
         <v>8.23</v>
@@ -11535,6 +11544,15 @@
       <c r="AC131" t="n">
         <v>6.4</v>
       </c>
+      <c r="AD131" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>-8.23</v>
+      </c>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -11543,7 +11561,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -11644,11 +11662,11 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA132" t="n">
         <v>0.49</v>
@@ -11659,6 +11677,15 @@
       <c r="AC132" t="n">
         <v>-3.82</v>
       </c>
+      <c r="AD132" t="n">
+        <v>-8.99</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>-9.109999999999999</v>
+      </c>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -11667,7 +11694,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -11768,11 +11795,11 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA133" t="n">
         <v>-9.25</v>
@@ -11783,6 +11810,15 @@
       <c r="AC133" t="n">
         <v>0.47</v>
       </c>
+      <c r="AD133" t="n">
+        <v>-9.16</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>-14.49</v>
+      </c>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -11791,7 +11827,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -11892,11 +11928,11 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z134" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA134" t="n">
         <v>-9.83</v>
@@ -11907,6 +11943,15 @@
       <c r="AC134" t="n">
         <v>-13.94</v>
       </c>
+      <c r="AD134" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>-17.65</v>
+      </c>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -11915,7 +11960,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -12016,11 +12061,11 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z135" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA135" t="n">
         <v>-0.97</v>
@@ -12031,6 +12076,15 @@
       <c r="AC135" t="n">
         <v>3.11</v>
       </c>
+      <c r="AD135" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-9.609999999999999</v>
+      </c>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -12039,7 +12093,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -12140,11 +12194,11 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA136" t="n">
         <v>13.17</v>
@@ -12155,6 +12209,15 @@
       <c r="AC136" t="n">
         <v>1.96</v>
       </c>
+      <c r="AD136" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-2.31</v>
+      </c>
       <c r="AG136" t="b">
         <v>1</v>
       </c>
@@ -12163,7 +12226,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -12261,11 +12324,11 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z137" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA137" t="n">
         <v>9.27</v>
@@ -12276,6 +12339,15 @@
       <c r="AC137" t="n">
         <v>15.06</v>
       </c>
+      <c r="AD137" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-3.09</v>
+      </c>
       <c r="AG137" t="b">
         <v>1</v>
       </c>
@@ -12284,7 +12356,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -12385,11 +12457,11 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z138" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA138" t="n">
         <v>2.36</v>
@@ -12400,6 +12472,15 @@
       <c r="AC138" t="n">
         <v>19.55</v>
       </c>
+      <c r="AD138" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-2.76</v>
+      </c>
       <c r="AG138" t="b">
         <v>1</v>
       </c>
@@ -12408,7 +12489,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -12509,11 +12590,11 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA139" t="n">
         <v>0.68</v>
@@ -12524,6 +12605,15 @@
       <c r="AC139" t="n">
         <v>15.99</v>
       </c>
+      <c r="AD139" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-3.25</v>
+      </c>
       <c r="AG139" t="b">
         <v>1</v>
       </c>
@@ -12532,7 +12622,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -12633,11 +12723,11 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA140" t="n">
         <v>8.130000000000001</v>
@@ -12648,6 +12738,15 @@
       <c r="AC140" t="n">
         <v>22.87</v>
       </c>
+      <c r="AD140" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>51.13</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>-3.4</v>
+      </c>
       <c r="AG140" t="b">
         <v>1</v>
       </c>
@@ -12656,7 +12755,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -12757,11 +12856,11 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA141" t="n">
         <v>-4.37</v>
@@ -12772,6 +12871,15 @@
       <c r="AC141" t="n">
         <v>-16.68</v>
       </c>
+      <c r="AD141" t="n">
+        <v>-16.94</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>-23.76</v>
+      </c>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -12780,7 +12888,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -12881,11 +12989,11 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA142" t="n">
         <v>-3.47</v>
@@ -12896,6 +13004,15 @@
       <c r="AC142" t="n">
         <v>-7.51</v>
       </c>
+      <c r="AD142" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>-11.45</v>
+      </c>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -12904,7 +13021,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -13005,11 +13122,11 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA143" t="n">
         <v>0.63</v>
@@ -13020,6 +13137,15 @@
       <c r="AC143" t="n">
         <v>7.68</v>
       </c>
+      <c r="AD143" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-5.96</v>
+      </c>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -13028,7 +13154,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -13129,11 +13255,11 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA144" t="n">
         <v>6.43</v>
@@ -13144,6 +13270,15 @@
       <c r="AC144" t="n">
         <v>0.36</v>
       </c>
+      <c r="AD144" t="n">
+        <v>-13.93</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>-16.79</v>
+      </c>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -13152,7 +13287,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -13253,11 +13388,11 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA145" t="n">
         <v>-66.26000000000001</v>
@@ -13268,6 +13403,15 @@
       <c r="AC145" t="n">
         <v>-63.44</v>
       </c>
+      <c r="AD145" t="n">
+        <v>-63.83</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>-55.08</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>-67.91</v>
+      </c>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -13276,7 +13420,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13525,7 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -13505,7 +13649,7 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -13629,7 +13773,7 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -13753,7 +13897,7 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -13877,7 +14021,7 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -14001,7 +14145,7 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -14125,7 +14269,7 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -14249,7 +14393,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -14373,7 +14517,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -14497,7 +14641,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -14621,7 +14765,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -14745,7 +14889,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -14869,7 +15013,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -14993,7 +15137,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -15117,7 +15261,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -15241,7 +15385,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -15365,7 +15509,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -15489,7 +15633,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -15613,7 +15757,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -15737,7 +15881,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -15861,7 +16005,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -15985,7 +16129,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -16220,7 +16364,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -16344,7 +16488,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -16468,7 +16612,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -16592,7 +16736,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -16716,7 +16860,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -16840,7 +16984,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -16964,7 +17108,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -17088,7 +17232,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -17212,7 +17356,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -17336,7 +17480,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -17571,7 +17715,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -17695,7 +17839,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -17819,7 +17963,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -17943,7 +18087,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -18067,7 +18211,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -18191,7 +18335,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -18315,7 +18459,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -18439,13 +18583,16 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
       </c>
       <c r="AB187" t="n">
         <v>1.53</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>-3.21</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -18560,13 +18707,16 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
       </c>
       <c r="AB188" t="n">
         <v>-1.69</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>-7.43</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -18681,13 +18831,16 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
       </c>
       <c r="AB189" t="n">
         <v>-4.29</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>-9.44</v>
       </c>
       <c r="AG189" t="b">
         <v>0</v>
@@ -18802,13 +18955,16 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
       </c>
       <c r="AB190" t="n">
         <v>4.12</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>-8.73</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -18923,13 +19079,16 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
       </c>
       <c r="AB191" t="n">
         <v>-6.91</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>-5.08</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -19044,13 +19203,16 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
       </c>
       <c r="AB192" t="n">
         <v>5.3</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>6.71</v>
       </c>
       <c r="AG192" t="b">
         <v>0</v>
@@ -19165,13 +19327,16 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
       </c>
       <c r="AB193" t="n">
         <v>10.19</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>6.8</v>
       </c>
       <c r="AG193" t="b">
         <v>1</v>
@@ -19286,13 +19451,16 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
       </c>
       <c r="AB194" t="n">
         <v>15.21</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>16.82</v>
       </c>
       <c r="AG194" t="b">
         <v>1</v>
@@ -19407,13 +19575,16 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
       </c>
       <c r="AB195" t="n">
         <v>10.56</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>-2.22</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -19528,13 +19699,16 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
       </c>
       <c r="AB196" t="n">
         <v>13.64</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>5.86</v>
       </c>
       <c r="AG196" t="b">
         <v>1</v>
@@ -19649,13 +19823,16 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
       </c>
       <c r="AB197" t="n">
         <v>-3.78</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>-2.52</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -19992,13 +20169,16 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
       </c>
       <c r="AB200" t="n">
         <v>7</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>8.35</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -20113,13 +20293,16 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
       </c>
       <c r="AB201" t="n">
         <v>-5.7</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>-19.13</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -20234,13 +20417,16 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
       </c>
       <c r="AB202" t="n">
         <v>-63.66</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>-64.05</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -20355,7 +20541,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -20476,7 +20662,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -20597,7 +20783,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -20718,7 +20904,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -20839,7 +21025,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -20960,7 +21146,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -21081,7 +21267,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21202,7 +21388,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21323,7 +21509,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -21444,7 +21630,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -21676,7 +21862,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -21797,7 +21983,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -21918,7 +22104,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -22039,7 +22225,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -22160,7 +22346,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22281,7 +22467,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -22402,7 +22588,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -22523,7 +22709,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -22644,7 +22830,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -22765,7 +22951,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -22886,7 +23072,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23007,7 +23193,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23128,7 +23314,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23249,7 +23435,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -23370,7 +23556,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -23491,7 +23677,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -23612,7 +23798,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -23624,7 +23810,7 @@
         <v>0</v>
       </c>
       <c r="AH230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
@@ -23733,7 +23919,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -23965,7 +24151,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24308,7 +24494,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -24429,7 +24615,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -24550,7 +24736,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -24671,7 +24857,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -24792,7 +24978,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -24913,7 +25099,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25034,7 +25220,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25155,7 +25341,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -25276,7 +25462,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -25397,7 +25583,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -25518,7 +25704,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -25639,7 +25825,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -25760,7 +25946,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -25881,7 +26067,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26002,7 +26188,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -26123,7 +26309,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -26244,7 +26430,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -26365,7 +26551,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -26377,7 +26563,7 @@
         <v>0</v>
       </c>
       <c r="AH253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
@@ -26486,7 +26672,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -26607,7 +26793,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -26950,7 +27136,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -27293,7 +27479,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -27414,7 +27600,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -27535,7 +27721,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -27656,7 +27842,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -27888,7 +28074,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28009,7 +28195,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -28130,7 +28316,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -28251,7 +28437,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -28372,7 +28558,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -28493,7 +28679,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -28614,7 +28800,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -28735,7 +28921,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -28856,7 +29042,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -28977,7 +29163,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -29098,7 +29284,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -29219,7 +29405,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -29340,7 +29526,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -29461,7 +29647,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -29582,7 +29768,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -29703,7 +29889,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -29824,7 +30010,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -29945,7 +30131,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30066,7 +30252,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -30187,7 +30373,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -30308,7 +30494,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -30429,7 +30615,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -30550,7 +30736,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -30671,7 +30857,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -30792,7 +30978,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -30913,7 +31099,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -31034,7 +31220,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -31046,7 +31232,7 @@
         <v>0</v>
       </c>
       <c r="AH292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI292" t="inlineStr">
         <is>
@@ -31155,7 +31341,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -31609,7 +31795,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -31730,7 +31916,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -31851,7 +32037,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -32083,10 +32269,13 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>-8.550000000000001</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -32201,10 +32390,13 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>-5.54</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
@@ -32319,10 +32511,13 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>-6.12</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -32437,10 +32632,13 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>-8.800000000000001</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -32555,10 +32753,13 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>-8.82</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -32673,10 +32874,13 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>4.53</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -32791,10 +32995,13 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>-13.29</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -32909,10 +33116,13 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>-2.68</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -33027,10 +33237,13 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>-8.119999999999999</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -33145,10 +33358,13 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>-20.65</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -33263,10 +33479,13 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>-4.46</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -33381,10 +33600,13 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>-2.63</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -33499,10 +33721,13 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>-3.66</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
@@ -33617,10 +33842,13 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>-10.14</v>
       </c>
       <c r="AG314" t="b">
         <v>0</v>
@@ -33735,9 +33963,12 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA315" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AB315" t="n">
         <v>-2.18</v>
       </c>
       <c r="AG315" t="b">
@@ -33853,10 +34084,13 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>4.14</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -33971,10 +34205,13 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -34089,10 +34326,13 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>9.16</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -34207,10 +34447,13 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>7.69</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -34325,10 +34568,13 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>-5.21</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -34443,10 +34689,13 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>-20.12</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -34561,16 +34810,19 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
       </c>
+      <c r="AB322" t="n">
+        <v>-8.65</v>
+      </c>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
       <c r="AH322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI322" t="inlineStr">
         <is>
@@ -34679,10 +34931,13 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>-7.36</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -34797,10 +35052,13 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>-2.49</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -35137,10 +35395,13 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>0.67</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -35255,10 +35516,13 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>1.24</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -35373,10 +35637,13 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>-21.52</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -35713,10 +35980,13 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>-11.43</v>
       </c>
       <c r="AG332" t="b">
         <v>0</v>
@@ -35831,7 +36101,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -35949,7 +36219,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -36067,7 +36337,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -36185,7 +36455,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -36303,7 +36573,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -36421,7 +36691,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -36539,7 +36809,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -36657,7 +36927,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -36775,7 +37045,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -36893,7 +37163,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -37011,7 +37281,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -37129,7 +37399,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -37247,7 +37517,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -37365,7 +37635,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -37483,7 +37753,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -37601,7 +37871,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -37719,7 +37989,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -37837,7 +38107,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -37955,7 +38225,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -38073,7 +38343,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -38191,7 +38461,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -38753,7 +39023,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -38871,7 +39141,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -38989,7 +39259,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -39107,7 +39377,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -39225,7 +39495,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -39343,7 +39613,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -39461,7 +39731,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -39579,7 +39849,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -39697,7 +39967,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -39815,7 +40085,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -39933,7 +40203,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -40051,7 +40321,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -40169,7 +40439,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -40287,7 +40557,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -40405,7 +40675,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -40523,7 +40793,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -40641,7 +40911,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -40759,7 +41029,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -40877,7 +41147,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -40995,7 +41265,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -41335,7 +41605,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -41453,7 +41723,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -41682,7 +41952,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -41800,7 +42070,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -41809,7 +42079,7 @@
         <v>0</v>
       </c>
       <c r="AH384" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI384" t="inlineStr">
         <is>
@@ -41918,7 +42188,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -42036,7 +42306,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -42154,7 +42424,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -42272,7 +42542,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -42390,7 +42660,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -42505,7 +42775,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -42623,7 +42893,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -42741,7 +43011,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -42859,7 +43129,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -42977,7 +43247,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -43095,7 +43365,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -43213,7 +43483,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -43331,7 +43601,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -43449,7 +43719,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -43567,7 +43837,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -43685,7 +43955,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -43803,7 +44073,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -43921,7 +44191,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -44039,7 +44309,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -44157,7 +44427,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -44275,7 +44545,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -44393,7 +44663,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -44511,7 +44781,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -44629,7 +44899,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -44747,7 +45017,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -45198,7 +45468,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -45316,7 +45586,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -45434,7 +45704,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -45552,7 +45822,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -45670,7 +45940,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -45788,7 +46058,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -45906,7 +46176,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -46024,7 +46294,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -46142,7 +46412,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -46260,7 +46530,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -46378,7 +46648,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -46496,7 +46766,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -46614,7 +46884,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -46732,7 +47002,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -46850,7 +47120,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -46968,7 +47238,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -47086,7 +47356,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -47204,7 +47474,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -47322,7 +47592,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -47440,7 +47710,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -47449,7 +47719,7 @@
         <v>0</v>
       </c>
       <c r="AH432" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI432" t="inlineStr">
         <is>
@@ -47558,7 +47828,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -47676,7 +47946,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -48016,7 +48286,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -48245,7 +48515,10 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>0</v>
       </c>
       <c r="AG439" t="b">
         <v>0</v>
@@ -48360,7 +48633,10 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>-4.76</v>
       </c>
       <c r="AG440" t="b">
         <v>0</v>
@@ -48475,7 +48751,10 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>-5.74</v>
       </c>
       <c r="AG441" t="b">
         <v>0</v>
@@ -48590,13 +48869,16 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>-6.8</v>
       </c>
       <c r="AG442" t="b">
         <v>0</v>
       </c>
       <c r="AH442" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI442" t="inlineStr">
         <is>
@@ -48705,7 +48987,10 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>1.09</v>
       </c>
       <c r="AG443" t="b">
         <v>0</v>
@@ -48820,7 +49105,10 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>-5.41</v>
       </c>
       <c r="AG444" t="b">
         <v>0</v>
@@ -48935,7 +49223,10 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>-8.17</v>
       </c>
       <c r="AG445" t="b">
         <v>0</v>
@@ -49050,7 +49341,10 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>-5.94</v>
       </c>
       <c r="AG446" t="b">
         <v>0</v>
@@ -49165,7 +49459,10 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>0</v>
       </c>
       <c r="AG447" t="b">
         <v>0</v>
@@ -49280,7 +49577,10 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>1.69</v>
       </c>
       <c r="AG448" t="b">
         <v>0</v>
@@ -49395,7 +49695,10 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>1.34</v>
       </c>
       <c r="AG449" t="b">
         <v>0</v>
@@ -49510,7 +49813,10 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>-3.08</v>
       </c>
       <c r="AG450" t="b">
         <v>0</v>
@@ -49625,7 +49931,10 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>2.28</v>
       </c>
       <c r="AG451" t="b">
         <v>0</v>
@@ -49740,7 +50049,10 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>0.22</v>
       </c>
       <c r="AG452" t="b">
         <v>0</v>
@@ -49855,7 +50167,10 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>1.4</v>
       </c>
       <c r="AG453" t="b">
         <v>0</v>
@@ -49970,7 +50285,10 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>2.53</v>
       </c>
       <c r="AG454" t="b">
         <v>0</v>
@@ -50085,7 +50403,10 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>4.49</v>
       </c>
       <c r="AG455" t="b">
         <v>0</v>
@@ -50200,7 +50521,10 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>-11.56</v>
       </c>
       <c r="AG456" t="b">
         <v>0</v>
@@ -50315,7 +50639,10 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>-5.18</v>
       </c>
       <c r="AG457" t="b">
         <v>0</v>
@@ -50430,7 +50757,10 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>5.08</v>
       </c>
       <c r="AG458" t="b">
         <v>0</v>
@@ -50767,7 +51097,10 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>1.26</v>
       </c>
       <c r="AG461" t="b">
         <v>0</v>
@@ -50882,7 +51215,10 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG462" t="b">
         <v>0</v>
@@ -50997,7 +51333,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -51112,7 +51448,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG464" t="b">
         <v>0</v>
@@ -51227,7 +51563,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG465" t="b">
         <v>0</v>
@@ -51342,7 +51678,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG466" t="b">
         <v>0</v>
@@ -51457,7 +51793,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -51572,7 +51908,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
@@ -51687,7 +52023,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG469" t="b">
         <v>0</v>
@@ -51802,7 +52138,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -51917,7 +52253,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -52032,7 +52368,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -52147,7 +52483,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -52262,7 +52598,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -52377,7 +52713,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -52492,7 +52828,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
@@ -52607,7 +52943,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG477" t="b">
         <v>0</v>
@@ -52722,7 +53058,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG478" t="b">
         <v>0</v>
@@ -53170,7 +53506,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG482" t="b">
         <v>0</v>
@@ -53285,7 +53621,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG483" t="b">
         <v>0</v>
@@ -53400,7 +53736,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -53515,7 +53851,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -53630,7 +53966,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG486" t="b">
         <v>0</v>
@@ -53745,13 +54081,13 @@
         </is>
       </c>
       <c r="Z487" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG487" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH487" t="b">
         <v>1</v>
-      </c>
-      <c r="AG487" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH487" t="b">
-        <v>0</v>
       </c>
       <c r="AI487" t="inlineStr">
         <is>
@@ -53860,7 +54196,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -53975,7 +54311,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -54090,7 +54426,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -54205,7 +54541,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -54320,7 +54656,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -54435,7 +54771,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -54550,7 +54886,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -54665,7 +55001,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -54780,7 +55116,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -54895,7 +55231,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -55010,7 +55346,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -55125,7 +55461,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG499" t="b">
         <v>0</v>
@@ -55240,7 +55576,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -55355,7 +55691,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG501" t="b">
         <v>0</v>
@@ -55470,7 +55806,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -55585,7 +55921,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG503" t="b">
         <v>0</v>
@@ -55700,7 +56036,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -55815,7 +56151,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG505" t="b">
         <v>0</v>
@@ -55930,7 +56266,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG506" t="b">
         <v>0</v>
@@ -56045,7 +56381,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG507" t="b">
         <v>0</v>
@@ -56160,7 +56496,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG508" t="b">
         <v>0</v>
@@ -56275,7 +56611,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG509" t="b">
         <v>0</v>
@@ -56390,7 +56726,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG510" t="b">
         <v>0</v>
@@ -56505,7 +56841,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG511" t="b">
         <v>0</v>
@@ -56620,7 +56956,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG512" t="b">
         <v>0</v>
@@ -56735,7 +57071,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG513" t="b">
         <v>0</v>
@@ -56850,7 +57186,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG514" t="b">
         <v>0</v>
@@ -56965,7 +57301,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>
@@ -57080,7 +57416,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG516" t="b">
         <v>0</v>
@@ -57195,7 +57531,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG517" t="b">
         <v>0</v>
@@ -57310,7 +57646,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG518" t="b">
         <v>0</v>
@@ -57425,7 +57761,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG519" t="b">
         <v>0</v>
@@ -57540,7 +57876,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG520" t="b">
         <v>0</v>
@@ -57655,7 +57991,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG521" t="b">
         <v>0</v>
@@ -57664,13 +58000,1738 @@
         <v>0</v>
       </c>
       <c r="AI521" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>74.62</v>
+      </c>
+      <c r="F522" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I522" t="b">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K522" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M522" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N522" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P522" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="Q522" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S522" t="n">
+        <v>6.8569</v>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V522" t="n">
+        <v>18</v>
+      </c>
+      <c r="W522" t="n">
+        <v>20.3328</v>
+      </c>
+      <c r="X522" t="n">
+        <v>16.7658</v>
+      </c>
+      <c r="Y522" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z522" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG522" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH522" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI522" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>82.34</v>
+      </c>
+      <c r="F523" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I523" t="b">
+        <v>0</v>
+      </c>
+      <c r="J523" t="n">
+        <v>10</v>
+      </c>
+      <c r="K523" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M523" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N523" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P523" t="n">
+        <v>43.73</v>
+      </c>
+      <c r="Q523" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S523" t="n">
+        <v>7</v>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V523" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="W523" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="X523" t="n">
+        <v>43.617</v>
+      </c>
+      <c r="Y523" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z523" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG523" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH523" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI523" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="F524" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I524" t="b">
+        <v>0</v>
+      </c>
+      <c r="J524" t="n">
+        <v>10</v>
+      </c>
+      <c r="K524" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M524" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N524" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P524" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="Q524" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S524" t="n">
+        <v>6.101</v>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V524" t="n">
+        <v>151</v>
+      </c>
+      <c r="W524" t="n">
+        <v>180.5933</v>
+      </c>
+      <c r="X524" t="n">
+        <v>141.7875</v>
+      </c>
+      <c r="Y524" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z524" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG524" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH524" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI524" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="F525" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I525" t="b">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K525" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M525" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N525" t="n">
+        <v>3</v>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P525" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="Q525" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S525" t="n">
+        <v>7</v>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V525" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="W525" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="X525" t="n">
+        <v>35.4795</v>
+      </c>
+      <c r="Y525" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z525" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG525" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH525" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI525" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="F526" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I526" t="b">
+        <v>0</v>
+      </c>
+      <c r="J526" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K526" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M526" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N526" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P526" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="Q526" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S526" t="n">
+        <v>7</v>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V526" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="W526" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="X526" t="n">
+        <v>42.4545</v>
+      </c>
+      <c r="Y526" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z526" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG526" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH526" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI526" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>76.22</v>
+      </c>
+      <c r="F527" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I527" t="b">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="K527" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M527" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N527" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P527" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="Q527" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S527" t="n">
+        <v>7</v>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V527" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="W527" t="n">
+        <v>59.9725</v>
+      </c>
+      <c r="X527" t="n">
+        <v>48.174</v>
+      </c>
+      <c r="Y527" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z527" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG527" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH527" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI527" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>77.56</v>
+      </c>
+      <c r="F528" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I528" t="b">
+        <v>0</v>
+      </c>
+      <c r="J528" t="n">
+        <v>10</v>
+      </c>
+      <c r="K528" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M528" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N528" t="n">
+        <v>5</v>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P528" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="Q528" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S528" t="n">
+        <v>7</v>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V528" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="W528" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="X528" t="n">
+        <v>40.362</v>
+      </c>
+      <c r="Y528" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z528" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG528" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH528" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI528" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="F529" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I529" t="b">
+        <v>0</v>
+      </c>
+      <c r="J529" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K529" t="n">
+        <v>49</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M529" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N529" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P529" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="Q529" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S529" t="n">
+        <v>7</v>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V529" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="W529" t="n">
+        <v>52.1733</v>
+      </c>
+      <c r="X529" t="n">
+        <v>41.4315</v>
+      </c>
+      <c r="Y529" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z529" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG529" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH529" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI529" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="F530" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I530" t="b">
+        <v>0</v>
+      </c>
+      <c r="J530" t="n">
+        <v>10</v>
+      </c>
+      <c r="K530" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M530" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N530" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P530" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S530" t="n">
+        <v>6.6384</v>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V530" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="W530" t="n">
+        <v>76.9096</v>
+      </c>
+      <c r="X530" t="n">
+        <v>65.07299999999999</v>
+      </c>
+      <c r="Y530" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z530" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG530" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH530" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI530" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F531" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I531" t="b">
+        <v>0</v>
+      </c>
+      <c r="J531" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K531" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M531" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N531" t="n">
+        <v>5</v>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P531" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>79.28</v>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S531" t="n">
+        <v>7</v>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V531" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="W531" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="X531" t="n">
+        <v>36.7815</v>
+      </c>
+      <c r="Y531" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z531" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG531" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH531" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI531" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="F532" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I532" t="b">
+        <v>0</v>
+      </c>
+      <c r="J532" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="K532" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M532" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N532" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P532" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S532" t="n">
+        <v>7</v>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V532" t="n">
+        <v>124</v>
+      </c>
+      <c r="W532" t="n">
+        <v>141.4793</v>
+      </c>
+      <c r="X532" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="Y532" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z532" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG532" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH532" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI532" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="F533" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I533" t="b">
+        <v>0</v>
+      </c>
+      <c r="J533" t="n">
+        <v>10</v>
+      </c>
+      <c r="K533" t="n">
+        <v>6638.5</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M533" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N533" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P533" t="n">
+        <v>6127.5</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S533" t="n">
+        <v>6.3529</v>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V533" t="n">
+        <v>6035</v>
+      </c>
+      <c r="W533" t="n">
+        <v>7242</v>
+      </c>
+      <c r="X533" t="n">
+        <v>5651.6</v>
+      </c>
+      <c r="Y533" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z533" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG533" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH533" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI533" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F534" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I534" t="b">
+        <v>0</v>
+      </c>
+      <c r="J534" t="n">
+        <v>10</v>
+      </c>
+      <c r="K534" t="n">
+        <v>447.7</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M534" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N534" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P534" t="n">
+        <v>405.75</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S534" t="n">
+        <v>7</v>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V534" t="n">
+        <v>407</v>
+      </c>
+      <c r="W534" t="n">
+        <v>488.4</v>
+      </c>
+      <c r="X534" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="Y534" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z534" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG534" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH534" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI534" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="F535" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I535" t="b">
+        <v>0</v>
+      </c>
+      <c r="J535" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="K535" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M535" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N535" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P535" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S535" t="n">
+        <v>5.9088</v>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V535" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="W535" t="n">
+        <v>116.6318</v>
+      </c>
+      <c r="X535" t="n">
+        <v>100.2071</v>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z535" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG535" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH535" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI535" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="F536" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I536" t="b">
+        <v>0</v>
+      </c>
+      <c r="J536" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K536" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M536" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N536" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P536" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S536" t="n">
+        <v>6.0278</v>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V536" t="n">
+        <v>27</v>
+      </c>
+      <c r="W536" t="n">
+        <v>30.1157</v>
+      </c>
+      <c r="X536" t="n">
+        <v>25.3725</v>
+      </c>
+      <c r="Y536" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z536" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG536" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH536" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI536" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ521"/>
+  <autoFilter ref="A1:AJ536"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -57743,7 +59804,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-12.33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5333</v>
       </c>
     </row>
     <row r="3">
@@ -57753,7 +59832,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-17.57</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-17.65</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -57857,6 +59954,24 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51.13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -57867,7 +59982,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-16.59</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -57877,7 +60010,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-9.49</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7143</v>
       </c>
     </row>
     <row r="5">
@@ -57956,7 +60107,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 14:24:08</t>
+          <t>2026-09-15 14:24:07</t>
         </is>
       </c>
     </row>
@@ -58003,7 +60154,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>520</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7">
@@ -58013,7 +60164,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -58023,7 +60174,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$536</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$556</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ536"/>
+  <dimension ref="A1:AJ556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13521,11 +13521,11 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA146" t="n">
         <v>4.14</v>
@@ -13536,6 +13536,15 @@
       <c r="AC146" t="n">
         <v>4.73</v>
       </c>
+      <c r="AD146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -13544,7 +13553,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -13645,11 +13654,11 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA147" t="n">
         <v>0.26</v>
@@ -13660,6 +13669,15 @@
       <c r="AC147" t="n">
         <v>-1.94</v>
       </c>
+      <c r="AD147" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>-4.65</v>
+      </c>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -13668,7 +13686,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -13769,11 +13787,11 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA148" t="n">
         <v>-0.14</v>
@@ -13784,6 +13802,15 @@
       <c r="AC148" t="n">
         <v>2.37</v>
       </c>
+      <c r="AD148" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>-3.34</v>
+      </c>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -13792,7 +13819,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -13893,11 +13920,11 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA149" t="n">
         <v>12.25</v>
@@ -13908,6 +13935,15 @@
       <c r="AC149" t="n">
         <v>6.95</v>
       </c>
+      <c r="AD149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>-8.23</v>
+      </c>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -13916,7 +13952,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -14017,11 +14053,11 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA150" t="n">
         <v>-3.95</v>
@@ -14032,6 +14068,15 @@
       <c r="AC150" t="n">
         <v>-2.7</v>
       </c>
+      <c r="AD150" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>-6.24</v>
+      </c>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -14040,7 +14085,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -14141,11 +14186,11 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA151" t="n">
         <v>13.33</v>
@@ -14156,6 +14201,15 @@
       <c r="AC151" t="n">
         <v>23.78</v>
       </c>
+      <c r="AD151" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>-5.23</v>
+      </c>
       <c r="AG151" t="b">
         <v>1</v>
       </c>
@@ -14164,7 +14218,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -14265,11 +14319,11 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA152" t="n">
         <v>2.65</v>
@@ -14280,6 +14334,15 @@
       <c r="AC152" t="n">
         <v>-12.12</v>
       </c>
+      <c r="AD152" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>-22.74</v>
+      </c>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -14288,7 +14351,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14456,7 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -14517,7 +14580,7 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -14641,7 +14704,7 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -14765,7 +14828,7 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -14889,7 +14952,7 @@
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -15013,7 +15076,7 @@
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -15137,7 +15200,7 @@
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -15261,7 +15324,7 @@
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -15385,7 +15448,7 @@
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -15509,7 +15572,7 @@
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -15633,7 +15696,7 @@
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -15757,7 +15820,7 @@
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -15881,7 +15944,7 @@
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -16005,7 +16068,7 @@
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -16129,7 +16192,7 @@
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -16364,7 +16427,7 @@
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -16488,7 +16551,7 @@
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -16612,7 +16675,7 @@
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -16736,7 +16799,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -16860,7 +16923,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -16984,7 +17047,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -17108,7 +17171,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -17232,7 +17295,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -17356,7 +17419,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -17480,7 +17543,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -17715,7 +17778,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -17839,7 +17902,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -17854,7 +17917,7 @@
         <v>0</v>
       </c>
       <c r="AH181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
@@ -17963,7 +18026,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -18087,7 +18150,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -18211,7 +18274,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -18335,7 +18398,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -18459,7 +18522,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -18583,7 +18646,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -18707,7 +18770,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -18831,7 +18894,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -18955,7 +19018,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -19079,7 +19142,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -19203,7 +19266,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -19327,7 +19390,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -19451,7 +19514,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19575,7 +19638,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19699,7 +19762,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -19823,7 +19886,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -20169,7 +20232,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -20293,7 +20356,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -20417,7 +20480,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -20541,13 +20604,16 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
       </c>
       <c r="AB203" t="n">
         <v>-2.66</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>-6.73</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -20662,13 +20728,16 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
       </c>
       <c r="AB204" t="n">
         <v>-4.72</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>-9.77</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -20783,13 +20852,16 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
       </c>
       <c r="AB205" t="n">
         <v>2.7</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.35</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -20904,13 +20976,16 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
       </c>
       <c r="AB206" t="n">
         <v>-5.01</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>-8.789999999999999</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -21025,13 +21100,16 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
       </c>
       <c r="AB207" t="n">
         <v>0.82</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
@@ -21146,13 +21224,16 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
       </c>
       <c r="AB208" t="n">
         <v>-5.09</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1.02</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -21267,13 +21348,16 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
       </c>
       <c r="AB209" t="n">
         <v>1.16</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>-4.74</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -21388,7 +21472,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21396,8 +21480,11 @@
       <c r="AB210" t="n">
         <v>13.07</v>
       </c>
+      <c r="AC210" t="n">
+        <v>18.4</v>
+      </c>
       <c r="AG210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH210" t="b">
         <v>0</v>
@@ -21509,13 +21596,16 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
       </c>
       <c r="AB211" t="n">
         <v>-14.4</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>-17.16</v>
       </c>
       <c r="AG211" t="b">
         <v>0</v>
@@ -21630,13 +21720,16 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
       </c>
       <c r="AB212" t="n">
         <v>-7.83</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>-6.92</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -21862,13 +21955,16 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
       </c>
       <c r="AB214" t="n">
         <v>-1.39</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>-15.53</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -21983,13 +22079,16 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
       </c>
       <c r="AB215" t="n">
         <v>-15.14</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>-23.97</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -22104,13 +22203,16 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
       </c>
       <c r="AB216" t="n">
         <v>-10.83</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>-9.85</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -22225,13 +22327,16 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
       </c>
       <c r="AB217" t="n">
         <v>-65.73</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>-68.09</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -22346,7 +22451,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22467,7 +22572,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -22588,7 +22693,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -22709,7 +22814,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -22830,7 +22935,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -22951,7 +23056,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -23072,7 +23177,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23193,7 +23298,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23314,7 +23419,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23435,7 +23540,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -23556,7 +23661,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -23677,7 +23782,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -23798,7 +23903,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -23919,7 +24024,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -24151,7 +24256,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24494,7 +24599,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -24615,7 +24720,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -24736,7 +24841,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -24857,7 +24962,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -24978,7 +25083,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -25099,7 +25204,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25220,7 +25325,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25341,7 +25446,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -25462,7 +25567,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -25583,7 +25688,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -25704,7 +25809,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -25825,7 +25930,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -25946,7 +26051,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26067,7 +26172,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26188,7 +26293,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -26309,7 +26414,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -26430,7 +26535,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -26551,7 +26656,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -26672,7 +26777,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -26793,7 +26898,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27136,7 +27241,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -27479,7 +27584,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -27600,7 +27705,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -27721,7 +27826,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -27842,7 +27947,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28074,7 +28179,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28195,7 +28300,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -28316,7 +28421,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -28437,7 +28542,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -28558,7 +28663,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -28679,7 +28784,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -28800,7 +28905,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -28921,7 +29026,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -29042,7 +29147,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -29163,7 +29268,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -29284,7 +29389,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -29405,7 +29510,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -29526,7 +29631,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -29647,7 +29752,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -29768,7 +29873,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -29889,7 +29994,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -30010,7 +30115,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -30131,7 +30236,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30252,7 +30357,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -30373,7 +30478,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -30494,7 +30599,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -30615,7 +30720,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -30736,7 +30841,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -30857,7 +30962,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -30978,7 +31083,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -30987,7 +31092,7 @@
         <v>12.97</v>
       </c>
       <c r="AG290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH290" t="b">
         <v>0</v>
@@ -31099,7 +31204,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -31220,7 +31325,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -31341,7 +31446,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -31795,7 +31900,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -31916,7 +32021,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -32037,7 +32142,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -32269,7 +32374,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -32390,7 +32495,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -32511,7 +32616,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -32632,7 +32737,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -32753,7 +32858,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -32874,7 +32979,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -32995,7 +33100,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -33116,7 +33221,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -33237,7 +33342,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -33358,7 +33463,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -33479,7 +33584,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -33600,7 +33705,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -33721,7 +33826,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -33842,7 +33947,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -33963,7 +34068,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -34084,7 +34189,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -34205,7 +34310,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -34326,7 +34431,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -34447,7 +34552,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -34568,7 +34673,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -34689,7 +34794,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -34810,7 +34915,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -34931,7 +35036,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -35052,7 +35157,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -35395,7 +35500,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -35516,7 +35621,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -35637,7 +35742,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -35980,7 +36085,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -36101,10 +36206,13 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>-6.59</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -36219,10 +36327,13 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>-5.68</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
@@ -36337,10 +36448,13 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>-9.619999999999999</v>
       </c>
       <c r="AG335" t="b">
         <v>0</v>
@@ -36455,10 +36569,13 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>-4.72</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -36573,10 +36690,13 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>-12.06</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
@@ -36691,10 +36811,13 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>-7.03</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -36809,10 +36932,13 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>-3.18</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -36927,10 +37053,13 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>1.04</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -37045,10 +37174,13 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>-4.92</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -37163,10 +37295,13 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>2.68</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -37281,10 +37416,13 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>6.62</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -37399,10 +37537,13 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>3.21</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -37517,10 +37658,13 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>10.28</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -37635,10 +37779,13 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>14.69</v>
       </c>
       <c r="AG346" t="b">
         <v>1</v>
@@ -37753,10 +37900,13 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>7.77</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -37871,10 +38021,13 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>7.47</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -37989,10 +38142,13 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>10.34</v>
       </c>
       <c r="AG349" t="b">
         <v>0</v>
@@ -38107,10 +38263,13 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>-0.18</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -38225,10 +38384,13 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>-20.29</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
@@ -38343,10 +38505,13 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>-5.96</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -38461,10 +38626,13 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>0.4</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -39023,10 +39191,13 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>-20.36</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
@@ -39141,10 +39312,13 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>-17.05</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -39259,7 +39433,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -39377,7 +39551,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -39495,7 +39669,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -39613,7 +39787,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -39731,7 +39905,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -39849,7 +40023,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -39967,7 +40141,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -40085,7 +40259,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -40203,7 +40377,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -40321,7 +40495,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -40439,7 +40613,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -40557,7 +40731,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -40675,7 +40849,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -40793,7 +40967,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -40911,7 +41085,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -41029,7 +41203,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -41147,7 +41321,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -41265,7 +41439,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -41605,7 +41779,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -41723,7 +41897,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -41952,7 +42126,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -42070,7 +42244,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -42188,7 +42362,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -42306,7 +42480,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -42424,7 +42598,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -42542,7 +42716,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -42660,7 +42834,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -42775,7 +42949,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -42893,7 +43067,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -43011,7 +43185,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -43129,7 +43303,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -43247,7 +43421,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -43365,7 +43539,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -43483,7 +43657,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -43601,7 +43775,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -43719,7 +43893,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -43837,7 +44011,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -43955,7 +44129,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -44073,7 +44247,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -44191,7 +44365,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -44309,7 +44483,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -44427,7 +44601,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -44545,7 +44719,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -44663,7 +44837,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -44781,7 +44955,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -44899,7 +45073,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -45017,7 +45191,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -45468,7 +45642,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -45586,7 +45760,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -45704,7 +45878,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -45822,7 +45996,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -45940,7 +46114,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -46058,7 +46232,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -46176,7 +46350,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -46294,7 +46468,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -46412,7 +46586,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -46530,7 +46704,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -46648,7 +46822,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -46766,7 +46940,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -46884,7 +47058,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -47002,7 +47176,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -47120,7 +47294,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -47238,7 +47412,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -47356,7 +47530,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -47474,7 +47648,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -47592,7 +47766,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -47710,7 +47884,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -47828,7 +48002,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -47946,7 +48120,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -48286,7 +48460,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -48515,7 +48689,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -48633,7 +48807,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -48751,7 +48925,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -48869,7 +49043,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -48987,7 +49161,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -49105,7 +49279,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -49223,7 +49397,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -49341,7 +49515,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -49459,7 +49633,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -49577,7 +49751,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -49695,7 +49869,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -49813,7 +49987,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -49931,7 +50105,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -50049,7 +50223,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -50167,7 +50341,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -50285,7 +50459,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -50403,7 +50577,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -50521,7 +50695,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -50639,7 +50813,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -50757,7 +50931,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -51097,7 +51271,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -51215,7 +51389,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -51333,7 +51507,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -51448,7 +51622,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG464" t="b">
         <v>0</v>
@@ -51563,7 +51737,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG465" t="b">
         <v>0</v>
@@ -51678,7 +51852,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG466" t="b">
         <v>0</v>
@@ -51793,7 +51967,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -51908,7 +52082,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
@@ -52023,7 +52197,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG469" t="b">
         <v>0</v>
@@ -52138,7 +52312,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -52253,7 +52427,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -52368,7 +52542,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -52483,7 +52657,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -52598,7 +52772,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -52713,7 +52887,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -52828,7 +53002,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
@@ -52943,7 +53117,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG477" t="b">
         <v>0</v>
@@ -53058,7 +53232,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG478" t="b">
         <v>0</v>
@@ -53506,7 +53680,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG482" t="b">
         <v>0</v>
@@ -53621,7 +53795,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG483" t="b">
         <v>0</v>
@@ -53736,7 +53910,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -53851,7 +54025,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -53966,7 +54140,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG486" t="b">
         <v>0</v>
@@ -54081,7 +54255,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG487" t="b">
         <v>0</v>
@@ -54196,7 +54370,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -54311,7 +54485,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -54426,7 +54600,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -54541,7 +54715,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -54656,7 +54830,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -54771,7 +54945,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -54886,7 +55060,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -55001,7 +55175,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -55116,7 +55290,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -55231,7 +55405,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -55346,7 +55520,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -55461,7 +55635,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG499" t="b">
         <v>0</v>
@@ -55576,7 +55750,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -55691,7 +55865,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG501" t="b">
         <v>0</v>
@@ -55806,7 +55980,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -55921,7 +56095,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG503" t="b">
         <v>0</v>
@@ -56036,7 +56210,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -56151,7 +56325,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG505" t="b">
         <v>0</v>
@@ -56266,7 +56440,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG506" t="b">
         <v>0</v>
@@ -56381,7 +56555,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG507" t="b">
         <v>0</v>
@@ -56496,7 +56670,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG508" t="b">
         <v>0</v>
@@ -56611,7 +56785,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG509" t="b">
         <v>0</v>
@@ -56726,7 +56900,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG510" t="b">
         <v>0</v>
@@ -56841,7 +57015,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG511" t="b">
         <v>0</v>
@@ -56956,7 +57130,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG512" t="b">
         <v>0</v>
@@ -57071,7 +57245,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG513" t="b">
         <v>0</v>
@@ -57186,7 +57360,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG514" t="b">
         <v>0</v>
@@ -57301,7 +57475,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>
@@ -57416,7 +57590,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG516" t="b">
         <v>0</v>
@@ -57531,7 +57705,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG517" t="b">
         <v>0</v>
@@ -57646,7 +57820,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG518" t="b">
         <v>0</v>
@@ -57761,7 +57935,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG519" t="b">
         <v>0</v>
@@ -57876,7 +58050,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG520" t="b">
         <v>0</v>
@@ -57991,7 +58165,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG521" t="b">
         <v>0</v>
@@ -58106,7 +58280,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -58221,7 +58395,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -58336,7 +58510,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -58451,7 +58625,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -58566,7 +58740,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -58681,7 +58855,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -58796,7 +58970,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG528" t="b">
         <v>0</v>
@@ -58911,7 +59085,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -59026,7 +59200,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -59141,7 +59315,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -59256,7 +59430,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -59371,7 +59545,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG533" t="b">
         <v>0</v>
@@ -59486,7 +59660,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG534" t="b">
         <v>0</v>
@@ -59601,7 +59775,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -59716,7 +59890,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -59727,11 +59901,2299 @@
       <c r="AI536" t="inlineStr">
         <is>
           <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="F537" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I537" t="b">
+        <v>0</v>
+      </c>
+      <c r="J537" t="n">
+        <v>10</v>
+      </c>
+      <c r="K537" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M537" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N537" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P537" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S537" t="n">
+        <v>7</v>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V537" t="n">
+        <v>142</v>
+      </c>
+      <c r="W537" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="X537" t="n">
+        <v>132.06</v>
+      </c>
+      <c r="Y537" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z537" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG537" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH537" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI537" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="F538" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I538" t="b">
+        <v>0</v>
+      </c>
+      <c r="J538" t="n">
+        <v>10</v>
+      </c>
+      <c r="K538" t="n">
+        <v>374.55</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M538" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N538" t="n">
+        <v>10</v>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P538" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S538" t="n">
+        <v>4.1527</v>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V538" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="W538" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="X538" t="n">
+        <v>326.36</v>
+      </c>
+      <c r="Y538" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z538" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG538" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH538" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI538" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="F539" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I539" t="b">
+        <v>0</v>
+      </c>
+      <c r="J539" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="K539" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M539" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N539" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P539" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S539" t="n">
+        <v>7</v>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V539" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W539" t="n">
+        <v>20.7126</v>
+      </c>
+      <c r="X539" t="n">
+        <v>16.926</v>
+      </c>
+      <c r="Y539" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z539" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG539" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH539" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI539" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>82</v>
+      </c>
+      <c r="F540" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I540" t="b">
+        <v>0</v>
+      </c>
+      <c r="J540" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K540" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M540" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N540" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P540" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>81.77</v>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S540" t="n">
+        <v>7</v>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V540" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="W540" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="X540" t="n">
+        <v>44.0355</v>
+      </c>
+      <c r="Y540" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z540" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG540" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH540" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI540" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="F541" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I541" t="b">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>10</v>
+      </c>
+      <c r="K541" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M541" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N541" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P541" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S541" t="n">
+        <v>7</v>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V541" t="n">
+        <v>153</v>
+      </c>
+      <c r="W541" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="X541" t="n">
+        <v>142.29</v>
+      </c>
+      <c r="Y541" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z541" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG541" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH541" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI541" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="F542" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I542" t="b">
+        <v>0</v>
+      </c>
+      <c r="J542" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="K542" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M542" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N542" t="n">
+        <v>10</v>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P542" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S542" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V542" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="W542" t="n">
+        <v>133.8926</v>
+      </c>
+      <c r="X542" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="Y542" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z542" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG542" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH542" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI542" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="F543" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I543" t="b">
+        <v>0</v>
+      </c>
+      <c r="J543" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K543" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M543" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N543" t="n">
+        <v>3</v>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P543" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S543" t="n">
+        <v>7</v>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V543" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="W543" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="X543" t="n">
+        <v>36.4095</v>
+      </c>
+      <c r="Y543" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z543" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG543" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH543" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI543" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="F544" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I544" t="b">
+        <v>0</v>
+      </c>
+      <c r="J544" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K544" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M544" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N544" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P544" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S544" t="n">
+        <v>7</v>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V544" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="W544" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="X544" t="n">
+        <v>43.1985</v>
+      </c>
+      <c r="Y544" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z544" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG544" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH544" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI544" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="F545" t="n">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I545" t="b">
+        <v>0</v>
+      </c>
+      <c r="J545" t="n">
+        <v>10</v>
+      </c>
+      <c r="K545" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M545" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N545" t="n">
+        <v>10</v>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P545" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S545" t="n">
+        <v>4.9445</v>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V545" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="W545" t="n">
+        <v>79.1795</v>
+      </c>
+      <c r="X545" t="n">
+        <v>65.96850000000001</v>
+      </c>
+      <c r="Y545" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z545" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG545" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH545" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI545" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>86.52</v>
+      </c>
+      <c r="F546" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I546" t="b">
+        <v>0</v>
+      </c>
+      <c r="J546" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K546" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M546" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N546" t="n">
+        <v>3</v>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P546" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="Q546" t="n">
+        <v>81.54000000000001</v>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S546" t="n">
+        <v>7</v>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V546" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="W546" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="X546" t="n">
+        <v>41.292</v>
+      </c>
+      <c r="Y546" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z546" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG546" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH546" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI546" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F547" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I547" t="b">
+        <v>0</v>
+      </c>
+      <c r="J547" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K547" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M547" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N547" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P547" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="Q547" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S547" t="n">
+        <v>7</v>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V547" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="W547" t="n">
+        <v>53.8461</v>
+      </c>
+      <c r="X547" t="n">
+        <v>42.129</v>
+      </c>
+      <c r="Y547" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z547" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG547" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH547" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI547" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>76.20999999999999</v>
+      </c>
+      <c r="F548" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I548" t="b">
+        <v>0</v>
+      </c>
+      <c r="J548" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="K548" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M548" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N548" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P548" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="Q548" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S548" t="n">
+        <v>7</v>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V548" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="W548" t="n">
+        <v>80.5244</v>
+      </c>
+      <c r="X548" t="n">
+        <v>65.84399999999999</v>
+      </c>
+      <c r="Y548" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z548" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG548" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH548" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI548" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>83.17</v>
+      </c>
+      <c r="F549" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I549" t="b">
+        <v>0</v>
+      </c>
+      <c r="J549" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K549" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M549" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N549" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P549" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="Q549" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S549" t="n">
+        <v>7</v>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V549" t="n">
+        <v>40</v>
+      </c>
+      <c r="W549" t="n">
+        <v>48</v>
+      </c>
+      <c r="X549" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="Y549" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z549" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG549" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH549" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI549" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>81.43000000000001</v>
+      </c>
+      <c r="F550" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I550" t="b">
+        <v>0</v>
+      </c>
+      <c r="J550" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="K550" t="n">
+        <v>134</v>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M550" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N550" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P550" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q550" t="n">
+        <v>73.70999999999999</v>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S550" t="n">
+        <v>7</v>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V550" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="W550" t="n">
+        <v>140.1546</v>
+      </c>
+      <c r="X550" t="n">
+        <v>115.785</v>
+      </c>
+      <c r="Y550" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z550" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG550" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH550" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI550" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="F551" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I551" t="b">
+        <v>0</v>
+      </c>
+      <c r="J551" t="n">
+        <v>10</v>
+      </c>
+      <c r="K551" t="n">
+        <v>519.75</v>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M551" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N551" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P551" t="n">
+        <v>456</v>
+      </c>
+      <c r="Q551" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S551" t="n">
+        <v>7</v>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V551" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="W551" t="n">
+        <v>567</v>
+      </c>
+      <c r="X551" t="n">
+        <v>439.425</v>
+      </c>
+      <c r="Y551" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI551" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ551" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="F552" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I552" t="b">
+        <v>0</v>
+      </c>
+      <c r="J552" t="n">
+        <v>10</v>
+      </c>
+      <c r="K552" t="n">
+        <v>1496</v>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M552" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N552" t="n">
+        <v>3</v>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P552" t="n">
+        <v>1372.5</v>
+      </c>
+      <c r="Q552" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S552" t="n">
+        <v>7</v>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V552" t="n">
+        <v>1360</v>
+      </c>
+      <c r="W552" t="n">
+        <v>1632</v>
+      </c>
+      <c r="X552" t="n">
+        <v>1264.8</v>
+      </c>
+      <c r="Y552" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI552" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ552" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F553" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I553" t="b">
+        <v>0</v>
+      </c>
+      <c r="J553" t="n">
+        <v>10</v>
+      </c>
+      <c r="K553" t="n">
+        <v>6787</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M553" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N553" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P553" t="n">
+        <v>6127.5</v>
+      </c>
+      <c r="Q553" t="n">
+        <v>57</v>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S553" t="n">
+        <v>7</v>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V553" t="n">
+        <v>6170</v>
+      </c>
+      <c r="W553" t="n">
+        <v>7404</v>
+      </c>
+      <c r="X553" t="n">
+        <v>5738.1</v>
+      </c>
+      <c r="Y553" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z553" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG553" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH553" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI553" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="F554" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I554" t="b">
+        <v>0</v>
+      </c>
+      <c r="J554" t="n">
+        <v>10</v>
+      </c>
+      <c r="K554" t="n">
+        <v>484</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M554" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N554" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P554" t="n">
+        <v>411.5</v>
+      </c>
+      <c r="Q554" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S554" t="n">
+        <v>7</v>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V554" t="n">
+        <v>440</v>
+      </c>
+      <c r="W554" t="n">
+        <v>528</v>
+      </c>
+      <c r="X554" t="n">
+        <v>409.2</v>
+      </c>
+      <c r="Y554" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z554" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG554" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH554" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI554" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="F555" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I555" t="b">
+        <v>0</v>
+      </c>
+      <c r="J555" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K555" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M555" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N555" t="n">
+        <v>10</v>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P555" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="Q555" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S555" t="n">
+        <v>4.6837</v>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V555" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="W555" t="n">
+        <v>30.7077</v>
+      </c>
+      <c r="X555" t="n">
+        <v>26.069</v>
+      </c>
+      <c r="Y555" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z555" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG555" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH555" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI555" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="F556" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I556" t="b">
+        <v>0</v>
+      </c>
+      <c r="J556" t="n">
+        <v>10</v>
+      </c>
+      <c r="K556" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M556" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N556" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P556" t="n">
+        <v>189.25</v>
+      </c>
+      <c r="Q556" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S556" t="n">
+        <v>7</v>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>RangeRotation</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V556" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="W556" t="n">
+        <v>249</v>
+      </c>
+      <c r="X556" t="n">
+        <v>192.975</v>
+      </c>
+      <c r="Y556" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI556" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ556" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ536"/>
+  <autoFilter ref="A1:AJ556"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59804,25 +62266,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4</v>
+        <v>0.4211</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.4</v>
+        <v>-2.85</v>
       </c>
       <c r="E2" t="n">
-        <v>12.87</v>
+        <v>14.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.33</v>
+        <v>-11.81</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333</v>
+        <v>0.3158</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5333</v>
+        <v>0.5263</v>
       </c>
     </row>
     <row r="3">
@@ -59832,25 +62294,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-17.57</v>
+        <v>-4.67</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08</v>
+        <v>3.22</v>
       </c>
       <c r="F3" t="n">
-        <v>-17.65</v>
+        <v>-7.13</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -59954,22 +62416,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="D2" t="n">
-        <v>14.46</v>
+        <v>8.67</v>
       </c>
       <c r="E2" t="n">
-        <v>51.13</v>
+        <v>33.94</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.4</v>
+        <v>-4.96</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -59982,25 +62444,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>0.375</v>
+        <v>0.4545</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.859999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3.06</v>
+        <v>5.29</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.59</v>
+        <v>-14.88</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>0.1818</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="4">
@@ -60010,25 +62472,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2857</v>
+        <v>0.2222</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6</v>
+        <v>-1.08</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77</v>
+        <v>14.25</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.49</v>
+        <v>-8.27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2857</v>
+        <v>0.2222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7143</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="5">
@@ -60107,7 +62569,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15 14:24:07</t>
+          <t>2026-09-16 14:22:24</t>
         </is>
       </c>
     </row>
@@ -60154,7 +62616,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>535</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7">
@@ -60164,7 +62626,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -60174,7 +62636,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$556</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$584</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ556"/>
+  <dimension ref="A1:AJ584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14452,11 +14452,11 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA153" t="n">
         <v>-2.82</v>
@@ -14467,6 +14467,15 @@
       <c r="AC153" t="n">
         <v>-0</v>
       </c>
+      <c r="AD153" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>-4.23</v>
+      </c>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -14475,7 +14484,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -14576,11 +14585,11 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA154" t="n">
         <v>1.15</v>
@@ -14591,6 +14600,15 @@
       <c r="AC154" t="n">
         <v>2.16</v>
       </c>
+      <c r="AD154" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>-1.15</v>
+      </c>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -14599,7 +14617,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -14700,11 +14718,11 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA155" t="n">
         <v>-1.41</v>
@@ -14715,6 +14733,15 @@
       <c r="AC155" t="n">
         <v>-3.32</v>
       </c>
+      <c r="AD155" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -14723,7 +14750,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -14824,11 +14851,11 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA156" t="n">
         <v>-2.74</v>
@@ -14839,6 +14866,15 @@
       <c r="AC156" t="n">
         <v>-1.88</v>
       </c>
+      <c r="AD156" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>-6.34</v>
+      </c>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -14847,7 +14883,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -14948,11 +14984,11 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z157" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA157" t="n">
         <v>5.91</v>
@@ -14963,6 +14999,15 @@
       <c r="AC157" t="n">
         <v>-1.24</v>
       </c>
+      <c r="AD157" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>-4.54</v>
+      </c>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -14971,7 +15016,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -15072,11 +15117,11 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z158" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA158" t="n">
         <v>-1.91</v>
@@ -15087,6 +15132,15 @@
       <c r="AC158" t="n">
         <v>-0.95</v>
       </c>
+      <c r="AD158" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>-14.46</v>
+      </c>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -15095,7 +15149,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -15196,11 +15250,11 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z159" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA159" t="n">
         <v>11.07</v>
@@ -15211,6 +15265,15 @@
       <c r="AC159" t="n">
         <v>7.38</v>
       </c>
+      <c r="AD159" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>-7.38</v>
+      </c>
       <c r="AG159" t="b">
         <v>1</v>
       </c>
@@ -15219,7 +15282,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -15320,11 +15383,11 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z160" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA160" t="n">
         <v>-8.1</v>
@@ -15335,6 +15398,15 @@
       <c r="AC160" t="n">
         <v>-10.19</v>
       </c>
+      <c r="AD160" t="n">
+        <v>-21.55</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>-22.56</v>
+      </c>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -15343,7 +15415,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -15444,11 +15516,11 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z161" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA161" t="n">
         <v>-1.03</v>
@@ -15459,6 +15531,15 @@
       <c r="AC161" t="n">
         <v>-3.37</v>
       </c>
+      <c r="AD161" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>-5.72</v>
+      </c>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -15467,7 +15548,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -15568,11 +15649,11 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z162" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA162" t="n">
         <v>4.64</v>
@@ -15583,6 +15664,15 @@
       <c r="AC162" t="n">
         <v>-0.39</v>
       </c>
+      <c r="AD162" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>-9.960000000000001</v>
+      </c>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
@@ -15591,7 +15681,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -15692,11 +15782,11 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z163" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA163" t="n">
         <v>-4.52</v>
@@ -15707,6 +15797,15 @@
       <c r="AC163" t="n">
         <v>-5.13</v>
       </c>
+      <c r="AD163" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>-7.39</v>
+      </c>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -15715,7 +15814,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -15816,11 +15915,11 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z164" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA164" t="n">
         <v>-3.02</v>
@@ -15831,6 +15930,15 @@
       <c r="AC164" t="n">
         <v>-2.85</v>
       </c>
+      <c r="AD164" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>-6.53</v>
+      </c>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -15839,7 +15947,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -15940,11 +16048,11 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z165" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA165" t="n">
         <v>5.09</v>
@@ -15955,6 +16063,15 @@
       <c r="AC165" t="n">
         <v>2.31</v>
       </c>
+      <c r="AD165" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>-1.39</v>
+      </c>
       <c r="AG165" t="b">
         <v>1</v>
       </c>
@@ -15963,7 +16080,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -16064,11 +16181,11 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z166" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA166" t="n">
         <v>25.39</v>
@@ -16079,6 +16196,15 @@
       <c r="AC166" t="n">
         <v>21.85</v>
       </c>
+      <c r="AD166" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>-4.62</v>
+      </c>
       <c r="AG166" t="b">
         <v>1</v>
       </c>
@@ -16087,7 +16213,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -16188,11 +16314,11 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z167" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA167" t="n">
         <v>3.51</v>
@@ -16203,6 +16329,15 @@
       <c r="AC167" t="n">
         <v>-12.81</v>
       </c>
+      <c r="AD167" t="n">
+        <v>-17.54</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>-23.42</v>
+      </c>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -16211,7 +16346,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -16423,11 +16558,11 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z169" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA169" t="n">
         <v>7.4</v>
@@ -16438,6 +16573,15 @@
       <c r="AC169" t="n">
         <v>-2.82</v>
       </c>
+      <c r="AD169" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>-9.99</v>
+      </c>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -16446,7 +16590,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -16547,11 +16691,11 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z170" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA170" t="n">
         <v>5.15</v>
@@ -16562,6 +16706,15 @@
       <c r="AC170" t="n">
         <v>10.57</v>
       </c>
+      <c r="AD170" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>-7.55</v>
+      </c>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -16570,7 +16723,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -16671,11 +16824,11 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z171" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA171" t="n">
         <v>-63.88</v>
@@ -16686,6 +16839,15 @@
       <c r="AC171" t="n">
         <v>-62.92</v>
       </c>
+      <c r="AD171" t="n">
+        <v>-66.25</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>-54.55</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>-67.53</v>
+      </c>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -16694,7 +16856,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -16799,7 +16961,7 @@
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -16923,7 +17085,7 @@
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -17047,7 +17209,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -17171,7 +17333,7 @@
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -17295,7 +17457,7 @@
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -17419,7 +17581,7 @@
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -17543,7 +17705,7 @@
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -17778,7 +17940,7 @@
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -17902,7 +18064,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -18026,7 +18188,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -18150,7 +18312,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -18274,7 +18436,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -18398,7 +18560,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -18522,7 +18684,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -18646,7 +18808,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -18770,7 +18932,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -18894,7 +19056,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -19018,7 +19180,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -19142,7 +19304,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -19266,7 +19428,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -19390,7 +19552,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -19514,7 +19676,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19638,7 +19800,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19762,7 +19924,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -19886,7 +20048,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -20232,7 +20394,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -20356,7 +20518,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -20480,7 +20642,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -20604,7 +20766,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -20728,7 +20890,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -20852,7 +21014,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -20976,7 +21138,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -21100,7 +21262,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -21224,7 +21386,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -21348,7 +21510,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21472,7 +21634,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21596,7 +21758,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -21720,7 +21882,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -21955,7 +22117,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -22079,7 +22241,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -22203,7 +22365,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -22327,7 +22489,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -22451,13 +22613,16 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
       </c>
       <c r="AB218" t="n">
         <v>3.96</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>2.38</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -22572,13 +22737,16 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
       </c>
       <c r="AB219" t="n">
         <v>-3.81</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>-3.41</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -22693,13 +22861,16 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
       </c>
       <c r="AB220" t="n">
         <v>-6.75</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>-8.44</v>
       </c>
       <c r="AG220" t="b">
         <v>0</v>
@@ -22814,13 +22985,16 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
       </c>
       <c r="AB221" t="n">
         <v>-2.83</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>-4.5</v>
       </c>
       <c r="AG221" t="b">
         <v>0</v>
@@ -22935,13 +23109,16 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
       </c>
       <c r="AB222" t="n">
         <v>-3.32</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>-7.64</v>
       </c>
       <c r="AG222" t="b">
         <v>0</v>
@@ -23056,13 +23233,16 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
       </c>
       <c r="AB223" t="n">
         <v>-2.77</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>-5.91</v>
       </c>
       <c r="AG223" t="b">
         <v>0</v>
@@ -23177,13 +23357,16 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
       </c>
       <c r="AB224" t="n">
         <v>2.17</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>-2.07</v>
       </c>
       <c r="AG224" t="b">
         <v>0</v>
@@ -23298,13 +23481,16 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
       </c>
       <c r="AB225" t="n">
         <v>1.46</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>-7.77</v>
       </c>
       <c r="AG225" t="b">
         <v>1</v>
@@ -23419,13 +23605,16 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
       </c>
       <c r="AB226" t="n">
         <v>-2.37</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.63</v>
       </c>
       <c r="AG226" t="b">
         <v>0</v>
@@ -23540,13 +23729,16 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
       </c>
       <c r="AB227" t="n">
         <v>-4.81</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>-9.800000000000001</v>
       </c>
       <c r="AG227" t="b">
         <v>0</v>
@@ -23661,13 +23853,16 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
       </c>
       <c r="AB228" t="n">
         <v>4.95</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>7.07</v>
       </c>
       <c r="AG228" t="b">
         <v>0</v>
@@ -23782,13 +23977,16 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
       </c>
       <c r="AB229" t="n">
         <v>13.87</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.64</v>
       </c>
       <c r="AG229" t="b">
         <v>0</v>
@@ -23903,13 +24101,16 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
       </c>
       <c r="AB230" t="n">
         <v>3.59</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>-4.64</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -24024,13 +24225,16 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
       </c>
       <c r="AB231" t="n">
         <v>-15.76</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>-20.34</v>
       </c>
       <c r="AG231" t="b">
         <v>0</v>
@@ -24256,13 +24460,16 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
       </c>
       <c r="AB233" t="n">
         <v>-9.52</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>-11.93</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -24599,13 +24806,16 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
       </c>
       <c r="AB236" t="n">
         <v>5.15</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="AG236" t="b">
         <v>0</v>
@@ -24720,7 +24930,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -24728,8 +24938,11 @@
       <c r="AB237" t="n">
         <v>4.06</v>
       </c>
+      <c r="AC237" t="n">
+        <v>12.06</v>
+      </c>
       <c r="AG237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH237" t="b">
         <v>0</v>
@@ -24841,13 +25054,16 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
       </c>
       <c r="AB238" t="n">
         <v>-6.18</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>-9.470000000000001</v>
       </c>
       <c r="AG238" t="b">
         <v>0</v>
@@ -24962,13 +25178,16 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
       </c>
       <c r="AB239" t="n">
         <v>-15.38</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>-23.4</v>
       </c>
       <c r="AG239" t="b">
         <v>0</v>
@@ -25083,13 +25302,16 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
       </c>
       <c r="AB240" t="n">
         <v>-7.74</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>-3.3</v>
       </c>
       <c r="AG240" t="b">
         <v>0</v>
@@ -25204,13 +25426,16 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
       </c>
       <c r="AB241" t="n">
         <v>-65.59</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>-68.67</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -25325,13 +25550,16 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
       </c>
       <c r="AB242" t="n">
         <v>-7.33</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>-14.29</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>
@@ -25446,7 +25674,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -25567,7 +25795,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -25688,7 +25916,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -25809,7 +26037,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -25930,7 +26158,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -26051,7 +26279,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26172,7 +26400,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26293,7 +26521,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -26414,7 +26642,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -26535,7 +26763,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -26656,7 +26884,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -26777,7 +27005,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -26898,7 +27126,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27241,7 +27469,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -27584,7 +27812,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -27705,7 +27933,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -27826,7 +28054,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -27947,7 +28175,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28179,7 +28407,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28300,7 +28528,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -28421,7 +28649,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -28542,7 +28770,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -28663,7 +28891,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -28784,7 +29012,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -28905,7 +29133,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29026,7 +29254,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -29147,7 +29375,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -29268,7 +29496,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -29389,7 +29617,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -29510,7 +29738,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -29631,7 +29859,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -29752,7 +29980,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -29873,7 +30101,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -29994,7 +30222,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -30115,7 +30343,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -30236,7 +30464,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30357,7 +30585,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -30478,7 +30706,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -30599,7 +30827,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -30720,7 +30948,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -30841,7 +31069,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -30850,7 +31078,7 @@
         <v>14.62</v>
       </c>
       <c r="AG288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH288" t="b">
         <v>0</v>
@@ -30962,7 +31190,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -31083,7 +31311,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -31204,7 +31432,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -31325,7 +31553,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -31446,7 +31674,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -31900,7 +32128,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32021,7 +32249,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -32142,7 +32370,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -32374,7 +32602,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -32495,7 +32723,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -32616,7 +32844,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -32737,7 +32965,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -32858,7 +33086,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -32979,7 +33207,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -33100,7 +33328,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -33221,7 +33449,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -33342,7 +33570,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -33463,7 +33691,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -33584,7 +33812,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -33705,7 +33933,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -33826,7 +34054,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -33947,7 +34175,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -34068,7 +34296,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -34189,7 +34417,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -34310,7 +34538,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -34431,7 +34659,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -34552,7 +34780,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -34673,7 +34901,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -34794,7 +35022,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -34915,7 +35143,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -35036,7 +35264,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -35157,7 +35385,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -35500,7 +35728,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -35621,7 +35849,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -35742,7 +35970,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -36085,7 +36313,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -36206,7 +36434,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -36327,7 +36555,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -36448,7 +36676,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -36569,7 +36797,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -36690,7 +36918,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -36811,7 +37039,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -36932,7 +37160,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -37053,7 +37281,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -37174,7 +37402,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -37295,7 +37523,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -37416,7 +37644,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -37537,7 +37765,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -37658,7 +37886,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -37779,7 +38007,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -37900,7 +38128,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -38021,7 +38249,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -38142,7 +38370,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -38151,7 +38379,7 @@
         <v>10.34</v>
       </c>
       <c r="AG349" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH349" t="b">
         <v>0</v>
@@ -38263,7 +38491,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -38384,7 +38612,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -38505,7 +38733,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -38626,7 +38854,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -39191,7 +39419,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -39312,7 +39540,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -39433,10 +39661,13 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>0.28</v>
       </c>
       <c r="AG360" t="b">
         <v>0</v>
@@ -39551,10 +39782,13 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AG361" t="b">
         <v>0</v>
@@ -39669,10 +39903,13 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>6.79</v>
       </c>
       <c r="AG362" t="b">
         <v>0</v>
@@ -39787,10 +40024,13 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>-7.02</v>
       </c>
       <c r="AG363" t="b">
         <v>0</v>
@@ -39905,10 +40145,13 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>-2.37</v>
       </c>
       <c r="AG364" t="b">
         <v>0</v>
@@ -40023,10 +40266,13 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>2.69</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -40141,10 +40387,13 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>3.69</v>
       </c>
       <c r="AG366" t="b">
         <v>0</v>
@@ -40259,10 +40508,13 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
+      </c>
+      <c r="AB367" t="n">
+        <v>4.33</v>
       </c>
       <c r="AG367" t="b">
         <v>0</v>
@@ -40377,10 +40629,13 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
+      </c>
+      <c r="AB368" t="n">
+        <v>3.06</v>
       </c>
       <c r="AG368" t="b">
         <v>0</v>
@@ -40495,10 +40750,13 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
+      </c>
+      <c r="AB369" t="n">
+        <v>-0.44</v>
       </c>
       <c r="AG369" t="b">
         <v>0</v>
@@ -40613,10 +40871,13 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
+      </c>
+      <c r="AB370" t="n">
+        <v>10.45</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -40731,10 +40992,13 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
+      </c>
+      <c r="AB371" t="n">
+        <v>9.49</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -40849,10 +41113,13 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
+      </c>
+      <c r="AB372" t="n">
+        <v>0.73</v>
       </c>
       <c r="AG372" t="b">
         <v>0</v>
@@ -40967,10 +41234,13 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
+      </c>
+      <c r="AB373" t="n">
+        <v>6.27</v>
       </c>
       <c r="AG373" t="b">
         <v>0</v>
@@ -41085,10 +41355,13 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
+      </c>
+      <c r="AB374" t="n">
+        <v>7.86</v>
       </c>
       <c r="AG374" t="b">
         <v>0</v>
@@ -41203,10 +41476,13 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
+      </c>
+      <c r="AB375" t="n">
+        <v>10.58</v>
       </c>
       <c r="AG375" t="b">
         <v>0</v>
@@ -41321,10 +41597,13 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
+      </c>
+      <c r="AB376" t="n">
+        <v>-15.8</v>
       </c>
       <c r="AG376" t="b">
         <v>0</v>
@@ -41439,10 +41718,13 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
+      </c>
+      <c r="AB377" t="n">
+        <v>5.08</v>
       </c>
       <c r="AG377" t="b">
         <v>0</v>
@@ -41779,10 +42061,13 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
+      </c>
+      <c r="AB380" t="n">
+        <v>-18.64</v>
       </c>
       <c r="AG380" t="b">
         <v>0</v>
@@ -41897,10 +42182,13 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
+      </c>
+      <c r="AB381" t="n">
+        <v>3.18</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -42126,10 +42414,13 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
+      </c>
+      <c r="AB383" t="n">
+        <v>-13.74</v>
       </c>
       <c r="AG383" t="b">
         <v>0</v>
@@ -42244,7 +42535,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -42362,7 +42653,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -42480,7 +42771,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -42598,7 +42889,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -42716,7 +43007,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -42834,7 +43125,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -42949,7 +43240,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -43067,7 +43358,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -43185,7 +43476,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -43303,7 +43594,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -43421,7 +43712,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -43539,7 +43830,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -43657,7 +43948,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -43775,7 +44066,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -43893,7 +44184,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -44011,7 +44302,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -44129,7 +44420,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -44247,7 +44538,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -44365,7 +44656,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -44483,7 +44774,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -44601,7 +44892,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -44719,7 +45010,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -44837,7 +45128,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -44955,7 +45246,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -45073,7 +45364,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -45191,7 +45482,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -45642,7 +45933,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -45760,7 +46051,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -45878,7 +46169,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -45996,7 +46287,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -46114,7 +46405,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -46232,7 +46523,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -46350,7 +46641,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -46468,7 +46759,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -46586,7 +46877,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -46704,7 +46995,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -46822,7 +47113,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -46940,7 +47231,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -47058,7 +47349,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -47176,7 +47467,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -47294,7 +47585,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -47412,7 +47703,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -47530,7 +47821,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -47648,7 +47939,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -47766,7 +48057,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -47884,7 +48175,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -48002,7 +48293,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -48120,7 +48411,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -48460,7 +48751,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -48689,7 +48980,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -48807,7 +49098,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -48925,7 +49216,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -49043,7 +49334,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -49161,7 +49452,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -49279,7 +49570,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -49397,7 +49688,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -49515,7 +49806,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -49633,7 +49924,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -49751,7 +50042,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -49869,7 +50160,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -49987,7 +50278,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -50105,7 +50396,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -50223,7 +50514,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -50341,7 +50632,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -50459,7 +50750,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -50577,7 +50868,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -50695,7 +50986,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -50813,7 +51104,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -50931,7 +51222,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -51271,7 +51562,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -51389,7 +51680,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -51507,7 +51798,10 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>-0.42</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -51622,7 +51916,10 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>-1.52</v>
       </c>
       <c r="AG464" t="b">
         <v>0</v>
@@ -51737,7 +52034,10 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>-3.28</v>
       </c>
       <c r="AG465" t="b">
         <v>0</v>
@@ -51852,7 +52152,10 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>-3.79</v>
       </c>
       <c r="AG466" t="b">
         <v>0</v>
@@ -51967,7 +52270,10 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>3.51</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -52082,7 +52388,10 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>-4.15</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
@@ -52197,7 +52506,10 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>-3.85</v>
       </c>
       <c r="AG469" t="b">
         <v>0</v>
@@ -52312,7 +52624,10 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>-4.66</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -52427,7 +52742,10 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>4.75</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -52542,7 +52860,10 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>6.92</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -52657,7 +52978,10 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA473" t="n">
+        <v>6.59</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -52772,7 +53096,10 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>5.23</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -52887,7 +53214,10 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>7.24</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -53002,7 +53332,10 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>-10.74</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
@@ -53117,7 +53450,10 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>-7.95</v>
       </c>
       <c r="AG477" t="b">
         <v>0</v>
@@ -53232,7 +53568,10 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>3.33</v>
       </c>
       <c r="AG478" t="b">
         <v>0</v>
@@ -53680,7 +54019,10 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>4.42</v>
       </c>
       <c r="AG482" t="b">
         <v>0</v>
@@ -53795,7 +54137,10 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>7.68</v>
       </c>
       <c r="AG483" t="b">
         <v>0</v>
@@ -53910,7 +54255,10 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>2.61</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -54025,7 +54373,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -54140,7 +54488,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG486" t="b">
         <v>0</v>
@@ -54255,7 +54603,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG487" t="b">
         <v>0</v>
@@ -54370,7 +54718,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -54485,7 +54833,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -54600,7 +54948,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -54715,7 +55063,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -54830,7 +55178,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -54945,7 +55293,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -55060,7 +55408,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -55175,7 +55523,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -55290,7 +55638,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -55405,7 +55753,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -55520,7 +55868,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -55635,7 +55983,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG499" t="b">
         <v>0</v>
@@ -55750,7 +56098,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -55865,7 +56213,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG501" t="b">
         <v>0</v>
@@ -55980,7 +56328,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -56095,7 +56443,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG503" t="b">
         <v>0</v>
@@ -56210,7 +56558,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -56325,7 +56673,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG505" t="b">
         <v>0</v>
@@ -56440,7 +56788,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG506" t="b">
         <v>0</v>
@@ -56555,7 +56903,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG507" t="b">
         <v>0</v>
@@ -56670,7 +57018,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG508" t="b">
         <v>0</v>
@@ -56785,7 +57133,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG509" t="b">
         <v>0</v>
@@ -56900,7 +57248,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG510" t="b">
         <v>0</v>
@@ -57015,7 +57363,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG511" t="b">
         <v>0</v>
@@ -57130,7 +57478,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG512" t="b">
         <v>0</v>
@@ -57245,7 +57593,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG513" t="b">
         <v>0</v>
@@ -57360,7 +57708,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG514" t="b">
         <v>0</v>
@@ -57475,7 +57823,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>
@@ -57590,7 +57938,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG516" t="b">
         <v>0</v>
@@ -57705,7 +58053,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG517" t="b">
         <v>0</v>
@@ -57820,7 +58168,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG518" t="b">
         <v>0</v>
@@ -57935,7 +58283,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG519" t="b">
         <v>0</v>
@@ -58050,7 +58398,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG520" t="b">
         <v>0</v>
@@ -58165,7 +58513,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG521" t="b">
         <v>0</v>
@@ -58280,7 +58628,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -58395,7 +58743,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -58510,7 +58858,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -58625,7 +58973,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -58740,7 +59088,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -58855,7 +59203,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -58970,7 +59318,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG528" t="b">
         <v>0</v>
@@ -59085,7 +59433,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -59200,7 +59548,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -59315,7 +59663,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -59430,7 +59778,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -59545,7 +59893,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG533" t="b">
         <v>0</v>
@@ -59660,7 +60008,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG534" t="b">
         <v>0</v>
@@ -59775,7 +60123,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -59890,7 +60238,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -60005,7 +60353,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG537" t="b">
         <v>0</v>
@@ -60120,7 +60468,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG538" t="b">
         <v>0</v>
@@ -60235,7 +60583,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG539" t="b">
         <v>0</v>
@@ -60350,7 +60698,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG540" t="b">
         <v>0</v>
@@ -60465,7 +60813,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG541" t="b">
         <v>0</v>
@@ -60580,7 +60928,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG542" t="b">
         <v>0</v>
@@ -60695,7 +61043,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG543" t="b">
         <v>0</v>
@@ -60810,7 +61158,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG544" t="b">
         <v>0</v>
@@ -60925,7 +61273,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG545" t="b">
         <v>0</v>
@@ -61040,7 +61388,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG546" t="b">
         <v>0</v>
@@ -61155,7 +61503,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG547" t="b">
         <v>0</v>
@@ -61270,7 +61618,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG548" t="b">
         <v>0</v>
@@ -61385,7 +61733,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG549" t="b">
         <v>0</v>
@@ -61500,7 +61848,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG550" t="b">
         <v>0</v>
@@ -61837,7 +62185,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG553" t="b">
         <v>0</v>
@@ -61952,7 +62300,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG554" t="b">
         <v>0</v>
@@ -62067,7 +62415,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG555" t="b">
         <v>0</v>
@@ -62192,8 +62540,3209 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="F557" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I557" t="b">
+        <v>0</v>
+      </c>
+      <c r="J557" t="n">
+        <v>10</v>
+      </c>
+      <c r="K557" t="n">
+        <v>71.06</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M557" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="N557" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P557" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Q557" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S557" t="n">
+        <v>5.7368</v>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V557" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="W557" t="n">
+        <v>77.1831</v>
+      </c>
+      <c r="X557" t="n">
+        <v>60.894</v>
+      </c>
+      <c r="Y557" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z557" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG557" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH557" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI557" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F558" t="n">
+        <v>53.17</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I558" t="b">
+        <v>0</v>
+      </c>
+      <c r="J558" t="n">
+        <v>10</v>
+      </c>
+      <c r="K558" t="n">
+        <v>259.6</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M558" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N558" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P558" t="n">
+        <v>233</v>
+      </c>
+      <c r="Q558" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S558" t="n">
+        <v>7</v>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V558" t="n">
+        <v>236</v>
+      </c>
+      <c r="W558" t="n">
+        <v>283.2</v>
+      </c>
+      <c r="X558" t="n">
+        <v>219.48</v>
+      </c>
+      <c r="Y558" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z558" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG558" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH558" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI558" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="F559" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I559" t="b">
+        <v>0</v>
+      </c>
+      <c r="J559" t="n">
+        <v>10</v>
+      </c>
+      <c r="K559" t="n">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M559" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N559" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P559" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="Q559" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S559" t="n">
+        <v>5.8666</v>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V559" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="W559" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="X559" t="n">
+        <v>64.57550000000001</v>
+      </c>
+      <c r="Y559" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z559" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG559" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH559" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI559" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>80.61</v>
+      </c>
+      <c r="F560" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I560" t="b">
+        <v>0</v>
+      </c>
+      <c r="J560" t="n">
+        <v>10</v>
+      </c>
+      <c r="K560" t="n">
+        <v>162.25</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M560" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N560" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P560" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="Q560" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S560" t="n">
+        <v>7</v>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V560" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="W560" t="n">
+        <v>177</v>
+      </c>
+      <c r="X560" t="n">
+        <v>137.175</v>
+      </c>
+      <c r="Y560" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z560" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG560" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH560" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI560" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>77.81999999999999</v>
+      </c>
+      <c r="F561" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I561" t="b">
+        <v>0</v>
+      </c>
+      <c r="J561" t="n">
+        <v>10</v>
+      </c>
+      <c r="K561" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M561" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N561" t="n">
+        <v>10</v>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P561" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S561" t="n">
+        <v>5.1279</v>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V561" t="n">
+        <v>344</v>
+      </c>
+      <c r="W561" t="n">
+        <v>386.5798</v>
+      </c>
+      <c r="X561" t="n">
+        <v>326.36</v>
+      </c>
+      <c r="Y561" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z561" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG561" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH561" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI561" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="F562" t="n">
+        <v>49.81</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I562" t="b">
+        <v>0</v>
+      </c>
+      <c r="J562" t="n">
+        <v>10</v>
+      </c>
+      <c r="K562" t="n">
+        <v>33</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M562" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N562" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P562" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="Q562" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S562" t="n">
+        <v>7</v>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V562" t="n">
+        <v>30</v>
+      </c>
+      <c r="W562" t="n">
+        <v>36</v>
+      </c>
+      <c r="X562" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="Y562" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z562" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG562" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH562" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI562" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>萬海</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="F563" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I563" t="b">
+        <v>0</v>
+      </c>
+      <c r="J563" t="n">
+        <v>10</v>
+      </c>
+      <c r="K563" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M563" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N563" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Q563" t="n">
+        <v>56</v>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S563" t="n">
+        <v>7</v>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="V563" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="W563" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="X563" t="n">
+        <v>112.065</v>
+      </c>
+      <c r="Y563" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z563" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG563" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH563" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI563" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="F564" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I564" t="b">
+        <v>0</v>
+      </c>
+      <c r="J564" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K564" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M564" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N564" t="n">
+        <v>5</v>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P564" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="Q564" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S564" t="n">
+        <v>7</v>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V564" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="W564" t="n">
+        <v>21.9553</v>
+      </c>
+      <c r="X564" t="n">
+        <v>17.4375</v>
+      </c>
+      <c r="Y564" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z564" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG564" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH564" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI564" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="F565" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I565" t="b">
+        <v>0</v>
+      </c>
+      <c r="J565" t="n">
+        <v>10</v>
+      </c>
+      <c r="K565" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M565" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N565" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P565" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="Q565" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S565" t="n">
+        <v>7</v>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V565" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="W565" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="X565" t="n">
+        <v>44.547</v>
+      </c>
+      <c r="Y565" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z565" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG565" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH565" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI565" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="F566" t="n">
+        <v>72.89</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I566" t="b">
+        <v>0</v>
+      </c>
+      <c r="J566" t="n">
+        <v>10</v>
+      </c>
+      <c r="K566" t="n">
+        <v>166.65</v>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M566" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N566" t="n">
+        <v>10</v>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P566" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q566" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S566" t="n">
+        <v>5.4257</v>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V566" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="W566" t="n">
+        <v>181.3463</v>
+      </c>
+      <c r="X566" t="n">
+        <v>143.28</v>
+      </c>
+      <c r="Y566" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z566" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG566" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH566" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI566" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="F567" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I567" t="b">
+        <v>0</v>
+      </c>
+      <c r="J567" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K567" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M567" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="N567" t="n">
+        <v>10</v>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P567" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q567" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S567" t="n">
+        <v>4.0536</v>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V567" t="n">
+        <v>112</v>
+      </c>
+      <c r="W567" t="n">
+        <v>131.8665</v>
+      </c>
+      <c r="X567" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="Y567" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z567" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG567" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH567" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI567" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="F568" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I568" t="b">
+        <v>0</v>
+      </c>
+      <c r="J568" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K568" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M568" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N568" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P568" t="n">
+        <v>37.38</v>
+      </c>
+      <c r="Q568" t="n">
+        <v>69.61</v>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S568" t="n">
+        <v>7</v>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V568" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="W568" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="X568" t="n">
+        <v>36.8745</v>
+      </c>
+      <c r="Y568" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z568" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG568" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH568" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI568" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="F569" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I569" t="b">
+        <v>0</v>
+      </c>
+      <c r="J569" t="n">
+        <v>10</v>
+      </c>
+      <c r="K569" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M569" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N569" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P569" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="Q569" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S569" t="n">
+        <v>7</v>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V569" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W569" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="X569" t="n">
+        <v>43.989</v>
+      </c>
+      <c r="Y569" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z569" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG569" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH569" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI569" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F570" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I570" t="b">
+        <v>0</v>
+      </c>
+      <c r="J570" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K570" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M570" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N570" t="n">
+        <v>10</v>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P570" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="Q570" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S570" t="n">
+        <v>1.6536</v>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V570" t="n">
+        <v>69</v>
+      </c>
+      <c r="W570" t="n">
+        <v>77.9504</v>
+      </c>
+      <c r="X570" t="n">
+        <v>67.85899999999999</v>
+      </c>
+      <c r="Y570" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z570" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG570" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH570" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI570" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F571" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I571" t="b">
+        <v>0</v>
+      </c>
+      <c r="J571" t="n">
+        <v>10</v>
+      </c>
+      <c r="K571" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M571" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N571" t="n">
+        <v>10</v>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P571" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="Q571" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S571" t="n">
+        <v>5.4846</v>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V571" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="W571" t="n">
+        <v>59.7078</v>
+      </c>
+      <c r="X571" t="n">
+        <v>49.0535</v>
+      </c>
+      <c r="Y571" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z571" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG571" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH571" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI571" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>81.86</v>
+      </c>
+      <c r="F572" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I572" t="b">
+        <v>0</v>
+      </c>
+      <c r="J572" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="K572" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M572" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N572" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P572" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="Q572" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S572" t="n">
+        <v>7</v>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V572" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="W572" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="X572" t="n">
+        <v>40.9665</v>
+      </c>
+      <c r="Y572" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z572" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG572" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH572" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI572" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>89.48999999999999</v>
+      </c>
+      <c r="F573" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I573" t="b">
+        <v>0</v>
+      </c>
+      <c r="J573" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K573" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M573" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N573" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P573" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="Q573" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S573" t="n">
+        <v>7</v>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V573" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="W573" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="X573" t="n">
+        <v>42.7335</v>
+      </c>
+      <c r="Y573" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z573" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG573" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH573" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI573" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>77.62</v>
+      </c>
+      <c r="F574" t="n">
+        <v>52.76</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I574" t="b">
+        <v>0</v>
+      </c>
+      <c r="J574" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="K574" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M574" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N574" t="n">
+        <v>7</v>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P574" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="Q574" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S574" t="n">
+        <v>7</v>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V574" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="W574" t="n">
+        <v>82.17749999999999</v>
+      </c>
+      <c r="X574" t="n">
+        <v>66.21599999999999</v>
+      </c>
+      <c r="Y574" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z574" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG574" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH574" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI574" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="F575" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I575" t="b">
+        <v>0</v>
+      </c>
+      <c r="J575" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="K575" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M575" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N575" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P575" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="Q575" t="n">
+        <v>72.77</v>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S575" t="n">
+        <v>7</v>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V575" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="W575" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="X575" t="n">
+        <v>37.8975</v>
+      </c>
+      <c r="Y575" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z575" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG575" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH575" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI575" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="F576" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I576" t="b">
+        <v>0</v>
+      </c>
+      <c r="J576" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="K576" t="n">
+        <v>133</v>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M576" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N576" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P576" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="Q576" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S576" t="n">
+        <v>6.5181</v>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V576" t="n">
+        <v>124</v>
+      </c>
+      <c r="W576" t="n">
+        <v>137.24</v>
+      </c>
+      <c r="X576" t="n">
+        <v>115.9175</v>
+      </c>
+      <c r="Y576" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z576" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG576" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH576" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI576" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="F577" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I577" t="b">
+        <v>0</v>
+      </c>
+      <c r="J577" t="n">
+        <v>10</v>
+      </c>
+      <c r="K577" t="n">
+        <v>518.1</v>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M577" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N577" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P577" t="n">
+        <v>463.5</v>
+      </c>
+      <c r="Q577" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S577" t="n">
+        <v>7</v>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V577" t="n">
+        <v>471</v>
+      </c>
+      <c r="W577" t="n">
+        <v>565.2</v>
+      </c>
+      <c r="X577" t="n">
+        <v>438.03</v>
+      </c>
+      <c r="Y577" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI577" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ577" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>72.64</v>
+      </c>
+      <c r="F578" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I578" t="b">
+        <v>0</v>
+      </c>
+      <c r="J578" t="n">
+        <v>10</v>
+      </c>
+      <c r="K578" t="n">
+        <v>1523.5</v>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M578" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N578" t="n">
+        <v>5</v>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P578" t="n">
+        <v>1372.5</v>
+      </c>
+      <c r="Q578" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S578" t="n">
+        <v>7</v>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V578" t="n">
+        <v>1385</v>
+      </c>
+      <c r="W578" t="n">
+        <v>1662</v>
+      </c>
+      <c r="X578" t="n">
+        <v>1288.05</v>
+      </c>
+      <c r="Y578" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI578" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ578" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="F579" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I579" t="b">
+        <v>0</v>
+      </c>
+      <c r="J579" t="n">
+        <v>10</v>
+      </c>
+      <c r="K579" t="n">
+        <v>471.9</v>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M579" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N579" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P579" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="Q579" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S579" t="n">
+        <v>6.5303</v>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V579" t="n">
+        <v>429</v>
+      </c>
+      <c r="W579" t="n">
+        <v>514.8</v>
+      </c>
+      <c r="X579" t="n">
+        <v>400.985</v>
+      </c>
+      <c r="Y579" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI579" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ579" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>80</v>
+      </c>
+      <c r="F580" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I580" t="b">
+        <v>0</v>
+      </c>
+      <c r="J580" t="n">
+        <v>10</v>
+      </c>
+      <c r="K580" t="n">
+        <v>7150</v>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M580" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N580" t="n">
+        <v>3</v>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P580" t="n">
+        <v>6145</v>
+      </c>
+      <c r="Q580" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S580" t="n">
+        <v>7</v>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V580" t="n">
+        <v>6500</v>
+      </c>
+      <c r="W580" t="n">
+        <v>7800</v>
+      </c>
+      <c r="X580" t="n">
+        <v>6045</v>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z580" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI580" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="F581" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I581" t="b">
+        <v>0</v>
+      </c>
+      <c r="J581" t="n">
+        <v>10</v>
+      </c>
+      <c r="K581" t="n">
+        <v>485.65</v>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M581" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N581" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P581" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q581" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S581" t="n">
+        <v>7</v>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V581" t="n">
+        <v>441.5</v>
+      </c>
+      <c r="W581" t="n">
+        <v>529.8</v>
+      </c>
+      <c r="X581" t="n">
+        <v>410.595</v>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z581" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI581" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="F582" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I582" t="b">
+        <v>0</v>
+      </c>
+      <c r="J582" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K582" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M582" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N582" t="n">
+        <v>10</v>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P582" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q582" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S582" t="n">
+        <v>4.7042</v>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V582" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="W582" t="n">
+        <v>115.5977</v>
+      </c>
+      <c r="X582" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z582" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI582" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="F583" t="n">
+        <v>67.47</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I583" t="b">
+        <v>0</v>
+      </c>
+      <c r="J583" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="K583" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M583" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N583" t="n">
+        <v>10</v>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P583" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="Q583" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S583" t="n">
+        <v>5.3757</v>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V583" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="W583" t="n">
+        <v>31.0643</v>
+      </c>
+      <c r="X583" t="n">
+        <v>26.069</v>
+      </c>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z583" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG583" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH583" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI583" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="F584" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I584" t="b">
+        <v>0</v>
+      </c>
+      <c r="J584" t="n">
+        <v>10</v>
+      </c>
+      <c r="K584" t="n">
+        <v>230.45</v>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M584" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N584" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P584" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q584" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S584" t="n">
+        <v>7</v>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V584" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="W584" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="X584" t="n">
+        <v>194.835</v>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI584" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ584" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ556"/>
+  <autoFilter ref="A1:AJ584"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -62266,25 +65815,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4211</v>
+        <v>0.3939</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.85</v>
+        <v>-4.45</v>
       </c>
       <c r="E2" t="n">
-        <v>14.5</v>
+        <v>11.79</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.81</v>
+        <v>-12.65</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3158</v>
+        <v>0.2424</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5263</v>
+        <v>0.5758</v>
       </c>
     </row>
     <row r="3">
@@ -62294,25 +65843,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.67</v>
+        <v>-2.24</v>
       </c>
       <c r="E3" t="n">
-        <v>3.22</v>
+        <v>4.19</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.13</v>
+        <v>-5.74</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="4">
@@ -62416,22 +65965,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="D2" t="n">
-        <v>8.67</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>33.94</v>
+        <v>31.59</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.96</v>
+        <v>-4.07</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -62444,25 +65993,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4545</v>
+        <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.1</v>
+        <v>-6.21</v>
       </c>
       <c r="E3" t="n">
-        <v>5.29</v>
+        <v>7.27</v>
       </c>
       <c r="F3" t="n">
-        <v>-14.88</v>
+        <v>-12.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1818</v>
+        <v>0.15</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5455</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="4">
@@ -62472,25 +66021,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2222</v>
+        <v>0.3125</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.08</v>
+        <v>-4.79</v>
       </c>
       <c r="E4" t="n">
-        <v>14.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.27</v>
+        <v>-12.31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2222</v>
+        <v>0.125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5556</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="5">
@@ -62500,6 +66049,24 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -62569,7 +66136,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-16 14:22:24</t>
+          <t>2026-09-17 14:26:37</t>
         </is>
       </c>
     </row>
@@ -62616,7 +66183,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>555</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7">
@@ -62626,7 +66193,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8">
@@ -62636,7 +66203,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$584</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$614</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ584"/>
+  <dimension ref="A1:AJ614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16957,11 +16957,11 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z172" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA172" t="n">
         <v>-2.21</v>
@@ -16972,6 +16972,15 @@
       <c r="AC172" t="n">
         <v>-1.41</v>
       </c>
+      <c r="AD172" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>-4.43</v>
+      </c>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -16980,7 +16989,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -17081,11 +17090,11 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z173" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA173" t="n">
         <v>-1.14</v>
@@ -17096,6 +17105,15 @@
       <c r="AC173" t="n">
         <v>1</v>
       </c>
+      <c r="AD173" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>-1.86</v>
+      </c>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -17104,7 +17122,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -17205,11 +17223,11 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA174" t="n">
         <v>-7.41</v>
@@ -17220,6 +17238,15 @@
       <c r="AC174" t="n">
         <v>-5.6</v>
       </c>
+      <c r="AD174" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>-9.880000000000001</v>
+      </c>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -17228,7 +17255,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -17329,11 +17356,11 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z175" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA175" t="n">
         <v>2.27</v>
@@ -17344,6 +17371,15 @@
       <c r="AC175" t="n">
         <v>-6.63</v>
       </c>
+      <c r="AD175" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>-11.84</v>
+      </c>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -17352,7 +17388,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -17453,11 +17489,11 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z176" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA176" t="n">
         <v>7.46</v>
@@ -17468,6 +17504,15 @@
       <c r="AC176" t="n">
         <v>10.82</v>
       </c>
+      <c r="AD176" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>-2.24</v>
+      </c>
       <c r="AG176" t="b">
         <v>1</v>
       </c>
@@ -17476,7 +17521,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -17577,11 +17622,11 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z177" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA177" t="n">
         <v>0.67</v>
@@ -17592,6 +17637,15 @@
       <c r="AC177" t="n">
         <v>14.5</v>
       </c>
+      <c r="AD177" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>-2.15</v>
+      </c>
       <c r="AG177" t="b">
         <v>1</v>
       </c>
@@ -17600,7 +17654,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -17701,11 +17755,11 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z178" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA178" t="n">
         <v>25.94</v>
@@ -17716,6 +17770,15 @@
       <c r="AC178" t="n">
         <v>18.72</v>
       </c>
+      <c r="AD178" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>-5.61</v>
+      </c>
       <c r="AG178" t="b">
         <v>1</v>
       </c>
@@ -17724,7 +17787,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -17936,11 +17999,11 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z180" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA180" t="n">
         <v>7.41</v>
@@ -17951,15 +18014,24 @@
       <c r="AC180" t="n">
         <v>9.289999999999999</v>
       </c>
+      <c r="AD180" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>-7.05</v>
+      </c>
       <c r="AG180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH180" t="b">
         <v>1</v>
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18136,7 @@
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -18188,7 +18260,7 @@
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -18312,7 +18384,7 @@
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -18436,7 +18508,7 @@
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -18560,7 +18632,7 @@
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -18684,7 +18756,7 @@
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -18808,7 +18880,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -18932,7 +19004,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -19056,7 +19128,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -19180,7 +19252,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -19304,7 +19376,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -19428,7 +19500,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -19552,7 +19624,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -19676,7 +19748,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19800,7 +19872,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19924,7 +19996,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -20048,7 +20120,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -20394,7 +20466,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -20406,7 +20478,7 @@
         <v>8.35</v>
       </c>
       <c r="AG200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH200" t="b">
         <v>0</v>
@@ -20518,7 +20590,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -20642,7 +20714,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -20766,7 +20838,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -20890,7 +20962,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -21014,7 +21086,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -21138,7 +21210,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -21262,7 +21334,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -21386,7 +21458,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -21510,7 +21582,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21634,7 +21706,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21758,7 +21830,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -21882,7 +21954,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -22117,7 +22189,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -22241,7 +22313,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -22365,7 +22437,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -22489,7 +22561,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -22613,7 +22685,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22737,7 +22809,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -22861,7 +22933,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -22985,7 +23057,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -23109,7 +23181,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -23233,7 +23305,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -23357,7 +23429,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23481,7 +23553,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23605,7 +23677,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23729,7 +23801,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -23853,7 +23925,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -23977,7 +24049,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -24101,7 +24173,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -24225,7 +24297,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -24460,7 +24532,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24806,7 +24878,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -24818,7 +24890,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH236" t="b">
         <v>0</v>
@@ -24930,7 +25002,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -25054,7 +25126,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -25178,7 +25250,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -25302,7 +25374,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -25426,7 +25498,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25550,7 +25622,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25674,13 +25746,16 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
       </c>
       <c r="AB243" t="n">
         <v>3.03</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>3.67</v>
       </c>
       <c r="AG243" t="b">
         <v>0</v>
@@ -25795,13 +25870,16 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
       </c>
       <c r="AB244" t="n">
         <v>6.35</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>7.94</v>
       </c>
       <c r="AG244" t="b">
         <v>0</v>
@@ -25916,12 +25994,15 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
       </c>
       <c r="AB245" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="AC245" t="n">
         <v>-4.27</v>
       </c>
       <c r="AG245" t="b">
@@ -26037,13 +26118,16 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
       </c>
       <c r="AB246" t="n">
         <v>-5.7</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>-4.5</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -26158,13 +26242,16 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
       </c>
       <c r="AB247" t="n">
         <v>-12.76</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>-11.18</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -26279,13 +26366,16 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
       </c>
       <c r="AB248" t="n">
         <v>1.2</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>3.16</v>
       </c>
       <c r="AG248" t="b">
         <v>0</v>
@@ -26400,13 +26490,16 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
       </c>
       <c r="AB249" t="n">
         <v>0.75</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>3.14</v>
       </c>
       <c r="AG249" t="b">
         <v>0</v>
@@ -26521,13 +26614,16 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
       </c>
       <c r="AB250" t="n">
         <v>-8.699999999999999</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>-2.78</v>
       </c>
       <c r="AG250" t="b">
         <v>0</v>
@@ -26642,13 +26738,16 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
       </c>
       <c r="AB251" t="n">
         <v>3.12</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>4.51</v>
       </c>
       <c r="AG251" t="b">
         <v>0</v>
@@ -26763,13 +26862,16 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
       </c>
       <c r="AB252" t="n">
         <v>-5.73</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>-8.99</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -26884,13 +26986,16 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
       </c>
       <c r="AB253" t="n">
         <v>0.3</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>2.08</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
@@ -27005,13 +27110,16 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
       </c>
       <c r="AB254" t="n">
         <v>-6.09</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>5.54</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -27126,13 +27234,16 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
       </c>
       <c r="AB255" t="n">
         <v>-11.98</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>-11.62</v>
       </c>
       <c r="AG255" t="b">
         <v>0</v>
@@ -27469,13 +27580,16 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
       </c>
       <c r="AB258" t="n">
         <v>-8.57</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>-7.45</v>
       </c>
       <c r="AG258" t="b">
         <v>0</v>
@@ -27812,13 +27926,16 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
       </c>
       <c r="AB261" t="n">
         <v>1.75</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>18.87</v>
       </c>
       <c r="AG261" t="b">
         <v>0</v>
@@ -27933,13 +28050,16 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
       </c>
       <c r="AB262" t="n">
         <v>-6.01</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>-6.28</v>
       </c>
       <c r="AG262" t="b">
         <v>0</v>
@@ -28054,13 +28174,16 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
       </c>
       <c r="AB263" t="n">
         <v>-10.21</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>-12.92</v>
       </c>
       <c r="AG263" t="b">
         <v>0</v>
@@ -28175,13 +28298,16 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
       </c>
       <c r="AB264" t="n">
         <v>-0.48</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>2.74</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -28407,13 +28533,16 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
       </c>
       <c r="AB266" t="n">
         <v>-17.15</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>-23.62</v>
       </c>
       <c r="AG266" t="b">
         <v>0</v>
@@ -28528,13 +28657,16 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
       </c>
       <c r="AB267" t="n">
         <v>-67.92</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>-70.28</v>
       </c>
       <c r="AG267" t="b">
         <v>0</v>
@@ -28649,13 +28781,16 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
       </c>
       <c r="AB268" t="n">
         <v>-14.95</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>-11.84</v>
       </c>
       <c r="AG268" t="b">
         <v>0</v>
@@ -28770,7 +28905,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -28891,7 +29026,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -29012,7 +29147,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -29133,7 +29268,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29254,7 +29389,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -29263,7 +29398,7 @@
         <v>10.47</v>
       </c>
       <c r="AG273" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH273" t="b">
         <v>0</v>
@@ -29375,7 +29510,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -29496,7 +29631,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -29617,7 +29752,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -29738,7 +29873,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -29859,7 +29994,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -29980,7 +30115,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -30101,7 +30236,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -30222,7 +30357,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -30343,7 +30478,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -30464,7 +30599,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30585,7 +30720,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -30706,7 +30841,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -30827,7 +30962,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -30948,7 +31083,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -31069,7 +31204,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -31190,7 +31325,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -31311,7 +31446,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -31432,7 +31567,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -31553,7 +31688,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -31674,7 +31809,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -32128,7 +32263,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32249,7 +32384,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -32370,7 +32505,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -32602,7 +32737,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -32723,7 +32858,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -32844,7 +32979,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -32965,7 +33100,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -33086,7 +33221,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -33207,7 +33342,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -33216,7 +33351,7 @@
         <v>4.53</v>
       </c>
       <c r="AG306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH306" t="b">
         <v>1</v>
@@ -33328,7 +33463,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -33449,7 +33584,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -33570,7 +33705,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -33691,7 +33826,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -33812,7 +33947,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -33933,7 +34068,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -34054,7 +34189,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -34175,7 +34310,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -34296,7 +34431,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -34417,7 +34552,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -34538,7 +34673,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -34659,7 +34794,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -34780,7 +34915,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -34901,7 +35036,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -35022,7 +35157,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -35143,7 +35278,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -35264,7 +35399,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -35385,7 +35520,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -35728,7 +35863,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -35849,7 +35984,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -35970,7 +36105,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -36313,7 +36448,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -36434,7 +36569,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -36555,7 +36690,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -36676,7 +36811,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -36797,7 +36932,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -36918,7 +37053,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -37039,7 +37174,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -37160,7 +37295,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -37281,7 +37416,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -37402,7 +37537,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -37523,7 +37658,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -37644,7 +37779,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -37765,7 +37900,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -37886,7 +38021,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -38007,7 +38142,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -38128,7 +38263,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -38249,7 +38384,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -38370,7 +38505,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -38491,7 +38626,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -38612,7 +38747,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -38733,7 +38868,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -38854,7 +38989,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -39419,7 +39554,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -39540,7 +39675,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -39661,7 +39796,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -39782,7 +39917,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -39903,7 +40038,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -40024,7 +40159,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -40145,7 +40280,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -40266,7 +40401,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -40387,7 +40522,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -40508,7 +40643,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -40629,7 +40764,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -40750,7 +40885,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -40871,7 +41006,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -40992,7 +41127,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -41113,7 +41248,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -41234,7 +41369,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -41355,7 +41490,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -41476,7 +41611,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -41597,7 +41732,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -41718,7 +41853,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -42061,7 +42196,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -42182,7 +42317,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -42414,7 +42549,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -42535,10 +42670,13 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
+      </c>
+      <c r="AB384" t="n">
+        <v>-1.52</v>
       </c>
       <c r="AG384" t="b">
         <v>0</v>
@@ -42653,10 +42791,13 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
+      </c>
+      <c r="AB385" t="n">
+        <v>5.54</v>
       </c>
       <c r="AG385" t="b">
         <v>0</v>
@@ -42771,9 +42912,12 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA386" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="AB386" t="n">
         <v>-3.74</v>
       </c>
       <c r="AG386" t="b">
@@ -42889,10 +43033,13 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
+      </c>
+      <c r="AB387" t="n">
+        <v>-3.35</v>
       </c>
       <c r="AG387" t="b">
         <v>0</v>
@@ -43007,10 +43154,13 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
+      </c>
+      <c r="AB388" t="n">
+        <v>-8.44</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
@@ -43125,10 +43275,13 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
+      </c>
+      <c r="AB389" t="n">
+        <v>-9.369999999999999</v>
       </c>
       <c r="AG389" t="b">
         <v>0</v>
@@ -43240,10 +43393,13 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
+      </c>
+      <c r="AB390" t="n">
+        <v>-2.29</v>
       </c>
       <c r="AG390" t="b">
         <v>0</v>
@@ -43358,10 +43514,13 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
+      </c>
+      <c r="AB391" t="n">
+        <v>-6.34</v>
       </c>
       <c r="AG391" t="b">
         <v>0</v>
@@ -43476,10 +43635,13 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
+      </c>
+      <c r="AB392" t="n">
+        <v>-4.02</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -43594,10 +43756,13 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
+      </c>
+      <c r="AB393" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AG393" t="b">
         <v>0</v>
@@ -43712,10 +43877,13 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
+      </c>
+      <c r="AB394" t="n">
+        <v>-4.07</v>
       </c>
       <c r="AG394" t="b">
         <v>0</v>
@@ -43830,10 +43998,13 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>-2.95</v>
       </c>
       <c r="AG395" t="b">
         <v>0</v>
@@ -43948,10 +44119,13 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
+      </c>
+      <c r="AB396" t="n">
+        <v>6.68</v>
       </c>
       <c r="AG396" t="b">
         <v>0</v>
@@ -44066,10 +44240,13 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
+      </c>
+      <c r="AB397" t="n">
+        <v>4.81</v>
       </c>
       <c r="AG397" t="b">
         <v>0</v>
@@ -44184,10 +44361,13 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
+      </c>
+      <c r="AB398" t="n">
+        <v>4.78</v>
       </c>
       <c r="AG398" t="b">
         <v>0</v>
@@ -44302,10 +44482,13 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
+      </c>
+      <c r="AB399" t="n">
+        <v>0</v>
       </c>
       <c r="AG399" t="b">
         <v>0</v>
@@ -44420,9 +44603,12 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA400" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="AB400" t="n">
         <v>-3.91</v>
       </c>
       <c r="AG400" t="b">
@@ -44538,10 +44724,13 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
+      </c>
+      <c r="AB401" t="n">
+        <v>7.08</v>
       </c>
       <c r="AG401" t="b">
         <v>0</v>
@@ -44656,10 +44845,13 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
+      </c>
+      <c r="AB402" t="n">
+        <v>6.54</v>
       </c>
       <c r="AG402" t="b">
         <v>0</v>
@@ -44774,10 +44966,13 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
+      </c>
+      <c r="AB403" t="n">
+        <v>6.99</v>
       </c>
       <c r="AG403" t="b">
         <v>0</v>
@@ -44892,10 +45087,13 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
+      </c>
+      <c r="AB404" t="n">
+        <v>5.6</v>
       </c>
       <c r="AG404" t="b">
         <v>0</v>
@@ -45010,10 +45208,13 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
+      </c>
+      <c r="AB405" t="n">
+        <v>6.7</v>
       </c>
       <c r="AG405" t="b">
         <v>0</v>
@@ -45128,10 +45329,13 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
+      </c>
+      <c r="AB406" t="n">
+        <v>4.49</v>
       </c>
       <c r="AG406" t="b">
         <v>0</v>
@@ -45246,10 +45450,13 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
+      </c>
+      <c r="AB407" t="n">
+        <v>-13.11</v>
       </c>
       <c r="AG407" t="b">
         <v>0</v>
@@ -45364,10 +45571,13 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
+      </c>
+      <c r="AB408" t="n">
+        <v>-3.92</v>
       </c>
       <c r="AG408" t="b">
         <v>0</v>
@@ -45482,10 +45692,13 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
+      </c>
+      <c r="AB409" t="n">
+        <v>5.08</v>
       </c>
       <c r="AG409" t="b">
         <v>0</v>
@@ -45933,10 +46146,13 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
+      </c>
+      <c r="AB413" t="n">
+        <v>-16.11</v>
       </c>
       <c r="AG413" t="b">
         <v>0</v>
@@ -46051,10 +46267,13 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
+      </c>
+      <c r="AB414" t="n">
+        <v>2.44</v>
       </c>
       <c r="AG414" t="b">
         <v>0</v>
@@ -46169,7 +46388,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -46287,7 +46506,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -46405,7 +46624,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -46523,7 +46742,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -46641,7 +46860,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -46759,7 +46978,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -46877,7 +47096,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -46995,7 +47214,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -47113,7 +47332,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -47231,7 +47450,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -47349,7 +47568,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -47467,7 +47686,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -47585,7 +47804,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -47703,7 +47922,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -47821,7 +48040,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -47939,7 +48158,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -48057,7 +48276,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -48175,7 +48394,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -48293,7 +48512,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -48411,7 +48630,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -48751,13 +48970,13 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
       </c>
       <c r="AG437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH437" t="b">
         <v>0</v>
@@ -48980,7 +49199,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -49098,7 +49317,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -49216,7 +49435,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -49334,7 +49553,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -49452,7 +49671,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -49570,7 +49789,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -49688,7 +49907,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -49806,7 +50025,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -49924,7 +50143,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -50042,7 +50261,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -50160,7 +50379,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -50278,7 +50497,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -50396,7 +50615,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -50514,7 +50733,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -50632,7 +50851,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -50750,7 +50969,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -50868,7 +51087,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -50986,7 +51205,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -51104,7 +51323,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -51222,7 +51441,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -51562,7 +51781,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -51680,7 +51899,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -51798,7 +52017,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -51916,7 +52135,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -52034,7 +52253,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -52152,7 +52371,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -52270,7 +52489,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -52388,7 +52607,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -52506,7 +52725,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -52624,7 +52843,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -52742,7 +52961,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -52860,7 +53079,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -52978,7 +53197,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -53096,7 +53315,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -53214,7 +53433,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -53332,7 +53551,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -53450,7 +53669,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -53568,7 +53787,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -54019,7 +54238,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -54137,7 +54356,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -54255,7 +54474,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -54373,7 +54592,10 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA485" t="n">
+        <v>-0.42</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -54488,7 +54710,10 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA486" t="n">
+        <v>1.49</v>
       </c>
       <c r="AG486" t="b">
         <v>0</v>
@@ -54603,7 +54828,10 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA487" t="n">
+        <v>0.5</v>
       </c>
       <c r="AG487" t="b">
         <v>0</v>
@@ -54718,7 +54946,10 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA488" t="n">
+        <v>3.56</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -54833,7 +55064,10 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA489" t="n">
+        <v>2.73</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -54948,7 +55182,10 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA490" t="n">
+        <v>1.94</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -55063,7 +55300,10 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA491" t="n">
+        <v>3.93</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -55178,7 +55418,10 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA492" t="n">
+        <v>3.83</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -55293,7 +55536,10 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA493" t="n">
+        <v>0.22</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -55408,7 +55654,10 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA494" t="n">
+        <v>-1.16</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -55523,7 +55772,10 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA495" t="n">
+        <v>4.1</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -55638,7 +55890,10 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA496" t="n">
+        <v>3.55</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -55753,7 +56008,10 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA497" t="n">
+        <v>2.31</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -55868,7 +56126,10 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA498" t="n">
+        <v>2.01</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -55983,7 +56244,10 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA499" t="n">
+        <v>1.97</v>
       </c>
       <c r="AG499" t="b">
         <v>0</v>
@@ -56098,7 +56362,10 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA500" t="n">
+        <v>2.48</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -56213,7 +56480,10 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA501" t="n">
+        <v>16.83</v>
       </c>
       <c r="AG501" t="b">
         <v>0</v>
@@ -56328,7 +56598,10 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA502" t="n">
+        <v>5.79</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -56443,7 +56716,10 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA503" t="n">
+        <v>1.42</v>
       </c>
       <c r="AG503" t="b">
         <v>0</v>
@@ -56558,7 +56834,10 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA504" t="n">
+        <v>0.37</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -56673,7 +56952,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG505" t="b">
         <v>0</v>
@@ -56788,7 +57067,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG506" t="b">
         <v>0</v>
@@ -56903,7 +57182,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG507" t="b">
         <v>0</v>
@@ -57018,7 +57297,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG508" t="b">
         <v>0</v>
@@ -57133,7 +57412,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG509" t="b">
         <v>0</v>
@@ -57248,7 +57527,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG510" t="b">
         <v>0</v>
@@ -57363,7 +57642,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG511" t="b">
         <v>0</v>
@@ -57478,7 +57757,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG512" t="b">
         <v>0</v>
@@ -57593,7 +57872,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG513" t="b">
         <v>0</v>
@@ -57708,7 +57987,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG514" t="b">
         <v>0</v>
@@ -57823,7 +58102,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>
@@ -57938,7 +58217,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG516" t="b">
         <v>0</v>
@@ -58053,7 +58332,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG517" t="b">
         <v>0</v>
@@ -58168,7 +58447,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG518" t="b">
         <v>0</v>
@@ -58283,7 +58562,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG519" t="b">
         <v>0</v>
@@ -58398,7 +58677,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG520" t="b">
         <v>0</v>
@@ -58513,7 +58792,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG521" t="b">
         <v>0</v>
@@ -58628,7 +58907,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -58743,7 +59022,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -58858,7 +59137,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -58973,7 +59252,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -59088,7 +59367,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -59203,7 +59482,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -59318,7 +59597,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG528" t="b">
         <v>0</v>
@@ -59433,7 +59712,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -59548,7 +59827,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -59663,7 +59942,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -59778,7 +60057,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -59893,7 +60172,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG533" t="b">
         <v>0</v>
@@ -60008,7 +60287,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG534" t="b">
         <v>0</v>
@@ -60123,7 +60402,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -60238,7 +60517,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -60353,7 +60632,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG537" t="b">
         <v>0</v>
@@ -60468,7 +60747,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG538" t="b">
         <v>0</v>
@@ -60583,7 +60862,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG539" t="b">
         <v>0</v>
@@ -60698,7 +60977,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG540" t="b">
         <v>0</v>
@@ -60813,7 +61092,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG541" t="b">
         <v>0</v>
@@ -60928,7 +61207,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG542" t="b">
         <v>0</v>
@@ -61043,7 +61322,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG543" t="b">
         <v>0</v>
@@ -61158,7 +61437,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG544" t="b">
         <v>0</v>
@@ -61273,7 +61552,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG545" t="b">
         <v>0</v>
@@ -61388,7 +61667,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG546" t="b">
         <v>0</v>
@@ -61503,7 +61782,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG547" t="b">
         <v>0</v>
@@ -61618,7 +61897,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG548" t="b">
         <v>0</v>
@@ -61733,7 +62012,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG549" t="b">
         <v>0</v>
@@ -61848,7 +62127,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG550" t="b">
         <v>0</v>
@@ -62185,7 +62464,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG553" t="b">
         <v>0</v>
@@ -62300,7 +62579,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG554" t="b">
         <v>0</v>
@@ -62415,7 +62694,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG555" t="b">
         <v>0</v>
@@ -62641,7 +62920,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG557" t="b">
         <v>0</v>
@@ -62756,7 +63035,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG558" t="b">
         <v>0</v>
@@ -62871,7 +63150,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG559" t="b">
         <v>0</v>
@@ -62986,7 +63265,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG560" t="b">
         <v>0</v>
@@ -63101,7 +63380,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG561" t="b">
         <v>0</v>
@@ -63216,7 +63495,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG562" t="b">
         <v>0</v>
@@ -63328,7 +63607,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG563" t="b">
         <v>0</v>
@@ -63443,7 +63722,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG564" t="b">
         <v>0</v>
@@ -63558,7 +63837,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG565" t="b">
         <v>0</v>
@@ -63673,7 +63952,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG566" t="b">
         <v>0</v>
@@ -63788,7 +64067,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG567" t="b">
         <v>0</v>
@@ -63903,7 +64182,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG568" t="b">
         <v>0</v>
@@ -64018,7 +64297,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG569" t="b">
         <v>0</v>
@@ -64133,7 +64412,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG570" t="b">
         <v>0</v>
@@ -64248,7 +64527,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG571" t="b">
         <v>0</v>
@@ -64363,7 +64642,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG572" t="b">
         <v>0</v>
@@ -64478,7 +64757,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG573" t="b">
         <v>0</v>
@@ -64593,7 +64872,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG574" t="b">
         <v>0</v>
@@ -64708,7 +64987,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG575" t="b">
         <v>0</v>
@@ -64823,7 +65102,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG576" t="b">
         <v>0</v>
@@ -65271,7 +65550,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG580" t="b">
         <v>0</v>
@@ -65386,7 +65665,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG581" t="b">
         <v>0</v>
@@ -65501,7 +65780,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG582" t="b">
         <v>0</v>
@@ -65616,7 +65895,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG583" t="b">
         <v>0</v>
@@ -65741,8 +66020,3429 @@
         </is>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F585" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I585" t="b">
+        <v>0</v>
+      </c>
+      <c r="J585" t="n">
+        <v>10</v>
+      </c>
+      <c r="K585" t="n">
+        <v>261.8</v>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M585" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N585" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P585" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="Q585" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S585" t="n">
+        <v>7</v>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V585" t="n">
+        <v>238</v>
+      </c>
+      <c r="W585" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="X585" t="n">
+        <v>221.34</v>
+      </c>
+      <c r="Y585" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z585" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG585" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH585" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI585" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>台化</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="F586" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I586" t="b">
+        <v>0</v>
+      </c>
+      <c r="J586" t="n">
+        <v>10</v>
+      </c>
+      <c r="K586" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M586" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N586" t="n">
+        <v>10</v>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P586" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="Q586" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S586" t="n">
+        <v>5.1755</v>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V586" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="W586" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="X586" t="n">
+        <v>64.57550000000001</v>
+      </c>
+      <c r="Y586" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z586" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG586" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH586" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI586" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>75.38</v>
+      </c>
+      <c r="F587" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I587" t="b">
+        <v>0</v>
+      </c>
+      <c r="J587" t="n">
+        <v>10</v>
+      </c>
+      <c r="K587" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M587" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N587" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P587" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="Q587" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S587" t="n">
+        <v>7</v>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V587" t="n">
+        <v>156</v>
+      </c>
+      <c r="W587" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="X587" t="n">
+        <v>145.08</v>
+      </c>
+      <c r="Y587" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z587" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG587" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH587" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI587" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="F588" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I588" t="b">
+        <v>0</v>
+      </c>
+      <c r="J588" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="K588" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M588" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N588" t="n">
+        <v>10</v>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P588" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Q588" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S588" t="n">
+        <v>4.3354</v>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V588" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="W588" t="n">
+        <v>98.4457</v>
+      </c>
+      <c r="X588" t="n">
+        <v>86.8635</v>
+      </c>
+      <c r="Y588" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z588" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG588" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH588" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI588" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="F589" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I589" t="b">
+        <v>0</v>
+      </c>
+      <c r="J589" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K589" t="n">
+        <v>375</v>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M589" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N589" t="n">
+        <v>10</v>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P589" t="n">
+        <v>339.75</v>
+      </c>
+      <c r="Q589" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S589" t="n">
+        <v>4.8513</v>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V589" t="n">
+        <v>343</v>
+      </c>
+      <c r="W589" t="n">
+        <v>383.048</v>
+      </c>
+      <c r="X589" t="n">
+        <v>326.36</v>
+      </c>
+      <c r="Y589" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z589" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG589" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH589" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI589" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="F590" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I590" t="b">
+        <v>0</v>
+      </c>
+      <c r="J590" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="K590" t="n">
+        <v>33.39</v>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M590" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N590" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P590" t="n">
+        <v>29.28</v>
+      </c>
+      <c r="Q590" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S590" t="n">
+        <v>7</v>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V590" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="W590" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="X590" t="n">
+        <v>28.2255</v>
+      </c>
+      <c r="Y590" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z590" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG590" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH590" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI590" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F591" t="n">
+        <v>62.74</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I591" t="b">
+        <v>0</v>
+      </c>
+      <c r="J591" t="n">
+        <v>10</v>
+      </c>
+      <c r="K591" t="n">
+        <v>5181</v>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M591" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="N591" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P591" t="n">
+        <v>4572.5</v>
+      </c>
+      <c r="Q591" t="n">
+        <v>68.28</v>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S591" t="n">
+        <v>6.4151</v>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V591" t="n">
+        <v>4710</v>
+      </c>
+      <c r="W591" t="n">
+        <v>5652</v>
+      </c>
+      <c r="X591" t="n">
+        <v>4407.85</v>
+      </c>
+      <c r="Y591" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z591" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG591" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH591" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI591" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>74.56999999999999</v>
+      </c>
+      <c r="F592" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I592" t="b">
+        <v>0</v>
+      </c>
+      <c r="J592" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="K592" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M592" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N592" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P592" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="Q592" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S592" t="n">
+        <v>7</v>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V592" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="W592" t="n">
+        <v>21.084</v>
+      </c>
+      <c r="X592" t="n">
+        <v>17.0655</v>
+      </c>
+      <c r="Y592" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z592" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG592" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH592" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI592" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2880</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>華南金</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>91.59</v>
+      </c>
+      <c r="F593" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I593" t="b">
+        <v>0</v>
+      </c>
+      <c r="J593" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K593" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M593" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N593" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P593" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="Q593" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S593" t="n">
+        <v>7</v>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V593" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="W593" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="X593" t="n">
+        <v>44.3145</v>
+      </c>
+      <c r="Y593" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z593" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG593" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH593" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI593" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="F594" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I594" t="b">
+        <v>0</v>
+      </c>
+      <c r="J594" t="n">
+        <v>10</v>
+      </c>
+      <c r="K594" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M594" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N594" t="n">
+        <v>10</v>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q594" t="n">
+        <v>49</v>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S594" t="n">
+        <v>4.7973</v>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V594" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="W594" t="n">
+        <v>173.5702</v>
+      </c>
+      <c r="X594" t="n">
+        <v>143.28</v>
+      </c>
+      <c r="Y594" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z594" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG594" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH594" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI594" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="F595" t="n">
+        <v>69.64</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I595" t="b">
+        <v>0</v>
+      </c>
+      <c r="J595" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="K595" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M595" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N595" t="n">
+        <v>10</v>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P595" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q595" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S595" t="n">
+        <v>2.7511</v>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V595" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="W595" t="n">
+        <v>125.5144</v>
+      </c>
+      <c r="X595" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="Y595" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z595" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG595" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH595" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI595" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>86.62</v>
+      </c>
+      <c r="F596" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I596" t="b">
+        <v>0</v>
+      </c>
+      <c r="J596" t="n">
+        <v>10</v>
+      </c>
+      <c r="K596" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M596" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N596" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P596" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="Q596" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S596" t="n">
+        <v>7</v>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V596" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="W596" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="X596" t="n">
+        <v>36.549</v>
+      </c>
+      <c r="Y596" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z596" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG596" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH596" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI596" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="F597" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I597" t="b">
+        <v>0</v>
+      </c>
+      <c r="J597" t="n">
+        <v>10</v>
+      </c>
+      <c r="K597" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M597" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N597" t="n">
+        <v>5</v>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P597" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="Q597" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S597" t="n">
+        <v>7</v>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V597" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="W597" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="X597" t="n">
+        <v>43.152</v>
+      </c>
+      <c r="Y597" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z597" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG597" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH597" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI597" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>77</v>
+      </c>
+      <c r="F598" t="n">
+        <v>78.59</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I598" t="b">
+        <v>0</v>
+      </c>
+      <c r="J598" t="n">
+        <v>10</v>
+      </c>
+      <c r="K598" t="n">
+        <v>77</v>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M598" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N598" t="n">
+        <v>10</v>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P598" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Q598" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S598" t="n">
+        <v>3.0586</v>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V598" t="n">
+        <v>70</v>
+      </c>
+      <c r="W598" t="n">
+        <v>78.2658</v>
+      </c>
+      <c r="X598" t="n">
+        <v>67.85899999999999</v>
+      </c>
+      <c r="Y598" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z598" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG598" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH598" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI598" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>兆豐金</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>77.11</v>
+      </c>
+      <c r="F599" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I599" t="b">
+        <v>0</v>
+      </c>
+      <c r="J599" t="n">
+        <v>10</v>
+      </c>
+      <c r="K599" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M599" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N599" t="n">
+        <v>10</v>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P599" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Q599" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S599" t="n">
+        <v>4.0049</v>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V599" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="W599" t="n">
+        <v>57.8007</v>
+      </c>
+      <c r="X599" t="n">
+        <v>49.0535</v>
+      </c>
+      <c r="Y599" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z599" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG599" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH599" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI599" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>87.36</v>
+      </c>
+      <c r="F600" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I600" t="b">
+        <v>0</v>
+      </c>
+      <c r="J600" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K600" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M600" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N600" t="n">
+        <v>5</v>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P600" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="Q600" t="n">
+        <v>72.77</v>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S600" t="n">
+        <v>7</v>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V600" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="W600" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="X600" t="n">
+        <v>41.292</v>
+      </c>
+      <c r="Y600" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z600" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG600" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH600" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI600" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="F601" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I601" t="b">
+        <v>0</v>
+      </c>
+      <c r="J601" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K601" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M601" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="N601" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P601" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="Q601" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S601" t="n">
+        <v>7</v>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V601" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="W601" t="n">
+        <v>53.3954</v>
+      </c>
+      <c r="X601" t="n">
+        <v>42.0825</v>
+      </c>
+      <c r="Y601" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z601" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG601" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH601" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI601" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>84.43000000000001</v>
+      </c>
+      <c r="F602" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I602" t="b">
+        <v>0</v>
+      </c>
+      <c r="J602" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="K602" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M602" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N602" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P602" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="Q602" t="n">
+        <v>66.41</v>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S602" t="n">
+        <v>7</v>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V602" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="W602" t="n">
+        <v>47.76</v>
+      </c>
+      <c r="X602" t="n">
+        <v>37.014</v>
+      </c>
+      <c r="Y602" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z602" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG602" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH602" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI602" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>晶豪科</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="F603" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I603" t="b">
+        <v>0</v>
+      </c>
+      <c r="J603" t="n">
+        <v>10</v>
+      </c>
+      <c r="K603" t="n">
+        <v>320.1</v>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M603" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N603" t="n">
+        <v>7</v>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P603" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q603" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S603" t="n">
+        <v>7</v>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V603" t="n">
+        <v>291</v>
+      </c>
+      <c r="W603" t="n">
+        <v>349.2</v>
+      </c>
+      <c r="X603" t="n">
+        <v>270.63</v>
+      </c>
+      <c r="Y603" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z603" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG603" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH603" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI603" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="F604" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I604" t="b">
+        <v>0</v>
+      </c>
+      <c r="J604" t="n">
+        <v>10</v>
+      </c>
+      <c r="K604" t="n">
+        <v>3773</v>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M604" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N604" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P604" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="Q604" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S604" t="n">
+        <v>7</v>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V604" t="n">
+        <v>3430</v>
+      </c>
+      <c r="W604" t="n">
+        <v>4116</v>
+      </c>
+      <c r="X604" t="n">
+        <v>3189.9</v>
+      </c>
+      <c r="Y604" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z604" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG604" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH604" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI604" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>84.56999999999999</v>
+      </c>
+      <c r="F605" t="n">
+        <v>59.47</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I605" t="b">
+        <v>0</v>
+      </c>
+      <c r="J605" t="n">
+        <v>10</v>
+      </c>
+      <c r="K605" t="n">
+        <v>569.8</v>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M605" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N605" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P605" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="Q605" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S605" t="n">
+        <v>7</v>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V605" t="n">
+        <v>518</v>
+      </c>
+      <c r="W605" t="n">
+        <v>621.1205</v>
+      </c>
+      <c r="X605" t="n">
+        <v>481.74</v>
+      </c>
+      <c r="Y605" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z605" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG605" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH605" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI605" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="F606" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I606" t="b">
+        <v>0</v>
+      </c>
+      <c r="J606" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="K606" t="n">
+        <v>136</v>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M606" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N606" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q606" t="n">
+        <v>55</v>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S606" t="n">
+        <v>6.5181</v>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V606" t="n">
+        <v>124</v>
+      </c>
+      <c r="W606" t="n">
+        <v>137.0897</v>
+      </c>
+      <c r="X606" t="n">
+        <v>115.9175</v>
+      </c>
+      <c r="Y606" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z606" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG606" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH606" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI606" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="F607" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I607" t="b">
+        <v>0</v>
+      </c>
+      <c r="J607" t="n">
+        <v>10</v>
+      </c>
+      <c r="K607" t="n">
+        <v>550</v>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M607" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N607" t="n">
+        <v>1</v>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P607" t="n">
+        <v>463.5</v>
+      </c>
+      <c r="Q607" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S607" t="n">
+        <v>7</v>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V607" t="n">
+        <v>500</v>
+      </c>
+      <c r="W607" t="n">
+        <v>600</v>
+      </c>
+      <c r="X607" t="n">
+        <v>465</v>
+      </c>
+      <c r="Y607" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI607" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ607" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>71.92</v>
+      </c>
+      <c r="F608" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I608" t="b">
+        <v>0</v>
+      </c>
+      <c r="J608" t="n">
+        <v>10</v>
+      </c>
+      <c r="K608" t="n">
+        <v>1628</v>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M608" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N608" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P608" t="n">
+        <v>1377.5</v>
+      </c>
+      <c r="Q608" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S608" t="n">
+        <v>7</v>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V608" t="n">
+        <v>1480</v>
+      </c>
+      <c r="W608" t="n">
+        <v>1776</v>
+      </c>
+      <c r="X608" t="n">
+        <v>1376.4</v>
+      </c>
+      <c r="Y608" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI608" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ608" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="F609" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I609" t="b">
+        <v>0</v>
+      </c>
+      <c r="J609" t="n">
+        <v>10</v>
+      </c>
+      <c r="K609" t="n">
+        <v>488.95</v>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M609" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N609" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P609" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="Q609" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S609" t="n">
+        <v>7</v>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V609" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="W609" t="n">
+        <v>533.4</v>
+      </c>
+      <c r="X609" t="n">
+        <v>413.385</v>
+      </c>
+      <c r="Y609" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI609" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ609" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="F610" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I610" t="b">
+        <v>0</v>
+      </c>
+      <c r="J610" t="n">
+        <v>10</v>
+      </c>
+      <c r="K610" t="n">
+        <v>3129.5</v>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M610" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N610" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P610" t="n">
+        <v>2610</v>
+      </c>
+      <c r="Q610" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S610" t="n">
+        <v>7</v>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V610" t="n">
+        <v>2845</v>
+      </c>
+      <c r="W610" t="n">
+        <v>3414</v>
+      </c>
+      <c r="X610" t="n">
+        <v>2645.85</v>
+      </c>
+      <c r="Y610" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI610" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ610" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="F611" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I611" t="b">
+        <v>0</v>
+      </c>
+      <c r="J611" t="n">
+        <v>10</v>
+      </c>
+      <c r="K611" t="n">
+        <v>492.25</v>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M611" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N611" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P611" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q611" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S611" t="n">
+        <v>7</v>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V611" t="n">
+        <v>447.5</v>
+      </c>
+      <c r="W611" t="n">
+        <v>537</v>
+      </c>
+      <c r="X611" t="n">
+        <v>416.175</v>
+      </c>
+      <c r="Y611" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z611" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG611" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH611" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI611" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="F612" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I612" t="b">
+        <v>0</v>
+      </c>
+      <c r="J612" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K612" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M612" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N612" t="n">
+        <v>10</v>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q612" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S612" t="n">
+        <v>5.1495</v>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V612" t="n">
+        <v>107</v>
+      </c>
+      <c r="W612" t="n">
+        <v>116.0818</v>
+      </c>
+      <c r="X612" t="n">
+        <v>101.49</v>
+      </c>
+      <c r="Y612" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z612" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG612" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH612" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI612" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="F613" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I613" t="b">
+        <v>0</v>
+      </c>
+      <c r="J613" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K613" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M613" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N613" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P613" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="Q613" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S613" t="n">
+        <v>7</v>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V613" t="n">
+        <v>172</v>
+      </c>
+      <c r="W613" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="X613" t="n">
+        <v>159.96</v>
+      </c>
+      <c r="Y613" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI613" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ613" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>合庫金</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>78.92</v>
+      </c>
+      <c r="F614" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I614" t="b">
+        <v>0</v>
+      </c>
+      <c r="J614" t="n">
+        <v>10</v>
+      </c>
+      <c r="K614" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M614" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N614" t="n">
+        <v>10</v>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P614" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="Q614" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S614" t="n">
+        <v>4.5092</v>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V614" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W614" t="n">
+        <v>30.3144</v>
+      </c>
+      <c r="X614" t="n">
+        <v>26.069</v>
+      </c>
+      <c r="Y614" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z614" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG614" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH614" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI614" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ584"/>
+  <autoFilter ref="A1:AJ614"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65815,25 +69515,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3939</v>
+        <v>0.4211</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.45</v>
+        <v>-2.45</v>
       </c>
       <c r="E2" t="n">
-        <v>11.79</v>
+        <v>12.85</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.65</v>
+        <v>-11.94</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2424</v>
+        <v>0.2632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5758</v>
+        <v>0.5789</v>
       </c>
     </row>
     <row r="3">
@@ -65843,25 +69543,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>0.375</v>
+        <v>0.4545</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.24</v>
+        <v>-0.64</v>
       </c>
       <c r="E3" t="n">
-        <v>4.19</v>
+        <v>5.09</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.74</v>
+        <v>-4.95</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -65993,25 +69693,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0.4583</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.21</v>
+        <v>-4.34</v>
       </c>
       <c r="E3" t="n">
-        <v>7.27</v>
+        <v>8.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.29</v>
+        <v>-11.06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.15</v>
+        <v>0.2083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.45</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="4">
@@ -66021,25 +69721,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3125</v>
+        <v>0.35</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.79</v>
+        <v>-1.62</v>
       </c>
       <c r="E4" t="n">
-        <v>9.109999999999999</v>
+        <v>10.32</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.31</v>
+        <v>-11.12</v>
       </c>
       <c r="G4" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6875</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="5">
@@ -66136,7 +69836,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17 14:26:37</t>
+          <t>2026-09-18 14:24:26</t>
         </is>
       </c>
     </row>
@@ -66183,7 +69883,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>583</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7">
@@ -66193,7 +69893,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
@@ -66203,7 +69903,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>420</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$614</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$637</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ614"/>
+  <dimension ref="A1:AJ637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18132,11 +18132,11 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z181" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA181" t="n">
         <v>-3.74</v>
@@ -18147,6 +18147,15 @@
       <c r="AC181" t="n">
         <v>-4.58</v>
       </c>
+      <c r="AD181" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>-7.13</v>
+      </c>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
@@ -18155,7 +18164,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -18256,11 +18265,11 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z182" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA182" t="n">
         <v>-3</v>
@@ -18271,6 +18280,15 @@
       <c r="AC182" t="n">
         <v>-8.890000000000001</v>
       </c>
+      <c r="AD182" t="n">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>-11.54</v>
+      </c>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -18279,7 +18297,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -18380,11 +18398,11 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z183" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA183" t="n">
         <v>-6.79</v>
@@ -18395,6 +18413,15 @@
       <c r="AC183" t="n">
         <v>-5.39</v>
       </c>
+      <c r="AD183" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>-9.98</v>
+      </c>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -18403,7 +18430,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -18504,11 +18531,11 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z184" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA184" t="n">
         <v>42.06</v>
@@ -18519,6 +18546,15 @@
       <c r="AC184" t="n">
         <v>11.33</v>
       </c>
+      <c r="AD184" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>-1.67</v>
+      </c>
       <c r="AG184" t="b">
         <v>1</v>
       </c>
@@ -18527,7 +18563,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -18628,11 +18664,11 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z185" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA185" t="n">
         <v>-4.42</v>
@@ -18643,6 +18679,15 @@
       <c r="AC185" t="n">
         <v>-10.93</v>
       </c>
+      <c r="AD185" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>-13.25</v>
+      </c>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -18651,7 +18696,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -18752,11 +18797,11 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z186" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA186" t="n">
         <v>-62.24</v>
@@ -18767,6 +18812,15 @@
       <c r="AC186" t="n">
         <v>-63.97</v>
       </c>
+      <c r="AD186" t="n">
+        <v>-65.87</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>-54.37</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>-67.41</v>
+      </c>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -18775,7 +18829,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -18880,7 +18934,7 @@
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -19004,7 +19058,7 @@
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -19128,7 +19182,7 @@
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -19252,7 +19306,7 @@
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -19376,7 +19430,7 @@
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -19500,7 +19554,7 @@
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -19624,7 +19678,7 @@
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -19748,7 +19802,7 @@
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19872,7 +19926,7 @@
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19996,7 +20050,7 @@
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -20120,7 +20174,7 @@
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -20466,7 +20520,7 @@
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -20590,7 +20644,7 @@
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -20714,7 +20768,7 @@
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -20838,7 +20892,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -20962,7 +21016,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -21086,7 +21140,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -21210,7 +21264,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -21334,7 +21388,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -21458,7 +21512,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -21582,7 +21636,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21706,7 +21760,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21830,7 +21884,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -21954,7 +22008,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -22189,7 +22243,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -22313,7 +22367,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -22437,7 +22491,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -22561,7 +22615,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -22685,7 +22739,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22809,7 +22863,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -22933,7 +22987,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -23057,7 +23111,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -23181,7 +23235,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -23305,7 +23359,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -23429,7 +23483,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23553,7 +23607,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23677,7 +23731,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23801,7 +23855,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -23925,7 +23979,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -24049,7 +24103,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -24173,7 +24227,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -24297,7 +24351,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -24532,7 +24586,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24878,7 +24932,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -25002,7 +25056,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -25126,7 +25180,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -25250,7 +25304,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -25374,7 +25428,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -25498,7 +25552,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25622,7 +25676,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25746,7 +25800,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -25870,7 +25924,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -25994,7 +26048,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -26118,7 +26172,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -26242,7 +26296,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -26366,7 +26420,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26490,7 +26544,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26614,7 +26668,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -26738,7 +26792,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -26862,7 +26916,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -26986,7 +27040,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -27110,7 +27164,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -27234,7 +27288,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27580,7 +27634,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -27926,7 +27980,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -27938,7 +27992,7 @@
         <v>18.87</v>
       </c>
       <c r="AG261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH261" t="b">
         <v>0</v>
@@ -28050,7 +28104,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -28174,7 +28228,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -28298,7 +28352,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28533,7 +28587,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28657,7 +28711,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -28781,7 +28835,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -28905,13 +28959,16 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
       </c>
       <c r="AB269" t="n">
         <v>-4.98</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>-1.51</v>
       </c>
       <c r="AG269" t="b">
         <v>0</v>
@@ -29026,13 +29083,16 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
       </c>
       <c r="AB270" t="n">
         <v>-4.39</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>-1.51</v>
       </c>
       <c r="AG270" t="b">
         <v>0</v>
@@ -29147,13 +29207,16 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
       </c>
       <c r="AB271" t="n">
         <v>-5.61</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>-5.36</v>
       </c>
       <c r="AG271" t="b">
         <v>0</v>
@@ -29268,13 +29331,16 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
       </c>
       <c r="AB272" t="n">
         <v>-9.02</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>-5.41</v>
       </c>
       <c r="AG272" t="b">
         <v>0</v>
@@ -29389,13 +29455,16 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
       </c>
       <c r="AB273" t="n">
         <v>10.47</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>21.71</v>
       </c>
       <c r="AG273" t="b">
         <v>1</v>
@@ -29510,13 +29579,16 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
       </c>
       <c r="AB274" t="n">
         <v>-11.07</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>-10.66</v>
       </c>
       <c r="AG274" t="b">
         <v>0</v>
@@ -29631,13 +29703,16 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
       </c>
       <c r="AB275" t="n">
         <v>-6.07</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>-6.82</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -29752,13 +29827,16 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
       </c>
       <c r="AB276" t="n">
         <v>-0.32</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>2.06</v>
       </c>
       <c r="AG276" t="b">
         <v>0</v>
@@ -29873,13 +29951,16 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
       </c>
       <c r="AB277" t="n">
         <v>-6.51</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>-5.31</v>
       </c>
       <c r="AG277" t="b">
         <v>0</v>
@@ -29994,13 +30075,16 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
       </c>
       <c r="AB278" t="n">
         <v>-12.45</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>-10.3</v>
       </c>
       <c r="AG278" t="b">
         <v>0</v>
@@ -30115,13 +30199,16 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
       </c>
       <c r="AB279" t="n">
         <v>-2.9</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>-1.29</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -30236,13 +30323,16 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
       </c>
       <c r="AB280" t="n">
         <v>-1.77</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>1.77</v>
       </c>
       <c r="AG280" t="b">
         <v>0</v>
@@ -30357,13 +30447,16 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
       </c>
       <c r="AB281" t="n">
         <v>-1.03</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>4.28</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -30478,13 +30571,16 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
       </c>
       <c r="AB282" t="n">
         <v>-12.89</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>-4.97</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -30599,7 +30695,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30607,8 +30703,11 @@
       <c r="AB283" t="n">
         <v>1.75</v>
       </c>
+      <c r="AC283" t="n">
+        <v>17.32</v>
+      </c>
       <c r="AG283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH283" t="b">
         <v>0</v>
@@ -30720,13 +30819,16 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
       </c>
       <c r="AB284" t="n">
         <v>1.5</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>3.64</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -30841,13 +30943,16 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
       </c>
       <c r="AB285" t="n">
         <v>-0.88</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>2.63</v>
       </c>
       <c r="AG285" t="b">
         <v>0</v>
@@ -30962,13 +31067,16 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
       </c>
       <c r="AB286" t="n">
         <v>6.94</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>7.29</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -31083,13 +31191,16 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
       </c>
       <c r="AB287" t="n">
         <v>1.81</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>2.26</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -31204,13 +31315,16 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
       </c>
       <c r="AB288" t="n">
         <v>14.62</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>19.5</v>
       </c>
       <c r="AG288" t="b">
         <v>1</v>
@@ -31325,13 +31439,16 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
       </c>
       <c r="AB289" t="n">
         <v>16.6</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>16.23</v>
       </c>
       <c r="AG289" t="b">
         <v>1</v>
@@ -31446,13 +31563,16 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
       </c>
       <c r="AB290" t="n">
         <v>12.97</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>13.62</v>
       </c>
       <c r="AG290" t="b">
         <v>1</v>
@@ -31567,13 +31687,16 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
       </c>
       <c r="AB291" t="n">
         <v>-21.63</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>-16.34</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -31688,13 +31811,16 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
       </c>
       <c r="AB292" t="n">
         <v>-3.36</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>-0.29</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -31809,13 +31935,16 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
       </c>
       <c r="AB293" t="n">
         <v>2.72</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>5.54</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -32263,7 +32392,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32271,8 +32400,11 @@
       <c r="AB297" t="n">
         <v>4.92</v>
       </c>
+      <c r="AC297" t="n">
+        <v>24.84</v>
+      </c>
       <c r="AG297" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH297" t="b">
         <v>0</v>
@@ -32384,13 +32516,16 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
       </c>
       <c r="AB298" t="n">
         <v>-11.9</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>-10.06</v>
       </c>
       <c r="AG298" t="b">
         <v>0</v>
@@ -32505,13 +32640,16 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
       </c>
       <c r="AB299" t="n">
         <v>-68.01000000000001</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>-69.7</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -32737,7 +32875,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -32858,7 +32996,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -32979,7 +33117,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -33100,7 +33238,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -33221,7 +33359,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -33342,7 +33480,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -33463,7 +33601,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -33584,7 +33722,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -33705,7 +33843,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -33826,7 +33964,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -33947,7 +34085,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -34068,7 +34206,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -34189,7 +34327,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -34310,7 +34448,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -34431,7 +34569,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -34552,7 +34690,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -34673,7 +34811,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -34794,7 +34932,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -34915,7 +35053,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -35036,7 +35174,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -35157,7 +35295,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -35278,7 +35416,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -35399,7 +35537,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -35520,7 +35658,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -35863,7 +36001,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -35872,7 +36010,7 @@
         <v>0.67</v>
       </c>
       <c r="AG327" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH327" t="b">
         <v>0</v>
@@ -35984,7 +36122,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -36105,7 +36243,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -36448,7 +36586,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -36569,7 +36707,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -36690,7 +36828,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -36811,7 +36949,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -36932,7 +37070,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -37053,7 +37191,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -37174,7 +37312,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -37295,7 +37433,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -37416,7 +37554,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -37537,7 +37675,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -37658,7 +37796,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -37779,7 +37917,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -37900,7 +38038,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -38021,7 +38159,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -38142,7 +38280,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -38263,7 +38401,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -38384,7 +38522,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -38505,7 +38643,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -38626,7 +38764,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -38747,7 +38885,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -38868,7 +39006,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -38989,7 +39127,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -39554,7 +39692,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -39675,7 +39813,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -39796,7 +39934,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -39917,7 +40055,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -40038,7 +40176,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -40159,7 +40297,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -40280,7 +40418,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -40401,7 +40539,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -40522,7 +40660,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -40643,7 +40781,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -40764,7 +40902,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -40885,7 +41023,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -41006,7 +41144,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -41127,7 +41265,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -41248,7 +41386,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -41369,7 +41507,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -41490,7 +41628,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -41611,7 +41749,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -41732,7 +41870,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -41853,7 +41991,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -42196,7 +42334,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -42317,7 +42455,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -42549,7 +42687,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -42670,7 +42808,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -42791,7 +42929,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -42912,7 +43050,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -43033,7 +43171,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -43154,7 +43292,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -43275,7 +43413,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -43393,7 +43531,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -43514,7 +43652,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -43635,7 +43773,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -43756,7 +43894,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -43877,7 +44015,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -43998,7 +44136,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -44119,7 +44257,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -44240,7 +44378,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -44361,7 +44499,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -44482,7 +44620,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -44603,7 +44741,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -44724,7 +44862,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -44845,7 +44983,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -44966,7 +45104,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -45087,7 +45225,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -45208,7 +45346,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -45329,7 +45467,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -45450,7 +45588,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -45571,7 +45709,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -45692,7 +45830,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -46146,7 +46284,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -46267,7 +46405,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -46388,10 +46526,13 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
+      </c>
+      <c r="AB415" t="n">
+        <v>-2.1</v>
       </c>
       <c r="AG415" t="b">
         <v>0</v>
@@ -46506,10 +46647,13 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
+      </c>
+      <c r="AB416" t="n">
+        <v>3.9</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -46624,10 +46768,13 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
+      </c>
+      <c r="AB417" t="n">
+        <v>-5.7</v>
       </c>
       <c r="AG417" t="b">
         <v>0</v>
@@ -46742,10 +46889,13 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
+      </c>
+      <c r="AB418" t="n">
+        <v>-2.84</v>
       </c>
       <c r="AG418" t="b">
         <v>0</v>
@@ -46860,10 +47010,13 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
+      </c>
+      <c r="AB419" t="n">
+        <v>-7.5</v>
       </c>
       <c r="AG419" t="b">
         <v>0</v>
@@ -46978,10 +47131,13 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
+      </c>
+      <c r="AB420" t="n">
+        <v>-5.31</v>
       </c>
       <c r="AG420" t="b">
         <v>0</v>
@@ -47096,10 +47252,13 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
+      </c>
+      <c r="AB421" t="n">
+        <v>-0.86</v>
       </c>
       <c r="AG421" t="b">
         <v>0</v>
@@ -47214,10 +47373,13 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
+      </c>
+      <c r="AB422" t="n">
+        <v>10.44</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
@@ -47332,10 +47494,13 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
+      </c>
+      <c r="AB423" t="n">
+        <v>5.25</v>
       </c>
       <c r="AG423" t="b">
         <v>0</v>
@@ -47450,10 +47615,13 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
+      </c>
+      <c r="AB424" t="n">
+        <v>2.18</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
@@ -47568,10 +47736,13 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
+      </c>
+      <c r="AB425" t="n">
+        <v>3.34</v>
       </c>
       <c r="AG425" t="b">
         <v>0</v>
@@ -47686,10 +47857,13 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
+      </c>
+      <c r="AB426" t="n">
+        <v>-1.31</v>
       </c>
       <c r="AG426" t="b">
         <v>0</v>
@@ -47804,10 +47978,13 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
+      </c>
+      <c r="AB427" t="n">
+        <v>9.470000000000001</v>
       </c>
       <c r="AG427" t="b">
         <v>0</v>
@@ -47922,10 +48099,13 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
+      </c>
+      <c r="AB428" t="n">
+        <v>6.08</v>
       </c>
       <c r="AG428" t="b">
         <v>0</v>
@@ -48040,10 +48220,13 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
+      </c>
+      <c r="AB429" t="n">
+        <v>6.57</v>
       </c>
       <c r="AG429" t="b">
         <v>0</v>
@@ -48158,10 +48341,13 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
+      </c>
+      <c r="AB430" t="n">
+        <v>7.28</v>
       </c>
       <c r="AG430" t="b">
         <v>0</v>
@@ -48276,10 +48462,13 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
+      </c>
+      <c r="AB431" t="n">
+        <v>6.57</v>
       </c>
       <c r="AG431" t="b">
         <v>0</v>
@@ -48394,10 +48583,13 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
+      </c>
+      <c r="AB432" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AG432" t="b">
         <v>0</v>
@@ -48512,10 +48704,13 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
+      </c>
+      <c r="AB433" t="n">
+        <v>6.29</v>
       </c>
       <c r="AG433" t="b">
         <v>0</v>
@@ -48630,10 +48825,13 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>6.41</v>
       </c>
       <c r="AG434" t="b">
         <v>0</v>
@@ -48970,10 +49168,13 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>28.31</v>
       </c>
       <c r="AG437" t="b">
         <v>1</v>
@@ -49199,7 +49400,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -49317,7 +49518,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -49435,7 +49636,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -49553,7 +49754,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -49671,7 +49872,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -49789,7 +49990,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -49907,7 +50108,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -50025,7 +50226,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -50143,7 +50344,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -50261,7 +50462,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -50379,7 +50580,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -50497,7 +50698,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -50615,7 +50816,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -50733,7 +50934,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -50851,7 +51052,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -50969,7 +51170,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -51087,7 +51288,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -51205,7 +51406,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -51323,7 +51524,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -51441,7 +51642,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -51781,13 +51982,13 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
       </c>
       <c r="AG461" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH461" t="b">
         <v>0</v>
@@ -51899,7 +52100,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -52017,7 +52218,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -52135,7 +52336,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -52253,7 +52454,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -52371,7 +52572,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -52489,7 +52690,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -52607,7 +52808,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -52725,7 +52926,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -52843,7 +53044,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -52961,7 +53162,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -53079,7 +53280,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -53197,7 +53398,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -53315,7 +53516,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -53433,7 +53634,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -53551,7 +53752,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -53669,7 +53870,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -53787,7 +53988,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -54238,13 +54439,13 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
       </c>
       <c r="AG482" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH482" t="b">
         <v>0</v>
@@ -54356,7 +54557,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -54474,7 +54675,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -54592,7 +54793,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -54710,7 +54911,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -54828,7 +55029,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -54946,7 +55147,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -55064,7 +55265,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -55182,7 +55383,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -55300,7 +55501,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -55418,7 +55619,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -55536,7 +55737,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -55654,7 +55855,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -55772,7 +55973,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -55890,7 +56091,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -56008,7 +56209,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -56126,7 +56327,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -56244,7 +56445,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -56362,7 +56563,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -56480,13 +56681,13 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
       </c>
       <c r="AG501" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH501" t="b">
         <v>0</v>
@@ -56598,7 +56799,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -56716,7 +56917,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -56834,7 +57035,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -56952,7 +57153,10 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA505" t="n">
+        <v>10.18</v>
       </c>
       <c r="AG505" t="b">
         <v>0</v>
@@ -57067,7 +57271,10 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA506" t="n">
+        <v>0</v>
       </c>
       <c r="AG506" t="b">
         <v>0</v>
@@ -57182,7 +57389,10 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA507" t="n">
+        <v>0.76</v>
       </c>
       <c r="AG507" t="b">
         <v>0</v>
@@ -57297,7 +57507,10 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA508" t="n">
+        <v>0.32</v>
       </c>
       <c r="AG508" t="b">
         <v>0</v>
@@ -57412,7 +57625,10 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA509" t="n">
+        <v>4.25</v>
       </c>
       <c r="AG509" t="b">
         <v>0</v>
@@ -57527,7 +57743,10 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA510" t="n">
+        <v>-0.32</v>
       </c>
       <c r="AG510" t="b">
         <v>0</v>
@@ -57642,7 +57861,10 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA511" t="n">
+        <v>-2.67</v>
       </c>
       <c r="AG511" t="b">
         <v>0</v>
@@ -57757,7 +57979,10 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA512" t="n">
+        <v>0.57</v>
       </c>
       <c r="AG512" t="b">
         <v>0</v>
@@ -57872,7 +58097,10 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA513" t="n">
+        <v>2.01</v>
       </c>
       <c r="AG513" t="b">
         <v>0</v>
@@ -57987,7 +58215,10 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA514" t="n">
+        <v>-0.25</v>
       </c>
       <c r="AG514" t="b">
         <v>0</v>
@@ -58102,7 +58333,10 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA515" t="n">
+        <v>-1.44</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>
@@ -58217,7 +58451,10 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA516" t="n">
+        <v>2.75</v>
       </c>
       <c r="AG516" t="b">
         <v>0</v>
@@ -58332,7 +58569,10 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA517" t="n">
+        <v>2.47</v>
       </c>
       <c r="AG517" t="b">
         <v>0</v>
@@ -58447,10 +58687,13 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA518" t="n">
+        <v>18.98</v>
       </c>
       <c r="AG518" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH518" t="b">
         <v>0</v>
@@ -58562,7 +58805,10 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA519" t="n">
+        <v>5.77</v>
       </c>
       <c r="AG519" t="b">
         <v>0</v>
@@ -58677,7 +58923,10 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA520" t="n">
+        <v>0</v>
       </c>
       <c r="AG520" t="b">
         <v>0</v>
@@ -58792,7 +59041,10 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA521" t="n">
+        <v>-0.91</v>
       </c>
       <c r="AG521" t="b">
         <v>0</v>
@@ -58907,7 +59159,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -59022,7 +59274,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -59137,7 +59389,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -59252,7 +59504,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -59367,7 +59619,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -59482,7 +59734,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -59597,7 +59849,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG528" t="b">
         <v>0</v>
@@ -59712,7 +59964,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -59827,7 +60079,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -59942,7 +60194,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -60057,7 +60309,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -60172,10 +60424,10 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG533" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH533" t="b">
         <v>0</v>
@@ -60287,7 +60539,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG534" t="b">
         <v>0</v>
@@ -60402,7 +60654,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -60517,7 +60769,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -60632,7 +60884,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG537" t="b">
         <v>0</v>
@@ -60747,7 +60999,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG538" t="b">
         <v>0</v>
@@ -60862,7 +61114,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG539" t="b">
         <v>0</v>
@@ -60977,7 +61229,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG540" t="b">
         <v>0</v>
@@ -61092,7 +61344,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG541" t="b">
         <v>0</v>
@@ -61207,7 +61459,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG542" t="b">
         <v>0</v>
@@ -61322,7 +61574,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG543" t="b">
         <v>0</v>
@@ -61437,7 +61689,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG544" t="b">
         <v>0</v>
@@ -61552,7 +61804,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG545" t="b">
         <v>0</v>
@@ -61667,7 +61919,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG546" t="b">
         <v>0</v>
@@ -61782,7 +62034,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG547" t="b">
         <v>0</v>
@@ -61897,7 +62149,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG548" t="b">
         <v>0</v>
@@ -62012,7 +62264,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG549" t="b">
         <v>0</v>
@@ -62127,7 +62379,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG550" t="b">
         <v>0</v>
@@ -62464,10 +62716,10 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH553" t="b">
         <v>0</v>
@@ -62579,7 +62831,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG554" t="b">
         <v>0</v>
@@ -62694,7 +62946,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG555" t="b">
         <v>0</v>
@@ -62920,7 +63172,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG557" t="b">
         <v>0</v>
@@ -63035,7 +63287,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG558" t="b">
         <v>0</v>
@@ -63150,7 +63402,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG559" t="b">
         <v>0</v>
@@ -63265,7 +63517,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG560" t="b">
         <v>0</v>
@@ -63380,7 +63632,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG561" t="b">
         <v>0</v>
@@ -63495,7 +63747,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG562" t="b">
         <v>0</v>
@@ -63607,7 +63859,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG563" t="b">
         <v>0</v>
@@ -63722,7 +63974,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG564" t="b">
         <v>0</v>
@@ -63837,7 +64089,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG565" t="b">
         <v>0</v>
@@ -63952,7 +64204,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG566" t="b">
         <v>0</v>
@@ -64067,7 +64319,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG567" t="b">
         <v>0</v>
@@ -64182,7 +64434,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG568" t="b">
         <v>0</v>
@@ -64297,7 +64549,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG569" t="b">
         <v>0</v>
@@ -64412,7 +64664,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG570" t="b">
         <v>0</v>
@@ -64527,7 +64779,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG571" t="b">
         <v>0</v>
@@ -64642,7 +64894,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG572" t="b">
         <v>0</v>
@@ -64757,7 +65009,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG573" t="b">
         <v>0</v>
@@ -64872,7 +65124,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG574" t="b">
         <v>0</v>
@@ -64987,7 +65239,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG575" t="b">
         <v>0</v>
@@ -65102,7 +65354,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG576" t="b">
         <v>0</v>
@@ -65550,7 +65802,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG580" t="b">
         <v>0</v>
@@ -65665,7 +65917,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG581" t="b">
         <v>0</v>
@@ -65780,7 +66032,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG582" t="b">
         <v>0</v>
@@ -65895,7 +66147,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG583" t="b">
         <v>0</v>
@@ -66121,7 +66373,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG585" t="b">
         <v>0</v>
@@ -66236,7 +66488,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG586" t="b">
         <v>0</v>
@@ -66351,7 +66603,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG587" t="b">
         <v>0</v>
@@ -66466,7 +66718,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG588" t="b">
         <v>0</v>
@@ -66581,7 +66833,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG589" t="b">
         <v>0</v>
@@ -66696,7 +66948,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG590" t="b">
         <v>0</v>
@@ -66811,7 +67063,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG591" t="b">
         <v>0</v>
@@ -66926,7 +67178,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG592" t="b">
         <v>0</v>
@@ -67041,7 +67293,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG593" t="b">
         <v>0</v>
@@ -67153,7 +67405,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG594" t="b">
         <v>0</v>
@@ -67268,7 +67520,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG595" t="b">
         <v>0</v>
@@ -67383,7 +67635,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -67498,7 +67750,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -67613,7 +67865,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -67728,7 +67980,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -67843,7 +68095,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG600" t="b">
         <v>0</v>
@@ -67958,7 +68210,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG601" t="b">
         <v>0</v>
@@ -68073,7 +68325,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG602" t="b">
         <v>0</v>
@@ -68188,7 +68440,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG603" t="b">
         <v>0</v>
@@ -68303,7 +68555,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG604" t="b">
         <v>0</v>
@@ -68418,7 +68670,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG605" t="b">
         <v>0</v>
@@ -68530,7 +68782,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG606" t="b">
         <v>0</v>
@@ -69089,7 +69341,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG611" t="b">
         <v>0</v>
@@ -69201,7 +69453,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG612" t="b">
         <v>0</v>
@@ -69427,7 +69679,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG614" t="b">
         <v>0</v>
@@ -69438,11 +69690,2630 @@
       <c r="AI614" t="inlineStr">
         <is>
           <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F615" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I615" t="b">
+        <v>0</v>
+      </c>
+      <c r="J615" t="n">
+        <v>10</v>
+      </c>
+      <c r="K615" t="n">
+        <v>263.45</v>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M615" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N615" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P615" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="Q615" t="n">
+        <v>54.68</v>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S615" t="n">
+        <v>7</v>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V615" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="W615" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="X615" t="n">
+        <v>222.735</v>
+      </c>
+      <c r="Y615" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z615" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG615" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH615" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI615" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="F616" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I616" t="b">
+        <v>0</v>
+      </c>
+      <c r="J616" t="n">
+        <v>10</v>
+      </c>
+      <c r="K616" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M616" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N616" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P616" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="Q616" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S616" t="n">
+        <v>7</v>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V616" t="n">
+        <v>157</v>
+      </c>
+      <c r="W616" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="X616" t="n">
+        <v>146.01</v>
+      </c>
+      <c r="Y616" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z616" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG616" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH616" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI616" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="F617" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I617" t="b">
+        <v>0</v>
+      </c>
+      <c r="J617" t="n">
+        <v>10</v>
+      </c>
+      <c r="K617" t="n">
+        <v>2612.5</v>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M617" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N617" t="n">
+        <v>3</v>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P617" t="n">
+        <v>2245</v>
+      </c>
+      <c r="Q617" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S617" t="n">
+        <v>7</v>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V617" t="n">
+        <v>2375</v>
+      </c>
+      <c r="W617" t="n">
+        <v>2850</v>
+      </c>
+      <c r="X617" t="n">
+        <v>2208.75</v>
+      </c>
+      <c r="Y617" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z617" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG617" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH617" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI617" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="F618" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I618" t="b">
+        <v>0</v>
+      </c>
+      <c r="J618" t="n">
+        <v>10</v>
+      </c>
+      <c r="K618" t="n">
+        <v>404.8</v>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M618" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N618" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P618" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="Q618" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S618" t="n">
+        <v>7</v>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V618" t="n">
+        <v>368</v>
+      </c>
+      <c r="W618" t="n">
+        <v>420.2638</v>
+      </c>
+      <c r="X618" t="n">
+        <v>342.24</v>
+      </c>
+      <c r="Y618" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z618" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG618" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH618" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI618" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="F619" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I619" t="b">
+        <v>0</v>
+      </c>
+      <c r="J619" t="n">
+        <v>10</v>
+      </c>
+      <c r="K619" t="n">
+        <v>5511</v>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M619" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N619" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P619" t="n">
+        <v>4687.5</v>
+      </c>
+      <c r="Q619" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S619" t="n">
+        <v>7</v>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V619" t="n">
+        <v>5010</v>
+      </c>
+      <c r="W619" t="n">
+        <v>6012</v>
+      </c>
+      <c r="X619" t="n">
+        <v>4659.3</v>
+      </c>
+      <c r="Y619" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z619" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG619" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH619" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI619" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="F620" t="n">
+        <v>60.72</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I620" t="b">
+        <v>0</v>
+      </c>
+      <c r="J620" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="K620" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M620" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N620" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P620" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="Q620" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S620" t="n">
+        <v>7</v>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V620" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="W620" t="n">
+        <v>21.0253</v>
+      </c>
+      <c r="X620" t="n">
+        <v>17.0655</v>
+      </c>
+      <c r="Y620" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z620" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG620" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH620" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI620" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>77.73999999999999</v>
+      </c>
+      <c r="F621" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I621" t="b">
+        <v>0</v>
+      </c>
+      <c r="J621" t="n">
+        <v>10</v>
+      </c>
+      <c r="K621" t="n">
+        <v>169.95</v>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M621" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N621" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q621" t="n">
+        <v>51</v>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S621" t="n">
+        <v>7</v>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V621" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="W621" t="n">
+        <v>183.6506</v>
+      </c>
+      <c r="X621" t="n">
+        <v>143.685</v>
+      </c>
+      <c r="Y621" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z621" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG621" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH621" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI621" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>國泰金</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>72</v>
+      </c>
+      <c r="F622" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I622" t="b">
+        <v>0</v>
+      </c>
+      <c r="J622" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K622" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M622" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N622" t="n">
+        <v>10</v>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P622" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q622" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="S622" t="n">
+        <v>4.9027</v>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V622" t="n">
+        <v>113</v>
+      </c>
+      <c r="W622" t="n">
+        <v>131.7036</v>
+      </c>
+      <c r="X622" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="Y622" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z622" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG622" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH622" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI622" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="F623" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I623" t="b">
+        <v>0</v>
+      </c>
+      <c r="J623" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K623" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M623" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N623" t="n">
+        <v>3</v>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P623" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="Q623" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S623" t="n">
+        <v>7</v>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V623" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="W623" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="X623" t="n">
+        <v>37.6185</v>
+      </c>
+      <c r="Y623" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z623" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG623" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH623" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI623" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F624" t="n">
+        <v>73.79000000000001</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I624" t="b">
+        <v>0</v>
+      </c>
+      <c r="J624" t="n">
+        <v>10</v>
+      </c>
+      <c r="K624" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M624" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N624" t="n">
+        <v>10</v>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P624" t="n">
+        <v>69.55</v>
+      </c>
+      <c r="Q624" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S624" t="n">
+        <v>3.6094</v>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V624" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="W624" t="n">
+        <v>79.7363</v>
+      </c>
+      <c r="X624" t="n">
+        <v>67.85899999999999</v>
+      </c>
+      <c r="Y624" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z624" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG624" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH624" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI624" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>85.53</v>
+      </c>
+      <c r="F625" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I625" t="b">
+        <v>0</v>
+      </c>
+      <c r="J625" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="K625" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M625" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N625" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P625" t="n">
+        <v>44.23</v>
+      </c>
+      <c r="Q625" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S625" t="n">
+        <v>7</v>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V625" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="W625" t="n">
+        <v>54.7109</v>
+      </c>
+      <c r="X625" t="n">
+        <v>42.501</v>
+      </c>
+      <c r="Y625" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z625" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG625" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH625" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI625" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="F626" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I626" t="b">
+        <v>0</v>
+      </c>
+      <c r="J626" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K626" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M626" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N626" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P626" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q626" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S626" t="n">
+        <v>6.7188</v>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V626" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="W626" t="n">
+        <v>80.29600000000001</v>
+      </c>
+      <c r="X626" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="Y626" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z626" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG626" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH626" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI626" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="F627" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I627" t="b">
+        <v>0</v>
+      </c>
+      <c r="J627" t="n">
+        <v>10</v>
+      </c>
+      <c r="K627" t="n">
+        <v>3756.5</v>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M627" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N627" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P627" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="Q627" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S627" t="n">
+        <v>7</v>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V627" t="n">
+        <v>3415</v>
+      </c>
+      <c r="W627" t="n">
+        <v>4098</v>
+      </c>
+      <c r="X627" t="n">
+        <v>3175.95</v>
+      </c>
+      <c r="Y627" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z627" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG627" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH627" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI627" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="F628" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I628" t="b">
+        <v>0</v>
+      </c>
+      <c r="J628" t="n">
+        <v>10</v>
+      </c>
+      <c r="K628" t="n">
+        <v>576.4</v>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M628" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N628" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P628" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="Q628" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S628" t="n">
+        <v>7</v>
+      </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V628" t="n">
+        <v>524</v>
+      </c>
+      <c r="W628" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="X628" t="n">
+        <v>487.32</v>
+      </c>
+      <c r="Y628" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z628" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG628" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH628" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI628" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>台灣大</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="F629" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I629" t="b">
+        <v>0</v>
+      </c>
+      <c r="J629" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="K629" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M629" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N629" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q629" t="n">
+        <v>57</v>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S629" t="n">
+        <v>6.6867</v>
+      </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V629" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="W629" t="n">
+        <v>138.2425</v>
+      </c>
+      <c r="X629" t="n">
+        <v>116.175</v>
+      </c>
+      <c r="Y629" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z629" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG629" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH629" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI629" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>72.67</v>
+      </c>
+      <c r="F630" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I630" t="b">
+        <v>0</v>
+      </c>
+      <c r="J630" t="n">
+        <v>10</v>
+      </c>
+      <c r="K630" t="n">
+        <v>539.55</v>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M630" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N630" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P630" t="n">
+        <v>463.5</v>
+      </c>
+      <c r="Q630" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S630" t="n">
+        <v>7</v>
+      </c>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V630" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="W630" t="n">
+        <v>588.6</v>
+      </c>
+      <c r="X630" t="n">
+        <v>456.165</v>
+      </c>
+      <c r="Y630" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI630" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ630" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="F631" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I631" t="b">
+        <v>0</v>
+      </c>
+      <c r="J631" t="n">
+        <v>10</v>
+      </c>
+      <c r="K631" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M631" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N631" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P631" t="n">
+        <v>1387.5</v>
+      </c>
+      <c r="Q631" t="n">
+        <v>60.13</v>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S631" t="n">
+        <v>7</v>
+      </c>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V631" t="n">
+        <v>1520</v>
+      </c>
+      <c r="W631" t="n">
+        <v>1824</v>
+      </c>
+      <c r="X631" t="n">
+        <v>1413.6</v>
+      </c>
+      <c r="Y631" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI631" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ631" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>70.47</v>
+      </c>
+      <c r="F632" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I632" t="b">
+        <v>0</v>
+      </c>
+      <c r="J632" t="n">
+        <v>10</v>
+      </c>
+      <c r="K632" t="n">
+        <v>487.3</v>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M632" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N632" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P632" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="Q632" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S632" t="n">
+        <v>7</v>
+      </c>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V632" t="n">
+        <v>443</v>
+      </c>
+      <c r="W632" t="n">
+        <v>531.6</v>
+      </c>
+      <c r="X632" t="n">
+        <v>411.99</v>
+      </c>
+      <c r="Y632" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI632" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ632" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="F633" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I633" t="b">
+        <v>0</v>
+      </c>
+      <c r="J633" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K633" t="n">
+        <v>7945</v>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M633" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N633" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P633" t="n">
+        <v>6717.5</v>
+      </c>
+      <c r="Q633" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S633" t="n">
+        <v>7</v>
+      </c>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V633" t="n">
+        <v>7615</v>
+      </c>
+      <c r="W633" t="n">
+        <v>9138</v>
+      </c>
+      <c r="X633" t="n">
+        <v>7081.95</v>
+      </c>
+      <c r="Y633" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z633" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG633" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH633" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI633" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="F634" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I634" t="b">
+        <v>0</v>
+      </c>
+      <c r="J634" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="K634" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M634" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N634" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P634" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="Q634" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S634" t="n">
+        <v>7</v>
+      </c>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V634" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="W634" t="n">
+        <v>59.5243</v>
+      </c>
+      <c r="X634" t="n">
+        <v>46.872</v>
+      </c>
+      <c r="Y634" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z634" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG634" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH634" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI634" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="F635" t="n">
+        <v>54</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I635" t="b">
+        <v>0</v>
+      </c>
+      <c r="J635" t="n">
+        <v>10</v>
+      </c>
+      <c r="K635" t="n">
+        <v>3113</v>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M635" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N635" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P635" t="n">
+        <v>2652.5</v>
+      </c>
+      <c r="Q635" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S635" t="n">
+        <v>7</v>
+      </c>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V635" t="n">
+        <v>2830</v>
+      </c>
+      <c r="W635" t="n">
+        <v>3396</v>
+      </c>
+      <c r="X635" t="n">
+        <v>2631.9</v>
+      </c>
+      <c r="Y635" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI635" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ635" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="F636" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I636" t="b">
+        <v>0</v>
+      </c>
+      <c r="J636" t="n">
+        <v>10</v>
+      </c>
+      <c r="K636" t="n">
+        <v>484</v>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M636" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N636" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P636" t="n">
+        <v>429.5</v>
+      </c>
+      <c r="Q636" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S636" t="n">
+        <v>7</v>
+      </c>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V636" t="n">
+        <v>440</v>
+      </c>
+      <c r="W636" t="n">
+        <v>528</v>
+      </c>
+      <c r="X636" t="n">
+        <v>409.2</v>
+      </c>
+      <c r="Y636" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z636" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG636" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH636" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI636" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>75.87</v>
+      </c>
+      <c r="F637" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I637" t="b">
+        <v>0</v>
+      </c>
+      <c r="J637" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K637" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M637" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="N637" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P637" t="n">
+        <v>161.25</v>
+      </c>
+      <c r="Q637" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S637" t="n">
+        <v>7</v>
+      </c>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V637" t="n">
+        <v>172</v>
+      </c>
+      <c r="W637" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="X637" t="n">
+        <v>159.96</v>
+      </c>
+      <c r="Y637" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI637" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ637" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ614"/>
+  <autoFilter ref="A1:AJ637"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -69515,25 +72386,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4211</v>
+        <v>0.3953</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.45</v>
+        <v>-3.73</v>
       </c>
       <c r="E2" t="n">
-        <v>12.85</v>
+        <v>11.39</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.94</v>
+        <v>-12.97</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2632</v>
+        <v>0.2558</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5789</v>
+        <v>0.6047</v>
       </c>
     </row>
     <row r="3">
@@ -69543,25 +72414,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4545</v>
+        <v>0.4167</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.64</v>
+        <v>-1.04</v>
       </c>
       <c r="E3" t="n">
-        <v>5.09</v>
+        <v>4.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.95</v>
+        <v>-5.13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="4">
@@ -69693,25 +72564,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4583</v>
+        <v>0.4074</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.34</v>
+        <v>-4.45</v>
       </c>
       <c r="E3" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.06</v>
+        <v>-10.95</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2083</v>
+        <v>0.1852</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4167</v>
+        <v>0.4815</v>
       </c>
     </row>
     <row r="4">
@@ -69721,25 +72592,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>0.35</v>
+        <v>0.3478</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.62</v>
+        <v>-3.87</v>
       </c>
       <c r="E4" t="n">
-        <v>10.32</v>
+        <v>8.77</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.12</v>
+        <v>-13.18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.15</v>
+        <v>0.1739</v>
       </c>
       <c r="H4" t="n">
-        <v>0.65</v>
+        <v>0.6522</v>
       </c>
     </row>
     <row r="5">
@@ -69836,7 +72707,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:24:26</t>
+          <t>2026-09-21 14:25:41</t>
         </is>
       </c>
     </row>
@@ -69883,7 +72754,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>613</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7">
@@ -69893,7 +72764,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -69903,7 +72774,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>442</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$637</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$656</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ637"/>
+  <dimension ref="A1:AJ656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18930,11 +18930,11 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z187" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA187" t="n">
         <v>6.14</v>
@@ -18945,6 +18945,15 @@
       <c r="AC187" t="n">
         <v>-3.21</v>
       </c>
+      <c r="AD187" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>-3.21</v>
+      </c>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -18953,7 +18962,7 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -19054,11 +19063,11 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z188" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA188" t="n">
         <v>1.52</v>
@@ -19069,6 +19078,15 @@
       <c r="AC188" t="n">
         <v>-7.43</v>
       </c>
+      <c r="AD188" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>-8.449999999999999</v>
+      </c>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
@@ -19077,7 +19095,7 @@
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -19178,11 +19196,11 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z189" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA189" t="n">
         <v>-2.21</v>
@@ -19193,6 +19211,15 @@
       <c r="AC189" t="n">
         <v>-9.44</v>
       </c>
+      <c r="AD189" t="n">
+        <v>-9.19</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>-9.800000000000001</v>
+      </c>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
@@ -19201,7 +19228,7 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -19302,11 +19329,11 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z190" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA190" t="n">
         <v>1.57</v>
@@ -19317,6 +19344,15 @@
       <c r="AC190" t="n">
         <v>-8.73</v>
       </c>
+      <c r="AD190" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>-8.73</v>
+      </c>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -19325,7 +19361,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -19426,11 +19462,11 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z191" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA191" t="n">
         <v>-3.25</v>
@@ -19441,6 +19477,15 @@
       <c r="AC191" t="n">
         <v>-5.08</v>
       </c>
+      <c r="AD191" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>-8.33</v>
+      </c>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -19449,7 +19494,7 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -19550,11 +19595,11 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z192" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA192" t="n">
         <v>2.47</v>
@@ -19565,6 +19610,15 @@
       <c r="AC192" t="n">
         <v>6.71</v>
       </c>
+      <c r="AD192" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>-2.47</v>
+      </c>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -19573,7 +19627,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -19674,11 +19728,11 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z193" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA193" t="n">
         <v>7.77</v>
@@ -19689,6 +19743,15 @@
       <c r="AC193" t="n">
         <v>6.8</v>
       </c>
+      <c r="AD193" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>-0.97</v>
+      </c>
       <c r="AG193" t="b">
         <v>1</v>
       </c>
@@ -19697,7 +19760,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -19798,11 +19861,11 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z194" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA194" t="n">
         <v>8.48</v>
@@ -19813,6 +19876,15 @@
       <c r="AC194" t="n">
         <v>16.82</v>
       </c>
+      <c r="AD194" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>-0.54</v>
+      </c>
       <c r="AG194" t="b">
         <v>1</v>
       </c>
@@ -19821,7 +19893,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -19922,11 +19994,11 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z195" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA195" t="n">
         <v>3.15</v>
@@ -19937,6 +20009,15 @@
       <c r="AC195" t="n">
         <v>-2.22</v>
       </c>
+      <c r="AD195" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>-2.59</v>
+      </c>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -19945,7 +20026,7 @@
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -20046,11 +20127,11 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z196" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA196" t="n">
         <v>32.52</v>
@@ -20061,6 +20142,15 @@
       <c r="AC196" t="n">
         <v>5.86</v>
       </c>
+      <c r="AD196" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>0</v>
+      </c>
       <c r="AG196" t="b">
         <v>1</v>
       </c>
@@ -20069,7 +20159,7 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -20170,11 +20260,11 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z197" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA197" t="n">
         <v>-0.54</v>
@@ -20185,6 +20275,15 @@
       <c r="AC197" t="n">
         <v>-2.52</v>
       </c>
+      <c r="AD197" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>-6.49</v>
+      </c>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20193,7 +20292,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -20516,11 +20615,11 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z200" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA200" t="n">
         <v>7.63</v>
@@ -20531,6 +20630,15 @@
       <c r="AC200" t="n">
         <v>8.35</v>
       </c>
+      <c r="AD200" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>0</v>
+      </c>
       <c r="AG200" t="b">
         <v>1</v>
       </c>
@@ -20539,7 +20647,7 @@
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -20640,11 +20748,11 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z201" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA201" t="n">
         <v>-12.08</v>
@@ -20655,6 +20763,15 @@
       <c r="AC201" t="n">
         <v>-19.13</v>
       </c>
+      <c r="AD201" t="n">
+        <v>-22.15</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -20663,7 +20780,7 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -20764,11 +20881,11 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z202" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA202" t="n">
         <v>-59.39</v>
@@ -20779,6 +20896,15 @@
       <c r="AC202" t="n">
         <v>-64.05</v>
       </c>
+      <c r="AD202" t="n">
+        <v>-67.16</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>-55.36</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>-67.62</v>
+      </c>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -20787,7 +20913,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -20892,7 +21018,7 @@
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -21016,7 +21142,7 @@
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -21140,7 +21266,7 @@
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -21264,7 +21390,7 @@
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -21388,7 +21514,7 @@
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -21512,7 +21638,7 @@
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -21636,7 +21762,7 @@
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21760,7 +21886,7 @@
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21884,7 +22010,7 @@
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -22008,7 +22134,7 @@
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -22243,7 +22369,7 @@
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -22367,7 +22493,7 @@
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -22491,7 +22617,7 @@
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -22615,7 +22741,7 @@
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -22739,7 +22865,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22863,7 +22989,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -22987,7 +23113,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -23111,7 +23237,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -23235,7 +23361,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -23359,7 +23485,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -23483,7 +23609,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23607,7 +23733,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23731,7 +23857,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23855,7 +23981,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -23979,7 +24105,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -24103,7 +24229,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -24227,7 +24353,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -24351,7 +24477,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -24586,7 +24712,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24932,7 +25058,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -25056,7 +25182,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -25180,7 +25306,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -25304,7 +25430,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -25428,7 +25554,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -25552,7 +25678,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25676,7 +25802,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25800,7 +25926,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -25924,7 +26050,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -26048,7 +26174,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -26172,7 +26298,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -26296,7 +26422,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -26420,7 +26546,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26544,7 +26670,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26668,7 +26794,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -26792,7 +26918,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -26916,7 +27042,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -27040,7 +27166,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -27164,7 +27290,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -27288,7 +27414,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27634,7 +27760,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -27980,7 +28106,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -28104,7 +28230,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -28228,7 +28354,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -28352,7 +28478,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28587,7 +28713,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28711,7 +28837,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -28835,7 +28961,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -28959,7 +29085,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -29083,7 +29209,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -29207,7 +29333,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -29331,7 +29457,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29455,7 +29581,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -29579,7 +29705,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -29703,7 +29829,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -29827,7 +29953,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -29951,7 +30077,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -30075,7 +30201,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -30199,7 +30325,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -30323,7 +30449,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -30447,7 +30573,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -30571,7 +30697,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -30695,7 +30821,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30819,7 +30945,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -30943,7 +31069,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -31067,7 +31193,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -31191,7 +31317,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -31315,7 +31441,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -31439,7 +31565,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -31563,7 +31689,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -31687,7 +31813,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -31811,7 +31937,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -31935,7 +32061,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -32392,7 +32518,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32516,7 +32642,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -32640,7 +32766,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -32875,13 +33001,16 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
       </c>
       <c r="AB301" t="n">
         <v>-8.550000000000001</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>-4.72</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -32996,13 +33125,16 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
       </c>
       <c r="AB302" t="n">
         <v>-5.54</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>-1.28</v>
       </c>
       <c r="AG302" t="b">
         <v>0</v>
@@ -33117,13 +33249,16 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
       </c>
       <c r="AB303" t="n">
         <v>-6.12</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>-6.67</v>
       </c>
       <c r="AG303" t="b">
         <v>0</v>
@@ -33238,13 +33373,16 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
       </c>
       <c r="AB304" t="n">
         <v>-8.800000000000001</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>-6.44</v>
       </c>
       <c r="AG304" t="b">
         <v>0</v>
@@ -33359,13 +33497,16 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
       </c>
       <c r="AB305" t="n">
         <v>-8.82</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>-5.32</v>
       </c>
       <c r="AG305" t="b">
         <v>0</v>
@@ -33480,13 +33621,16 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
       </c>
       <c r="AB306" t="n">
         <v>4.53</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>20.75</v>
       </c>
       <c r="AG306" t="b">
         <v>1</v>
@@ -33601,13 +33745,16 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
       </c>
       <c r="AB307" t="n">
         <v>-13.29</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>-11.9</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -33722,13 +33869,16 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
       </c>
       <c r="AB308" t="n">
         <v>-2.68</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>-1.1</v>
       </c>
       <c r="AG308" t="b">
         <v>0</v>
@@ -33843,13 +33993,16 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
       </c>
       <c r="AB309" t="n">
         <v>-8.119999999999999</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>-5.64</v>
       </c>
       <c r="AG309" t="b">
         <v>0</v>
@@ -33964,13 +34117,16 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
       </c>
       <c r="AB310" t="n">
         <v>-20.65</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>-15.1</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -34085,13 +34241,16 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="AB311" t="n">
         <v>-4.46</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>2.09</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -34206,13 +34365,16 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
       </c>
       <c r="AB312" t="n">
         <v>-2.63</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>0</v>
       </c>
       <c r="AG312" t="b">
         <v>0</v>
@@ -34327,13 +34489,16 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
       </c>
       <c r="AB313" t="n">
         <v>-3.66</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>-1.13</v>
       </c>
       <c r="AG313" t="b">
         <v>0</v>
@@ -34448,13 +34613,16 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
       </c>
       <c r="AB314" t="n">
         <v>-10.14</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>-4.05</v>
       </c>
       <c r="AG314" t="b">
         <v>0</v>
@@ -34569,13 +34737,16 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
       </c>
       <c r="AB315" t="n">
         <v>-2.18</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>1.75</v>
       </c>
       <c r="AG315" t="b">
         <v>0</v>
@@ -34690,13 +34861,16 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
       </c>
       <c r="AB316" t="n">
         <v>4.14</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>6.55</v>
       </c>
       <c r="AG316" t="b">
         <v>0</v>
@@ -34811,13 +34985,16 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
       </c>
       <c r="AB317" t="n">
         <v>-0.9</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>0.9</v>
       </c>
       <c r="AG317" t="b">
         <v>0</v>
@@ -34932,13 +35109,16 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
       </c>
       <c r="AB318" t="n">
         <v>9.16</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>12.45</v>
       </c>
       <c r="AG318" t="b">
         <v>0</v>
@@ -35053,13 +35233,16 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
       </c>
       <c r="AB319" t="n">
         <v>7.69</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>6.45</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -35174,13 +35357,16 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
       </c>
       <c r="AB320" t="n">
         <v>-5.21</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>0</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -35295,13 +35481,16 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
       </c>
       <c r="AB321" t="n">
         <v>-20.12</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>-15.5</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -35416,13 +35605,16 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
       </c>
       <c r="AB322" t="n">
         <v>-8.65</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>-0.59</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -35537,13 +35729,16 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
       </c>
       <c r="AB323" t="n">
         <v>-7.36</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>10.63</v>
       </c>
       <c r="AG323" t="b">
         <v>0</v>
@@ -35658,13 +35853,16 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
       </c>
       <c r="AB324" t="n">
         <v>-2.49</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>7.16</v>
       </c>
       <c r="AG324" t="b">
         <v>0</v>
@@ -36001,13 +36199,16 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
       </c>
       <c r="AB327" t="n">
         <v>0.67</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>39.7</v>
       </c>
       <c r="AG327" t="b">
         <v>1</v>
@@ -36122,13 +36323,16 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
       </c>
       <c r="AB328" t="n">
         <v>1.24</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>8.08</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -36243,13 +36447,16 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
       </c>
       <c r="AB329" t="n">
         <v>-21.52</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>-13.1</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -36586,13 +36793,16 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
       </c>
       <c r="AB332" t="n">
         <v>-11.43</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>-4.9</v>
       </c>
       <c r="AG332" t="b">
         <v>0</v>
@@ -36707,7 +36917,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -36828,7 +37038,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -36949,7 +37159,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -37070,7 +37280,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -37191,7 +37401,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -37312,7 +37522,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -37433,7 +37643,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -37554,7 +37764,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -37675,7 +37885,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -37796,7 +38006,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -37917,7 +38127,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -38038,7 +38248,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -38159,7 +38369,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -38280,7 +38490,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -38401,7 +38611,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -38522,7 +38732,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -38643,7 +38853,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -38764,7 +38974,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -38885,7 +39095,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -39006,7 +39216,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -39127,7 +39337,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -39692,7 +39902,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -39813,7 +40023,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -39934,7 +40144,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -40055,7 +40265,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -40176,7 +40386,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -40297,7 +40507,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -40418,7 +40628,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -40539,7 +40749,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -40660,7 +40870,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -40669,7 +40879,7 @@
         <v>3.69</v>
       </c>
       <c r="AG366" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH366" t="b">
         <v>0</v>
@@ -40781,7 +40991,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -40902,7 +41112,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -41023,7 +41233,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -41144,7 +41354,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -41265,7 +41475,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -41386,7 +41596,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -41507,7 +41717,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -41628,7 +41838,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -41749,7 +41959,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -41870,7 +42080,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -41991,7 +42201,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -42334,7 +42544,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -42455,7 +42665,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -42687,7 +42897,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -42808,7 +43018,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -42929,7 +43139,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -43050,7 +43260,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -43171,7 +43381,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -43292,7 +43502,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -43413,7 +43623,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -43531,7 +43741,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -43652,7 +43862,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -43773,7 +43983,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -43894,7 +44104,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -44015,7 +44225,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -44136,7 +44346,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -44257,7 +44467,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -44266,7 +44476,7 @@
         <v>6.68</v>
       </c>
       <c r="AG396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH396" t="b">
         <v>0</v>
@@ -44378,7 +44588,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -44499,7 +44709,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -44620,7 +44830,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -44741,7 +44951,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -44862,7 +45072,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -44983,7 +45193,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -45104,7 +45314,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -45225,7 +45435,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -45346,7 +45556,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -45467,7 +45677,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -45588,7 +45798,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -45709,7 +45919,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -45830,7 +46040,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -46284,7 +46494,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -46405,7 +46615,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -46526,7 +46736,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -46647,7 +46857,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -46768,7 +46978,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -46889,7 +47099,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -47010,7 +47220,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -47131,7 +47341,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -47252,7 +47462,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -47373,7 +47583,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -47382,7 +47592,7 @@
         <v>10.44</v>
       </c>
       <c r="AG422" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH422" t="b">
         <v>1</v>
@@ -47494,7 +47704,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -47615,7 +47825,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -47736,7 +47946,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -47857,7 +48067,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -47978,7 +48188,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -48099,7 +48309,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -48220,7 +48430,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -48341,7 +48551,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -48462,7 +48672,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -48583,7 +48793,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -48704,7 +48914,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -48825,7 +49035,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -49168,7 +49378,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -49400,10 +49610,13 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>0.71</v>
       </c>
       <c r="AG439" t="b">
         <v>0</v>
@@ -49518,10 +49731,13 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AG440" t="b">
         <v>0</v>
@@ -49636,10 +49852,13 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>-1.49</v>
       </c>
       <c r="AG441" t="b">
         <v>0</v>
@@ -49754,10 +49973,13 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>-5.81</v>
       </c>
       <c r="AG442" t="b">
         <v>0</v>
@@ -49872,13 +50094,16 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
       </c>
+      <c r="AB443" t="n">
+        <v>16.79</v>
+      </c>
       <c r="AG443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH443" t="b">
         <v>0</v>
@@ -49990,10 +50215,13 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>-3.9</v>
       </c>
       <c r="AG444" t="b">
         <v>0</v>
@@ -50108,10 +50336,13 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>7.73</v>
       </c>
       <c r="AG445" t="b">
         <v>0</v>
@@ -50226,10 +50457,13 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>9.98</v>
       </c>
       <c r="AG446" t="b">
         <v>0</v>
@@ -50344,10 +50578,13 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>4.02</v>
       </c>
       <c r="AG447" t="b">
         <v>0</v>
@@ -50462,10 +50699,13 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>3.11</v>
       </c>
       <c r="AG448" t="b">
         <v>0</v>
@@ -50580,10 +50820,13 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>3.69</v>
       </c>
       <c r="AG449" t="b">
         <v>0</v>
@@ -50698,10 +50941,13 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
+      </c>
+      <c r="AB450" t="n">
+        <v>-1.32</v>
       </c>
       <c r="AG450" t="b">
         <v>0</v>
@@ -50816,10 +51062,13 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>5.36</v>
       </c>
       <c r="AG451" t="b">
         <v>0</v>
@@ -50934,10 +51183,13 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>1.1</v>
       </c>
       <c r="AG452" t="b">
         <v>0</v>
@@ -51052,10 +51304,13 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>0.23</v>
       </c>
       <c r="AG453" t="b">
         <v>0</v>
@@ -51170,10 +51425,13 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>4.49</v>
       </c>
       <c r="AG454" t="b">
         <v>0</v>
@@ -51288,10 +51546,13 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>5.42</v>
       </c>
       <c r="AG455" t="b">
         <v>0</v>
@@ -51406,10 +51667,13 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>-6.7</v>
       </c>
       <c r="AG456" t="b">
         <v>0</v>
@@ -51524,10 +51788,13 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>3.2</v>
       </c>
       <c r="AG457" t="b">
         <v>0</v>
@@ -51642,10 +51909,13 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>4.24</v>
       </c>
       <c r="AG458" t="b">
         <v>0</v>
@@ -51982,10 +52252,13 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>40.52</v>
       </c>
       <c r="AG461" t="b">
         <v>1</v>
@@ -52100,10 +52373,13 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>0.74</v>
       </c>
       <c r="AG462" t="b">
         <v>0</v>
@@ -52218,7 +52494,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -52336,7 +52612,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -52454,7 +52730,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -52572,7 +52848,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -52690,7 +52966,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -52808,7 +53084,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -52926,7 +53202,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -53044,7 +53320,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -53162,7 +53438,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -53280,7 +53556,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -53398,7 +53674,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -53516,7 +53792,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -53634,7 +53910,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -53752,7 +54028,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -53870,7 +54146,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -53988,7 +54264,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -54439,7 +54715,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -54557,7 +54833,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -54675,7 +54951,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -54793,7 +55069,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -54911,7 +55187,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -55029,13 +55305,13 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
       </c>
       <c r="AG487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH487" t="b">
         <v>1</v>
@@ -55147,7 +55423,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -55265,7 +55541,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -55383,7 +55659,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -55501,7 +55777,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -55619,7 +55895,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -55737,7 +56013,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -55855,7 +56131,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -55973,7 +56249,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -56091,7 +56367,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -56209,7 +56485,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -56327,7 +56603,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -56445,7 +56721,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -56563,7 +56839,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -56681,7 +56957,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -56799,7 +57075,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -56917,7 +57193,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -57035,7 +57311,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -57153,7 +57429,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -57271,7 +57547,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -57389,7 +57665,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -57507,7 +57783,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -57625,7 +57901,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -57743,7 +58019,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -57861,7 +58137,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -57979,7 +58255,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -58097,7 +58373,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -58215,7 +58491,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -58333,7 +58609,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -58451,7 +58727,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -58569,7 +58845,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -58687,7 +58963,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -58805,7 +59081,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -58923,7 +59199,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -59041,7 +59317,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -59159,7 +59435,10 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA522" t="n">
+        <v>1.39</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -59274,7 +59553,10 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA523" t="n">
+        <v>-0.75</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -59389,7 +59671,10 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA524" t="n">
+        <v>2.32</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -59504,7 +59789,10 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA525" t="n">
+        <v>3.01</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -59619,7 +59907,10 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA526" t="n">
+        <v>0.88</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -59734,7 +60025,10 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA527" t="n">
+        <v>-2.51</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -59849,7 +60143,10 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA528" t="n">
+        <v>-1.15</v>
       </c>
       <c r="AG528" t="b">
         <v>0</v>
@@ -59964,7 +60261,10 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA529" t="n">
+        <v>1.91</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -60079,7 +60379,10 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA530" t="n">
+        <v>-0.14</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -60194,7 +60497,10 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA531" t="n">
+        <v>0.88</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -60309,7 +60615,10 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA532" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -60424,7 +60733,10 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA533" t="n">
+        <v>38.77</v>
       </c>
       <c r="AG533" t="b">
         <v>1</v>
@@ -60539,7 +60851,10 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA534" t="n">
+        <v>6.76</v>
       </c>
       <c r="AG534" t="b">
         <v>0</v>
@@ -60654,7 +60969,10 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA535" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -60769,7 +61087,10 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA536" t="n">
+        <v>0.19</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -60884,7 +61205,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG537" t="b">
         <v>0</v>
@@ -60999,7 +61320,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG538" t="b">
         <v>0</v>
@@ -61114,7 +61435,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG539" t="b">
         <v>0</v>
@@ -61229,7 +61550,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG540" t="b">
         <v>0</v>
@@ -61344,7 +61665,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG541" t="b">
         <v>0</v>
@@ -61459,7 +61780,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG542" t="b">
         <v>0</v>
@@ -61574,7 +61895,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG543" t="b">
         <v>0</v>
@@ -61689,7 +62010,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG544" t="b">
         <v>0</v>
@@ -61804,7 +62125,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG545" t="b">
         <v>0</v>
@@ -61919,7 +62240,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG546" t="b">
         <v>0</v>
@@ -62034,7 +62355,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG547" t="b">
         <v>0</v>
@@ -62149,7 +62470,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG548" t="b">
         <v>0</v>
@@ -62264,7 +62585,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG549" t="b">
         <v>0</v>
@@ -62379,7 +62700,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG550" t="b">
         <v>0</v>
@@ -62716,7 +63037,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG553" t="b">
         <v>1</v>
@@ -62831,7 +63152,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG554" t="b">
         <v>0</v>
@@ -62946,7 +63267,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG555" t="b">
         <v>0</v>
@@ -63172,7 +63493,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG557" t="b">
         <v>0</v>
@@ -63287,7 +63608,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG558" t="b">
         <v>0</v>
@@ -63402,7 +63723,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG559" t="b">
         <v>0</v>
@@ -63517,7 +63838,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG560" t="b">
         <v>0</v>
@@ -63632,7 +63953,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG561" t="b">
         <v>0</v>
@@ -63747,10 +64068,10 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG562" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH562" t="b">
         <v>0</v>
@@ -63859,7 +64180,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG563" t="b">
         <v>0</v>
@@ -63974,7 +64295,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG564" t="b">
         <v>0</v>
@@ -64089,7 +64410,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG565" t="b">
         <v>0</v>
@@ -64204,7 +64525,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG566" t="b">
         <v>0</v>
@@ -64319,7 +64640,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG567" t="b">
         <v>0</v>
@@ -64434,7 +64755,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG568" t="b">
         <v>0</v>
@@ -64549,7 +64870,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG569" t="b">
         <v>0</v>
@@ -64664,7 +64985,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG570" t="b">
         <v>0</v>
@@ -64779,7 +65100,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG571" t="b">
         <v>0</v>
@@ -64894,7 +65215,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG572" t="b">
         <v>0</v>
@@ -65009,7 +65330,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG573" t="b">
         <v>0</v>
@@ -65124,7 +65445,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG574" t="b">
         <v>0</v>
@@ -65239,7 +65560,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG575" t="b">
         <v>0</v>
@@ -65354,7 +65675,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG576" t="b">
         <v>0</v>
@@ -65802,10 +66123,10 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG580" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH580" t="b">
         <v>0</v>
@@ -65917,7 +66238,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG581" t="b">
         <v>0</v>
@@ -66032,7 +66353,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG582" t="b">
         <v>0</v>
@@ -66147,7 +66468,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG583" t="b">
         <v>0</v>
@@ -66373,7 +66694,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG585" t="b">
         <v>0</v>
@@ -66488,7 +66809,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG586" t="b">
         <v>0</v>
@@ -66603,7 +66924,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG587" t="b">
         <v>0</v>
@@ -66718,7 +67039,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG588" t="b">
         <v>0</v>
@@ -66833,7 +67154,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG589" t="b">
         <v>0</v>
@@ -66948,10 +67269,10 @@
         </is>
       </c>
       <c r="Z590" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG590" t="b">
         <v>1</v>
-      </c>
-      <c r="AG590" t="b">
-        <v>0</v>
       </c>
       <c r="AH590" t="b">
         <v>0</v>
@@ -67063,7 +67384,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG591" t="b">
         <v>0</v>
@@ -67178,7 +67499,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG592" t="b">
         <v>0</v>
@@ -67293,7 +67614,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG593" t="b">
         <v>0</v>
@@ -67405,7 +67726,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG594" t="b">
         <v>0</v>
@@ -67520,7 +67841,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG595" t="b">
         <v>0</v>
@@ -67635,7 +67956,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -67750,7 +68071,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -67865,7 +68186,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -67980,7 +68301,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -68095,7 +68416,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG600" t="b">
         <v>0</v>
@@ -68210,7 +68531,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG601" t="b">
         <v>0</v>
@@ -68325,7 +68646,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG602" t="b">
         <v>0</v>
@@ -68440,7 +68761,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG603" t="b">
         <v>0</v>
@@ -68555,7 +68876,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG604" t="b">
         <v>0</v>
@@ -68670,7 +68991,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG605" t="b">
         <v>0</v>
@@ -68782,7 +69103,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG606" t="b">
         <v>0</v>
@@ -69341,7 +69662,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG611" t="b">
         <v>0</v>
@@ -69453,7 +69774,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG612" t="b">
         <v>0</v>
@@ -69679,7 +70000,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG614" t="b">
         <v>0</v>
@@ -69794,7 +70115,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG615" t="b">
         <v>0</v>
@@ -69909,7 +70230,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG616" t="b">
         <v>0</v>
@@ -70024,7 +70345,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG617" t="b">
         <v>0</v>
@@ -70139,7 +70460,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG618" t="b">
         <v>0</v>
@@ -70254,7 +70575,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG619" t="b">
         <v>0</v>
@@ -70369,7 +70690,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG620" t="b">
         <v>0</v>
@@ -70481,7 +70802,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG621" t="b">
         <v>0</v>
@@ -70596,7 +70917,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG622" t="b">
         <v>0</v>
@@ -70711,7 +71032,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG623" t="b">
         <v>0</v>
@@ -70826,7 +71147,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG624" t="b">
         <v>0</v>
@@ -70941,7 +71262,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG625" t="b">
         <v>0</v>
@@ -71056,7 +71377,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG626" t="b">
         <v>0</v>
@@ -71171,7 +71492,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG627" t="b">
         <v>0</v>
@@ -71286,7 +71607,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG628" t="b">
         <v>0</v>
@@ -71398,7 +71719,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG629" t="b">
         <v>0</v>
@@ -71846,7 +72167,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG633" t="b">
         <v>0</v>
@@ -71961,7 +72282,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG634" t="b">
         <v>0</v>
@@ -72187,7 +72508,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG636" t="b">
         <v>0</v>
@@ -72312,8 +72633,2170 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>81.45</v>
+      </c>
+      <c r="F638" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I638" t="b">
+        <v>0</v>
+      </c>
+      <c r="J638" t="n">
+        <v>10</v>
+      </c>
+      <c r="K638" t="n">
+        <v>176</v>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M638" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N638" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P638" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="Q638" t="n">
+        <v>74.01000000000001</v>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S638" t="n">
+        <v>7</v>
+      </c>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V638" t="n">
+        <v>160</v>
+      </c>
+      <c r="W638" t="n">
+        <v>192</v>
+      </c>
+      <c r="X638" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="Y638" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z638" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG638" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH638" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI638" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="F639" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I639" t="b">
+        <v>0</v>
+      </c>
+      <c r="J639" t="n">
+        <v>10</v>
+      </c>
+      <c r="K639" t="n">
+        <v>2684</v>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M639" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N639" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P639" t="n">
+        <v>2305</v>
+      </c>
+      <c r="Q639" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S639" t="n">
+        <v>7</v>
+      </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V639" t="n">
+        <v>2440</v>
+      </c>
+      <c r="W639" t="n">
+        <v>2928</v>
+      </c>
+      <c r="X639" t="n">
+        <v>2269.2</v>
+      </c>
+      <c r="Y639" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z639" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG639" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH639" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI639" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>81.11</v>
+      </c>
+      <c r="F640" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I640" t="b">
+        <v>0</v>
+      </c>
+      <c r="J640" t="n">
+        <v>10</v>
+      </c>
+      <c r="K640" t="n">
+        <v>5698</v>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M640" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N640" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P640" t="n">
+        <v>4955</v>
+      </c>
+      <c r="Q640" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S640" t="n">
+        <v>7</v>
+      </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V640" t="n">
+        <v>5180</v>
+      </c>
+      <c r="W640" t="n">
+        <v>6216</v>
+      </c>
+      <c r="X640" t="n">
+        <v>4817.4</v>
+      </c>
+      <c r="Y640" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z640" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG640" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH640" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI640" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>臺企銀</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="F641" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I641" t="b">
+        <v>0</v>
+      </c>
+      <c r="J641" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="K641" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M641" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N641" t="n">
+        <v>10</v>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P641" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="Q641" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S641" t="n">
+        <v>4.3164</v>
+      </c>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V641" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="W641" t="n">
+        <v>20.6914</v>
+      </c>
+      <c r="X641" t="n">
+        <v>17.4622</v>
+      </c>
+      <c r="Y641" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z641" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG641" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH641" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI641" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>70.73999999999999</v>
+      </c>
+      <c r="F642" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I642" t="b">
+        <v>0</v>
+      </c>
+      <c r="J642" t="n">
+        <v>10</v>
+      </c>
+      <c r="K642" t="n">
+        <v>169.95</v>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M642" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N642" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q642" t="n">
+        <v>49</v>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S642" t="n">
+        <v>7</v>
+      </c>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V642" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="W642" t="n">
+        <v>177.3621</v>
+      </c>
+      <c r="X642" t="n">
+        <v>143.685</v>
+      </c>
+      <c r="Y642" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z642" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG642" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH642" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI642" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>81.81</v>
+      </c>
+      <c r="F643" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I643" t="b">
+        <v>0</v>
+      </c>
+      <c r="J643" t="n">
+        <v>10</v>
+      </c>
+      <c r="K643" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M643" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N643" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P643" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="Q643" t="n">
+        <v>66.69</v>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S643" t="n">
+        <v>7</v>
+      </c>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V643" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="W643" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="X643" t="n">
+        <v>36.549</v>
+      </c>
+      <c r="Y643" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z643" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG643" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH643" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI643" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="F644" t="n">
+        <v>63.19</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I644" t="b">
+        <v>0</v>
+      </c>
+      <c r="J644" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K644" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M644" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N644" t="n">
+        <v>10</v>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P644" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="Q644" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S644" t="n">
+        <v>5.3616</v>
+      </c>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V644" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="W644" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="X644" t="n">
+        <v>43.581</v>
+      </c>
+      <c r="Y644" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z644" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG644" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH644" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI644" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="F645" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I645" t="b">
+        <v>0</v>
+      </c>
+      <c r="J645" t="n">
+        <v>10</v>
+      </c>
+      <c r="K645" t="n">
+        <v>77.66</v>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M645" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N645" t="n">
+        <v>10</v>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P645" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="Q645" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S645" t="n">
+        <v>3.8824</v>
+      </c>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V645" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="W645" t="n">
+        <v>80.8412</v>
+      </c>
+      <c r="X645" t="n">
+        <v>67.85899999999999</v>
+      </c>
+      <c r="Y645" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z645" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG645" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH645" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI645" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="F646" t="n">
+        <v>71.27</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I646" t="b">
+        <v>0</v>
+      </c>
+      <c r="J646" t="n">
+        <v>10</v>
+      </c>
+      <c r="K646" t="n">
+        <v>47.19</v>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M646" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N646" t="n">
+        <v>8</v>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P646" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="Q646" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S646" t="n">
+        <v>3.6311</v>
+      </c>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V646" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="W646" t="n">
+        <v>50.5214</v>
+      </c>
+      <c r="X646" t="n">
+        <v>41.3422</v>
+      </c>
+      <c r="Y646" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z646" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG646" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH646" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI646" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="F647" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I647" t="b">
+        <v>0</v>
+      </c>
+      <c r="J647" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="K647" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M647" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N647" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P647" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="Q647" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S647" t="n">
+        <v>6.7462</v>
+      </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V647" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="W647" t="n">
+        <v>53.6061</v>
+      </c>
+      <c r="X647" t="n">
+        <v>42.3372</v>
+      </c>
+      <c r="Y647" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z647" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG647" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH647" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI647" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>78.73999999999999</v>
+      </c>
+      <c r="F648" t="n">
+        <v>59</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I648" t="b">
+        <v>0</v>
+      </c>
+      <c r="J648" t="n">
+        <v>10</v>
+      </c>
+      <c r="K648" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M648" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N648" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P648" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="Q648" t="n">
+        <v>50</v>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S648" t="n">
+        <v>7</v>
+      </c>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V648" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="W648" t="n">
+        <v>47.7959</v>
+      </c>
+      <c r="X648" t="n">
+        <v>37.107</v>
+      </c>
+      <c r="Y648" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z648" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG648" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH648" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI648" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>75.04000000000001</v>
+      </c>
+      <c r="F649" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I649" t="b">
+        <v>0</v>
+      </c>
+      <c r="J649" t="n">
+        <v>10</v>
+      </c>
+      <c r="K649" t="n">
+        <v>3729</v>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M649" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N649" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P649" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="Q649" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S649" t="n">
+        <v>7</v>
+      </c>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V649" t="n">
+        <v>3390</v>
+      </c>
+      <c r="W649" t="n">
+        <v>4068</v>
+      </c>
+      <c r="X649" t="n">
+        <v>3152.7</v>
+      </c>
+      <c r="Y649" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z649" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG649" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH649" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI649" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="F650" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I650" t="b">
+        <v>0</v>
+      </c>
+      <c r="J650" t="n">
+        <v>10</v>
+      </c>
+      <c r="K650" t="n">
+        <v>592.9</v>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M650" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N650" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P650" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="Q650" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S650" t="n">
+        <v>7</v>
+      </c>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V650" t="n">
+        <v>539</v>
+      </c>
+      <c r="W650" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="X650" t="n">
+        <v>501.27</v>
+      </c>
+      <c r="Y650" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z650" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG650" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH650" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI650" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="F651" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I651" t="b">
+        <v>0</v>
+      </c>
+      <c r="J651" t="n">
+        <v>10</v>
+      </c>
+      <c r="K651" t="n">
+        <v>551.1</v>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M651" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N651" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P651" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="Q651" t="n">
+        <v>63.66</v>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S651" t="n">
+        <v>7</v>
+      </c>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V651" t="n">
+        <v>501</v>
+      </c>
+      <c r="W651" t="n">
+        <v>601.2</v>
+      </c>
+      <c r="X651" t="n">
+        <v>465.93</v>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI651" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ651" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>77.45</v>
+      </c>
+      <c r="F652" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I652" t="b">
+        <v>0</v>
+      </c>
+      <c r="J652" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="K652" t="n">
+        <v>301</v>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M652" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N652" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P652" t="n">
+        <v>254.75</v>
+      </c>
+      <c r="Q652" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S652" t="n">
+        <v>7</v>
+      </c>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V652" t="n">
+        <v>276.5</v>
+      </c>
+      <c r="W652" t="n">
+        <v>331.8</v>
+      </c>
+      <c r="X652" t="n">
+        <v>257.145</v>
+      </c>
+      <c r="Y652" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI652" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ652" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>77.97</v>
+      </c>
+      <c r="F653" t="n">
+        <v>39.56</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I653" t="b">
+        <v>0</v>
+      </c>
+      <c r="J653" t="n">
+        <v>10</v>
+      </c>
+      <c r="K653" t="n">
+        <v>1760</v>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M653" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N653" t="n">
+        <v>1</v>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P653" t="n">
+        <v>1435</v>
+      </c>
+      <c r="Q653" t="n">
+        <v>63.74</v>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S653" t="n">
+        <v>7</v>
+      </c>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V653" t="n">
+        <v>1600</v>
+      </c>
+      <c r="W653" t="n">
+        <v>1920</v>
+      </c>
+      <c r="X653" t="n">
+        <v>1488</v>
+      </c>
+      <c r="Y653" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI653" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ653" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="F654" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I654" t="b">
+        <v>0</v>
+      </c>
+      <c r="J654" t="n">
+        <v>10</v>
+      </c>
+      <c r="K654" t="n">
+        <v>477.95</v>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M654" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N654" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P654" t="n">
+        <v>433.75</v>
+      </c>
+      <c r="Q654" t="n">
+        <v>63.08</v>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S654" t="n">
+        <v>7</v>
+      </c>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V654" t="n">
+        <v>434.5</v>
+      </c>
+      <c r="W654" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="X654" t="n">
+        <v>404.085</v>
+      </c>
+      <c r="Y654" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z654" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG654" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH654" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI654" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="F655" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I655" t="b">
+        <v>0</v>
+      </c>
+      <c r="J655" t="n">
+        <v>10</v>
+      </c>
+      <c r="K655" t="n">
+        <v>190.3</v>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M655" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N655" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P655" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="Q655" t="n">
+        <v>62.57</v>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S655" t="n">
+        <v>7</v>
+      </c>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V655" t="n">
+        <v>173</v>
+      </c>
+      <c r="W655" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="X655" t="n">
+        <v>160.89</v>
+      </c>
+      <c r="Y655" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI655" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ655" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="F656" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I656" t="b">
+        <v>0</v>
+      </c>
+      <c r="J656" t="n">
+        <v>10</v>
+      </c>
+      <c r="K656" t="n">
+        <v>240.9</v>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M656" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N656" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P656" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q656" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S656" t="n">
+        <v>7</v>
+      </c>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V656" t="n">
+        <v>219</v>
+      </c>
+      <c r="W656" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="X656" t="n">
+        <v>203.67</v>
+      </c>
+      <c r="Y656" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI656" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ656" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ637"/>
+  <autoFilter ref="A1:AJ656"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -72386,25 +74869,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3953</v>
+        <v>0.3929</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.73</v>
+        <v>-3.17</v>
       </c>
       <c r="E2" t="n">
-        <v>11.39</v>
+        <v>11.15</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.97</v>
+        <v>-12.48</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2558</v>
+        <v>0.2679</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6047</v>
+        <v>0.5714</v>
       </c>
     </row>
     <row r="3">
@@ -72414,25 +74897,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4167</v>
+        <v>0.4615</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.04</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.13</v>
+        <v>-4.93</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0833</v>
+        <v>0.0769</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1667</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="4">
@@ -72564,25 +75047,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4074</v>
+        <v>0.4194</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.45</v>
+        <v>-5.48</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9</v>
+        <v>7.07</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.95</v>
+        <v>-12.07</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1852</v>
+        <v>0.1935</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4815</v>
+        <v>0.4839</v>
       </c>
     </row>
     <row r="4">
@@ -72592,25 +75075,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3478</v>
+        <v>0.3636</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.87</v>
+        <v>-1.42</v>
       </c>
       <c r="E4" t="n">
-        <v>8.77</v>
+        <v>10.34</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.18</v>
+        <v>-11.16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1739</v>
+        <v>0.2121</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6522</v>
+        <v>0.5758</v>
       </c>
     </row>
     <row r="5">
@@ -72707,7 +75190,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-21 14:25:41</t>
+          <t>2026-09-22 14:25:26</t>
         </is>
       </c>
     </row>
@@ -72754,7 +75237,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>636</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7">
@@ -72764,7 +75247,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -72774,7 +75257,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$656</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$678</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ656"/>
+  <dimension ref="A1:AJ678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21014,11 +21014,11 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z203" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA203" t="n">
         <v>-3.05</v>
@@ -21029,6 +21029,15 @@
       <c r="AC203" t="n">
         <v>-6.73</v>
       </c>
+      <c r="AD203" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>-8.119999999999999</v>
+      </c>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -21037,7 +21046,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -21138,11 +21147,11 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z204" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA204" t="n">
         <v>2.61</v>
@@ -21153,6 +21162,15 @@
       <c r="AC204" t="n">
         <v>-9.77</v>
       </c>
+      <c r="AD204" t="n">
+        <v>-7.65</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>-11.73</v>
+      </c>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -21161,7 +21179,7 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -21262,11 +21280,11 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z205" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA205" t="n">
         <v>12.16</v>
@@ -21277,6 +21295,15 @@
       <c r="AC205" t="n">
         <v>1.35</v>
       </c>
+      <c r="AD205" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>-4.05</v>
+      </c>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
@@ -21285,7 +21312,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -21386,11 +21413,11 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z206" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA206" t="n">
         <v>-3.05</v>
@@ -21401,6 +21428,15 @@
       <c r="AC206" t="n">
         <v>-8.789999999999999</v>
       </c>
+      <c r="AD206" t="n">
+        <v>-10.13</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>-10.13</v>
+      </c>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
@@ -21409,7 +21445,7 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -21510,11 +21546,11 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z207" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA207" t="n">
         <v>4.02</v>
@@ -21525,6 +21561,15 @@
       <c r="AC207" t="n">
         <v>-3.3</v>
       </c>
+      <c r="AD207" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>-7.31</v>
+      </c>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -21533,7 +21578,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -21634,11 +21679,11 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z208" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA208" t="n">
         <v>0.58</v>
@@ -21649,6 +21694,15 @@
       <c r="AC208" t="n">
         <v>1.02</v>
       </c>
+      <c r="AD208" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>-6.25</v>
+      </c>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -21657,7 +21711,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -21758,11 +21812,11 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z209" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA209" t="n">
         <v>0.19</v>
@@ -21773,6 +21827,15 @@
       <c r="AC209" t="n">
         <v>-4.74</v>
       </c>
+      <c r="AD209" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>-9.960000000000001</v>
+      </c>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
@@ -21781,7 +21844,7 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -21882,11 +21945,11 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z210" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA210" t="n">
         <v>9.869999999999999</v>
@@ -21897,6 +21960,15 @@
       <c r="AC210" t="n">
         <v>18.4</v>
       </c>
+      <c r="AD210" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>-1.47</v>
+      </c>
       <c r="AG210" t="b">
         <v>1</v>
       </c>
@@ -21905,7 +21977,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -22006,11 +22078,11 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z211" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA211" t="n">
         <v>-16.12</v>
@@ -22021,6 +22093,15 @@
       <c r="AC211" t="n">
         <v>-17.16</v>
       </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>-24.74</v>
+      </c>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
@@ -22029,7 +22110,7 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -22130,11 +22211,11 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z212" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA212" t="n">
         <v>-3.86</v>
@@ -22145,6 +22226,15 @@
       <c r="AC212" t="n">
         <v>-6.92</v>
       </c>
+      <c r="AD212" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>-13.05</v>
+      </c>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -22153,7 +22243,7 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -22365,11 +22455,11 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z214" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA214" t="n">
         <v>6.06</v>
@@ -22380,6 +22470,15 @@
       <c r="AC214" t="n">
         <v>-15.53</v>
       </c>
+      <c r="AD214" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>-17.68</v>
+      </c>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -22388,7 +22487,7 @@
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -22489,11 +22588,11 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z215" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA215" t="n">
         <v>-17.67</v>
@@ -22504,6 +22603,15 @@
       <c r="AC215" t="n">
         <v>-23.97</v>
       </c>
+      <c r="AD215" t="n">
+        <v>-25.87</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>-29.02</v>
+      </c>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
@@ -22512,7 +22620,7 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -22613,11 +22721,11 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z216" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA216" t="n">
         <v>-7.55</v>
@@ -22628,6 +22736,15 @@
       <c r="AC216" t="n">
         <v>-9.85</v>
       </c>
+      <c r="AD216" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>-14</v>
+      </c>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -22636,7 +22753,7 @@
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -22737,11 +22854,11 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z217" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA217" t="n">
         <v>-61.53</v>
@@ -22752,6 +22869,15 @@
       <c r="AC217" t="n">
         <v>-68.09</v>
       </c>
+      <c r="AD217" t="n">
+        <v>-68.98</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>-57.63</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>-69.27</v>
+      </c>
       <c r="AG217" t="b">
         <v>0</v>
       </c>
@@ -22760,7 +22886,7 @@
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -22865,7 +22991,7 @@
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -22989,7 +23115,7 @@
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -23113,7 +23239,7 @@
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -23237,7 +23363,7 @@
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -23361,7 +23487,7 @@
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -23485,7 +23611,7 @@
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -23609,7 +23735,7 @@
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23733,7 +23859,7 @@
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23857,7 +23983,7 @@
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23981,7 +24107,7 @@
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -24105,7 +24231,7 @@
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -24229,7 +24355,7 @@
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -24353,7 +24479,7 @@
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -24477,7 +24603,7 @@
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -24712,7 +24838,7 @@
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -25058,7 +25184,7 @@
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -25182,7 +25308,7 @@
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -25306,7 +25432,7 @@
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -25430,7 +25556,7 @@
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -25554,7 +25680,7 @@
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -25678,7 +25804,7 @@
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25802,7 +25928,7 @@
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25926,7 +26052,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -26050,7 +26176,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -26174,7 +26300,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -26298,7 +26424,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -26422,7 +26548,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -26546,7 +26672,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26670,7 +26796,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26794,7 +26920,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -26918,7 +27044,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -27042,7 +27168,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -27166,7 +27292,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -27290,7 +27416,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -27414,7 +27540,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27760,7 +27886,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -28106,7 +28232,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -28230,7 +28356,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -28354,7 +28480,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -28478,7 +28604,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28713,7 +28839,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28837,7 +28963,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -28961,7 +29087,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -29085,7 +29211,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -29209,7 +29335,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -29333,7 +29459,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -29457,7 +29583,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29581,7 +29707,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -29705,7 +29831,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -29829,7 +29955,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -29953,7 +30079,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -30077,7 +30203,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -30201,7 +30327,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -30325,7 +30451,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -30449,7 +30575,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -30573,7 +30699,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -30697,7 +30823,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -30821,7 +30947,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -30945,7 +31071,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -31069,7 +31195,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -31193,7 +31319,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -31317,7 +31443,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -31441,7 +31567,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -31565,7 +31691,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -31689,7 +31815,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -31813,7 +31939,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -31937,7 +32063,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -32061,7 +32187,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -32518,7 +32644,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32642,7 +32768,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -32766,7 +32892,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -33001,7 +33127,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -33125,7 +33251,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -33249,7 +33375,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -33373,7 +33499,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -33497,7 +33623,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -33621,7 +33747,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -33745,7 +33871,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -33869,7 +33995,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -33993,7 +34119,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -34117,7 +34243,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -34241,7 +34367,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -34365,7 +34491,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -34489,7 +34615,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -34613,7 +34739,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -34737,7 +34863,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -34861,7 +34987,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -34985,7 +35111,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -35109,7 +35235,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -35233,7 +35359,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -35357,7 +35483,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -35481,7 +35607,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -35605,7 +35731,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -35729,7 +35855,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -35853,7 +35979,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -36199,7 +36325,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -36323,7 +36449,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -36447,7 +36573,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -36793,7 +36919,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -36917,13 +37043,16 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
       </c>
       <c r="AB333" t="n">
         <v>-6.59</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>-5.54</v>
       </c>
       <c r="AG333" t="b">
         <v>0</v>
@@ -37038,13 +37167,16 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
       </c>
       <c r="AB334" t="n">
         <v>-5.68</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>-4.21</v>
       </c>
       <c r="AG334" t="b">
         <v>0</v>
@@ -37159,13 +37291,16 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
       </c>
       <c r="AB335" t="n">
         <v>-9.619999999999999</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>-10.16</v>
       </c>
       <c r="AG335" t="b">
         <v>0</v>
@@ -37280,13 +37415,16 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="AB336" t="n">
         <v>-4.72</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>-4.99</v>
       </c>
       <c r="AG336" t="b">
         <v>0</v>
@@ -37401,13 +37539,16 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
       </c>
       <c r="AB337" t="n">
         <v>-12.06</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>-10</v>
       </c>
       <c r="AG337" t="b">
         <v>0</v>
@@ -37522,13 +37663,16 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
       </c>
       <c r="AB338" t="n">
         <v>-7.03</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>-5.15</v>
       </c>
       <c r="AG338" t="b">
         <v>0</v>
@@ -37643,13 +37787,16 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
       </c>
       <c r="AB339" t="n">
         <v>-3.18</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>0.97</v>
       </c>
       <c r="AG339" t="b">
         <v>0</v>
@@ -37764,13 +37911,16 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
       </c>
       <c r="AB340" t="n">
         <v>1.04</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>1.34</v>
       </c>
       <c r="AG340" t="b">
         <v>0</v>
@@ -37885,13 +38035,16 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
       </c>
       <c r="AB341" t="n">
         <v>-4.92</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>-0.58</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -38006,13 +38159,16 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
       </c>
       <c r="AB342" t="n">
         <v>2.68</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>1.34</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -38127,12 +38283,15 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
       </c>
       <c r="AB343" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AC343" t="n">
         <v>6.62</v>
       </c>
       <c r="AG343" t="b">
@@ -38248,13 +38407,16 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
       </c>
       <c r="AB344" t="n">
         <v>3.21</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>2.29</v>
       </c>
       <c r="AG344" t="b">
         <v>0</v>
@@ -38369,13 +38531,16 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
       </c>
       <c r="AB345" t="n">
         <v>10.28</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>10.85</v>
       </c>
       <c r="AG345" t="b">
         <v>0</v>
@@ -38490,13 +38655,16 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
       </c>
       <c r="AB346" t="n">
         <v>14.69</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>12.59</v>
       </c>
       <c r="AG346" t="b">
         <v>1</v>
@@ -38611,13 +38779,16 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
       </c>
       <c r="AB347" t="n">
         <v>7.77</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>4.25</v>
       </c>
       <c r="AG347" t="b">
         <v>0</v>
@@ -38732,13 +38903,16 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
       </c>
       <c r="AB348" t="n">
         <v>7.47</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>6.88</v>
       </c>
       <c r="AG348" t="b">
         <v>0</v>
@@ -38853,13 +39027,16 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
       </c>
       <c r="AB349" t="n">
         <v>10.34</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>9.93</v>
       </c>
       <c r="AG349" t="b">
         <v>1</v>
@@ -38974,13 +39151,16 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="AB350" t="n">
         <v>-0.18</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>-2.66</v>
       </c>
       <c r="AG350" t="b">
         <v>0</v>
@@ -39095,13 +39275,16 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
       </c>
       <c r="AB351" t="n">
         <v>-20.29</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>-20.74</v>
       </c>
       <c r="AG351" t="b">
         <v>0</v>
@@ -39216,13 +39399,16 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
       </c>
       <c r="AB352" t="n">
         <v>-5.96</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>10.57</v>
       </c>
       <c r="AG352" t="b">
         <v>0</v>
@@ -39337,13 +39523,16 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
       </c>
       <c r="AB353" t="n">
         <v>0.4</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>8.17</v>
       </c>
       <c r="AG353" t="b">
         <v>0</v>
@@ -39902,13 +40091,16 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
       </c>
       <c r="AB358" t="n">
         <v>-20.36</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>-10.48</v>
       </c>
       <c r="AG358" t="b">
         <v>0</v>
@@ -40023,13 +40215,16 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
       </c>
       <c r="AB359" t="n">
         <v>-17.05</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>-19.35</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -40144,7 +40339,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -40265,7 +40460,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -40386,7 +40581,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -40507,7 +40702,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -40628,7 +40823,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -40749,7 +40944,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -40870,7 +41065,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -40991,7 +41186,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -41112,7 +41307,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -41233,7 +41428,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -41354,7 +41549,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -41475,7 +41670,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -41596,7 +41791,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -41717,7 +41912,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -41838,7 +42033,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -41959,7 +42154,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -42080,7 +42275,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -42201,7 +42396,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -42544,7 +42739,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -42665,7 +42860,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -42897,7 +43092,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -43018,7 +43213,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -43139,7 +43334,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -43260,7 +43455,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -43381,7 +43576,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -43502,7 +43697,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -43623,7 +43818,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -43741,7 +43936,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -43862,7 +44057,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -43983,7 +44178,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -44104,7 +44299,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -44225,7 +44420,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -44346,7 +44541,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -44467,7 +44662,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -44588,7 +44783,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -44709,7 +44904,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -44830,7 +45025,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -44951,7 +45146,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -45072,7 +45267,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -45193,7 +45388,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -45314,7 +45509,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -45435,7 +45630,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -45556,7 +45751,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -45677,7 +45872,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -45798,7 +45993,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -45919,7 +46114,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -46040,7 +46235,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -46494,7 +46689,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -46615,7 +46810,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -46736,7 +46931,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -46857,7 +47052,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -46978,7 +47173,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -47099,7 +47294,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -47220,7 +47415,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -47341,7 +47536,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -47462,7 +47657,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -47583,7 +47778,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -47704,7 +47899,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -47825,7 +48020,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -47946,7 +48141,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -48067,7 +48262,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -48188,7 +48383,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -48309,7 +48504,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -48430,7 +48625,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -48551,7 +48746,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -48672,7 +48867,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -48793,7 +48988,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -48914,7 +49109,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -49035,7 +49230,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -49378,7 +49573,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -49610,7 +49805,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -49731,7 +49926,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -49852,7 +50047,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -49973,7 +50168,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -50094,7 +50289,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -50215,7 +50410,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -50336,7 +50531,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -50457,7 +50652,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -50578,7 +50773,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -50699,7 +50894,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -50820,7 +51015,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -50941,7 +51136,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -51062,7 +51257,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -51183,7 +51378,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -51304,7 +51499,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -51425,7 +51620,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -51546,7 +51741,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -51667,7 +51862,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -51788,7 +51983,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -51909,7 +52104,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -52252,7 +52447,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -52373,7 +52568,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -52494,7 +52689,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -52612,7 +52807,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -52730,7 +52925,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -52848,7 +53043,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -52966,7 +53161,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -53084,7 +53279,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -53202,7 +53397,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -53320,7 +53515,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -53438,7 +53633,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -53556,7 +53751,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -53674,7 +53869,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -53792,7 +53987,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -53910,7 +54105,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -54028,7 +54223,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -54146,7 +54341,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -54264,7 +54459,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -54715,7 +54910,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -54833,7 +55028,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -54951,7 +55146,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -55069,7 +55264,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -55187,7 +55382,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -55305,7 +55500,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -55423,7 +55618,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -55541,7 +55736,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -55659,7 +55854,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -55777,7 +55972,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -55895,7 +56090,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -56013,7 +56208,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -56131,7 +56326,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -56249,7 +56444,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -56367,7 +56562,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -56485,7 +56680,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -56603,7 +56798,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -56721,7 +56916,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -56839,7 +57034,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -56957,7 +57152,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -57075,7 +57270,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -57193,7 +57388,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -57311,7 +57506,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -57429,7 +57624,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -57547,7 +57742,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -57665,7 +57860,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -57783,7 +57978,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -57901,7 +58096,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -58019,7 +58214,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -58137,7 +58332,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -58255,7 +58450,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -58373,7 +58568,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -58491,7 +58686,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -58609,7 +58804,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -58727,7 +58922,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -58845,7 +59040,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -58963,7 +59158,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -59081,7 +59276,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -59199,7 +59394,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -59317,7 +59512,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -59435,7 +59630,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
@@ -59553,7 +59748,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
@@ -59671,7 +59866,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
@@ -59789,7 +59984,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
@@ -59907,7 +60102,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
@@ -60025,7 +60220,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
@@ -60143,7 +60338,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
@@ -60261,7 +60456,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
@@ -60379,7 +60574,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
@@ -60497,7 +60692,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
@@ -60615,7 +60810,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
@@ -60733,7 +60928,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
@@ -60851,7 +61046,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
@@ -60969,7 +61164,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
@@ -61087,7 +61282,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
@@ -61205,7 +61400,10 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA537" t="n">
+        <v>12.68</v>
       </c>
       <c r="AG537" t="b">
         <v>0</v>
@@ -61320,7 +61518,10 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA538" t="n">
+        <v>0.29</v>
       </c>
       <c r="AG538" t="b">
         <v>0</v>
@@ -61435,7 +61636,10 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA539" t="n">
+        <v>-1.65</v>
       </c>
       <c r="AG539" t="b">
         <v>0</v>
@@ -61550,7 +61754,10 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA540" t="n">
+        <v>-3.27</v>
       </c>
       <c r="AG540" t="b">
         <v>0</v>
@@ -61665,7 +61872,10 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA541" t="n">
+        <v>0</v>
       </c>
       <c r="AG541" t="b">
         <v>0</v>
@@ -61780,7 +61990,10 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA542" t="n">
+        <v>-0.89</v>
       </c>
       <c r="AG542" t="b">
         <v>0</v>
@@ -61895,7 +62108,10 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA543" t="n">
+        <v>0.51</v>
       </c>
       <c r="AG543" t="b">
         <v>0</v>
@@ -62010,7 +62226,10 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA544" t="n">
+        <v>-1.83</v>
       </c>
       <c r="AG544" t="b">
         <v>0</v>
@@ -62125,7 +62344,10 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA545" t="n">
+        <v>0.29</v>
       </c>
       <c r="AG545" t="b">
         <v>0</v>
@@ -62240,7 +62462,10 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA546" t="n">
+        <v>-3.27</v>
       </c>
       <c r="AG546" t="b">
         <v>0</v>
@@ -62355,7 +62580,10 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA547" t="n">
+        <v>-0.55</v>
       </c>
       <c r="AG547" t="b">
         <v>0</v>
@@ -62470,7 +62698,10 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA548" t="n">
+        <v>-2.68</v>
       </c>
       <c r="AG548" t="b">
         <v>0</v>
@@ -62585,7 +62816,10 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA549" t="n">
+        <v>-0.38</v>
       </c>
       <c r="AG549" t="b">
         <v>0</v>
@@ -62700,7 +62934,10 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA550" t="n">
+        <v>-1.2</v>
       </c>
       <c r="AG550" t="b">
         <v>0</v>
@@ -63037,7 +63274,10 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA553" t="n">
+        <v>35.9</v>
       </c>
       <c r="AG553" t="b">
         <v>1</v>
@@ -63152,7 +63392,10 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA554" t="n">
+        <v>1.14</v>
       </c>
       <c r="AG554" t="b">
         <v>0</v>
@@ -63267,7 +63510,10 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA555" t="n">
+        <v>-2.19</v>
       </c>
       <c r="AG555" t="b">
         <v>0</v>
@@ -63493,7 +63739,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG557" t="b">
         <v>0</v>
@@ -63608,7 +63854,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG558" t="b">
         <v>0</v>
@@ -63723,7 +63969,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG559" t="b">
         <v>0</v>
@@ -63838,7 +64084,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG560" t="b">
         <v>0</v>
@@ -63953,7 +64199,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG561" t="b">
         <v>0</v>
@@ -64068,7 +64314,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG562" t="b">
         <v>1</v>
@@ -64180,7 +64426,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG563" t="b">
         <v>0</v>
@@ -64295,7 +64541,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG564" t="b">
         <v>0</v>
@@ -64410,7 +64656,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG565" t="b">
         <v>0</v>
@@ -64525,7 +64771,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG566" t="b">
         <v>0</v>
@@ -64640,7 +64886,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG567" t="b">
         <v>0</v>
@@ -64755,7 +65001,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG568" t="b">
         <v>0</v>
@@ -64870,7 +65116,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG569" t="b">
         <v>0</v>
@@ -64985,7 +65231,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG570" t="b">
         <v>0</v>
@@ -65100,7 +65346,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG571" t="b">
         <v>0</v>
@@ -65215,7 +65461,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG572" t="b">
         <v>0</v>
@@ -65330,7 +65576,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG573" t="b">
         <v>0</v>
@@ -65445,7 +65691,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG574" t="b">
         <v>0</v>
@@ -65560,7 +65806,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG575" t="b">
         <v>0</v>
@@ -65675,7 +65921,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG576" t="b">
         <v>0</v>
@@ -66123,7 +66369,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG580" t="b">
         <v>1</v>
@@ -66238,7 +66484,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG581" t="b">
         <v>0</v>
@@ -66353,7 +66599,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG582" t="b">
         <v>0</v>
@@ -66468,7 +66714,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG583" t="b">
         <v>0</v>
@@ -66694,7 +66940,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG585" t="b">
         <v>0</v>
@@ -66809,7 +67055,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG586" t="b">
         <v>0</v>
@@ -66924,7 +67170,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG587" t="b">
         <v>0</v>
@@ -67039,7 +67285,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG588" t="b">
         <v>0</v>
@@ -67154,7 +67400,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG589" t="b">
         <v>0</v>
@@ -67269,7 +67515,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG590" t="b">
         <v>1</v>
@@ -67384,7 +67630,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG591" t="b">
         <v>0</v>
@@ -67499,7 +67745,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG592" t="b">
         <v>0</v>
@@ -67614,7 +67860,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG593" t="b">
         <v>0</v>
@@ -67726,7 +67972,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG594" t="b">
         <v>0</v>
@@ -67841,7 +68087,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG595" t="b">
         <v>0</v>
@@ -67956,7 +68202,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -68071,7 +68317,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -68186,7 +68432,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -68301,7 +68547,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -68416,7 +68662,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG600" t="b">
         <v>0</v>
@@ -68531,7 +68777,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG601" t="b">
         <v>0</v>
@@ -68646,7 +68892,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG602" t="b">
         <v>0</v>
@@ -68761,7 +69007,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG603" t="b">
         <v>0</v>
@@ -68876,7 +69122,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG604" t="b">
         <v>0</v>
@@ -68991,7 +69237,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG605" t="b">
         <v>0</v>
@@ -69103,7 +69349,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG606" t="b">
         <v>0</v>
@@ -69662,7 +69908,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG611" t="b">
         <v>0</v>
@@ -69774,7 +70020,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG612" t="b">
         <v>0</v>
@@ -70000,7 +70246,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG614" t="b">
         <v>0</v>
@@ -70115,7 +70361,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG615" t="b">
         <v>0</v>
@@ -70230,7 +70476,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG616" t="b">
         <v>0</v>
@@ -70345,7 +70591,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG617" t="b">
         <v>0</v>
@@ -70460,7 +70706,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG618" t="b">
         <v>0</v>
@@ -70575,7 +70821,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG619" t="b">
         <v>0</v>
@@ -70690,7 +70936,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG620" t="b">
         <v>0</v>
@@ -70802,7 +71048,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG621" t="b">
         <v>0</v>
@@ -70917,7 +71163,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG622" t="b">
         <v>0</v>
@@ -71032,7 +71278,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG623" t="b">
         <v>0</v>
@@ -71147,7 +71393,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG624" t="b">
         <v>0</v>
@@ -71262,7 +71508,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG625" t="b">
         <v>0</v>
@@ -71377,7 +71623,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG626" t="b">
         <v>0</v>
@@ -71492,7 +71738,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG627" t="b">
         <v>0</v>
@@ -71607,7 +71853,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG628" t="b">
         <v>0</v>
@@ -71719,7 +71965,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG629" t="b">
         <v>0</v>
@@ -72167,7 +72413,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG633" t="b">
         <v>0</v>
@@ -72282,7 +72528,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG634" t="b">
         <v>0</v>
@@ -72508,7 +72754,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG636" t="b">
         <v>0</v>
@@ -72734,7 +72980,7 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG638" t="b">
         <v>0</v>
@@ -72849,7 +73095,7 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG639" t="b">
         <v>0</v>
@@ -72964,7 +73210,7 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG640" t="b">
         <v>0</v>
@@ -73079,7 +73325,7 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG641" t="b">
         <v>0</v>
@@ -73191,7 +73437,7 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG642" t="b">
         <v>0</v>
@@ -73306,7 +73552,7 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG643" t="b">
         <v>0</v>
@@ -73421,7 +73667,7 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG644" t="b">
         <v>0</v>
@@ -73536,7 +73782,7 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG645" t="b">
         <v>0</v>
@@ -73651,7 +73897,7 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG646" t="b">
         <v>0</v>
@@ -73766,7 +74012,7 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG647" t="b">
         <v>0</v>
@@ -73881,7 +74127,7 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG648" t="b">
         <v>0</v>
@@ -73996,7 +74242,7 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG649" t="b">
         <v>0</v>
@@ -74111,7 +74357,7 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG650" t="b">
         <v>0</v>
@@ -74559,7 +74805,7 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG654" t="b">
         <v>0</v>
@@ -74795,8 +75041,2523 @@
         </is>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="F657" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I657" t="b">
+        <v>0</v>
+      </c>
+      <c r="J657" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K657" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M657" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N657" t="n">
+        <v>10</v>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P657" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="Q657" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S657" t="n">
+        <v>3.6829</v>
+      </c>
+      <c r="T657" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V657" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="W657" t="n">
+        <v>38.107</v>
+      </c>
+      <c r="X657" t="n">
+        <v>34.626</v>
+      </c>
+      <c r="Y657" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z657" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG657" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH657" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI657" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="F658" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I658" t="b">
+        <v>0</v>
+      </c>
+      <c r="J658" t="n">
+        <v>10</v>
+      </c>
+      <c r="K658" t="n">
+        <v>176</v>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M658" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N658" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P658" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="Q658" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S658" t="n">
+        <v>7</v>
+      </c>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V658" t="n">
+        <v>160</v>
+      </c>
+      <c r="W658" t="n">
+        <v>192</v>
+      </c>
+      <c r="X658" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="Y658" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z658" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG658" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH658" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI658" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="F659" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I659" t="b">
+        <v>0</v>
+      </c>
+      <c r="J659" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="K659" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M659" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N659" t="n">
+        <v>10</v>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P659" t="n">
+        <v>250.25</v>
+      </c>
+      <c r="Q659" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S659" t="n">
+        <v>4.5578</v>
+      </c>
+      <c r="T659" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V659" t="n">
+        <v>256</v>
+      </c>
+      <c r="W659" t="n">
+        <v>276.4976</v>
+      </c>
+      <c r="X659" t="n">
+        <v>244.3321</v>
+      </c>
+      <c r="Y659" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z659" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG659" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH659" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI659" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="F660" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I660" t="b">
+        <v>0</v>
+      </c>
+      <c r="J660" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K660" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M660" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N660" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P660" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Q660" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S660" t="n">
+        <v>7</v>
+      </c>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V660" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="W660" t="n">
+        <v>106.7116</v>
+      </c>
+      <c r="X660" t="n">
+        <v>87.88500000000001</v>
+      </c>
+      <c r="Y660" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z660" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG660" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH660" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI660" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="F661" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I661" t="b">
+        <v>0</v>
+      </c>
+      <c r="J661" t="n">
+        <v>10</v>
+      </c>
+      <c r="K661" t="n">
+        <v>2557.5</v>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M661" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N661" t="n">
+        <v>3</v>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P661" t="n">
+        <v>2305</v>
+      </c>
+      <c r="Q661" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S661" t="n">
+        <v>7</v>
+      </c>
+      <c r="T661" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V661" t="n">
+        <v>2325</v>
+      </c>
+      <c r="W661" t="n">
+        <v>2790</v>
+      </c>
+      <c r="X661" t="n">
+        <v>2162.25</v>
+      </c>
+      <c r="Y661" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z661" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG661" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH661" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI661" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="F662" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I662" t="b">
+        <v>0</v>
+      </c>
+      <c r="J662" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K662" t="n">
+        <v>154</v>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M662" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N662" t="n">
+        <v>10</v>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P662" t="n">
+        <v>141.25</v>
+      </c>
+      <c r="Q662" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S662" t="n">
+        <v>5.2528</v>
+      </c>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V662" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="W662" t="n">
+        <v>157.2458</v>
+      </c>
+      <c r="X662" t="n">
+        <v>137.8571</v>
+      </c>
+      <c r="Y662" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z662" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG662" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH662" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI662" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="F663" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I663" t="b">
+        <v>0</v>
+      </c>
+      <c r="J663" t="n">
+        <v>10</v>
+      </c>
+      <c r="K663" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M663" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N663" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P663" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="Q663" t="n">
+        <v>64.39</v>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S663" t="n">
+        <v>7</v>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V663" t="n">
+        <v>304</v>
+      </c>
+      <c r="W663" t="n">
+        <v>364.8</v>
+      </c>
+      <c r="X663" t="n">
+        <v>282.72</v>
+      </c>
+      <c r="Y663" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z663" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG663" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH663" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI663" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>79.63</v>
+      </c>
+      <c r="F664" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I664" t="b">
+        <v>0</v>
+      </c>
+      <c r="J664" t="n">
+        <v>10</v>
+      </c>
+      <c r="K664" t="n">
+        <v>5703.5</v>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M664" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N664" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P664" t="n">
+        <v>4955</v>
+      </c>
+      <c r="Q664" t="n">
+        <v>69.64</v>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S664" t="n">
+        <v>7</v>
+      </c>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V664" t="n">
+        <v>5185</v>
+      </c>
+      <c r="W664" t="n">
+        <v>6222</v>
+      </c>
+      <c r="X664" t="n">
+        <v>4822.05</v>
+      </c>
+      <c r="Y664" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z664" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG664" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH664" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI664" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="F665" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I665" t="b">
+        <v>0</v>
+      </c>
+      <c r="J665" t="n">
+        <v>10</v>
+      </c>
+      <c r="K665" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M665" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N665" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q665" t="n">
+        <v>45</v>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S665" t="n">
+        <v>6.3529</v>
+      </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V665" t="n">
+        <v>153</v>
+      </c>
+      <c r="W665" t="n">
+        <v>176.0499</v>
+      </c>
+      <c r="X665" t="n">
+        <v>143.28</v>
+      </c>
+      <c r="Y665" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z665" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG665" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH665" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI665" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="F666" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I666" t="b">
+        <v>0</v>
+      </c>
+      <c r="J666" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K666" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M666" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N666" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P666" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="Q666" t="n">
+        <v>64.69</v>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S666" t="n">
+        <v>7</v>
+      </c>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V666" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="W666" t="n">
+        <v>47.22</v>
+      </c>
+      <c r="X666" t="n">
+        <v>36.5955</v>
+      </c>
+      <c r="Y666" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z666" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG666" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH666" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI666" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F667" t="n">
+        <v>75.12</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I667" t="b">
+        <v>0</v>
+      </c>
+      <c r="J667" t="n">
+        <v>10</v>
+      </c>
+      <c r="K667" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M667" t="n">
+        <v>3</v>
+      </c>
+      <c r="N667" t="n">
+        <v>10</v>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P667" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="Q667" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S667" t="n">
+        <v>3.3366</v>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V667" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="W667" t="n">
+        <v>54.6551</v>
+      </c>
+      <c r="X667" t="n">
+        <v>44.0785</v>
+      </c>
+      <c r="Y667" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z667" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG667" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH667" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI667" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="F668" t="n">
+        <v>78.31</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I668" t="b">
+        <v>0</v>
+      </c>
+      <c r="J668" t="n">
+        <v>10</v>
+      </c>
+      <c r="K668" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M668" t="n">
+        <v>4</v>
+      </c>
+      <c r="N668" t="n">
+        <v>10</v>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P668" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="Q668" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S668" t="n">
+        <v>2.5014</v>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V668" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="W668" t="n">
+        <v>78.1118</v>
+      </c>
+      <c r="X668" t="n">
+        <v>67.85899999999999</v>
+      </c>
+      <c r="Y668" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z668" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG668" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH668" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI668" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="F669" t="n">
+        <v>73.22</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I669" t="b">
+        <v>0</v>
+      </c>
+      <c r="J669" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K669" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M669" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N669" t="n">
+        <v>10</v>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P669" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="Q669" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S669" t="n">
+        <v>3.7433</v>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V669" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="W669" t="n">
+        <v>50.1929</v>
+      </c>
+      <c r="X669" t="n">
+        <v>41.3422</v>
+      </c>
+      <c r="Y669" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z669" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG669" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH669" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI669" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>77.95</v>
+      </c>
+      <c r="F670" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I670" t="b">
+        <v>0</v>
+      </c>
+      <c r="J670" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="K670" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M670" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N670" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P670" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="Q670" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S670" t="n">
+        <v>6.0216</v>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V670" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="W670" t="n">
+        <v>52.8834</v>
+      </c>
+      <c r="X670" t="n">
+        <v>42.3372</v>
+      </c>
+      <c r="Y670" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z670" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG670" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH670" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI670" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="F671" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I671" t="b">
+        <v>0</v>
+      </c>
+      <c r="J671" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K671" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M671" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N671" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P671" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="Q671" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S671" t="n">
+        <v>6.7422</v>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V671" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="W671" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="X671" t="n">
+        <v>37.1632</v>
+      </c>
+      <c r="Y671" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z671" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG671" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH671" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI671" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="F672" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I672" t="b">
+        <v>0</v>
+      </c>
+      <c r="J672" t="n">
+        <v>10</v>
+      </c>
+      <c r="K672" t="n">
+        <v>3817</v>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M672" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N672" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P672" t="n">
+        <v>3345</v>
+      </c>
+      <c r="Q672" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S672" t="n">
+        <v>7</v>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V672" t="n">
+        <v>3470</v>
+      </c>
+      <c r="W672" t="n">
+        <v>4164</v>
+      </c>
+      <c r="X672" t="n">
+        <v>3227.1</v>
+      </c>
+      <c r="Y672" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z672" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG672" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH672" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI672" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="F673" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I673" t="b">
+        <v>0</v>
+      </c>
+      <c r="J673" t="n">
+        <v>10</v>
+      </c>
+      <c r="K673" t="n">
+        <v>597.3</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M673" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N673" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P673" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="Q673" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S673" t="n">
+        <v>7</v>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V673" t="n">
+        <v>543</v>
+      </c>
+      <c r="W673" t="n">
+        <v>651.6</v>
+      </c>
+      <c r="X673" t="n">
+        <v>504.99</v>
+      </c>
+      <c r="Y673" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z673" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG673" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH673" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI673" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>73.14</v>
+      </c>
+      <c r="F674" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I674" t="b">
+        <v>0</v>
+      </c>
+      <c r="J674" t="n">
+        <v>10</v>
+      </c>
+      <c r="K674" t="n">
+        <v>546.7</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M674" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N674" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P674" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q674" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S674" t="n">
+        <v>7</v>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V674" t="n">
+        <v>497</v>
+      </c>
+      <c r="W674" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="X674" t="n">
+        <v>462.21</v>
+      </c>
+      <c r="Y674" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI674" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ674" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="F675" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I675" t="b">
+        <v>0</v>
+      </c>
+      <c r="J675" t="n">
+        <v>10</v>
+      </c>
+      <c r="K675" t="n">
+        <v>1754.5</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M675" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N675" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P675" t="n">
+        <v>1435</v>
+      </c>
+      <c r="Q675" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S675" t="n">
+        <v>7</v>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V675" t="n">
+        <v>1595</v>
+      </c>
+      <c r="W675" t="n">
+        <v>1914</v>
+      </c>
+      <c r="X675" t="n">
+        <v>1483.35</v>
+      </c>
+      <c r="Y675" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI675" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ675" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="F676" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I676" t="b">
+        <v>0</v>
+      </c>
+      <c r="J676" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="K676" t="n">
+        <v>9095</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M676" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N676" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P676" t="n">
+        <v>7135</v>
+      </c>
+      <c r="Q676" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S676" t="n">
+        <v>7</v>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V676" t="n">
+        <v>8385</v>
+      </c>
+      <c r="W676" t="n">
+        <v>10062</v>
+      </c>
+      <c r="X676" t="n">
+        <v>7798.05</v>
+      </c>
+      <c r="Y676" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z676" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG676" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH676" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI676" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="F677" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I677" t="b">
+        <v>0</v>
+      </c>
+      <c r="J677" t="n">
+        <v>10</v>
+      </c>
+      <c r="K677" t="n">
+        <v>3635.5</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M677" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N677" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P677" t="n">
+        <v>2940</v>
+      </c>
+      <c r="Q677" t="n">
+        <v>69.87</v>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S677" t="n">
+        <v>7</v>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V677" t="n">
+        <v>3305</v>
+      </c>
+      <c r="W677" t="n">
+        <v>3966</v>
+      </c>
+      <c r="X677" t="n">
+        <v>3073.65</v>
+      </c>
+      <c r="Y677" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI677" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ677" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="F678" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I678" t="b">
+        <v>0</v>
+      </c>
+      <c r="J678" t="n">
+        <v>10</v>
+      </c>
+      <c r="K678" t="n">
+        <v>489.5</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M678" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N678" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P678" t="n">
+        <v>435.5</v>
+      </c>
+      <c r="Q678" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S678" t="n">
+        <v>7</v>
+      </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V678" t="n">
+        <v>445</v>
+      </c>
+      <c r="W678" t="n">
+        <v>534</v>
+      </c>
+      <c r="X678" t="n">
+        <v>413.85</v>
+      </c>
+      <c r="Y678" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z678" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG678" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH678" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI678" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ656"/>
+  <autoFilter ref="A1:AJ678"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -74869,25 +77630,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3929</v>
+        <v>0.3714</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.17</v>
+        <v>-4.12</v>
       </c>
       <c r="E2" t="n">
-        <v>11.15</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.48</v>
+        <v>-13.22</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2679</v>
+        <v>0.2286</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5714</v>
+        <v>0.6143</v>
       </c>
     </row>
     <row r="3">
@@ -75047,25 +77808,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4194</v>
+        <v>0.3611</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.48</v>
+        <v>-7.02</v>
       </c>
       <c r="E3" t="n">
-        <v>7.07</v>
+        <v>5.16</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.07</v>
+        <v>-13.51</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1935</v>
+        <v>0.1667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4839</v>
+        <v>0.5556</v>
       </c>
     </row>
     <row r="4">
@@ -75075,25 +77836,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3636</v>
+        <v>0.381</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.42</v>
+        <v>-1.78</v>
       </c>
       <c r="E4" t="n">
-        <v>10.34</v>
+        <v>9.93</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.16</v>
+        <v>-11.49</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2121</v>
+        <v>0.1905</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5758</v>
+        <v>0.5952</v>
       </c>
     </row>
     <row r="5">
@@ -75190,7 +77951,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22 14:25:26</t>
+          <t>2026-09-23 14:25:14</t>
         </is>
       </c>
     </row>
@@ -75237,7 +77998,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>655</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7">
@@ -75247,7 +78008,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
@@ -75257,7 +78018,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$678</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$697</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ678"/>
+  <dimension ref="A1:AJ697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22987,11 +22987,11 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z218" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA218" t="n">
         <v>4.12</v>
@@ -23002,6 +23002,15 @@
       <c r="AC218" t="n">
         <v>2.38</v>
       </c>
+      <c r="AD218" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>-3.01</v>
+      </c>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
@@ -23010,7 +23019,7 @@
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -23111,11 +23120,11 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z219" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA219" t="n">
         <v>-3.27</v>
@@ -23126,6 +23135,15 @@
       <c r="AC219" t="n">
         <v>-3.41</v>
       </c>
+      <c r="AD219" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>-7.9</v>
+      </c>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -23134,7 +23152,7 @@
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -23235,11 +23253,11 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z220" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA220" t="n">
         <v>-6.23</v>
@@ -23250,6 +23268,15 @@
       <c r="AC220" t="n">
         <v>-8.44</v>
       </c>
+      <c r="AD220" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>-9.869999999999999</v>
+      </c>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23258,7 +23285,7 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -23359,11 +23386,11 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z221" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA221" t="n">
         <v>-3.34</v>
@@ -23374,6 +23401,15 @@
       <c r="AC221" t="n">
         <v>-4.5</v>
       </c>
+      <c r="AD221" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>-6.94</v>
+      </c>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -23382,7 +23418,7 @@
       </c>
       <c r="AI221" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -23483,11 +23519,11 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z222" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA222" t="n">
         <v>-0.66</v>
@@ -23498,6 +23534,15 @@
       <c r="AC222" t="n">
         <v>-7.64</v>
       </c>
+      <c r="AD222" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>-9.970000000000001</v>
+      </c>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
@@ -23506,7 +23551,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -23607,11 +23652,11 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z223" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA223" t="n">
         <v>-2.52</v>
@@ -23622,6 +23667,15 @@
       <c r="AC223" t="n">
         <v>-5.91</v>
       </c>
+      <c r="AD223" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>-8.68</v>
+      </c>
       <c r="AG223" t="b">
         <v>0</v>
       </c>
@@ -23630,7 +23684,7 @@
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -23731,11 +23785,11 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z224" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA224" t="n">
         <v>0.31</v>
@@ -23746,6 +23800,15 @@
       <c r="AC224" t="n">
         <v>-2.07</v>
       </c>
+      <c r="AD224" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>-7.02</v>
+      </c>
       <c r="AG224" t="b">
         <v>0</v>
       </c>
@@ -23754,7 +23817,7 @@
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -23855,11 +23918,11 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z225" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA225" t="n">
         <v>6.8</v>
@@ -23870,6 +23933,15 @@
       <c r="AC225" t="n">
         <v>-7.77</v>
       </c>
+      <c r="AD225" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>-7.77</v>
+      </c>
       <c r="AG225" t="b">
         <v>1</v>
       </c>
@@ -23878,7 +23950,7 @@
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -23979,11 +24051,11 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z226" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA226" t="n">
         <v>-0.15</v>
@@ -23994,6 +24066,15 @@
       <c r="AC226" t="n">
         <v>1.63</v>
       </c>
+      <c r="AD226" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>-4.44</v>
+      </c>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -24002,7 +24083,7 @@
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -24103,11 +24184,11 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z227" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA227" t="n">
         <v>-11.74</v>
@@ -24118,6 +24199,15 @@
       <c r="AC227" t="n">
         <v>-9.800000000000001</v>
       </c>
+      <c r="AD227" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>-13.96</v>
+      </c>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -24126,7 +24216,7 @@
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -24227,11 +24317,11 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z228" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA228" t="n">
         <v>3.89</v>
@@ -24242,6 +24332,15 @@
       <c r="AC228" t="n">
         <v>7.07</v>
       </c>
+      <c r="AD228" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>-0.71</v>
+      </c>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -24250,7 +24349,7 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -24351,11 +24450,11 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z229" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA229" t="n">
         <v>1.09</v>
@@ -24366,6 +24465,15 @@
       <c r="AC229" t="n">
         <v>1.64</v>
       </c>
+      <c r="AD229" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>-4.01</v>
+      </c>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -24374,7 +24482,7 @@
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -24475,11 +24583,11 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z230" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA230" t="n">
         <v>-1.2</v>
@@ -24490,6 +24598,15 @@
       <c r="AC230" t="n">
         <v>-4.64</v>
       </c>
+      <c r="AD230" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>-7.19</v>
+      </c>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
@@ -24498,7 +24615,7 @@
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -24599,11 +24716,11 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z231" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA231" t="n">
         <v>-21.78</v>
@@ -24614,6 +24731,15 @@
       <c r="AC231" t="n">
         <v>-20.34</v>
       </c>
+      <c r="AD231" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>-26.02</v>
+      </c>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -24622,7 +24748,7 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -24834,11 +24960,11 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z233" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA233" t="n">
         <v>-15.21</v>
@@ -24849,6 +24975,15 @@
       <c r="AC233" t="n">
         <v>-11.93</v>
       </c>
+      <c r="AD233" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>-16.19</v>
+      </c>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -24857,7 +24992,7 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -25180,11 +25315,11 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z236" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA236" t="n">
         <v>-2.03</v>
@@ -25195,6 +25330,15 @@
       <c r="AC236" t="n">
         <v>9.800000000000001</v>
       </c>
+      <c r="AD236" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>-4.05</v>
+      </c>
       <c r="AG236" t="b">
         <v>1</v>
       </c>
@@ -25203,7 +25347,7 @@
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -25304,11 +25448,11 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z237" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA237" t="n">
         <v>-3.3</v>
@@ -25319,6 +25463,15 @@
       <c r="AC237" t="n">
         <v>12.06</v>
       </c>
+      <c r="AD237" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>-6.73</v>
+      </c>
       <c r="AG237" t="b">
         <v>1</v>
       </c>
@@ -25327,7 +25480,7 @@
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -25428,11 +25581,11 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z238" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA238" t="n">
         <v>-2.37</v>
@@ -25443,6 +25596,15 @@
       <c r="AC238" t="n">
         <v>-9.470000000000001</v>
       </c>
+      <c r="AD238" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>-12.63</v>
+      </c>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
@@ -25451,7 +25613,7 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -25552,11 +25714,11 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z239" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA239" t="n">
         <v>-13.46</v>
@@ -25567,6 +25729,15 @@
       <c r="AC239" t="n">
         <v>-23.4</v>
       </c>
+      <c r="AD239" t="n">
+        <v>-25.96</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>-27.88</v>
+      </c>
       <c r="AG239" t="b">
         <v>0</v>
       </c>
@@ -25575,7 +25746,7 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -25676,11 +25847,11 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z240" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA240" t="n">
         <v>-6.37</v>
@@ -25691,6 +25862,15 @@
       <c r="AC240" t="n">
         <v>-3.3</v>
       </c>
+      <c r="AD240" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>-10.58</v>
+      </c>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
@@ -25699,7 +25879,7 @@
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -25800,11 +25980,11 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z241" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA241" t="n">
         <v>-63.68</v>
@@ -25815,6 +25995,15 @@
       <c r="AC241" t="n">
         <v>-68.67</v>
       </c>
+      <c r="AD241" t="n">
+        <v>-68.97</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>-57.81</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>-69.55</v>
+      </c>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
@@ -25823,7 +26012,7 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -25924,11 +26113,11 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z242" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA242" t="n">
         <v>-4.29</v>
@@ -25939,6 +26128,15 @@
       <c r="AC242" t="n">
         <v>-14.29</v>
       </c>
+      <c r="AD242" t="n">
+        <v>-13.71</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>-18.76</v>
+      </c>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
@@ -25947,7 +26145,7 @@
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26250,7 @@
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -26176,7 +26374,7 @@
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -26300,7 +26498,7 @@
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -26424,7 +26622,7 @@
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -26548,7 +26746,7 @@
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -26672,7 +26870,7 @@
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26796,7 +26994,7 @@
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -26920,7 +27118,7 @@
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -27044,7 +27242,7 @@
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -27168,7 +27366,7 @@
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -27292,7 +27490,7 @@
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -27416,7 +27614,7 @@
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -27540,7 +27738,7 @@
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27886,7 +28084,7 @@
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -28232,7 +28430,7 @@
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -28356,7 +28554,7 @@
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -28480,7 +28678,7 @@
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -28604,7 +28802,7 @@
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28839,7 +29037,7 @@
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -28963,7 +29161,7 @@
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -29087,7 +29285,7 @@
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -29211,7 +29409,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -29335,7 +29533,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -29459,7 +29657,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -29583,7 +29781,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29707,7 +29905,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -29831,7 +30029,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -29955,7 +30153,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -30079,7 +30277,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -30203,7 +30401,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -30327,7 +30525,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -30451,7 +30649,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -30575,7 +30773,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -30699,7 +30897,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -30823,7 +31021,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -30947,7 +31145,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -31071,7 +31269,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -31195,7 +31393,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -31319,7 +31517,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -31443,7 +31641,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -31567,7 +31765,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -31691,7 +31889,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -31815,7 +32013,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -31939,7 +32137,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -32063,7 +32261,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -32187,7 +32385,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -32644,7 +32842,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32768,7 +32966,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -32892,7 +33090,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -33127,7 +33325,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -33251,7 +33449,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -33375,7 +33573,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -33499,7 +33697,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -33623,7 +33821,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -33747,7 +33945,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -33871,7 +34069,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -33995,7 +34193,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -34119,7 +34317,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -34243,7 +34441,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -34367,7 +34565,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -34491,7 +34689,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -34615,7 +34813,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -34739,7 +34937,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -34863,7 +35061,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -34987,7 +35185,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -35111,7 +35309,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -35235,7 +35433,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -35359,7 +35557,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -35483,7 +35681,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -35607,7 +35805,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -35731,7 +35929,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -35855,7 +36053,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -35979,7 +36177,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -36325,7 +36523,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -36449,7 +36647,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -36573,7 +36771,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -36919,7 +37117,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -37043,7 +37241,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -37167,7 +37365,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -37291,7 +37489,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -37415,7 +37613,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -37539,7 +37737,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -37663,7 +37861,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -37787,7 +37985,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -37911,7 +38109,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -38035,7 +38233,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -38159,7 +38357,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -38283,7 +38481,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -38407,7 +38605,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -38531,7 +38729,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -38655,7 +38853,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -38779,7 +38977,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -38903,7 +39101,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -39027,7 +39225,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -39151,7 +39349,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -39275,7 +39473,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -39399,7 +39597,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -39523,7 +39721,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -40091,7 +40289,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -40215,7 +40413,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -40339,13 +40537,16 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
       </c>
       <c r="AB360" t="n">
         <v>0.28</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>1.42</v>
       </c>
       <c r="AG360" t="b">
         <v>0</v>
@@ -40460,13 +40661,16 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
       </c>
       <c r="AB361" t="n">
         <v>-1.67</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>-2.44</v>
       </c>
       <c r="AG361" t="b">
         <v>0</v>
@@ -40581,13 +40785,16 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
       </c>
       <c r="AB362" t="n">
         <v>6.79</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>7.69</v>
       </c>
       <c r="AG362" t="b">
         <v>0</v>
@@ -40702,13 +40909,16 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
       </c>
       <c r="AB363" t="n">
         <v>-7.02</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>-4.01</v>
       </c>
       <c r="AG363" t="b">
         <v>0</v>
@@ -40823,13 +41033,16 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
       </c>
       <c r="AB364" t="n">
         <v>-2.37</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>-1.85</v>
       </c>
       <c r="AG364" t="b">
         <v>0</v>
@@ -40944,13 +41157,16 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
       </c>
       <c r="AB365" t="n">
         <v>2.69</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>1.04</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -41065,13 +41281,16 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
       </c>
       <c r="AB366" t="n">
         <v>3.69</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>21.77</v>
       </c>
       <c r="AG366" t="b">
         <v>1</v>
@@ -41186,13 +41405,16 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
       </c>
       <c r="AB367" t="n">
         <v>4.33</v>
+      </c>
+      <c r="AC367" t="n">
+        <v>0</v>
       </c>
       <c r="AG367" t="b">
         <v>0</v>
@@ -41307,13 +41529,16 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
       </c>
       <c r="AB368" t="n">
         <v>3.06</v>
+      </c>
+      <c r="AC368" t="n">
+        <v>2.04</v>
       </c>
       <c r="AG368" t="b">
         <v>0</v>
@@ -41428,13 +41653,16 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
       </c>
       <c r="AB369" t="n">
         <v>-0.44</v>
+      </c>
+      <c r="AC369" t="n">
+        <v>-1.78</v>
       </c>
       <c r="AG369" t="b">
         <v>0</v>
@@ -41549,13 +41777,16 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
       </c>
       <c r="AB370" t="n">
         <v>10.45</v>
+      </c>
+      <c r="AC370" t="n">
+        <v>8.5</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -41670,13 +41901,16 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
       </c>
       <c r="AB371" t="n">
         <v>9.49</v>
+      </c>
+      <c r="AC371" t="n">
+        <v>5.56</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -41791,13 +42025,16 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
       </c>
       <c r="AB372" t="n">
         <v>0.73</v>
+      </c>
+      <c r="AC372" t="n">
+        <v>1.02</v>
       </c>
       <c r="AG372" t="b">
         <v>0</v>
@@ -41912,13 +42149,16 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
       </c>
       <c r="AB373" t="n">
         <v>6.27</v>
+      </c>
+      <c r="AC373" t="n">
+        <v>2.53</v>
       </c>
       <c r="AG373" t="b">
         <v>0</v>
@@ -42033,13 +42273,16 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
       </c>
       <c r="AB374" t="n">
         <v>7.86</v>
+      </c>
+      <c r="AC374" t="n">
+        <v>5.99</v>
       </c>
       <c r="AG374" t="b">
         <v>0</v>
@@ -42154,13 +42397,16 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
       </c>
       <c r="AB375" t="n">
         <v>10.58</v>
+      </c>
+      <c r="AC375" t="n">
+        <v>7.19</v>
       </c>
       <c r="AG375" t="b">
         <v>0</v>
@@ -42275,13 +42521,16 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
       </c>
       <c r="AB376" t="n">
         <v>-15.8</v>
+      </c>
+      <c r="AC376" t="n">
+        <v>-12.66</v>
       </c>
       <c r="AG376" t="b">
         <v>0</v>
@@ -42396,13 +42645,16 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
       </c>
       <c r="AB377" t="n">
         <v>5.08</v>
+      </c>
+      <c r="AC377" t="n">
+        <v>3.81</v>
       </c>
       <c r="AG377" t="b">
         <v>0</v>
@@ -42739,13 +42991,16 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
       </c>
       <c r="AB380" t="n">
         <v>-18.64</v>
+      </c>
+      <c r="AC380" t="n">
+        <v>-6.91</v>
       </c>
       <c r="AG380" t="b">
         <v>0</v>
@@ -42860,13 +43115,16 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AB381" t="n">
         <v>3.18</v>
+      </c>
+      <c r="AC381" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -43092,13 +43350,16 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
       </c>
       <c r="AB383" t="n">
         <v>-13.74</v>
+      </c>
+      <c r="AC383" t="n">
+        <v>-14.55</v>
       </c>
       <c r="AG383" t="b">
         <v>0</v>
@@ -43213,7 +43474,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -43334,7 +43595,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -43455,7 +43716,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -43576,7 +43837,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -43697,7 +43958,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -43818,7 +44079,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -43936,7 +44197,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -44057,7 +44318,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -44178,7 +44439,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -44299,7 +44560,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -44420,7 +44681,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -44541,7 +44802,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -44662,7 +44923,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -44783,7 +45044,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -44904,7 +45165,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -45025,7 +45286,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -45146,7 +45407,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -45267,7 +45528,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -45388,7 +45649,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -45509,7 +45770,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -45630,7 +45891,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -45751,7 +46012,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -45872,7 +46133,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -45993,7 +46254,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -46114,7 +46375,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -46235,7 +46496,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -46689,7 +46950,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -46810,7 +47071,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -46931,7 +47192,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -47052,7 +47313,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -47173,7 +47434,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -47294,7 +47555,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -47415,7 +47676,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -47536,7 +47797,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -47657,7 +47918,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -47778,7 +48039,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -47899,7 +48160,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -48020,7 +48281,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -48141,7 +48402,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -48262,7 +48523,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -48383,7 +48644,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -48504,7 +48765,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -48625,7 +48886,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -48746,7 +49007,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -48867,7 +49128,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -48988,7 +49249,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -49109,7 +49370,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -49230,7 +49491,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -49573,7 +49834,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -49805,7 +50066,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -49926,7 +50187,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -50047,7 +50308,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -50168,7 +50429,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -50289,7 +50550,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -50410,7 +50671,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -50531,7 +50792,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -50652,7 +50913,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -50773,7 +51034,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -50894,7 +51155,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -51015,7 +51276,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -51136,7 +51397,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -51257,7 +51518,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -51378,7 +51639,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -51499,7 +51760,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -51620,7 +51881,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -51741,7 +52002,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -51862,7 +52123,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -51983,7 +52244,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -52104,7 +52365,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -52447,7 +52708,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -52568,7 +52829,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -52689,10 +52950,13 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>0.71</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -52807,10 +53071,13 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>-2.29</v>
       </c>
       <c r="AG464" t="b">
         <v>0</v>
@@ -52925,10 +53192,13 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>-2.46</v>
       </c>
       <c r="AG465" t="b">
         <v>0</v>
@@ -53043,10 +53313,13 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
+      </c>
+      <c r="AB466" t="n">
+        <v>-6.03</v>
       </c>
       <c r="AG466" t="b">
         <v>0</v>
@@ -53161,10 +53434,13 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>8.07</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -53279,10 +53555,13 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
+      </c>
+      <c r="AB468" t="n">
+        <v>-3.64</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
@@ -53397,10 +53676,13 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>9.619999999999999</v>
       </c>
       <c r="AG469" t="b">
         <v>0</v>
@@ -53515,10 +53797,13 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
+      </c>
+      <c r="AB470" t="n">
+        <v>11.97</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -53633,10 +53918,13 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
+      </c>
+      <c r="AB471" t="n">
+        <v>-0.28</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -53751,10 +54039,13 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>2.12</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -53869,10 +54160,13 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
+      </c>
+      <c r="AB473" t="n">
+        <v>4.7</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -53987,10 +54281,13 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>1.45</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -54105,10 +54402,13 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
+      </c>
+      <c r="AB475" t="n">
+        <v>3.95</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -54223,10 +54523,13 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
+      </c>
+      <c r="AB476" t="n">
+        <v>-11.86</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
@@ -54341,10 +54644,13 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
+      </c>
+      <c r="AB477" t="n">
+        <v>2.75</v>
       </c>
       <c r="AG477" t="b">
         <v>0</v>
@@ -54459,10 +54765,13 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
+      </c>
+      <c r="AB478" t="n">
+        <v>2.08</v>
       </c>
       <c r="AG478" t="b">
         <v>0</v>
@@ -54910,10 +55219,13 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
+      </c>
+      <c r="AB482" t="n">
+        <v>36.95</v>
       </c>
       <c r="AG482" t="b">
         <v>1</v>
@@ -55028,10 +55340,13 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
+      </c>
+      <c r="AB483" t="n">
+        <v>10.37</v>
       </c>
       <c r="AG483" t="b">
         <v>0</v>
@@ -55146,10 +55461,13 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
+      </c>
+      <c r="AB484" t="n">
+        <v>-1.49</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -55264,7 +55582,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -55382,7 +55700,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -55500,7 +55818,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -55618,7 +55936,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -55736,7 +56054,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -55854,7 +56172,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -55972,7 +56290,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -56090,7 +56408,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -56208,7 +56526,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -56326,7 +56644,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -56444,7 +56762,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -56562,7 +56880,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -56680,7 +56998,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -56798,7 +57116,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -56916,7 +57234,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -57034,7 +57352,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -57152,7 +57470,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -57270,7 +57588,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -57388,7 +57706,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -57506,7 +57824,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -57624,7 +57942,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -57742,7 +58060,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -57860,7 +58178,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -57978,7 +58296,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -58096,7 +58414,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -58214,7 +58532,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -58332,7 +58650,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -58450,7 +58768,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -58568,7 +58886,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -58686,7 +59004,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -58804,7 +59122,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -58922,7 +59240,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -59040,7 +59358,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -59158,7 +59476,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -59276,7 +59594,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -59394,7 +59712,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -59512,7 +59830,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -59630,7 +59948,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
@@ -59748,7 +60066,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
@@ -59866,7 +60184,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
@@ -59984,7 +60302,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
@@ -60102,7 +60420,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
@@ -60220,7 +60538,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
@@ -60338,7 +60656,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
@@ -60456,7 +60774,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
@@ -60574,7 +60892,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
@@ -60692,7 +61010,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
@@ -60810,7 +61128,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
@@ -60928,7 +61246,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
@@ -61046,7 +61364,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
@@ -61164,7 +61482,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
@@ -61282,7 +61600,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
@@ -61400,7 +61718,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
@@ -61518,7 +61836,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -61636,7 +61954,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
@@ -61754,7 +62072,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
@@ -61872,7 +62190,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
@@ -61990,7 +62308,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
@@ -62108,7 +62426,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
@@ -62226,7 +62544,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
@@ -62344,7 +62662,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
@@ -62462,7 +62780,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
@@ -62580,7 +62898,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
@@ -62698,7 +63016,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
@@ -62816,7 +63134,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
@@ -62934,7 +63252,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
@@ -63274,7 +63592,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
@@ -63392,7 +63710,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
@@ -63510,7 +63828,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
@@ -63739,7 +64057,10 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA557" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AG557" t="b">
         <v>0</v>
@@ -63854,7 +64175,10 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA558" t="n">
+        <v>0.85</v>
       </c>
       <c r="AG558" t="b">
         <v>0</v>
@@ -63969,13 +64293,16 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA559" t="n">
+        <v>-2.33</v>
       </c>
       <c r="AG559" t="b">
         <v>0</v>
       </c>
       <c r="AH559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI559" t="inlineStr">
         <is>
@@ -64084,7 +64411,10 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA560" t="n">
+        <v>4.41</v>
       </c>
       <c r="AG560" t="b">
         <v>0</v>
@@ -64199,7 +64529,10 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA561" t="n">
+        <v>-1.6</v>
       </c>
       <c r="AG561" t="b">
         <v>0</v>
@@ -64314,7 +64647,10 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA562" t="n">
+        <v>14</v>
       </c>
       <c r="AG562" t="b">
         <v>1</v>
@@ -64426,7 +64762,10 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA563" t="n">
+        <v>-4.15</v>
       </c>
       <c r="AG563" t="b">
         <v>0</v>
@@ -64541,7 +64880,10 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA564" t="n">
+        <v>-4.8</v>
       </c>
       <c r="AG564" t="b">
         <v>0</v>
@@ -64656,7 +64998,10 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA565" t="n">
+        <v>-4.49</v>
       </c>
       <c r="AG565" t="b">
         <v>0</v>
@@ -64771,7 +65116,10 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA566" t="n">
+        <v>-0.99</v>
       </c>
       <c r="AG566" t="b">
         <v>0</v>
@@ -64886,7 +65234,10 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA567" t="n">
+        <v>-1.34</v>
       </c>
       <c r="AG567" t="b">
         <v>0</v>
@@ -65001,7 +65352,10 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA568" t="n">
+        <v>-1.77</v>
       </c>
       <c r="AG568" t="b">
         <v>0</v>
@@ -65116,7 +65470,10 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA569" t="n">
+        <v>-3.59</v>
       </c>
       <c r="AG569" t="b">
         <v>0</v>
@@ -65231,7 +65588,10 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA570" t="n">
+        <v>0.29</v>
       </c>
       <c r="AG570" t="b">
         <v>0</v>
@@ -65346,7 +65706,10 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA571" t="n">
+        <v>-4.43</v>
       </c>
       <c r="AG571" t="b">
         <v>0</v>
@@ -65461,7 +65824,10 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA572" t="n">
+        <v>-3.52</v>
       </c>
       <c r="AG572" t="b">
         <v>0</v>
@@ -65576,7 +65942,10 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA573" t="n">
+        <v>-1.74</v>
       </c>
       <c r="AG573" t="b">
         <v>0</v>
@@ -65691,7 +66060,10 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA574" t="n">
+        <v>-3.79</v>
       </c>
       <c r="AG574" t="b">
         <v>0</v>
@@ -65806,7 +66178,10 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA575" t="n">
+        <v>-3.07</v>
       </c>
       <c r="AG575" t="b">
         <v>0</v>
@@ -65921,7 +66296,10 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA576" t="n">
+        <v>-1.21</v>
       </c>
       <c r="AG576" t="b">
         <v>0</v>
@@ -66369,7 +66747,10 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA580" t="n">
+        <v>31.15</v>
       </c>
       <c r="AG580" t="b">
         <v>1</v>
@@ -66484,7 +66865,10 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA581" t="n">
+        <v>2.49</v>
       </c>
       <c r="AG581" t="b">
         <v>0</v>
@@ -66599,7 +66983,10 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA582" t="n">
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AG582" t="b">
         <v>0</v>
@@ -66714,7 +67101,10 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA583" t="n">
+        <v>-3.99</v>
       </c>
       <c r="AG583" t="b">
         <v>0</v>
@@ -66940,7 +67330,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG585" t="b">
         <v>0</v>
@@ -67055,13 +67445,13 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG586" t="b">
         <v>0</v>
       </c>
       <c r="AH586" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI586" t="inlineStr">
         <is>
@@ -67170,7 +67560,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG587" t="b">
         <v>0</v>
@@ -67285,7 +67675,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG588" t="b">
         <v>0</v>
@@ -67400,7 +67790,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG589" t="b">
         <v>0</v>
@@ -67515,7 +67905,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG590" t="b">
         <v>1</v>
@@ -67630,7 +68020,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG591" t="b">
         <v>0</v>
@@ -67745,7 +68135,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG592" t="b">
         <v>0</v>
@@ -67860,7 +68250,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG593" t="b">
         <v>0</v>
@@ -67972,7 +68362,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG594" t="b">
         <v>0</v>
@@ -68087,7 +68477,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG595" t="b">
         <v>0</v>
@@ -68202,7 +68592,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -68317,7 +68707,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -68432,7 +68822,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -68547,7 +68937,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -68662,7 +69052,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG600" t="b">
         <v>0</v>
@@ -68777,7 +69167,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG601" t="b">
         <v>0</v>
@@ -68892,7 +69282,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG602" t="b">
         <v>0</v>
@@ -69007,13 +69397,13 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG603" t="b">
         <v>0</v>
       </c>
       <c r="AH603" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI603" t="inlineStr">
         <is>
@@ -69122,7 +69512,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG604" t="b">
         <v>0</v>
@@ -69237,7 +69627,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG605" t="b">
         <v>0</v>
@@ -69349,7 +69739,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG606" t="b">
         <v>0</v>
@@ -69908,7 +70298,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG611" t="b">
         <v>0</v>
@@ -70020,7 +70410,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG612" t="b">
         <v>0</v>
@@ -70246,7 +70636,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG614" t="b">
         <v>0</v>
@@ -70361,7 +70751,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG615" t="b">
         <v>0</v>
@@ -70476,7 +70866,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG616" t="b">
         <v>0</v>
@@ -70591,7 +70981,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG617" t="b">
         <v>0</v>
@@ -70706,7 +71096,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG618" t="b">
         <v>0</v>
@@ -70821,7 +71211,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG619" t="b">
         <v>0</v>
@@ -70936,7 +71326,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG620" t="b">
         <v>0</v>
@@ -71048,7 +71438,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG621" t="b">
         <v>0</v>
@@ -71163,7 +71553,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG622" t="b">
         <v>0</v>
@@ -71278,7 +71668,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG623" t="b">
         <v>0</v>
@@ -71393,7 +71783,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG624" t="b">
         <v>0</v>
@@ -71508,7 +71898,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG625" t="b">
         <v>0</v>
@@ -71623,7 +72013,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG626" t="b">
         <v>0</v>
@@ -71738,7 +72128,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG627" t="b">
         <v>0</v>
@@ -71853,7 +72243,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG628" t="b">
         <v>0</v>
@@ -71965,7 +72355,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG629" t="b">
         <v>0</v>
@@ -72413,7 +72803,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG633" t="b">
         <v>0</v>
@@ -72528,7 +72918,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG634" t="b">
         <v>0</v>
@@ -72754,7 +73144,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG636" t="b">
         <v>0</v>
@@ -72980,7 +73370,7 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG638" t="b">
         <v>0</v>
@@ -73095,7 +73485,7 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG639" t="b">
         <v>0</v>
@@ -73210,7 +73600,7 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG640" t="b">
         <v>0</v>
@@ -73325,7 +73715,7 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG641" t="b">
         <v>0</v>
@@ -73437,7 +73827,7 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG642" t="b">
         <v>0</v>
@@ -73552,7 +73942,7 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG643" t="b">
         <v>0</v>
@@ -73667,7 +74057,7 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG644" t="b">
         <v>0</v>
@@ -73782,7 +74172,7 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG645" t="b">
         <v>0</v>
@@ -73897,7 +74287,7 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG646" t="b">
         <v>0</v>
@@ -74012,7 +74402,7 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG647" t="b">
         <v>0</v>
@@ -74127,7 +74517,7 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG648" t="b">
         <v>0</v>
@@ -74242,7 +74632,7 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG649" t="b">
         <v>0</v>
@@ -74357,7 +74747,7 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG650" t="b">
         <v>0</v>
@@ -74805,7 +75195,7 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG654" t="b">
         <v>0</v>
@@ -75142,7 +75532,7 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG657" t="b">
         <v>0</v>
@@ -75257,7 +75647,7 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG658" t="b">
         <v>0</v>
@@ -75372,7 +75762,7 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG659" t="b">
         <v>0</v>
@@ -75487,7 +75877,7 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG660" t="b">
         <v>0</v>
@@ -75602,7 +75992,7 @@
         </is>
       </c>
       <c r="Z661" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG661" t="b">
         <v>0</v>
@@ -75717,7 +76107,7 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG662" t="b">
         <v>0</v>
@@ -75832,7 +76222,7 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG663" t="b">
         <v>0</v>
@@ -75947,7 +76337,7 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG664" t="b">
         <v>0</v>
@@ -76059,7 +76449,7 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG665" t="b">
         <v>0</v>
@@ -76174,7 +76564,7 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG666" t="b">
         <v>0</v>
@@ -76289,7 +76679,7 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG667" t="b">
         <v>0</v>
@@ -76404,7 +76794,7 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG668" t="b">
         <v>0</v>
@@ -76519,7 +76909,7 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG669" t="b">
         <v>0</v>
@@ -76634,7 +77024,7 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG670" t="b">
         <v>0</v>
@@ -76749,7 +77139,7 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG671" t="b">
         <v>0</v>
@@ -76864,7 +77254,7 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG672" t="b">
         <v>0</v>
@@ -76979,7 +77369,7 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG673" t="b">
         <v>0</v>
@@ -77316,7 +77706,7 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG676" t="b">
         <v>0</v>
@@ -77542,7 +77932,7 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG678" t="b">
         <v>0</v>
@@ -77553,11 +77943,2172 @@
       <c r="AI678" t="inlineStr">
         <is>
           <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>82.79000000000001</v>
+      </c>
+      <c r="F679" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I679" t="b">
+        <v>0</v>
+      </c>
+      <c r="J679" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K679" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M679" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N679" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P679" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Q679" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S679" t="n">
+        <v>7</v>
+      </c>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V679" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="W679" t="n">
+        <v>106.9181</v>
+      </c>
+      <c r="X679" t="n">
+        <v>87.88500000000001</v>
+      </c>
+      <c r="Y679" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z679" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG679" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH679" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI679" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>73.79000000000001</v>
+      </c>
+      <c r="F680" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I680" t="b">
+        <v>0</v>
+      </c>
+      <c r="J680" t="n">
+        <v>10</v>
+      </c>
+      <c r="K680" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M680" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N680" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P680" t="n">
+        <v>686.5</v>
+      </c>
+      <c r="Q680" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S680" t="n">
+        <v>7</v>
+      </c>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V680" t="n">
+        <v>722</v>
+      </c>
+      <c r="W680" t="n">
+        <v>852.3422</v>
+      </c>
+      <c r="X680" t="n">
+        <v>671.46</v>
+      </c>
+      <c r="Y680" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z680" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG680" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH680" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI680" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>78.48999999999999</v>
+      </c>
+      <c r="F681" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I681" t="b">
+        <v>0</v>
+      </c>
+      <c r="J681" t="n">
+        <v>10</v>
+      </c>
+      <c r="K681" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M681" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N681" t="n">
+        <v>3</v>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P681" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="Q681" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S681" t="n">
+        <v>7</v>
+      </c>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V681" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="W681" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="X681" t="n">
+        <v>31.806</v>
+      </c>
+      <c r="Y681" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z681" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG681" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH681" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI681" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="F682" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I682" t="b">
+        <v>0</v>
+      </c>
+      <c r="J682" t="n">
+        <v>10</v>
+      </c>
+      <c r="K682" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M682" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N682" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P682" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="Q682" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S682" t="n">
+        <v>7</v>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V682" t="n">
+        <v>311</v>
+      </c>
+      <c r="W682" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="X682" t="n">
+        <v>289.23</v>
+      </c>
+      <c r="Y682" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z682" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG682" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH682" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI682" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="F683" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I683" t="b">
+        <v>0</v>
+      </c>
+      <c r="J683" t="n">
+        <v>10</v>
+      </c>
+      <c r="K683" t="n">
+        <v>5813.5</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M683" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N683" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P683" t="n">
+        <v>4955</v>
+      </c>
+      <c r="Q683" t="n">
+        <v>73.94</v>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S683" t="n">
+        <v>7</v>
+      </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V683" t="n">
+        <v>5285</v>
+      </c>
+      <c r="W683" t="n">
+        <v>6342</v>
+      </c>
+      <c r="X683" t="n">
+        <v>4915.05</v>
+      </c>
+      <c r="Y683" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z683" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG683" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH683" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI683" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="F684" t="n">
+        <v>75.48</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I684" t="b">
+        <v>0</v>
+      </c>
+      <c r="J684" t="n">
+        <v>10</v>
+      </c>
+      <c r="K684" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M684" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N684" t="n">
+        <v>10</v>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P684" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="Q684" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S684" t="n">
+        <v>3.2275</v>
+      </c>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V684" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="W684" t="n">
+        <v>54.5734</v>
+      </c>
+      <c r="X684" t="n">
+        <v>44.1282</v>
+      </c>
+      <c r="Y684" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z684" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG684" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH684" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI684" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>永豐金</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="F685" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I685" t="b">
+        <v>0</v>
+      </c>
+      <c r="J685" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="K685" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M685" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N685" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P685" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="Q685" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S685" t="n">
+        <v>6.1196</v>
+      </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V685" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="W685" t="n">
+        <v>53.0743</v>
+      </c>
+      <c r="X685" t="n">
+        <v>42.387</v>
+      </c>
+      <c r="Y685" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z685" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG685" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH685" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI685" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="F686" t="n">
+        <v>54.02</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I686" t="b">
+        <v>0</v>
+      </c>
+      <c r="J686" t="n">
+        <v>10</v>
+      </c>
+      <c r="K686" t="n">
+        <v>3910.5</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M686" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N686" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P686" t="n">
+        <v>3350</v>
+      </c>
+      <c r="Q686" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S686" t="n">
+        <v>7</v>
+      </c>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V686" t="n">
+        <v>3555</v>
+      </c>
+      <c r="W686" t="n">
+        <v>4236.4363</v>
+      </c>
+      <c r="X686" t="n">
+        <v>3306.15</v>
+      </c>
+      <c r="Y686" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z686" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG686" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH686" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI686" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="F687" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I687" t="b">
+        <v>0</v>
+      </c>
+      <c r="J687" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="K687" t="n">
+        <v>224</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M687" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N687" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P687" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="Q687" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S687" t="n">
+        <v>7</v>
+      </c>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V687" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="W687" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="X687" t="n">
+        <v>192.045</v>
+      </c>
+      <c r="Y687" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z687" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG687" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH687" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI687" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>78</v>
+      </c>
+      <c r="F688" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I688" t="b">
+        <v>0</v>
+      </c>
+      <c r="J688" t="n">
+        <v>10</v>
+      </c>
+      <c r="K688" t="n">
+        <v>591.8</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M688" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N688" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P688" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="Q688" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S688" t="n">
+        <v>7</v>
+      </c>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V688" t="n">
+        <v>538</v>
+      </c>
+      <c r="W688" t="n">
+        <v>645.6</v>
+      </c>
+      <c r="X688" t="n">
+        <v>500.34</v>
+      </c>
+      <c r="Y688" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z688" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG688" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH688" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI688" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="F689" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I689" t="b">
+        <v>0</v>
+      </c>
+      <c r="J689" t="n">
+        <v>10</v>
+      </c>
+      <c r="K689" t="n">
+        <v>552.2</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M689" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N689" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P689" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q689" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S689" t="n">
+        <v>7</v>
+      </c>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V689" t="n">
+        <v>502</v>
+      </c>
+      <c r="W689" t="n">
+        <v>602.4</v>
+      </c>
+      <c r="X689" t="n">
+        <v>466.86</v>
+      </c>
+      <c r="Y689" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI689" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ689" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="F690" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I690" t="b">
+        <v>0</v>
+      </c>
+      <c r="J690" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K690" t="n">
+        <v>773</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M690" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N690" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P690" t="n">
+        <v>730.5</v>
+      </c>
+      <c r="Q690" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S690" t="n">
+        <v>7</v>
+      </c>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V690" t="n">
+        <v>761</v>
+      </c>
+      <c r="W690" t="n">
+        <v>855.6825</v>
+      </c>
+      <c r="X690" t="n">
+        <v>707.73</v>
+      </c>
+      <c r="Y690" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI690" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ690" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="F691" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I691" t="b">
+        <v>0</v>
+      </c>
+      <c r="J691" t="n">
+        <v>10</v>
+      </c>
+      <c r="K691" t="n">
+        <v>1881</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M691" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N691" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P691" t="n">
+        <v>1495</v>
+      </c>
+      <c r="Q691" t="n">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S691" t="n">
+        <v>7</v>
+      </c>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V691" t="n">
+        <v>1710</v>
+      </c>
+      <c r="W691" t="n">
+        <v>2052</v>
+      </c>
+      <c r="X691" t="n">
+        <v>1590.3</v>
+      </c>
+      <c r="Y691" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI691" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ691" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>81.56999999999999</v>
+      </c>
+      <c r="F692" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I692" t="b">
+        <v>0</v>
+      </c>
+      <c r="J692" t="n">
+        <v>10</v>
+      </c>
+      <c r="K692" t="n">
+        <v>9377.5</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M692" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N692" t="n">
+        <v>3</v>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P692" t="n">
+        <v>7197.5</v>
+      </c>
+      <c r="Q692" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S692" t="n">
+        <v>7</v>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V692" t="n">
+        <v>8525</v>
+      </c>
+      <c r="W692" t="n">
+        <v>10230</v>
+      </c>
+      <c r="X692" t="n">
+        <v>7928.25</v>
+      </c>
+      <c r="Y692" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z692" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG692" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH692" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI692" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>79.17</v>
+      </c>
+      <c r="F693" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I693" t="b">
+        <v>0</v>
+      </c>
+      <c r="J693" t="n">
+        <v>10</v>
+      </c>
+      <c r="K693" t="n">
+        <v>3553</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M693" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N693" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P693" t="n">
+        <v>2940</v>
+      </c>
+      <c r="Q693" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S693" t="n">
+        <v>7</v>
+      </c>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V693" t="n">
+        <v>3230</v>
+      </c>
+      <c r="W693" t="n">
+        <v>3876</v>
+      </c>
+      <c r="X693" t="n">
+        <v>3003.9</v>
+      </c>
+      <c r="Y693" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI693" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ693" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F694" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I694" t="b">
+        <v>0</v>
+      </c>
+      <c r="J694" t="n">
+        <v>10</v>
+      </c>
+      <c r="K694" t="n">
+        <v>497.75</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M694" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N694" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P694" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q694" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S694" t="n">
+        <v>7</v>
+      </c>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V694" t="n">
+        <v>452.5</v>
+      </c>
+      <c r="W694" t="n">
+        <v>543</v>
+      </c>
+      <c r="X694" t="n">
+        <v>420.825</v>
+      </c>
+      <c r="Y694" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z694" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG694" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH694" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI694" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>72.37</v>
+      </c>
+      <c r="F695" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I695" t="b">
+        <v>0</v>
+      </c>
+      <c r="J695" t="n">
+        <v>10</v>
+      </c>
+      <c r="K695" t="n">
+        <v>768.9</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M695" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N695" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P695" t="n">
+        <v>651.5</v>
+      </c>
+      <c r="Q695" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S695" t="n">
+        <v>7</v>
+      </c>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V695" t="n">
+        <v>699</v>
+      </c>
+      <c r="W695" t="n">
+        <v>838.8</v>
+      </c>
+      <c r="X695" t="n">
+        <v>650.0700000000001</v>
+      </c>
+      <c r="Y695" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z695" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG695" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH695" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI695" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>73</v>
+      </c>
+      <c r="F696" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I696" t="b">
+        <v>0</v>
+      </c>
+      <c r="J696" t="n">
+        <v>10</v>
+      </c>
+      <c r="K696" t="n">
+        <v>234.85</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M696" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N696" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P696" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q696" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S696" t="n">
+        <v>7</v>
+      </c>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V696" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="W696" t="n">
+        <v>256.2</v>
+      </c>
+      <c r="X696" t="n">
+        <v>198.555</v>
+      </c>
+      <c r="Y696" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI696" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ696" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>合晶</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="F697" t="n">
+        <v>54.48</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I697" t="b">
+        <v>0</v>
+      </c>
+      <c r="J697" t="n">
+        <v>10</v>
+      </c>
+      <c r="K697" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M697" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N697" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P697" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q697" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S697" t="n">
+        <v>7</v>
+      </c>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V697" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="W697" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="X697" t="n">
+        <v>112.065</v>
+      </c>
+      <c r="Y697" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI697" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ697" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ678"/>
+  <autoFilter ref="A1:AJ697"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -77630,25 +80181,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3714</v>
+        <v>0.3626</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.12</v>
+        <v>-4.01</v>
       </c>
       <c r="E2" t="n">
-        <v>9.529999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.22</v>
+        <v>-13.28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2286</v>
+        <v>0.2088</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6143</v>
+        <v>0.6264</v>
       </c>
     </row>
     <row r="3">
@@ -77658,25 +80209,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4615</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.25</v>
+        <v>0.19</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2</v>
+        <v>5.59</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.93</v>
+        <v>-4.63</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0769</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1538</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="4">
@@ -77808,25 +80359,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3611</v>
+        <v>0.3478</v>
       </c>
       <c r="D3" t="n">
-        <v>-7.02</v>
+        <v>-6.53</v>
       </c>
       <c r="E3" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>-13.51</v>
+        <v>-13.99</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1667</v>
+        <v>0.1522</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5556</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="4">
@@ -77836,25 +80387,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>0.381</v>
+        <v>0.3889</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.78</v>
+        <v>-1.82</v>
       </c>
       <c r="E4" t="n">
-        <v>9.93</v>
+        <v>9.58</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.49</v>
+        <v>-11.29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1905</v>
+        <v>0.1852</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5952</v>
+        <v>0.5926</v>
       </c>
     </row>
     <row r="5">
@@ -77951,7 +80502,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-23 14:25:14</t>
+          <t>2026-09-24 14:25:17</t>
         </is>
       </c>
     </row>
@@ -77998,7 +80549,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>677</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7">
@@ -78008,7 +80559,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
@@ -78018,7 +80569,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$697</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$713</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ697"/>
+  <dimension ref="A1:AJ713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26246,11 +26246,11 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z243" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA243" t="n">
         <v>5.26</v>
@@ -26261,6 +26261,15 @@
       <c r="AC243" t="n">
         <v>3.67</v>
       </c>
+      <c r="AD243" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>-2.39</v>
+      </c>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
@@ -26269,7 +26278,7 @@
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -26370,11 +26379,11 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z244" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA244" t="n">
         <v>2.27</v>
@@ -26385,6 +26394,15 @@
       <c r="AC244" t="n">
         <v>7.94</v>
       </c>
+      <c r="AD244" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>-1.13</v>
+      </c>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
@@ -26393,7 +26411,7 @@
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -26494,11 +26512,11 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z245" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA245" t="n">
         <v>-0.55</v>
@@ -26509,6 +26527,15 @@
       <c r="AC245" t="n">
         <v>-4.27</v>
       </c>
+      <c r="AD245" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>-6.89</v>
+      </c>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -26517,7 +26544,7 @@
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -26618,11 +26645,11 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z246" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA246" t="n">
         <v>-1.19</v>
@@ -26633,6 +26660,15 @@
       <c r="AC246" t="n">
         <v>-4.5</v>
       </c>
+      <c r="AD246" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>-8.869999999999999</v>
+      </c>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -26641,7 +26677,7 @@
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -26742,11 +26778,11 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z247" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA247" t="n">
         <v>-2.99</v>
@@ -26757,6 +26793,15 @@
       <c r="AC247" t="n">
         <v>-11.18</v>
       </c>
+      <c r="AD247" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>-14.65</v>
+      </c>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
@@ -26765,7 +26810,7 @@
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -26866,11 +26911,11 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z248" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA248" t="n">
         <v>3.76</v>
@@ -26881,6 +26926,15 @@
       <c r="AC248" t="n">
         <v>3.16</v>
       </c>
+      <c r="AD248" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>-1.95</v>
+      </c>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -26889,7 +26943,7 @@
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -26990,11 +27044,11 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z249" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA249" t="n">
         <v>6.28</v>
@@ -27005,6 +27059,15 @@
       <c r="AC249" t="n">
         <v>3.14</v>
       </c>
+      <c r="AD249" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>-3.59</v>
+      </c>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -27013,7 +27076,7 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -27114,11 +27177,11 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z250" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA250" t="n">
         <v>-8.15</v>
@@ -27129,6 +27192,15 @@
       <c r="AC250" t="n">
         <v>-2.78</v>
       </c>
+      <c r="AD250" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>-13.8</v>
+      </c>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -27137,7 +27209,7 @@
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -27238,11 +27310,11 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z251" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA251" t="n">
         <v>4.51</v>
@@ -27253,6 +27325,15 @@
       <c r="AC251" t="n">
         <v>4.51</v>
       </c>
+      <c r="AD251" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>-1.74</v>
+      </c>
       <c r="AG251" t="b">
         <v>0</v>
       </c>
@@ -27261,7 +27342,7 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -27362,11 +27443,11 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z252" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA252" t="n">
         <v>4.74</v>
@@ -27377,6 +27458,15 @@
       <c r="AC252" t="n">
         <v>-8.99</v>
       </c>
+      <c r="AD252" t="n">
+        <v>-14.79</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>-16.07</v>
+      </c>
       <c r="AG252" t="b">
         <v>0</v>
       </c>
@@ -27385,7 +27475,7 @@
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -27486,11 +27576,11 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z253" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA253" t="n">
         <v>6.25</v>
@@ -27501,6 +27591,15 @@
       <c r="AC253" t="n">
         <v>2.08</v>
       </c>
+      <c r="AD253" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>-7.74</v>
+      </c>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
@@ -27509,7 +27608,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -27610,11 +27709,11 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z254" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA254" t="n">
         <v>-0.55</v>
@@ -27625,15 +27724,24 @@
       <c r="AC254" t="n">
         <v>5.54</v>
       </c>
+      <c r="AD254" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>-8.59</v>
+      </c>
       <c r="AG254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH254" t="b">
         <v>1</v>
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -27734,11 +27842,11 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z255" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA255" t="n">
         <v>-18.74</v>
@@ -27749,6 +27857,15 @@
       <c r="AC255" t="n">
         <v>-11.62</v>
       </c>
+      <c r="AD255" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>-21.35</v>
+      </c>
       <c r="AG255" t="b">
         <v>0</v>
       </c>
@@ -27757,7 +27874,7 @@
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -28080,11 +28197,11 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z258" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA258" t="n">
         <v>-8.9</v>
@@ -28095,6 +28212,15 @@
       <c r="AC258" t="n">
         <v>-7.45</v>
       </c>
+      <c r="AD258" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>-14.79</v>
+      </c>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
@@ -28103,7 +28229,7 @@
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -28426,11 +28552,11 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z261" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA261" t="n">
         <v>-3.41</v>
@@ -28441,6 +28567,15 @@
       <c r="AC261" t="n">
         <v>18.87</v>
       </c>
+      <c r="AD261" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>-5.57</v>
+      </c>
       <c r="AG261" t="b">
         <v>1</v>
       </c>
@@ -28449,7 +28584,7 @@
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -28550,11 +28685,11 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z262" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA262" t="n">
         <v>-5.07</v>
@@ -28565,6 +28700,15 @@
       <c r="AC262" t="n">
         <v>-6.28</v>
       </c>
+      <c r="AD262" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>-11.35</v>
+      </c>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
@@ -28573,7 +28717,7 @@
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -28674,11 +28818,11 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z263" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA263" t="n">
         <v>3.81</v>
@@ -28689,6 +28833,15 @@
       <c r="AC263" t="n">
         <v>-12.92</v>
       </c>
+      <c r="AD263" t="n">
+        <v>-9.35</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>-19.8</v>
+      </c>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
@@ -28697,7 +28850,7 @@
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -28798,11 +28951,11 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z264" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA264" t="n">
         <v>-5.31</v>
@@ -28813,6 +28966,15 @@
       <c r="AC264" t="n">
         <v>2.74</v>
       </c>
+      <c r="AD264" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>-9.02</v>
+      </c>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -28821,7 +28983,7 @@
       </c>
       <c r="AI264" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29033,11 +29195,11 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z266" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA266" t="n">
         <v>-15.21</v>
@@ -29048,6 +29210,15 @@
       <c r="AC266" t="n">
         <v>-23.62</v>
       </c>
+      <c r="AD266" t="n">
+        <v>-22.65</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>-27.18</v>
+      </c>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -29056,7 +29227,7 @@
       </c>
       <c r="AI266" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29157,11 +29328,11 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z267" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA267" t="n">
         <v>-64.38</v>
@@ -29172,6 +29343,15 @@
       <c r="AC267" t="n">
         <v>-70.28</v>
       </c>
+      <c r="AD267" t="n">
+        <v>-70.83</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>-60.07</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>-71.18000000000001</v>
+      </c>
       <c r="AG267" t="b">
         <v>0</v>
       </c>
@@ -29180,7 +29360,7 @@
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29281,11 +29461,11 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z268" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA268" t="n">
         <v>-3.98</v>
@@ -29296,6 +29476,15 @@
       <c r="AC268" t="n">
         <v>-11.84</v>
       </c>
+      <c r="AD268" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>-17.18</v>
+      </c>
       <c r="AG268" t="b">
         <v>0</v>
       </c>
@@ -29304,7 +29493,7 @@
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29409,7 +29598,7 @@
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -29533,7 +29722,7 @@
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -29657,7 +29846,7 @@
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -29781,7 +29970,7 @@
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29905,7 +30094,7 @@
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -30029,7 +30218,7 @@
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -30153,7 +30342,7 @@
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -30277,7 +30466,7 @@
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -30401,7 +30590,7 @@
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -30525,7 +30714,7 @@
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -30649,7 +30838,7 @@
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -30773,7 +30962,7 @@
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -30897,7 +31086,7 @@
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -31021,7 +31210,7 @@
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -31145,7 +31334,7 @@
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -31269,7 +31458,7 @@
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -31393,7 +31582,7 @@
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -31517,7 +31706,7 @@
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -31641,7 +31830,7 @@
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -31765,7 +31954,7 @@
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -31889,7 +32078,7 @@
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -32013,7 +32202,7 @@
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -32137,7 +32326,7 @@
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -32261,7 +32450,7 @@
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -32385,7 +32574,7 @@
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -32842,7 +33031,7 @@
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -32966,7 +33155,7 @@
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -33090,7 +33279,7 @@
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -33325,7 +33514,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -33449,7 +33638,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -33573,7 +33762,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -33697,7 +33886,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -33821,7 +34010,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -33945,7 +34134,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -34069,7 +34258,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -34193,7 +34382,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -34317,7 +34506,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -34441,7 +34630,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -34565,7 +34754,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -34689,7 +34878,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -34813,7 +35002,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -34937,7 +35126,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -35061,7 +35250,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -35185,7 +35374,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -35309,7 +35498,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -35433,7 +35622,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -35557,7 +35746,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -35681,7 +35870,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -35805,7 +35994,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -35929,7 +36118,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -36053,7 +36242,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -36177,7 +36366,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -36523,7 +36712,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -36647,7 +36836,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -36771,7 +36960,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -37117,7 +37306,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -37241,7 +37430,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -37365,7 +37554,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -37489,7 +37678,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -37613,7 +37802,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -37737,7 +37926,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -37861,7 +38050,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -37985,7 +38174,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -38109,7 +38298,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -38233,7 +38422,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -38357,7 +38546,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -38481,7 +38670,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -38605,7 +38794,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -38729,7 +38918,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -38853,7 +39042,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -38977,7 +39166,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -39101,7 +39290,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -39225,7 +39414,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -39349,7 +39538,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -39473,7 +39662,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -39597,7 +39786,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -39721,7 +39910,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -40289,7 +40478,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -40413,7 +40602,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -40537,7 +40726,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -40661,7 +40850,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -40785,7 +40974,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -40909,7 +41098,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -41033,7 +41222,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -41157,7 +41346,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -41281,7 +41470,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -41405,7 +41594,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -41529,7 +41718,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -41653,7 +41842,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -41777,7 +41966,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -41901,7 +42090,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -42025,7 +42214,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -42149,7 +42338,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -42273,7 +42462,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -42397,7 +42586,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -42521,7 +42710,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -42645,7 +42834,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -42991,7 +43180,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -43115,7 +43304,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -43350,7 +43539,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -43474,13 +43663,16 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
       </c>
       <c r="AB384" t="n">
         <v>-1.52</v>
+      </c>
+      <c r="AC384" t="n">
+        <v>-2.12</v>
       </c>
       <c r="AG384" t="b">
         <v>0</v>
@@ -43595,13 +43787,16 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
       </c>
       <c r="AB385" t="n">
         <v>5.54</v>
+      </c>
+      <c r="AC385" t="n">
+        <v>9.529999999999999</v>
       </c>
       <c r="AG385" t="b">
         <v>0</v>
@@ -43716,13 +43911,16 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
       </c>
       <c r="AB386" t="n">
         <v>-3.74</v>
+      </c>
+      <c r="AC386" t="n">
+        <v>-5.12</v>
       </c>
       <c r="AG386" t="b">
         <v>0</v>
@@ -43837,13 +44035,16 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
       </c>
       <c r="AB387" t="n">
         <v>-3.35</v>
+      </c>
+      <c r="AC387" t="n">
+        <v>-7.77</v>
       </c>
       <c r="AG387" t="b">
         <v>0</v>
@@ -43958,13 +44159,16 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
       </c>
       <c r="AB388" t="n">
         <v>-8.44</v>
+      </c>
+      <c r="AC388" t="n">
+        <v>-8.77</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
@@ -44079,13 +44283,16 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
       </c>
       <c r="AB389" t="n">
         <v>-9.369999999999999</v>
+      </c>
+      <c r="AC389" t="n">
+        <v>-13.34</v>
       </c>
       <c r="AG389" t="b">
         <v>0</v>
@@ -44197,13 +44404,16 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
       </c>
       <c r="AB390" t="n">
         <v>-2.29</v>
+      </c>
+      <c r="AC390" t="n">
+        <v>-3.98</v>
       </c>
       <c r="AG390" t="b">
         <v>0</v>
@@ -44318,13 +44528,16 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
       </c>
       <c r="AB391" t="n">
         <v>-6.34</v>
+      </c>
+      <c r="AC391" t="n">
+        <v>-6.05</v>
       </c>
       <c r="AG391" t="b">
         <v>0</v>
@@ -44439,13 +44652,16 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
       </c>
       <c r="AB392" t="n">
         <v>-4.02</v>
+      </c>
+      <c r="AC392" t="n">
+        <v>-6.5</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -44560,13 +44776,16 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
       </c>
       <c r="AB393" t="n">
         <v>-0.58</v>
+      </c>
+      <c r="AC393" t="n">
+        <v>-2.46</v>
       </c>
       <c r="AG393" t="b">
         <v>0</v>
@@ -44681,13 +44900,16 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
       </c>
       <c r="AB394" t="n">
         <v>-4.07</v>
+      </c>
+      <c r="AC394" t="n">
+        <v>-5.43</v>
       </c>
       <c r="AG394" t="b">
         <v>0</v>
@@ -44802,13 +45024,16 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
       </c>
       <c r="AB395" t="n">
         <v>-2.95</v>
+      </c>
+      <c r="AC395" t="n">
+        <v>2.67</v>
       </c>
       <c r="AG395" t="b">
         <v>0</v>
@@ -44923,13 +45148,16 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
       </c>
       <c r="AB396" t="n">
         <v>6.68</v>
+      </c>
+      <c r="AC396" t="n">
+        <v>11.21</v>
       </c>
       <c r="AG396" t="b">
         <v>1</v>
@@ -45044,13 +45272,16 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
       </c>
       <c r="AB397" t="n">
         <v>4.81</v>
+      </c>
+      <c r="AC397" t="n">
+        <v>0.34</v>
       </c>
       <c r="AG397" t="b">
         <v>0</v>
@@ -45165,13 +45396,16 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
       </c>
       <c r="AB398" t="n">
         <v>4.78</v>
+      </c>
+      <c r="AC398" t="n">
+        <v>-3.48</v>
       </c>
       <c r="AG398" t="b">
         <v>0</v>
@@ -45286,13 +45520,16 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
       </c>
       <c r="AB399" t="n">
         <v>0</v>
+      </c>
+      <c r="AC399" t="n">
+        <v>0.66</v>
       </c>
       <c r="AG399" t="b">
         <v>0</v>
@@ -45407,13 +45644,16 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
       </c>
       <c r="AB400" t="n">
         <v>-3.91</v>
+      </c>
+      <c r="AC400" t="n">
+        <v>-3.04</v>
       </c>
       <c r="AG400" t="b">
         <v>0</v>
@@ -45528,13 +45768,16 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
       </c>
       <c r="AB401" t="n">
         <v>7.08</v>
+      </c>
+      <c r="AC401" t="n">
+        <v>6.13</v>
       </c>
       <c r="AG401" t="b">
         <v>0</v>
@@ -45649,13 +45892,16 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
       </c>
       <c r="AB402" t="n">
         <v>6.54</v>
+      </c>
+      <c r="AC402" t="n">
+        <v>3.1</v>
       </c>
       <c r="AG402" t="b">
         <v>0</v>
@@ -45770,13 +46016,16 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
       </c>
       <c r="AB403" t="n">
         <v>6.99</v>
+      </c>
+      <c r="AC403" t="n">
+        <v>0.72</v>
       </c>
       <c r="AG403" t="b">
         <v>0</v>
@@ -45891,13 +46140,16 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
       </c>
       <c r="AB404" t="n">
         <v>5.6</v>
+      </c>
+      <c r="AC404" t="n">
+        <v>2.45</v>
       </c>
       <c r="AG404" t="b">
         <v>0</v>
@@ -46012,13 +46264,16 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
       </c>
       <c r="AB405" t="n">
         <v>6.7</v>
+      </c>
+      <c r="AC405" t="n">
+        <v>3.49</v>
       </c>
       <c r="AG405" t="b">
         <v>0</v>
@@ -46133,13 +46388,16 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
       </c>
       <c r="AB406" t="n">
         <v>4.49</v>
+      </c>
+      <c r="AC406" t="n">
+        <v>2.33</v>
       </c>
       <c r="AG406" t="b">
         <v>0</v>
@@ -46254,13 +46512,16 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
       </c>
       <c r="AB407" t="n">
         <v>-13.11</v>
+      </c>
+      <c r="AC407" t="n">
+        <v>-18.65</v>
       </c>
       <c r="AG407" t="b">
         <v>0</v>
@@ -46375,13 +46636,16 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
       </c>
       <c r="AB408" t="n">
         <v>-3.92</v>
+      </c>
+      <c r="AC408" t="n">
+        <v>-4.76</v>
       </c>
       <c r="AG408" t="b">
         <v>0</v>
@@ -46496,13 +46760,16 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
       </c>
       <c r="AB409" t="n">
         <v>5.08</v>
+      </c>
+      <c r="AC409" t="n">
+        <v>2.54</v>
       </c>
       <c r="AG409" t="b">
         <v>0</v>
@@ -46950,13 +47217,16 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
       </c>
       <c r="AB413" t="n">
         <v>-16.11</v>
+      </c>
+      <c r="AC413" t="n">
+        <v>-12.68</v>
       </c>
       <c r="AG413" t="b">
         <v>0</v>
@@ -47071,13 +47341,16 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
       </c>
       <c r="AB414" t="n">
         <v>2.44</v>
+      </c>
+      <c r="AC414" t="n">
+        <v>-2.25</v>
       </c>
       <c r="AG414" t="b">
         <v>0</v>
@@ -47192,7 +47465,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -47313,7 +47586,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -47434,7 +47707,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -47555,7 +47828,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -47676,7 +47949,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -47797,7 +48070,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -47918,7 +48191,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -48039,7 +48312,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -48160,7 +48433,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -48281,7 +48554,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -48402,7 +48675,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -48523,7 +48796,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -48644,7 +48917,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -48765,7 +49038,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -48886,7 +49159,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -49007,7 +49280,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -49128,7 +49401,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -49249,7 +49522,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -49370,7 +49643,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -49491,7 +49764,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -49834,7 +50107,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -50066,7 +50339,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -50187,7 +50460,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -50308,7 +50581,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -50429,7 +50702,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -50550,7 +50823,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -50671,7 +50944,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -50792,7 +51065,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -50913,7 +51186,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -51034,7 +51307,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -51155,7 +51428,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -51276,7 +51549,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -51397,7 +51670,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -51518,7 +51791,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -51639,7 +51912,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -51760,7 +52033,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -51881,7 +52154,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -52002,7 +52275,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -52123,7 +52396,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -52244,7 +52517,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -52365,7 +52638,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -52708,7 +52981,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -52829,7 +53102,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -52950,7 +53223,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -53071,7 +53344,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -53192,7 +53465,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -53313,7 +53586,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -53434,7 +53707,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -53555,7 +53828,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -53676,7 +53949,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -53797,7 +54070,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -53918,7 +54191,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -54039,7 +54312,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -54160,7 +54433,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -54281,7 +54554,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -54402,7 +54675,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -54523,7 +54796,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -54644,7 +54917,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -54765,7 +55038,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -55219,7 +55492,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -55340,7 +55613,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -55461,7 +55734,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -55582,10 +55855,13 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
+      </c>
+      <c r="AB485" t="n">
+        <v>-0</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -55700,10 +55976,13 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
+      </c>
+      <c r="AB486" t="n">
+        <v>5.33</v>
       </c>
       <c r="AG486" t="b">
         <v>0</v>
@@ -55818,10 +56097,13 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
+      </c>
+      <c r="AB487" t="n">
+        <v>16.06</v>
       </c>
       <c r="AG487" t="b">
         <v>1</v>
@@ -55936,10 +56218,13 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
+      </c>
+      <c r="AB488" t="n">
+        <v>2.49</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -56054,10 +56339,13 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
+      </c>
+      <c r="AB489" t="n">
+        <v>7.09</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -56172,10 +56460,13 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
+      </c>
+      <c r="AB490" t="n">
+        <v>-2.22</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -56290,10 +56581,13 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
+      </c>
+      <c r="AB491" t="n">
+        <v>-2.07</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -56408,10 +56702,13 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
+      </c>
+      <c r="AB492" t="n">
+        <v>2.91</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -56526,10 +56823,13 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
+      </c>
+      <c r="AB493" t="n">
+        <v>-3.02</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -56644,10 +56944,13 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
+      </c>
+      <c r="AB494" t="n">
+        <v>-5.03</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -56762,10 +57065,13 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
+      </c>
+      <c r="AB495" t="n">
+        <v>-1.99</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -56880,10 +57186,13 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
+      </c>
+      <c r="AB496" t="n">
+        <v>0.46</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -56998,10 +57307,13 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
+      </c>
+      <c r="AB497" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -57116,10 +57428,13 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
+      </c>
+      <c r="AB498" t="n">
+        <v>-1.28</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -57234,10 +57549,13 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
+      </c>
+      <c r="AB499" t="n">
+        <v>2.56</v>
       </c>
       <c r="AG499" t="b">
         <v>0</v>
@@ -57352,10 +57670,13 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
+      </c>
+      <c r="AB500" t="n">
+        <v>0</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -57470,10 +57791,13 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
+      </c>
+      <c r="AB501" t="n">
+        <v>29.49</v>
       </c>
       <c r="AG501" t="b">
         <v>1</v>
@@ -57588,10 +57912,13 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
+      </c>
+      <c r="AB502" t="n">
+        <v>7.33</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -57706,10 +58033,13 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
+      </c>
+      <c r="AB503" t="n">
+        <v>-0.95</v>
       </c>
       <c r="AG503" t="b">
         <v>0</v>
@@ -57824,10 +58154,13 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
+      </c>
+      <c r="AB504" t="n">
+        <v>-4.23</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -57942,7 +58275,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -58060,7 +58393,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -58178,7 +58511,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -58296,7 +58629,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -58414,7 +58747,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -58532,7 +58865,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -58650,7 +58983,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -58768,7 +59101,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -58886,7 +59219,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -59004,7 +59337,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -59122,7 +59455,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -59240,7 +59573,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -59358,7 +59691,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -59476,7 +59809,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -59594,7 +59927,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -59712,7 +60045,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -59830,7 +60163,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -59948,7 +60281,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
@@ -60066,7 +60399,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
@@ -60184,7 +60517,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
@@ -60302,7 +60635,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
@@ -60420,7 +60753,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
@@ -60538,7 +60871,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
@@ -60656,7 +60989,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
@@ -60774,7 +61107,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
@@ -60892,7 +61225,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
@@ -61010,7 +61343,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
@@ -61128,7 +61461,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
@@ -61246,7 +61579,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
@@ -61364,7 +61697,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
@@ -61482,7 +61815,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
@@ -61600,7 +61933,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
@@ -61718,7 +62051,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
@@ -61836,7 +62169,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -61954,7 +62287,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
@@ -62072,7 +62405,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
@@ -62190,7 +62523,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
@@ -62308,7 +62641,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
@@ -62426,7 +62759,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
@@ -62544,7 +62877,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
@@ -62662,7 +62995,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
@@ -62780,7 +63113,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
@@ -62898,7 +63231,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
@@ -63016,7 +63349,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
@@ -63134,7 +63467,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
@@ -63252,7 +63585,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
@@ -63592,7 +63925,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
@@ -63710,7 +64043,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
@@ -63828,7 +64161,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
@@ -63837,7 +64170,7 @@
         <v>0</v>
       </c>
       <c r="AH555" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI555" t="inlineStr">
         <is>
@@ -64057,7 +64390,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA557" t="n">
         <v>-0.77</v>
@@ -64175,7 +64508,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA558" t="n">
         <v>0.85</v>
@@ -64293,7 +64626,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA559" t="n">
         <v>-2.33</v>
@@ -64411,7 +64744,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA560" t="n">
         <v>4.41</v>
@@ -64529,7 +64862,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA561" t="n">
         <v>-1.6</v>
@@ -64647,7 +64980,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA562" t="n">
         <v>14</v>
@@ -64762,7 +65095,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA563" t="n">
         <v>-4.15</v>
@@ -64771,7 +65104,7 @@
         <v>0</v>
       </c>
       <c r="AH563" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI563" t="inlineStr">
         <is>
@@ -64880,7 +65213,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA564" t="n">
         <v>-4.8</v>
@@ -64998,7 +65331,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA565" t="n">
         <v>-4.49</v>
@@ -65116,7 +65449,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA566" t="n">
         <v>-0.99</v>
@@ -65234,7 +65567,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA567" t="n">
         <v>-1.34</v>
@@ -65352,7 +65685,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA568" t="n">
         <v>-1.77</v>
@@ -65470,7 +65803,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA569" t="n">
         <v>-3.59</v>
@@ -65588,7 +65921,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA570" t="n">
         <v>0.29</v>
@@ -65706,7 +66039,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA571" t="n">
         <v>-4.43</v>
@@ -65715,7 +66048,7 @@
         <v>0</v>
       </c>
       <c r="AH571" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI571" t="inlineStr">
         <is>
@@ -65824,7 +66157,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA572" t="n">
         <v>-3.52</v>
@@ -65942,7 +66275,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA573" t="n">
         <v>-1.74</v>
@@ -66060,7 +66393,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA574" t="n">
         <v>-3.79</v>
@@ -66178,7 +66511,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA575" t="n">
         <v>-3.07</v>
@@ -66296,7 +66629,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA576" t="n">
         <v>-1.21</v>
@@ -66747,7 +67080,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA580" t="n">
         <v>31.15</v>
@@ -66865,7 +67198,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA581" t="n">
         <v>2.49</v>
@@ -66983,7 +67316,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA582" t="n">
         <v>-0.9399999999999999</v>
@@ -67101,7 +67434,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA583" t="n">
         <v>-3.99</v>
@@ -67110,7 +67443,7 @@
         <v>0</v>
       </c>
       <c r="AH583" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI583" t="inlineStr">
         <is>
@@ -67330,7 +67663,10 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA585" t="n">
+        <v>3.78</v>
       </c>
       <c r="AG585" t="b">
         <v>0</v>
@@ -67445,7 +67781,10 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA586" t="n">
+        <v>-0.88</v>
       </c>
       <c r="AG586" t="b">
         <v>0</v>
@@ -67560,7 +67899,10 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA587" t="n">
+        <v>-1.6</v>
       </c>
       <c r="AG587" t="b">
         <v>0</v>
@@ -67675,10 +68017,13 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA588" t="n">
+        <v>4.07</v>
       </c>
       <c r="AG588" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH588" t="b">
         <v>0</v>
@@ -67790,7 +68135,10 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA589" t="n">
+        <v>-1.9</v>
       </c>
       <c r="AG589" t="b">
         <v>0</v>
@@ -67905,7 +68253,10 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA590" t="n">
+        <v>15.49</v>
       </c>
       <c r="AG590" t="b">
         <v>1</v>
@@ -68020,7 +68371,10 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA591" t="n">
+        <v>4.25</v>
       </c>
       <c r="AG591" t="b">
         <v>0</v>
@@ -68135,7 +68489,10 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA592" t="n">
+        <v>-4.09</v>
       </c>
       <c r="AG592" t="b">
         <v>0</v>
@@ -68250,7 +68607,10 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA593" t="n">
+        <v>-5.77</v>
       </c>
       <c r="AG593" t="b">
         <v>0</v>
@@ -68362,7 +68722,10 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA594" t="n">
+        <v>0.66</v>
       </c>
       <c r="AG594" t="b">
         <v>0</v>
@@ -68477,7 +68840,10 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA595" t="n">
+        <v>0.9</v>
       </c>
       <c r="AG595" t="b">
         <v>0</v>
@@ -68592,7 +68958,10 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA596" t="n">
+        <v>-0.89</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -68707,7 +69076,10 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA597" t="n">
+        <v>-3.23</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -68822,7 +69194,10 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA598" t="n">
+        <v>-1.86</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -68937,13 +69312,16 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA599" t="n">
+        <v>-3.91</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
       </c>
       <c r="AH599" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI599" t="inlineStr">
         <is>
@@ -69052,7 +69430,10 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA600" t="n">
+        <v>-5.86</v>
       </c>
       <c r="AG600" t="b">
         <v>0</v>
@@ -69167,7 +69548,10 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA601" t="n">
+        <v>-2.98</v>
       </c>
       <c r="AG601" t="b">
         <v>0</v>
@@ -69282,7 +69666,10 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA602" t="n">
+        <v>-3.02</v>
       </c>
       <c r="AG602" t="b">
         <v>0</v>
@@ -69397,7 +69784,10 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA603" t="n">
+        <v>-2.06</v>
       </c>
       <c r="AG603" t="b">
         <v>0</v>
@@ -69512,7 +69902,10 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA604" t="n">
+        <v>-0.87</v>
       </c>
       <c r="AG604" t="b">
         <v>0</v>
@@ -69627,7 +70020,10 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA605" t="n">
+        <v>0.58</v>
       </c>
       <c r="AG605" t="b">
         <v>0</v>
@@ -69739,7 +70135,10 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA606" t="n">
+        <v>-2.42</v>
       </c>
       <c r="AG606" t="b">
         <v>0</v>
@@ -70298,7 +70697,10 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA611" t="n">
+        <v>1.45</v>
       </c>
       <c r="AG611" t="b">
         <v>0</v>
@@ -70410,7 +70812,10 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA612" t="n">
+        <v>-2.34</v>
       </c>
       <c r="AG612" t="b">
         <v>0</v>
@@ -70636,13 +71041,16 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA614" t="n">
+        <v>-4.58</v>
       </c>
       <c r="AG614" t="b">
         <v>0</v>
       </c>
       <c r="AH614" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI614" t="inlineStr">
         <is>
@@ -70751,7 +71159,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG615" t="b">
         <v>0</v>
@@ -70866,7 +71274,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG616" t="b">
         <v>0</v>
@@ -70981,13 +71389,13 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG617" t="b">
         <v>0</v>
       </c>
       <c r="AH617" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI617" t="inlineStr">
         <is>
@@ -71096,7 +71504,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG618" t="b">
         <v>0</v>
@@ -71211,7 +71619,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG619" t="b">
         <v>0</v>
@@ -71326,7 +71734,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG620" t="b">
         <v>0</v>
@@ -71438,7 +71846,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG621" t="b">
         <v>0</v>
@@ -71553,7 +71961,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG622" t="b">
         <v>0</v>
@@ -71668,7 +72076,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG623" t="b">
         <v>0</v>
@@ -71783,7 +72191,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG624" t="b">
         <v>0</v>
@@ -71898,7 +72306,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG625" t="b">
         <v>0</v>
@@ -72013,7 +72421,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG626" t="b">
         <v>0</v>
@@ -72128,7 +72536,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG627" t="b">
         <v>0</v>
@@ -72243,7 +72651,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG628" t="b">
         <v>0</v>
@@ -72355,7 +72763,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG629" t="b">
         <v>0</v>
@@ -72803,7 +73211,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG633" t="b">
         <v>0</v>
@@ -72918,7 +73326,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG634" t="b">
         <v>0</v>
@@ -73144,7 +73552,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG636" t="b">
         <v>0</v>
@@ -73370,7 +73778,7 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG638" t="b">
         <v>0</v>
@@ -73485,13 +73893,13 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG639" t="b">
         <v>0</v>
       </c>
       <c r="AH639" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI639" t="inlineStr">
         <is>
@@ -73600,7 +74008,7 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG640" t="b">
         <v>0</v>
@@ -73715,7 +74123,7 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG641" t="b">
         <v>0</v>
@@ -73827,7 +74235,7 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG642" t="b">
         <v>0</v>
@@ -73942,7 +74350,7 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG643" t="b">
         <v>0</v>
@@ -74057,7 +74465,7 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG644" t="b">
         <v>0</v>
@@ -74172,7 +74580,7 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG645" t="b">
         <v>0</v>
@@ -74287,7 +74695,7 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG646" t="b">
         <v>0</v>
@@ -74402,7 +74810,7 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG647" t="b">
         <v>0</v>
@@ -74517,7 +74925,7 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG648" t="b">
         <v>0</v>
@@ -74632,7 +75040,7 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG649" t="b">
         <v>0</v>
@@ -74747,7 +75155,7 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG650" t="b">
         <v>0</v>
@@ -75195,7 +75603,7 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG654" t="b">
         <v>0</v>
@@ -75532,7 +75940,7 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG657" t="b">
         <v>0</v>
@@ -75647,7 +76055,7 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG658" t="b">
         <v>0</v>
@@ -75762,7 +76170,7 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG659" t="b">
         <v>0</v>
@@ -75877,7 +76285,7 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG660" t="b">
         <v>0</v>
@@ -75992,13 +76400,13 @@
         </is>
       </c>
       <c r="Z661" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG661" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH661" t="b">
         <v>1</v>
-      </c>
-      <c r="AG661" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH661" t="b">
-        <v>0</v>
       </c>
       <c r="AI661" t="inlineStr">
         <is>
@@ -76107,7 +76515,7 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG662" t="b">
         <v>0</v>
@@ -76222,7 +76630,7 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG663" t="b">
         <v>0</v>
@@ -76337,7 +76745,7 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG664" t="b">
         <v>0</v>
@@ -76449,7 +76857,7 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG665" t="b">
         <v>0</v>
@@ -76564,7 +76972,7 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG666" t="b">
         <v>0</v>
@@ -76679,7 +77087,7 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG667" t="b">
         <v>0</v>
@@ -76794,7 +77202,7 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG668" t="b">
         <v>0</v>
@@ -76909,7 +77317,7 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG669" t="b">
         <v>0</v>
@@ -77024,7 +77432,7 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG670" t="b">
         <v>0</v>
@@ -77139,7 +77547,7 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG671" t="b">
         <v>0</v>
@@ -77254,7 +77662,7 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG672" t="b">
         <v>0</v>
@@ -77369,7 +77777,7 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG673" t="b">
         <v>0</v>
@@ -77706,7 +78114,7 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG676" t="b">
         <v>0</v>
@@ -77932,7 +78340,7 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG678" t="b">
         <v>0</v>
@@ -78047,7 +78455,7 @@
         </is>
       </c>
       <c r="Z679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG679" t="b">
         <v>0</v>
@@ -78162,7 +78570,7 @@
         </is>
       </c>
       <c r="Z680" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG680" t="b">
         <v>0</v>
@@ -78277,7 +78685,7 @@
         </is>
       </c>
       <c r="Z681" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG681" t="b">
         <v>0</v>
@@ -78392,7 +78800,7 @@
         </is>
       </c>
       <c r="Z682" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG682" t="b">
         <v>0</v>
@@ -78507,13 +78915,13 @@
         </is>
       </c>
       <c r="Z683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG683" t="b">
         <v>0</v>
       </c>
       <c r="AH683" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI683" t="inlineStr">
         <is>
@@ -78622,7 +79030,7 @@
         </is>
       </c>
       <c r="Z684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG684" t="b">
         <v>0</v>
@@ -78737,7 +79145,7 @@
         </is>
       </c>
       <c r="Z685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG685" t="b">
         <v>0</v>
@@ -78852,13 +79260,13 @@
         </is>
       </c>
       <c r="Z686" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG686" t="b">
         <v>0</v>
       </c>
       <c r="AH686" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI686" t="inlineStr">
         <is>
@@ -78967,7 +79375,7 @@
         </is>
       </c>
       <c r="Z687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG687" t="b">
         <v>0</v>
@@ -79082,7 +79490,7 @@
         </is>
       </c>
       <c r="Z688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG688" t="b">
         <v>0</v>
@@ -79530,13 +79938,13 @@
         </is>
       </c>
       <c r="Z692" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG692" t="b">
         <v>0</v>
       </c>
       <c r="AH692" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI692" t="inlineStr">
         <is>
@@ -79756,7 +80164,7 @@
         </is>
       </c>
       <c r="Z694" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG694" t="b">
         <v>0</v>
@@ -79871,7 +80279,7 @@
         </is>
       </c>
       <c r="Z695" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG695" t="b">
         <v>0</v>
@@ -80107,8 +80515,1824 @@
         </is>
       </c>
     </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>85</v>
+      </c>
+      <c r="F698" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I698" t="b">
+        <v>0</v>
+      </c>
+      <c r="J698" t="n">
+        <v>10</v>
+      </c>
+      <c r="K698" t="n">
+        <v>271.7</v>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M698" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N698" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P698" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q698" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S698" t="n">
+        <v>7</v>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V698" t="n">
+        <v>247</v>
+      </c>
+      <c r="W698" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="X698" t="n">
+        <v>229.71</v>
+      </c>
+      <c r="Y698" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z698" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG698" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH698" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI698" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="F699" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I699" t="b">
+        <v>0</v>
+      </c>
+      <c r="J699" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K699" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M699" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N699" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P699" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="Q699" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S699" t="n">
+        <v>7</v>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V699" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="W699" t="n">
+        <v>107.7249</v>
+      </c>
+      <c r="X699" t="n">
+        <v>87.88500000000001</v>
+      </c>
+      <c r="Y699" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z699" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG699" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH699" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI699" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="F700" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I700" t="b">
+        <v>0</v>
+      </c>
+      <c r="J700" t="n">
+        <v>10</v>
+      </c>
+      <c r="K700" t="n">
+        <v>803</v>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M700" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N700" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P700" t="n">
+        <v>700.5</v>
+      </c>
+      <c r="Q700" t="n">
+        <v>62.46</v>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S700" t="n">
+        <v>7</v>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V700" t="n">
+        <v>730</v>
+      </c>
+      <c r="W700" t="n">
+        <v>868.6992</v>
+      </c>
+      <c r="X700" t="n">
+        <v>678.9</v>
+      </c>
+      <c r="Y700" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z700" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG700" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH700" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI700" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="F701" t="n">
+        <v>36.24</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I701" t="b">
+        <v>0</v>
+      </c>
+      <c r="J701" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K701" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M701" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N701" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P701" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="Q701" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S701" t="n">
+        <v>7</v>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V701" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="W701" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="X701" t="n">
+        <v>32.5965</v>
+      </c>
+      <c r="Y701" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z701" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG701" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH701" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI701" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="F702" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I702" t="b">
+        <v>0</v>
+      </c>
+      <c r="J702" t="n">
+        <v>10</v>
+      </c>
+      <c r="K702" t="n">
+        <v>5401</v>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M702" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N702" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P702" t="n">
+        <v>4955</v>
+      </c>
+      <c r="Q702" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S702" t="n">
+        <v>7</v>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V702" t="n">
+        <v>4910</v>
+      </c>
+      <c r="W702" t="n">
+        <v>5892</v>
+      </c>
+      <c r="X702" t="n">
+        <v>4566.3</v>
+      </c>
+      <c r="Y702" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z702" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG702" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH702" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI702" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>73.58</v>
+      </c>
+      <c r="F703" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I703" t="b">
+        <v>0</v>
+      </c>
+      <c r="J703" t="n">
+        <v>10</v>
+      </c>
+      <c r="K703" t="n">
+        <v>231</v>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M703" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N703" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P703" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q703" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S703" t="n">
+        <v>7</v>
+      </c>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V703" t="n">
+        <v>210</v>
+      </c>
+      <c r="W703" t="n">
+        <v>252</v>
+      </c>
+      <c r="X703" t="n">
+        <v>195.3</v>
+      </c>
+      <c r="Y703" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z703" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG703" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH703" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI703" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="F704" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I704" t="b">
+        <v>0</v>
+      </c>
+      <c r="J704" t="n">
+        <v>10</v>
+      </c>
+      <c r="K704" t="n">
+        <v>542.3</v>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M704" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N704" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P704" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q704" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S704" t="n">
+        <v>7</v>
+      </c>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V704" t="n">
+        <v>493</v>
+      </c>
+      <c r="W704" t="n">
+        <v>591.6</v>
+      </c>
+      <c r="X704" t="n">
+        <v>458.49</v>
+      </c>
+      <c r="Y704" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI704" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ704" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>70.97</v>
+      </c>
+      <c r="F705" t="n">
+        <v>49</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I705" t="b">
+        <v>0</v>
+      </c>
+      <c r="J705" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K705" t="n">
+        <v>853</v>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M705" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N705" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P705" t="n">
+        <v>741.5</v>
+      </c>
+      <c r="Q705" t="n">
+        <v>70.03</v>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S705" t="n">
+        <v>7</v>
+      </c>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V705" t="n">
+        <v>779</v>
+      </c>
+      <c r="W705" t="n">
+        <v>903.5572</v>
+      </c>
+      <c r="X705" t="n">
+        <v>724.47</v>
+      </c>
+      <c r="Y705" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI705" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ705" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="F706" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I706" t="b">
+        <v>0</v>
+      </c>
+      <c r="J706" t="n">
+        <v>10</v>
+      </c>
+      <c r="K706" t="n">
+        <v>1793</v>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M706" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N706" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P706" t="n">
+        <v>1495</v>
+      </c>
+      <c r="Q706" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S706" t="n">
+        <v>7</v>
+      </c>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V706" t="n">
+        <v>1630</v>
+      </c>
+      <c r="W706" t="n">
+        <v>1956</v>
+      </c>
+      <c r="X706" t="n">
+        <v>1515.9</v>
+      </c>
+      <c r="Y706" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI706" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ706" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>73.70999999999999</v>
+      </c>
+      <c r="F707" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I707" t="b">
+        <v>0</v>
+      </c>
+      <c r="J707" t="n">
+        <v>10</v>
+      </c>
+      <c r="K707" t="n">
+        <v>8717.5</v>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M707" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N707" t="n">
+        <v>1</v>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P707" t="n">
+        <v>7197.5</v>
+      </c>
+      <c r="Q707" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S707" t="n">
+        <v>7</v>
+      </c>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V707" t="n">
+        <v>7925</v>
+      </c>
+      <c r="W707" t="n">
+        <v>9510</v>
+      </c>
+      <c r="X707" t="n">
+        <v>7370.25</v>
+      </c>
+      <c r="Y707" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z707" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG707" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH707" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI707" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>84.51000000000001</v>
+      </c>
+      <c r="F708" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I708" t="b">
+        <v>0</v>
+      </c>
+      <c r="J708" t="n">
+        <v>10</v>
+      </c>
+      <c r="K708" t="n">
+        <v>3635.5</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M708" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N708" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P708" t="n">
+        <v>2970</v>
+      </c>
+      <c r="Q708" t="n">
+        <v>71.23</v>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S708" t="n">
+        <v>7</v>
+      </c>
+      <c r="T708" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U708" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V708" t="n">
+        <v>3305</v>
+      </c>
+      <c r="W708" t="n">
+        <v>3966</v>
+      </c>
+      <c r="X708" t="n">
+        <v>3073.65</v>
+      </c>
+      <c r="Y708" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI708" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ708" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="F709" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I709" t="b">
+        <v>0</v>
+      </c>
+      <c r="J709" t="n">
+        <v>10</v>
+      </c>
+      <c r="K709" t="n">
+        <v>499.4</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M709" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N709" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P709" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q709" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S709" t="n">
+        <v>7</v>
+      </c>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U709" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V709" t="n">
+        <v>454</v>
+      </c>
+      <c r="W709" t="n">
+        <v>544.8</v>
+      </c>
+      <c r="X709" t="n">
+        <v>422.22</v>
+      </c>
+      <c r="Y709" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z709" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG709" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH709" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI709" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>70.98999999999999</v>
+      </c>
+      <c r="F710" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I710" t="b">
+        <v>0</v>
+      </c>
+      <c r="J710" t="n">
+        <v>10</v>
+      </c>
+      <c r="K710" t="n">
+        <v>755.7</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M710" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N710" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P710" t="n">
+        <v>651.5</v>
+      </c>
+      <c r="Q710" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S710" t="n">
+        <v>7</v>
+      </c>
+      <c r="T710" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U710" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V710" t="n">
+        <v>687</v>
+      </c>
+      <c r="W710" t="n">
+        <v>824.4</v>
+      </c>
+      <c r="X710" t="n">
+        <v>638.91</v>
+      </c>
+      <c r="Y710" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z710" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG710" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH710" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI710" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="F711" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I711" t="b">
+        <v>0</v>
+      </c>
+      <c r="J711" t="n">
+        <v>10</v>
+      </c>
+      <c r="K711" t="n">
+        <v>548.35</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M711" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N711" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P711" t="n">
+        <v>487.75</v>
+      </c>
+      <c r="Q711" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="S711" t="n">
+        <v>7</v>
+      </c>
+      <c r="T711" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U711" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V711" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="W711" t="n">
+        <v>578.7611000000001</v>
+      </c>
+      <c r="X711" t="n">
+        <v>463.605</v>
+      </c>
+      <c r="Y711" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z711" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG711" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH711" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI711" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="F712" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I712" t="b">
+        <v>0</v>
+      </c>
+      <c r="J712" t="n">
+        <v>10</v>
+      </c>
+      <c r="K712" t="n">
+        <v>196.35</v>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M712" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N712" t="n">
+        <v>3</v>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P712" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="Q712" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S712" t="n">
+        <v>7</v>
+      </c>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U712" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V712" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="W712" t="n">
+        <v>214.2</v>
+      </c>
+      <c r="X712" t="n">
+        <v>166.005</v>
+      </c>
+      <c r="Y712" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI712" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ712" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>合晶</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>72.84999999999999</v>
+      </c>
+      <c r="F713" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I713" t="b">
+        <v>0</v>
+      </c>
+      <c r="J713" t="n">
+        <v>10</v>
+      </c>
+      <c r="K713" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M713" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N713" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P713" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="Q713" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S713" t="n">
+        <v>7</v>
+      </c>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U713" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V713" t="n">
+        <v>121</v>
+      </c>
+      <c r="W713" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="X713" t="n">
+        <v>112.53</v>
+      </c>
+      <c r="Y713" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI713" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ713" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ697"/>
+  <autoFilter ref="A1:AJ713"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -80181,25 +82405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3626</v>
+        <v>0.3909</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.01</v>
+        <v>-3.82</v>
       </c>
       <c r="E2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.28</v>
+        <v>-13.43</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2088</v>
+        <v>0.1818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6264</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="3">
@@ -80209,25 +82433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>5.59</v>
+        <v>5.64</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.63</v>
+        <v>-5.07</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1429</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="4">
@@ -80331,25 +82555,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>9.390000000000001</v>
+        <v>-8.01</v>
       </c>
       <c r="E2" t="n">
-        <v>31.59</v>
+        <v>13.24</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.07</v>
+        <v>-17.25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="3">
@@ -80359,25 +82583,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3478</v>
+        <v>0.3774</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.53</v>
+        <v>-5.75</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="F3" t="n">
-        <v>-13.99</v>
+        <v>-13.46</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1522</v>
+        <v>0.1321</v>
       </c>
       <c r="H3" t="n">
-        <v>0.587</v>
+        <v>0.5849</v>
       </c>
     </row>
     <row r="4">
@@ -80387,25 +82611,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3889</v>
+        <v>0.4242</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.82</v>
+        <v>-1.06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.58</v>
+        <v>9.84</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.29</v>
+        <v>-11.17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1852</v>
+        <v>0.1667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5926</v>
+        <v>0.6212</v>
       </c>
     </row>
     <row r="5">
@@ -80502,7 +82726,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24 14:25:17</t>
+          <t>2026-09-29 14:24:44</t>
         </is>
       </c>
     </row>
@@ -80549,7 +82773,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>696</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -80559,7 +82783,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
@@ -80569,7 +82793,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$713</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$730</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ713"/>
+  <dimension ref="A1:AJ730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29594,11 +29594,11 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z269" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA269" t="n">
         <v>0.6</v>
@@ -29609,6 +29609,15 @@
       <c r="AC269" t="n">
         <v>-1.51</v>
       </c>
+      <c r="AD269" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>-7.55</v>
+      </c>
       <c r="AG269" t="b">
         <v>0</v>
       </c>
@@ -29617,7 +29626,7 @@
       </c>
       <c r="AI269" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29718,11 +29727,11 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z270" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA270" t="n">
         <v>1.37</v>
@@ -29733,6 +29742,15 @@
       <c r="AC270" t="n">
         <v>-1.51</v>
       </c>
+      <c r="AD270" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>-5.62</v>
+      </c>
       <c r="AG270" t="b">
         <v>0</v>
       </c>
@@ -29741,7 +29759,7 @@
       </c>
       <c r="AI270" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29842,11 +29860,11 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z271" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA271" t="n">
         <v>-3.32</v>
@@ -29857,6 +29875,15 @@
       <c r="AC271" t="n">
         <v>-5.36</v>
       </c>
+      <c r="AD271" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>-7.65</v>
+      </c>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
@@ -29865,7 +29892,7 @@
       </c>
       <c r="AI271" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -29966,11 +29993,11 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z272" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA272" t="n">
         <v>-1.97</v>
@@ -29981,6 +30008,15 @@
       <c r="AC272" t="n">
         <v>-5.41</v>
       </c>
+      <c r="AD272" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>-11.15</v>
+      </c>
       <c r="AG272" t="b">
         <v>0</v>
       </c>
@@ -29989,7 +30025,7 @@
       </c>
       <c r="AI272" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -30090,11 +30126,11 @@
       </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z273" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA273" t="n">
         <v>10.85</v>
@@ -30105,6 +30141,15 @@
       <c r="AC273" t="n">
         <v>21.71</v>
       </c>
+      <c r="AD273" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>-4.65</v>
+      </c>
       <c r="AG273" t="b">
         <v>1</v>
       </c>
@@ -30113,7 +30158,7 @@
       </c>
       <c r="AI273" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -30214,11 +30259,11 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z274" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA274" t="n">
         <v>-3.42</v>
@@ -30229,6 +30274,15 @@
       <c r="AC274" t="n">
         <v>-10.66</v>
       </c>
+      <c r="AD274" t="n">
+        <v>-8.85</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>-14.29</v>
+      </c>
       <c r="AG274" t="b">
         <v>0</v>
       </c>
@@ -30237,7 +30291,7 @@
       </c>
       <c r="AI274" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -30338,11 +30392,11 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z275" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA275" t="n">
         <v>-0.74</v>
@@ -30353,6 +30407,15 @@
       <c r="AC275" t="n">
         <v>-6.82</v>
       </c>
+      <c r="AD275" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>-10.66</v>
+      </c>
       <c r="AG275" t="b">
         <v>0</v>
       </c>
@@ -30361,7 +30424,7 @@
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -30462,11 +30525,11 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z276" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA276" t="n">
         <v>2.54</v>
@@ -30477,6 +30540,15 @@
       <c r="AC276" t="n">
         <v>2.06</v>
       </c>
+      <c r="AD276" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>-2.38</v>
+      </c>
       <c r="AG276" t="b">
         <v>0</v>
       </c>
@@ -30485,7 +30557,7 @@
       </c>
       <c r="AI276" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -30586,11 +30658,11 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z277" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -30601,6 +30673,15 @@
       <c r="AC277" t="n">
         <v>-5.31</v>
       </c>
+      <c r="AD277" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>-9.91</v>
+      </c>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
@@ -30609,7 +30690,7 @@
       </c>
       <c r="AI277" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -30710,11 +30791,11 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z278" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA278" t="n">
         <v>-3.86</v>
@@ -30725,6 +30806,15 @@
       <c r="AC278" t="n">
         <v>-10.3</v>
       </c>
+      <c r="AD278" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>-18.45</v>
+      </c>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
@@ -30733,7 +30823,7 @@
       </c>
       <c r="AI278" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -30834,11 +30924,11 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z279" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA279" t="n">
         <v>2.26</v>
@@ -30849,6 +30939,15 @@
       <c r="AC279" t="n">
         <v>-1.29</v>
       </c>
+      <c r="AD279" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>-6.77</v>
+      </c>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
@@ -30857,7 +30956,7 @@
       </c>
       <c r="AI279" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -30958,11 +31057,11 @@
       </c>
       <c r="Y280" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z280" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA280" t="n">
         <v>2.66</v>
@@ -30973,6 +31072,15 @@
       <c r="AC280" t="n">
         <v>1.77</v>
       </c>
+      <c r="AD280" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>-3.1</v>
+      </c>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
@@ -30981,7 +31089,7 @@
       </c>
       <c r="AI280" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -31082,11 +31190,11 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z281" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA281" t="n">
         <v>0.44</v>
@@ -31097,6 +31205,15 @@
       <c r="AC281" t="n">
         <v>4.28</v>
       </c>
+      <c r="AD281" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>-4.73</v>
+      </c>
       <c r="AG281" t="b">
         <v>0</v>
       </c>
@@ -31105,7 +31222,7 @@
       </c>
       <c r="AI281" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -31206,11 +31323,11 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z282" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA282" t="n">
         <v>-4.79</v>
@@ -31221,6 +31338,15 @@
       <c r="AC282" t="n">
         <v>-4.97</v>
       </c>
+      <c r="AD282" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>-14.27</v>
+      </c>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
@@ -31229,7 +31355,7 @@
       </c>
       <c r="AI282" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -31330,11 +31456,11 @@
       </c>
       <c r="Y283" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z283" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA283" t="n">
         <v>6.23</v>
@@ -31345,6 +31471,15 @@
       <c r="AC283" t="n">
         <v>17.32</v>
       </c>
+      <c r="AD283" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>-1.56</v>
+      </c>
       <c r="AG283" t="b">
         <v>1</v>
       </c>
@@ -31353,7 +31488,7 @@
       </c>
       <c r="AI283" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -31454,11 +31589,11 @@
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z284" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA284" t="n">
         <v>-0.21</v>
@@ -31469,6 +31604,15 @@
       <c r="AC284" t="n">
         <v>3.64</v>
       </c>
+      <c r="AD284" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>-2.78</v>
+      </c>
       <c r="AG284" t="b">
         <v>0</v>
       </c>
@@ -31477,7 +31621,7 @@
       </c>
       <c r="AI284" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -31578,11 +31722,11 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z285" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA285" t="n">
         <v>0.44</v>
@@ -31593,6 +31737,15 @@
       <c r="AC285" t="n">
         <v>2.63</v>
       </c>
+      <c r="AD285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>-6.58</v>
+      </c>
       <c r="AG285" t="b">
         <v>0</v>
       </c>
@@ -31601,7 +31754,7 @@
       </c>
       <c r="AI285" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -31702,11 +31855,11 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z286" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA286" t="n">
         <v>3.82</v>
@@ -31717,6 +31870,15 @@
       <c r="AC286" t="n">
         <v>7.29</v>
       </c>
+      <c r="AD286" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>-1.74</v>
+      </c>
       <c r="AG286" t="b">
         <v>0</v>
       </c>
@@ -31725,7 +31887,7 @@
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -31826,11 +31988,11 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z287" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA287" t="n">
         <v>3.62</v>
@@ -31841,6 +32003,15 @@
       <c r="AC287" t="n">
         <v>2.26</v>
       </c>
+      <c r="AD287" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>-2.26</v>
+      </c>
       <c r="AG287" t="b">
         <v>0</v>
       </c>
@@ -31849,7 +32020,7 @@
       </c>
       <c r="AI287" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -31950,11 +32121,11 @@
       </c>
       <c r="Y288" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z288" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA288" t="n">
         <v>9.16</v>
@@ -31965,6 +32136,15 @@
       <c r="AC288" t="n">
         <v>19.5</v>
       </c>
+      <c r="AD288" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>0</v>
+      </c>
       <c r="AG288" t="b">
         <v>1</v>
       </c>
@@ -31973,7 +32153,7 @@
       </c>
       <c r="AI288" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -32074,11 +32254,11 @@
       </c>
       <c r="Y289" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z289" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA289" t="n">
         <v>9.56</v>
@@ -32089,6 +32269,15 @@
       <c r="AC289" t="n">
         <v>16.23</v>
       </c>
+      <c r="AD289" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>-1.89</v>
+      </c>
       <c r="AG289" t="b">
         <v>1</v>
       </c>
@@ -32097,7 +32286,7 @@
       </c>
       <c r="AI289" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -32198,11 +32387,11 @@
       </c>
       <c r="Y290" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z290" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA290" t="n">
         <v>6.61</v>
@@ -32213,6 +32402,15 @@
       <c r="AC290" t="n">
         <v>13.62</v>
       </c>
+      <c r="AD290" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>0</v>
+      </c>
       <c r="AG290" t="b">
         <v>1</v>
       </c>
@@ -32221,7 +32419,7 @@
       </c>
       <c r="AI290" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -32322,11 +32520,11 @@
       </c>
       <c r="Y291" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z291" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA291" t="n">
         <v>-12.94</v>
@@ -32337,6 +32535,15 @@
       <c r="AC291" t="n">
         <v>-16.34</v>
       </c>
+      <c r="AD291" t="n">
+        <v>-22.29</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>-22.48</v>
+      </c>
       <c r="AG291" t="b">
         <v>0</v>
       </c>
@@ -32345,7 +32552,7 @@
       </c>
       <c r="AI291" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -32446,11 +32653,11 @@
       </c>
       <c r="Y292" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z292" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA292" t="n">
         <v>-0.15</v>
@@ -32461,6 +32668,15 @@
       <c r="AC292" t="n">
         <v>-0.29</v>
       </c>
+      <c r="AD292" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>-9.49</v>
+      </c>
       <c r="AG292" t="b">
         <v>0</v>
       </c>
@@ -32469,7 +32685,7 @@
       </c>
       <c r="AI292" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -32570,11 +32786,11 @@
       </c>
       <c r="Y293" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z293" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA293" t="n">
         <v>-0.7</v>
@@ -32585,6 +32801,15 @@
       <c r="AC293" t="n">
         <v>5.54</v>
       </c>
+      <c r="AD293" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>-4.33</v>
+      </c>
       <c r="AG293" t="b">
         <v>0</v>
       </c>
@@ -32593,7 +32818,7 @@
       </c>
       <c r="AI293" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -33027,11 +33252,11 @@
       </c>
       <c r="Y297" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z297" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA297" t="n">
         <v>-2.7</v>
@@ -33042,6 +33267,15 @@
       <c r="AC297" t="n">
         <v>24.84</v>
       </c>
+      <c r="AD297" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>-6.89</v>
+      </c>
       <c r="AG297" t="b">
         <v>1</v>
       </c>
@@ -33050,7 +33284,7 @@
       </c>
       <c r="AI297" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -33151,11 +33385,11 @@
       </c>
       <c r="Y298" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z298" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA298" t="n">
         <v>-0.86</v>
@@ -33166,6 +33400,15 @@
       <c r="AC298" t="n">
         <v>-10.06</v>
       </c>
+      <c r="AD298" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>-20</v>
+      </c>
       <c r="AG298" t="b">
         <v>0</v>
       </c>
@@ -33174,7 +33417,7 @@
       </c>
       <c r="AI298" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -33275,11 +33518,11 @@
       </c>
       <c r="Y299" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z299" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA299" t="n">
         <v>-64.90000000000001</v>
@@ -33290,6 +33533,15 @@
       <c r="AC299" t="n">
         <v>-69.7</v>
       </c>
+      <c r="AD299" t="n">
+        <v>-70.54000000000001</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>-59.48</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>-70.75</v>
+      </c>
       <c r="AG299" t="b">
         <v>0</v>
       </c>
@@ -33298,7 +33550,7 @@
       </c>
       <c r="AI299" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -33514,7 +33766,7 @@
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -33638,7 +33890,7 @@
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -33762,7 +34014,7 @@
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -33886,7 +34138,7 @@
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -34010,7 +34262,7 @@
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -34134,7 +34386,7 @@
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -34258,7 +34510,7 @@
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -34382,7 +34634,7 @@
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -34506,7 +34758,7 @@
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -34630,7 +34882,7 @@
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -34754,7 +35006,7 @@
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -34878,7 +35130,7 @@
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -35002,7 +35254,7 @@
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -35126,7 +35378,7 @@
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -35250,7 +35502,7 @@
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -35374,7 +35626,7 @@
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -35498,7 +35750,7 @@
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -35622,7 +35874,7 @@
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -35746,7 +35998,7 @@
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -35870,7 +36122,7 @@
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -35994,7 +36246,7 @@
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -36118,7 +36370,7 @@
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -36242,7 +36494,7 @@
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -36366,7 +36618,7 @@
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -36712,7 +36964,7 @@
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -36836,7 +37088,7 @@
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -36848,7 +37100,7 @@
         <v>8.08</v>
       </c>
       <c r="AG328" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH328" t="b">
         <v>0</v>
@@ -36960,7 +37212,7 @@
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -37306,7 +37558,7 @@
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -37430,7 +37682,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -37554,7 +37806,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -37678,7 +37930,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -37802,7 +38054,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -37926,7 +38178,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -38050,7 +38302,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -38174,7 +38426,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -38298,7 +38550,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -38422,7 +38674,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -38546,7 +38798,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -38670,7 +38922,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -38794,7 +39046,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -38918,7 +39170,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -39042,7 +39294,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -39166,7 +39418,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -39290,7 +39542,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -39414,7 +39666,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -39538,7 +39790,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -39662,7 +39914,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -39786,7 +40038,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -39910,7 +40162,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -40478,7 +40730,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -40602,7 +40854,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -40726,7 +40978,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -40850,7 +41102,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -40974,7 +41226,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -41098,7 +41350,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -41222,7 +41474,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -41346,7 +41598,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -41470,7 +41722,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -41594,7 +41846,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -41718,7 +41970,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -41842,7 +42094,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -41966,7 +42218,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -42090,7 +42342,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -42214,7 +42466,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -42338,7 +42590,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -42462,7 +42714,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -42586,7 +42838,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -42710,7 +42962,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -42834,7 +43086,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -43180,7 +43432,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -43304,7 +43556,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -43539,7 +43791,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -43663,7 +43915,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -43787,7 +44039,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -43911,7 +44163,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -44035,7 +44287,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -44159,7 +44411,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -44283,7 +44535,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -44404,7 +44656,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -44528,7 +44780,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -44652,7 +44904,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -44776,7 +45028,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -44900,7 +45152,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -45024,7 +45276,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -45148,7 +45400,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -45272,7 +45524,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -45396,7 +45648,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -45520,7 +45772,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -45644,7 +45896,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -45768,7 +46020,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -45892,7 +46144,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -46016,7 +46268,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -46140,7 +46392,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -46264,7 +46516,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -46388,7 +46640,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -46512,7 +46764,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -46636,7 +46888,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -46760,7 +47012,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -47217,7 +47469,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -47341,7 +47593,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -47465,13 +47717,16 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
       </c>
       <c r="AB415" t="n">
         <v>-2.1</v>
+      </c>
+      <c r="AC415" t="n">
+        <v>2.25</v>
       </c>
       <c r="AG415" t="b">
         <v>0</v>
@@ -47586,13 +47841,16 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
       </c>
       <c r="AB416" t="n">
         <v>3.9</v>
+      </c>
+      <c r="AC416" t="n">
+        <v>10.85</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -47707,13 +47965,16 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
       </c>
       <c r="AB417" t="n">
         <v>-5.7</v>
+      </c>
+      <c r="AC417" t="n">
+        <v>-3.06</v>
       </c>
       <c r="AG417" t="b">
         <v>0</v>
@@ -47828,13 +48089,16 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
       </c>
       <c r="AB418" t="n">
         <v>-2.84</v>
+      </c>
+      <c r="AC418" t="n">
+        <v>-6.22</v>
       </c>
       <c r="AG418" t="b">
         <v>0</v>
@@ -47949,13 +48213,16 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
       </c>
       <c r="AB419" t="n">
         <v>-7.5</v>
+      </c>
+      <c r="AC419" t="n">
+        <v>-5.63</v>
       </c>
       <c r="AG419" t="b">
         <v>0</v>
@@ -48070,13 +48337,16 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
       </c>
       <c r="AB420" t="n">
         <v>-5.31</v>
+      </c>
+      <c r="AC420" t="n">
+        <v>-3.8</v>
       </c>
       <c r="AG420" t="b">
         <v>0</v>
@@ -48191,13 +48461,16 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
       </c>
       <c r="AB421" t="n">
         <v>-0.86</v>
+      </c>
+      <c r="AC421" t="n">
+        <v>-4.03</v>
       </c>
       <c r="AG421" t="b">
         <v>0</v>
@@ -48312,13 +48585,16 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
       </c>
       <c r="AB422" t="n">
         <v>10.44</v>
+      </c>
+      <c r="AC422" t="n">
+        <v>7.88</v>
       </c>
       <c r="AG422" t="b">
         <v>1</v>
@@ -48433,13 +48709,16 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
       </c>
       <c r="AB423" t="n">
         <v>5.25</v>
+      </c>
+      <c r="AC423" t="n">
+        <v>3.36</v>
       </c>
       <c r="AG423" t="b">
         <v>0</v>
@@ -48554,13 +48833,16 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
       </c>
       <c r="AB424" t="n">
         <v>2.18</v>
+      </c>
+      <c r="AC424" t="n">
+        <v>-0.44</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
@@ -48675,13 +48957,16 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
       </c>
       <c r="AB425" t="n">
         <v>3.34</v>
+      </c>
+      <c r="AC425" t="n">
+        <v>1</v>
       </c>
       <c r="AG425" t="b">
         <v>0</v>
@@ -48796,13 +49081,16 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
       </c>
       <c r="AB426" t="n">
         <v>-1.31</v>
+      </c>
+      <c r="AC426" t="n">
+        <v>-3.06</v>
       </c>
       <c r="AG426" t="b">
         <v>0</v>
@@ -48917,13 +49205,16 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
       </c>
       <c r="AB427" t="n">
         <v>9.470000000000001</v>
+      </c>
+      <c r="AC427" t="n">
+        <v>5.14</v>
       </c>
       <c r="AG427" t="b">
         <v>0</v>
@@ -49038,13 +49329,16 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
       </c>
       <c r="AB428" t="n">
         <v>6.08</v>
+      </c>
+      <c r="AC428" t="n">
+        <v>2.99</v>
       </c>
       <c r="AG428" t="b">
         <v>0</v>
@@ -49159,13 +49453,16 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
       </c>
       <c r="AB429" t="n">
         <v>6.57</v>
+      </c>
+      <c r="AC429" t="n">
+        <v>2.07</v>
       </c>
       <c r="AG429" t="b">
         <v>0</v>
@@ -49280,13 +49577,16 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
       </c>
       <c r="AB430" t="n">
         <v>7.28</v>
+      </c>
+      <c r="AC430" t="n">
+        <v>3.87</v>
       </c>
       <c r="AG430" t="b">
         <v>0</v>
@@ -49401,13 +49701,16 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
       </c>
       <c r="AB431" t="n">
         <v>6.57</v>
+      </c>
+      <c r="AC431" t="n">
+        <v>3.62</v>
       </c>
       <c r="AG431" t="b">
         <v>0</v>
@@ -49522,13 +49825,16 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
       </c>
       <c r="AB432" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="AC432" t="n">
+        <v>0.44</v>
       </c>
       <c r="AG432" t="b">
         <v>0</v>
@@ -49643,13 +49949,16 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
       </c>
       <c r="AB433" t="n">
         <v>6.29</v>
+      </c>
+      <c r="AC433" t="n">
+        <v>6.49</v>
       </c>
       <c r="AG433" t="b">
         <v>0</v>
@@ -49764,13 +50073,16 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
       </c>
       <c r="AB434" t="n">
         <v>6.41</v>
+      </c>
+      <c r="AC434" t="n">
+        <v>2.14</v>
       </c>
       <c r="AG434" t="b">
         <v>0</v>
@@ -50107,13 +50419,16 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
       </c>
       <c r="AB437" t="n">
         <v>28.31</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>35.47</v>
       </c>
       <c r="AG437" t="b">
         <v>1</v>
@@ -50339,7 +50654,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -50460,7 +50775,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -50581,7 +50896,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -50702,7 +51017,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -50823,7 +51138,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -50944,7 +51259,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -51065,7 +51380,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -51186,7 +51501,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -51307,7 +51622,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -51428,7 +51743,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -51549,7 +51864,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -51670,7 +51985,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -51791,7 +52106,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -51912,7 +52227,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -52033,7 +52348,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -52154,7 +52469,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -52275,7 +52590,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -52396,7 +52711,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -52517,7 +52832,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -52638,7 +52953,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -52981,7 +53296,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -53102,7 +53417,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -53223,7 +53538,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -53344,7 +53659,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -53465,7 +53780,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -53586,7 +53901,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -53707,7 +54022,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -53828,7 +54143,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -53949,7 +54264,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -53958,7 +54273,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="AG469" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH469" t="b">
         <v>1</v>
@@ -54070,7 +54385,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -54191,7 +54506,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -54312,7 +54627,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -54433,7 +54748,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -54554,7 +54869,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -54675,7 +54990,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -54796,7 +55111,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -54917,7 +55232,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -55038,7 +55353,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -55492,7 +55807,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -55613,7 +55928,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -55734,7 +56049,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -55855,7 +56170,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -55976,7 +56291,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -56097,7 +56412,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -56218,7 +56533,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -56339,7 +56654,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -56460,7 +56775,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -56581,7 +56896,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -56702,7 +57017,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -56823,7 +57138,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -56944,7 +57259,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -57065,7 +57380,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -57186,7 +57501,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -57307,7 +57622,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -57428,7 +57743,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -57549,7 +57864,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -57670,7 +57985,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -57791,7 +58106,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -57912,7 +58227,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -58033,7 +58348,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -58154,7 +58469,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -58275,10 +58590,13 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
+      </c>
+      <c r="AB505" t="n">
+        <v>8.42</v>
       </c>
       <c r="AG505" t="b">
         <v>0</v>
@@ -58393,10 +58711,13 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
+      </c>
+      <c r="AB506" t="n">
+        <v>-3.27</v>
       </c>
       <c r="AG506" t="b">
         <v>0</v>
@@ -58511,10 +58832,13 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
+      </c>
+      <c r="AB507" t="n">
+        <v>-2.05</v>
       </c>
       <c r="AG507" t="b">
         <v>0</v>
@@ -58629,10 +58953,13 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
+      </c>
+      <c r="AB508" t="n">
+        <v>-1.95</v>
       </c>
       <c r="AG508" t="b">
         <v>0</v>
@@ -58747,10 +59074,13 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
+      </c>
+      <c r="AB509" t="n">
+        <v>0.13</v>
       </c>
       <c r="AG509" t="b">
         <v>0</v>
@@ -58865,10 +59195,13 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
+      </c>
+      <c r="AB510" t="n">
+        <v>-3.24</v>
       </c>
       <c r="AG510" t="b">
         <v>0</v>
@@ -58983,10 +59316,13 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
+      </c>
+      <c r="AB511" t="n">
+        <v>-6.38</v>
       </c>
       <c r="AG511" t="b">
         <v>0</v>
@@ -59101,10 +59437,13 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
+      </c>
+      <c r="AB512" t="n">
+        <v>-3.67</v>
       </c>
       <c r="AG512" t="b">
         <v>0</v>
@@ -59219,10 +59558,13 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
+      </c>
+      <c r="AB513" t="n">
+        <v>-1.23</v>
       </c>
       <c r="AG513" t="b">
         <v>0</v>
@@ -59337,10 +59679,13 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="AB514" t="n">
+        <v>-3.01</v>
       </c>
       <c r="AG514" t="b">
         <v>0</v>
@@ -59455,10 +59800,13 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
+      </c>
+      <c r="AB515" t="n">
+        <v>-1.8</v>
       </c>
       <c r="AG515" t="b">
         <v>0</v>
@@ -59573,10 +59921,13 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
+      </c>
+      <c r="AB516" t="n">
+        <v>2.94</v>
       </c>
       <c r="AG516" t="b">
         <v>0</v>
@@ -59691,10 +60042,13 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
+      </c>
+      <c r="AB517" t="n">
+        <v>-1.65</v>
       </c>
       <c r="AG517" t="b">
         <v>0</v>
@@ -59809,10 +60163,13 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
+      </c>
+      <c r="AB518" t="n">
+        <v>25.63</v>
       </c>
       <c r="AG518" t="b">
         <v>1</v>
@@ -59927,10 +60284,13 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
+      </c>
+      <c r="AB519" t="n">
+        <v>13.22</v>
       </c>
       <c r="AG519" t="b">
         <v>0</v>
@@ -60045,10 +60405,13 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
+      </c>
+      <c r="AB520" t="n">
+        <v>-2.36</v>
       </c>
       <c r="AG520" t="b">
         <v>0</v>
@@ -60163,10 +60526,13 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
+      </c>
+      <c r="AB521" t="n">
+        <v>-4.92</v>
       </c>
       <c r="AG521" t="b">
         <v>0</v>
@@ -60281,7 +60647,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
@@ -60399,7 +60765,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
@@ -60517,7 +60883,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
@@ -60635,7 +61001,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
@@ -60753,7 +61119,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
@@ -60871,7 +61237,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
@@ -60989,7 +61355,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
@@ -61107,7 +61473,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
@@ -61225,7 +61591,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
@@ -61343,7 +61709,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
@@ -61461,7 +61827,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
@@ -61579,7 +61945,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
@@ -61697,13 +62063,13 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
       </c>
       <c r="AG534" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH534" t="b">
         <v>0</v>
@@ -61815,7 +62181,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
@@ -61933,7 +62299,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
@@ -62051,7 +62417,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
@@ -62169,7 +62535,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -62287,7 +62653,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
@@ -62405,7 +62771,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
@@ -62523,7 +62889,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
@@ -62641,7 +63007,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
@@ -62759,7 +63125,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
@@ -62877,7 +63243,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
@@ -62995,7 +63361,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
@@ -63113,7 +63479,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
@@ -63231,7 +63597,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
@@ -63349,7 +63715,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
@@ -63467,7 +63833,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
@@ -63585,7 +63951,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
@@ -63925,7 +64291,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
@@ -64043,7 +64409,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
@@ -64161,7 +64527,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
@@ -64390,7 +64756,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA557" t="n">
         <v>-0.77</v>
@@ -64508,7 +64874,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA558" t="n">
         <v>0.85</v>
@@ -64626,7 +64992,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA559" t="n">
         <v>-2.33</v>
@@ -64744,7 +65110,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA560" t="n">
         <v>4.41</v>
@@ -64862,7 +65228,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA561" t="n">
         <v>-1.6</v>
@@ -64980,7 +65346,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA562" t="n">
         <v>14</v>
@@ -65095,7 +65461,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA563" t="n">
         <v>-4.15</v>
@@ -65213,7 +65579,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA564" t="n">
         <v>-4.8</v>
@@ -65331,7 +65697,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA565" t="n">
         <v>-4.49</v>
@@ -65449,7 +65815,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA566" t="n">
         <v>-0.99</v>
@@ -65567,7 +65933,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA567" t="n">
         <v>-1.34</v>
@@ -65685,7 +66051,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA568" t="n">
         <v>-1.77</v>
@@ -65803,7 +66169,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA569" t="n">
         <v>-3.59</v>
@@ -65921,7 +66287,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA570" t="n">
         <v>0.29</v>
@@ -66039,7 +66405,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA571" t="n">
         <v>-4.43</v>
@@ -66157,7 +66523,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA572" t="n">
         <v>-3.52</v>
@@ -66275,7 +66641,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA573" t="n">
         <v>-1.74</v>
@@ -66393,7 +66759,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA574" t="n">
         <v>-3.79</v>
@@ -66511,7 +66877,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA575" t="n">
         <v>-3.07</v>
@@ -66629,7 +66995,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA576" t="n">
         <v>-1.21</v>
@@ -67080,7 +67446,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA580" t="n">
         <v>31.15</v>
@@ -67198,7 +67564,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA581" t="n">
         <v>2.49</v>
@@ -67316,7 +67682,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA582" t="n">
         <v>-0.9399999999999999</v>
@@ -67434,7 +67800,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA583" t="n">
         <v>-3.99</v>
@@ -67663,7 +68029,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA585" t="n">
         <v>3.78</v>
@@ -67781,7 +68147,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA586" t="n">
         <v>-0.88</v>
@@ -67899,7 +68265,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA587" t="n">
         <v>-1.6</v>
@@ -68017,7 +68383,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA588" t="n">
         <v>4.07</v>
@@ -68135,7 +68501,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA589" t="n">
         <v>-1.9</v>
@@ -68253,7 +68619,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA590" t="n">
         <v>15.49</v>
@@ -68371,7 +68737,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA591" t="n">
         <v>4.25</v>
@@ -68489,7 +68855,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA592" t="n">
         <v>-4.09</v>
@@ -68607,7 +68973,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA593" t="n">
         <v>-5.77</v>
@@ -68722,7 +69088,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA594" t="n">
         <v>0.66</v>
@@ -68840,7 +69206,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA595" t="n">
         <v>0.9</v>
@@ -68958,7 +69324,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA596" t="n">
         <v>-0.89</v>
@@ -69076,7 +69442,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA597" t="n">
         <v>-3.23</v>
@@ -69194,7 +69560,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA598" t="n">
         <v>-1.86</v>
@@ -69312,7 +69678,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA599" t="n">
         <v>-3.91</v>
@@ -69430,7 +69796,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA600" t="n">
         <v>-5.86</v>
@@ -69548,7 +69914,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA601" t="n">
         <v>-2.98</v>
@@ -69666,7 +70032,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA602" t="n">
         <v>-3.02</v>
@@ -69784,7 +70150,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA603" t="n">
         <v>-2.06</v>
@@ -69902,7 +70268,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA604" t="n">
         <v>-0.87</v>
@@ -70020,7 +70386,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA605" t="n">
         <v>0.58</v>
@@ -70135,7 +70501,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA606" t="n">
         <v>-2.42</v>
@@ -70697,7 +71063,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA611" t="n">
         <v>1.45</v>
@@ -70812,7 +71178,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA612" t="n">
         <v>-2.34</v>
@@ -71041,7 +71407,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA614" t="n">
         <v>-4.58</v>
@@ -71159,7 +71525,10 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA615" t="n">
+        <v>6.68</v>
       </c>
       <c r="AG615" t="b">
         <v>0</v>
@@ -71274,7 +71643,10 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA616" t="n">
+        <v>-1.59</v>
       </c>
       <c r="AG616" t="b">
         <v>0</v>
@@ -71389,7 +71761,10 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA617" t="n">
+        <v>-10.11</v>
       </c>
       <c r="AG617" t="b">
         <v>0</v>
@@ -71504,7 +71879,10 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA618" t="n">
+        <v>-2.58</v>
       </c>
       <c r="AG618" t="b">
         <v>0</v>
@@ -71619,7 +71997,10 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA619" t="n">
+        <v>-1.8</v>
       </c>
       <c r="AG619" t="b">
         <v>0</v>
@@ -71734,7 +72115,10 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA620" t="n">
+        <v>-3.27</v>
       </c>
       <c r="AG620" t="b">
         <v>0</v>
@@ -71846,7 +72230,10 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA621" t="n">
+        <v>-2.27</v>
       </c>
       <c r="AG621" t="b">
         <v>0</v>
@@ -71961,7 +72348,10 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA622" t="n">
+        <v>-1.77</v>
       </c>
       <c r="AG622" t="b">
         <v>0</v>
@@ -72076,7 +72466,10 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA623" t="n">
+        <v>-3.96</v>
       </c>
       <c r="AG623" t="b">
         <v>0</v>
@@ -72191,7 +72584,10 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA624" t="n">
+        <v>-2.7</v>
       </c>
       <c r="AG624" t="b">
         <v>0</v>
@@ -72306,7 +72702,10 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA625" t="n">
+        <v>-3.17</v>
       </c>
       <c r="AG625" t="b">
         <v>0</v>
@@ -72421,7 +72820,10 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA626" t="n">
+        <v>-2.84</v>
       </c>
       <c r="AG626" t="b">
         <v>0</v>
@@ -72536,7 +72938,10 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA627" t="n">
+        <v>0.59</v>
       </c>
       <c r="AG627" t="b">
         <v>0</v>
@@ -72651,7 +73056,10 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA628" t="n">
+        <v>0.19</v>
       </c>
       <c r="AG628" t="b">
         <v>0</v>
@@ -72763,7 +73171,10 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA629" t="n">
+        <v>-4.02</v>
       </c>
       <c r="AG629" t="b">
         <v>0</v>
@@ -73211,7 +73622,10 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA633" t="n">
+        <v>5.58</v>
       </c>
       <c r="AG633" t="b">
         <v>0</v>
@@ -73326,7 +73740,10 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA634" t="n">
+        <v>8.529999999999999</v>
       </c>
       <c r="AG634" t="b">
         <v>0</v>
@@ -73552,7 +73969,10 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA636" t="n">
+        <v>7.05</v>
       </c>
       <c r="AG636" t="b">
         <v>0</v>
@@ -73778,7 +74198,7 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG638" t="b">
         <v>0</v>
@@ -73893,7 +74313,7 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG639" t="b">
         <v>0</v>
@@ -74008,7 +74428,7 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG640" t="b">
         <v>0</v>
@@ -74123,7 +74543,7 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG641" t="b">
         <v>0</v>
@@ -74235,7 +74655,7 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG642" t="b">
         <v>0</v>
@@ -74350,7 +74770,7 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG643" t="b">
         <v>0</v>
@@ -74465,7 +74885,7 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG644" t="b">
         <v>0</v>
@@ -74580,7 +75000,7 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG645" t="b">
         <v>0</v>
@@ -74695,7 +75115,7 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG646" t="b">
         <v>0</v>
@@ -74810,7 +75230,7 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG647" t="b">
         <v>0</v>
@@ -74925,7 +75345,7 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG648" t="b">
         <v>0</v>
@@ -75040,7 +75460,7 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG649" t="b">
         <v>0</v>
@@ -75155,7 +75575,7 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG650" t="b">
         <v>0</v>
@@ -75603,7 +76023,7 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG654" t="b">
         <v>0</v>
@@ -75940,7 +76360,7 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG657" t="b">
         <v>0</v>
@@ -76055,7 +76475,7 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG658" t="b">
         <v>0</v>
@@ -76170,7 +76590,7 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG659" t="b">
         <v>0</v>
@@ -76285,7 +76705,7 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG660" t="b">
         <v>0</v>
@@ -76400,7 +76820,7 @@
         </is>
       </c>
       <c r="Z661" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG661" t="b">
         <v>0</v>
@@ -76515,7 +76935,7 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG662" t="b">
         <v>0</v>
@@ -76630,7 +77050,7 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG663" t="b">
         <v>0</v>
@@ -76745,7 +77165,7 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG664" t="b">
         <v>0</v>
@@ -76857,7 +77277,7 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG665" t="b">
         <v>0</v>
@@ -76972,7 +77392,7 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG666" t="b">
         <v>0</v>
@@ -77087,7 +77507,7 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG667" t="b">
         <v>0</v>
@@ -77202,7 +77622,7 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG668" t="b">
         <v>0</v>
@@ -77317,7 +77737,7 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG669" t="b">
         <v>0</v>
@@ -77432,7 +77852,7 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG670" t="b">
         <v>0</v>
@@ -77547,7 +77967,7 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG671" t="b">
         <v>0</v>
@@ -77662,7 +78082,7 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG672" t="b">
         <v>0</v>
@@ -77777,7 +78197,7 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG673" t="b">
         <v>0</v>
@@ -78114,7 +78534,7 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG676" t="b">
         <v>0</v>
@@ -78340,7 +78760,7 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG678" t="b">
         <v>0</v>
@@ -78455,7 +78875,7 @@
         </is>
       </c>
       <c r="Z679" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG679" t="b">
         <v>0</v>
@@ -78570,7 +78990,7 @@
         </is>
       </c>
       <c r="Z680" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG680" t="b">
         <v>0</v>
@@ -78685,7 +79105,7 @@
         </is>
       </c>
       <c r="Z681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG681" t="b">
         <v>0</v>
@@ -78800,7 +79220,7 @@
         </is>
       </c>
       <c r="Z682" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG682" t="b">
         <v>0</v>
@@ -78915,7 +79335,7 @@
         </is>
       </c>
       <c r="Z683" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG683" t="b">
         <v>0</v>
@@ -79030,7 +79450,7 @@
         </is>
       </c>
       <c r="Z684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG684" t="b">
         <v>0</v>
@@ -79145,7 +79565,7 @@
         </is>
       </c>
       <c r="Z685" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG685" t="b">
         <v>0</v>
@@ -79260,7 +79680,7 @@
         </is>
       </c>
       <c r="Z686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG686" t="b">
         <v>0</v>
@@ -79375,7 +79795,7 @@
         </is>
       </c>
       <c r="Z687" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG687" t="b">
         <v>0</v>
@@ -79490,7 +79910,7 @@
         </is>
       </c>
       <c r="Z688" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG688" t="b">
         <v>0</v>
@@ -79938,7 +80358,7 @@
         </is>
       </c>
       <c r="Z692" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG692" t="b">
         <v>0</v>
@@ -80164,7 +80584,7 @@
         </is>
       </c>
       <c r="Z694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG694" t="b">
         <v>0</v>
@@ -80279,7 +80699,7 @@
         </is>
       </c>
       <c r="Z695" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG695" t="b">
         <v>0</v>
@@ -80616,7 +81036,7 @@
         </is>
       </c>
       <c r="Z698" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG698" t="b">
         <v>0</v>
@@ -80731,7 +81151,7 @@
         </is>
       </c>
       <c r="Z699" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG699" t="b">
         <v>0</v>
@@ -80846,7 +81266,7 @@
         </is>
       </c>
       <c r="Z700" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG700" t="b">
         <v>0</v>
@@ -80961,7 +81381,7 @@
         </is>
       </c>
       <c r="Z701" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG701" t="b">
         <v>0</v>
@@ -81076,7 +81496,7 @@
         </is>
       </c>
       <c r="Z702" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG702" t="b">
         <v>0</v>
@@ -81191,7 +81611,7 @@
         </is>
       </c>
       <c r="Z703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG703" t="b">
         <v>0</v>
@@ -81639,7 +82059,7 @@
         </is>
       </c>
       <c r="Z707" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG707" t="b">
         <v>0</v>
@@ -81865,7 +82285,7 @@
         </is>
       </c>
       <c r="Z709" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG709" t="b">
         <v>0</v>
@@ -81980,7 +82400,7 @@
         </is>
       </c>
       <c r="Z710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG710" t="b">
         <v>0</v>
@@ -82095,7 +82515,7 @@
         </is>
       </c>
       <c r="Z711" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG711" t="b">
         <v>0</v>
@@ -82331,8 +82751,1951 @@
         </is>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="F714" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I714" t="b">
+        <v>0</v>
+      </c>
+      <c r="J714" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K714" t="n">
+        <v>27</v>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M714" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N714" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P714" t="n">
+        <v>25.23</v>
+      </c>
+      <c r="Q714" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S714" t="n">
+        <v>7</v>
+      </c>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V714" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W714" t="n">
+        <v>30.3747</v>
+      </c>
+      <c r="X714" t="n">
+        <v>24.459</v>
+      </c>
+      <c r="Y714" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z714" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG714" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH714" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI714" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="F715" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I715" t="b">
+        <v>0</v>
+      </c>
+      <c r="J715" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="K715" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>wedge_failure_measured_move_target</t>
+        </is>
+      </c>
+      <c r="M715" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N715" t="n">
+        <v>10</v>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P715" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="Q715" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S715" t="n">
+        <v>3.2793</v>
+      </c>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V715" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="W715" t="n">
+        <v>38.2707</v>
+      </c>
+      <c r="X715" t="n">
+        <v>34.626</v>
+      </c>
+      <c r="Y715" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z715" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG715" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH715" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI715" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="F716" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I716" t="b">
+        <v>0</v>
+      </c>
+      <c r="J716" t="n">
+        <v>10</v>
+      </c>
+      <c r="K716" t="n">
+        <v>281.05</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M716" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N716" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P716" t="n">
+        <v>242.75</v>
+      </c>
+      <c r="Q716" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S716" t="n">
+        <v>7</v>
+      </c>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V716" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="W716" t="n">
+        <v>306.6</v>
+      </c>
+      <c r="X716" t="n">
+        <v>237.615</v>
+      </c>
+      <c r="Y716" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z716" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG716" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH716" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI716" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="F717" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I717" t="b">
+        <v>0</v>
+      </c>
+      <c r="J717" t="n">
+        <v>10</v>
+      </c>
+      <c r="K717" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M717" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N717" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P717" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="Q717" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S717" t="n">
+        <v>7</v>
+      </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V717" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="W717" t="n">
+        <v>108.1337</v>
+      </c>
+      <c r="X717" t="n">
+        <v>88.25700000000001</v>
+      </c>
+      <c r="Y717" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z717" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG717" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH717" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI717" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>72.89</v>
+      </c>
+      <c r="F718" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I718" t="b">
+        <v>0</v>
+      </c>
+      <c r="J718" t="n">
+        <v>10</v>
+      </c>
+      <c r="K718" t="n">
+        <v>323.95</v>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M718" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N718" t="n">
+        <v>7</v>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P718" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="Q718" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S718" t="n">
+        <v>7</v>
+      </c>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V718" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="W718" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="X718" t="n">
+        <v>273.885</v>
+      </c>
+      <c r="Y718" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z718" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG718" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH718" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI718" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="F719" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I719" t="b">
+        <v>0</v>
+      </c>
+      <c r="J719" t="n">
+        <v>10</v>
+      </c>
+      <c r="K719" t="n">
+        <v>5412</v>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M719" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N719" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P719" t="n">
+        <v>4955</v>
+      </c>
+      <c r="Q719" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S719" t="n">
+        <v>7</v>
+      </c>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V719" t="n">
+        <v>4920</v>
+      </c>
+      <c r="W719" t="n">
+        <v>5904</v>
+      </c>
+      <c r="X719" t="n">
+        <v>4575.6</v>
+      </c>
+      <c r="Y719" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z719" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG719" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH719" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI719" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>開發金</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="F720" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I720" t="b">
+        <v>0</v>
+      </c>
+      <c r="J720" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K720" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M720" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N720" t="n">
+        <v>10</v>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P720" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="Q720" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S720" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="T720" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="V720" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="W720" t="n">
+        <v>45.335</v>
+      </c>
+      <c r="X720" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="Y720" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z720" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG720" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH720" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI720" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="F721" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I721" t="b">
+        <v>0</v>
+      </c>
+      <c r="J721" t="n">
+        <v>10</v>
+      </c>
+      <c r="K721" t="n">
+        <v>231.55</v>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M721" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N721" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P721" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q721" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S721" t="n">
+        <v>7</v>
+      </c>
+      <c r="T721" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U721" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V721" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="W721" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="X721" t="n">
+        <v>195.765</v>
+      </c>
+      <c r="Y721" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z721" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG721" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH721" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI721" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>71.97</v>
+      </c>
+      <c r="F722" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I722" t="b">
+        <v>0</v>
+      </c>
+      <c r="J722" t="n">
+        <v>10</v>
+      </c>
+      <c r="K722" t="n">
+        <v>1292.5</v>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M722" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N722" t="n">
+        <v>3</v>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P722" t="n">
+        <v>1066</v>
+      </c>
+      <c r="Q722" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S722" t="n">
+        <v>7</v>
+      </c>
+      <c r="T722" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U722" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V722" t="n">
+        <v>1175</v>
+      </c>
+      <c r="W722" t="n">
+        <v>1410</v>
+      </c>
+      <c r="X722" t="n">
+        <v>1092.75</v>
+      </c>
+      <c r="Y722" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z722" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG722" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH722" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI722" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="F723" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I723" t="b">
+        <v>0</v>
+      </c>
+      <c r="J723" t="n">
+        <v>10</v>
+      </c>
+      <c r="K723" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M723" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N723" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P723" t="n">
+        <v>890</v>
+      </c>
+      <c r="Q723" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S723" t="n">
+        <v>7</v>
+      </c>
+      <c r="T723" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U723" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V723" t="n">
+        <v>970</v>
+      </c>
+      <c r="W723" t="n">
+        <v>1164</v>
+      </c>
+      <c r="X723" t="n">
+        <v>902.1</v>
+      </c>
+      <c r="Y723" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z723" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG723" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH723" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI723" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="F724" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I724" t="b">
+        <v>0</v>
+      </c>
+      <c r="J724" t="n">
+        <v>10</v>
+      </c>
+      <c r="K724" t="n">
+        <v>866.8</v>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M724" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N724" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P724" t="n">
+        <v>741.5</v>
+      </c>
+      <c r="Q724" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S724" t="n">
+        <v>7</v>
+      </c>
+      <c r="T724" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U724" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V724" t="n">
+        <v>788</v>
+      </c>
+      <c r="W724" t="n">
+        <v>906.8134</v>
+      </c>
+      <c r="X724" t="n">
+        <v>732.84</v>
+      </c>
+      <c r="Y724" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI724" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ724" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>79.09</v>
+      </c>
+      <c r="F725" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I725" t="b">
+        <v>0</v>
+      </c>
+      <c r="J725" t="n">
+        <v>10</v>
+      </c>
+      <c r="K725" t="n">
+        <v>8844</v>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M725" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N725" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P725" t="n">
+        <v>7197.5</v>
+      </c>
+      <c r="Q725" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S725" t="n">
+        <v>7</v>
+      </c>
+      <c r="T725" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V725" t="n">
+        <v>8040</v>
+      </c>
+      <c r="W725" t="n">
+        <v>9648</v>
+      </c>
+      <c r="X725" t="n">
+        <v>7477.2</v>
+      </c>
+      <c r="Y725" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z725" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG725" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH725" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI725" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="F726" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I726" t="b">
+        <v>0</v>
+      </c>
+      <c r="J726" t="n">
+        <v>10</v>
+      </c>
+      <c r="K726" t="n">
+        <v>3635.5</v>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M726" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N726" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P726" t="n">
+        <v>3082.5</v>
+      </c>
+      <c r="Q726" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S726" t="n">
+        <v>7</v>
+      </c>
+      <c r="T726" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U726" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V726" t="n">
+        <v>3305</v>
+      </c>
+      <c r="W726" t="n">
+        <v>3966</v>
+      </c>
+      <c r="X726" t="n">
+        <v>3073.65</v>
+      </c>
+      <c r="Y726" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI726" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ726" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>77.91</v>
+      </c>
+      <c r="F727" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I727" t="b">
+        <v>0</v>
+      </c>
+      <c r="J727" t="n">
+        <v>10</v>
+      </c>
+      <c r="K727" t="n">
+        <v>518.1</v>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M727" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N727" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P727" t="n">
+        <v>444.25</v>
+      </c>
+      <c r="Q727" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S727" t="n">
+        <v>7</v>
+      </c>
+      <c r="T727" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V727" t="n">
+        <v>471</v>
+      </c>
+      <c r="W727" t="n">
+        <v>565.2</v>
+      </c>
+      <c r="X727" t="n">
+        <v>438.03</v>
+      </c>
+      <c r="Y727" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z727" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG727" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH727" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI727" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="F728" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I728" t="b">
+        <v>0</v>
+      </c>
+      <c r="J728" t="n">
+        <v>10</v>
+      </c>
+      <c r="K728" t="n">
+        <v>773.3</v>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M728" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N728" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P728" t="n">
+        <v>657.5</v>
+      </c>
+      <c r="Q728" t="n">
+        <v>63.58</v>
+      </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S728" t="n">
+        <v>7</v>
+      </c>
+      <c r="T728" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U728" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V728" t="n">
+        <v>703</v>
+      </c>
+      <c r="W728" t="n">
+        <v>843.6</v>
+      </c>
+      <c r="X728" t="n">
+        <v>653.79</v>
+      </c>
+      <c r="Y728" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z728" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG728" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH728" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI728" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="F729" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I729" t="b">
+        <v>0</v>
+      </c>
+      <c r="J729" t="n">
+        <v>10</v>
+      </c>
+      <c r="K729" t="n">
+        <v>199.1</v>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M729" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N729" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P729" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="Q729" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S729" t="n">
+        <v>7</v>
+      </c>
+      <c r="T729" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U729" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V729" t="n">
+        <v>181</v>
+      </c>
+      <c r="W729" t="n">
+        <v>217.2</v>
+      </c>
+      <c r="X729" t="n">
+        <v>168.33</v>
+      </c>
+      <c r="Y729" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI729" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ729" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="F730" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I730" t="b">
+        <v>0</v>
+      </c>
+      <c r="J730" t="n">
+        <v>10</v>
+      </c>
+      <c r="K730" t="n">
+        <v>1474</v>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M730" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N730" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P730" t="n">
+        <v>1182.5</v>
+      </c>
+      <c r="Q730" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S730" t="n">
+        <v>7</v>
+      </c>
+      <c r="T730" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U730" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V730" t="n">
+        <v>1340</v>
+      </c>
+      <c r="W730" t="n">
+        <v>1608</v>
+      </c>
+      <c r="X730" t="n">
+        <v>1246.2</v>
+      </c>
+      <c r="Y730" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z730" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG730" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH730" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI730" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ713"/>
+  <autoFilter ref="A1:AJ730"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -82405,25 +84768,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3909</v>
+        <v>0.374</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.82</v>
+        <v>-3.71</v>
       </c>
       <c r="E2" t="n">
-        <v>8.48</v>
+        <v>8.15</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.43</v>
+        <v>-13.12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1818</v>
+        <v>0.1832</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6455</v>
+        <v>0.6336000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -82433,25 +84796,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5</v>
+        <v>0.5652</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>1.74</v>
       </c>
       <c r="E3" t="n">
-        <v>5.64</v>
+        <v>7.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.07</v>
+        <v>-4.85</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0625</v>
+        <v>0.1304</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1875</v>
+        <v>0.1739</v>
       </c>
     </row>
     <row r="4">
@@ -82555,25 +84918,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.01</v>
+        <v>-8.43</v>
       </c>
       <c r="E2" t="n">
-        <v>13.24</v>
+        <v>11.44</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.25</v>
+        <v>-16.69</v>
       </c>
       <c r="G2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.3333</v>
       </c>
     </row>
     <row r="3">
@@ -82583,25 +84946,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3774</v>
+        <v>0.3571</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.75</v>
+        <v>-4.74</v>
       </c>
       <c r="E3" t="n">
-        <v>5.45</v>
+        <v>5.99</v>
       </c>
       <c r="F3" t="n">
-        <v>-13.46</v>
+        <v>-12.89</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1321</v>
+        <v>0.1571</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5849</v>
+        <v>0.5571</v>
       </c>
     </row>
     <row r="4">
@@ -82611,25 +84974,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4242</v>
+        <v>0.4324</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.06</v>
+        <v>-0.72</v>
       </c>
       <c r="E4" t="n">
-        <v>9.84</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.17</v>
+        <v>-10.62</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1667</v>
+        <v>0.1757</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6212</v>
+        <v>0.5946</v>
       </c>
     </row>
     <row r="5">
@@ -82639,19 +85002,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.41</v>
+        <v>2.92</v>
       </c>
       <c r="E5" t="n">
-        <v>5.24</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.23</v>
+        <v>-4.48</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -82726,7 +85089,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-29 14:24:44</t>
+          <t>2026-09-30 14:24:01</t>
         </is>
       </c>
     </row>
@@ -82773,7 +85136,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>712</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7">
@@ -82783,7 +85146,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>248</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
@@ -82793,7 +85156,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>464</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$751</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ730"/>
+  <dimension ref="A1:AJ751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -33762,11 +33762,11 @@
       </c>
       <c r="Y301" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z301" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA301" t="n">
         <v>-3.98</v>
@@ -33777,6 +33777,15 @@
       <c r="AC301" t="n">
         <v>-4.72</v>
       </c>
+      <c r="AD301" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>-9.73</v>
+      </c>
       <c r="AG301" t="b">
         <v>0</v>
       </c>
@@ -33785,7 +33794,7 @@
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -33886,11 +33895,11 @@
       </c>
       <c r="Y302" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z302" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA302" t="n">
         <v>0.21</v>
@@ -33901,6 +33910,15 @@
       <c r="AC302" t="n">
         <v>-1.28</v>
       </c>
+      <c r="AD302" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>-7.04</v>
+      </c>
       <c r="AG302" t="b">
         <v>0</v>
       </c>
@@ -33909,7 +33927,7 @@
       </c>
       <c r="AI302" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34010,11 +34028,11 @@
       </c>
       <c r="Y303" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z303" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA303" t="n">
         <v>-4.22</v>
@@ -34025,6 +34043,15 @@
       <c r="AC303" t="n">
         <v>-6.67</v>
       </c>
+      <c r="AD303" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>-8.029999999999999</v>
+      </c>
       <c r="AG303" t="b">
         <v>0</v>
       </c>
@@ -34033,7 +34060,7 @@
       </c>
       <c r="AI303" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34134,11 +34161,11 @@
       </c>
       <c r="Y304" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z304" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA304" t="n">
         <v>-4.34</v>
@@ -34149,6 +34176,15 @@
       <c r="AC304" t="n">
         <v>-6.44</v>
       </c>
+      <c r="AD304" t="n">
+        <v>-9.59</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>-9.720000000000001</v>
+      </c>
       <c r="AG304" t="b">
         <v>0</v>
       </c>
@@ -34157,7 +34193,7 @@
       </c>
       <c r="AI304" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34258,11 +34294,11 @@
       </c>
       <c r="Y305" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z305" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA305" t="n">
         <v>-3.16</v>
@@ -34273,6 +34309,15 @@
       <c r="AC305" t="n">
         <v>-5.32</v>
       </c>
+      <c r="AD305" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>-9.82</v>
+      </c>
       <c r="AG305" t="b">
         <v>0</v>
       </c>
@@ -34281,7 +34326,7 @@
       </c>
       <c r="AI305" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34382,11 +34427,11 @@
       </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z306" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA306" t="n">
         <v>3.4</v>
@@ -34397,6 +34442,15 @@
       <c r="AC306" t="n">
         <v>20.75</v>
       </c>
+      <c r="AD306" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>-7.17</v>
+      </c>
       <c r="AG306" t="b">
         <v>1</v>
       </c>
@@ -34405,7 +34459,7 @@
       </c>
       <c r="AI306" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34506,11 +34560,11 @@
       </c>
       <c r="Y307" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z307" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA307" t="n">
         <v>-8.33</v>
@@ -34521,6 +34575,15 @@
       <c r="AC307" t="n">
         <v>-11.9</v>
       </c>
+      <c r="AD307" t="n">
+        <v>-10.91</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>-15.48</v>
+      </c>
       <c r="AG307" t="b">
         <v>0</v>
       </c>
@@ -34529,7 +34592,7 @@
       </c>
       <c r="AI307" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34630,11 +34693,11 @@
       </c>
       <c r="Y308" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z308" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA308" t="n">
         <v>-2.2</v>
@@ -34645,6 +34708,15 @@
       <c r="AC308" t="n">
         <v>-1.1</v>
       </c>
+      <c r="AD308" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>-3.15</v>
+      </c>
       <c r="AG308" t="b">
         <v>0</v>
       </c>
@@ -34653,7 +34725,7 @@
       </c>
       <c r="AI308" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -34754,11 +34826,11 @@
       </c>
       <c r="Y309" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z309" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA309" t="n">
         <v>-4.16</v>
@@ -34769,6 +34841,15 @@
       <c r="AC309" t="n">
         <v>-5.64</v>
       </c>
+      <c r="AD309" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>-10.89</v>
+      </c>
       <c r="AG309" t="b">
         <v>0</v>
       </c>
@@ -34777,7 +34858,7 @@
       </c>
       <c r="AI309" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -34878,11 +34959,11 @@
       </c>
       <c r="Y310" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z310" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA310" t="n">
         <v>-12.24</v>
@@ -34893,6 +34974,15 @@
       <c r="AC310" t="n">
         <v>-15.1</v>
       </c>
+      <c r="AD310" t="n">
+        <v>-10.61</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>-22.45</v>
+      </c>
       <c r="AG310" t="b">
         <v>0</v>
       </c>
@@ -34901,7 +34991,7 @@
       </c>
       <c r="AI310" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -35002,11 +35092,11 @@
       </c>
       <c r="Y311" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z311" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA311" t="n">
         <v>-0.5600000000000001</v>
@@ -35017,6 +35107,15 @@
       <c r="AC311" t="n">
         <v>2.09</v>
       </c>
+      <c r="AD311" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>-5.01</v>
+      </c>
       <c r="AG311" t="b">
         <v>0</v>
       </c>
@@ -35025,7 +35124,7 @@
       </c>
       <c r="AI311" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -35126,11 +35225,11 @@
       </c>
       <c r="Y312" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z312" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA312" t="n">
         <v>-4.09</v>
@@ -35141,6 +35240,15 @@
       <c r="AC312" t="n">
         <v>0</v>
       </c>
+      <c r="AD312" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>-4.09</v>
+      </c>
       <c r="AG312" t="b">
         <v>0</v>
       </c>
@@ -35149,7 +35257,7 @@
       </c>
       <c r="AI312" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -35250,11 +35358,11 @@
       </c>
       <c r="Y313" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z313" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA313" t="n">
         <v>-7.59</v>
@@ -35265,6 +35373,15 @@
       <c r="AC313" t="n">
         <v>-1.13</v>
       </c>
+      <c r="AD313" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>-9.279999999999999</v>
+      </c>
       <c r="AG313" t="b">
         <v>0</v>
       </c>
@@ -35273,7 +35390,7 @@
       </c>
       <c r="AI313" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -35374,11 +35491,11 @@
       </c>
       <c r="Y314" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z314" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA314" t="n">
         <v>2.51</v>
@@ -35389,6 +35506,15 @@
       <c r="AC314" t="n">
         <v>-4.05</v>
       </c>
+      <c r="AD314" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>-10.14</v>
+      </c>
       <c r="AG314" t="b">
         <v>0</v>
       </c>
@@ -35397,7 +35523,7 @@
       </c>
       <c r="AI314" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -35498,11 +35624,11 @@
       </c>
       <c r="Y315" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z315" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA315" t="n">
         <v>-2.18</v>
@@ -35513,6 +35639,15 @@
       <c r="AC315" t="n">
         <v>1.75</v>
       </c>
+      <c r="AD315" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>-6.99</v>
+      </c>
       <c r="AG315" t="b">
         <v>0</v>
       </c>
@@ -35521,7 +35656,7 @@
       </c>
       <c r="AI315" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -35622,11 +35757,11 @@
       </c>
       <c r="Y316" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z316" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA316" t="n">
         <v>2.76</v>
@@ -35637,6 +35772,15 @@
       <c r="AC316" t="n">
         <v>6.55</v>
       </c>
+      <c r="AD316" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>-1.72</v>
+      </c>
       <c r="AG316" t="b">
         <v>0</v>
       </c>
@@ -35645,7 +35789,7 @@
       </c>
       <c r="AI316" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -35746,11 +35890,11 @@
       </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z317" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA317" t="n">
         <v>2.25</v>
@@ -35761,6 +35905,15 @@
       <c r="AC317" t="n">
         <v>0.9</v>
       </c>
+      <c r="AD317" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>-2.7</v>
+      </c>
       <c r="AG317" t="b">
         <v>0</v>
       </c>
@@ -35769,7 +35922,7 @@
       </c>
       <c r="AI317" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -35870,11 +36023,11 @@
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z318" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA318" t="n">
         <v>6.72</v>
@@ -35885,6 +36038,15 @@
       <c r="AC318" t="n">
         <v>12.45</v>
       </c>
+      <c r="AD318" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>-1</v>
+      </c>
       <c r="AG318" t="b">
         <v>0</v>
       </c>
@@ -35893,7 +36055,7 @@
       </c>
       <c r="AI318" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -35994,11 +36156,11 @@
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z319" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA319" t="n">
         <v>6.2</v>
@@ -36009,6 +36171,15 @@
       <c r="AC319" t="n">
         <v>6.45</v>
       </c>
+      <c r="AD319" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="AG319" t="b">
         <v>0</v>
       </c>
@@ -36017,7 +36188,7 @@
       </c>
       <c r="AI319" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -36118,11 +36289,11 @@
       </c>
       <c r="Y320" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z320" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA320" t="n">
         <v>7.18</v>
@@ -36133,6 +36304,15 @@
       <c r="AC320" t="n">
         <v>0</v>
       </c>
+      <c r="AD320" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>-5.57</v>
+      </c>
       <c r="AG320" t="b">
         <v>0</v>
       </c>
@@ -36141,7 +36321,7 @@
       </c>
       <c r="AI320" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -36242,11 +36422,11 @@
       </c>
       <c r="Y321" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z321" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA321" t="n">
         <v>-14.25</v>
@@ -36257,6 +36437,15 @@
       <c r="AC321" t="n">
         <v>-15.5</v>
       </c>
+      <c r="AD321" t="n">
+        <v>-18.14</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>-24.27</v>
+      </c>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
@@ -36265,7 +36454,7 @@
       </c>
       <c r="AI321" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -36366,11 +36555,11 @@
       </c>
       <c r="Y322" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z322" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA322" t="n">
         <v>-3.67</v>
@@ -36381,6 +36570,15 @@
       <c r="AC322" t="n">
         <v>-0.59</v>
       </c>
+      <c r="AD322" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>-9.09</v>
+      </c>
       <c r="AG322" t="b">
         <v>0</v>
       </c>
@@ -36389,7 +36587,7 @@
       </c>
       <c r="AI322" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -36490,11 +36688,11 @@
       </c>
       <c r="Y323" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z323" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA323" t="n">
         <v>-4.63</v>
@@ -36505,6 +36703,15 @@
       <c r="AC323" t="n">
         <v>10.63</v>
       </c>
+      <c r="AD323" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>-10.08</v>
+      </c>
       <c r="AG323" t="b">
         <v>0</v>
       </c>
@@ -36513,7 +36720,7 @@
       </c>
       <c r="AI323" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -36614,11 +36821,11 @@
       </c>
       <c r="Y324" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z324" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA324" t="n">
         <v>-3.78</v>
@@ -36629,6 +36836,15 @@
       <c r="AC324" t="n">
         <v>7.16</v>
       </c>
+      <c r="AD324" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>-5.57</v>
+      </c>
       <c r="AG324" t="b">
         <v>0</v>
       </c>
@@ -36637,7 +36853,7 @@
       </c>
       <c r="AI324" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -36960,11 +37176,11 @@
       </c>
       <c r="Y327" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z327" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA327" t="n">
         <v>-0.58</v>
@@ -36975,6 +37191,15 @@
       <c r="AC327" t="n">
         <v>39.7</v>
       </c>
+      <c r="AD327" t="n">
+        <v>31.78</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>-5.25</v>
+      </c>
       <c r="AG327" t="b">
         <v>1</v>
       </c>
@@ -36983,7 +37208,7 @@
       </c>
       <c r="AI327" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -37084,11 +37309,11 @@
       </c>
       <c r="Y328" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z328" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA328" t="n">
         <v>-1</v>
@@ -37099,6 +37324,15 @@
       <c r="AC328" t="n">
         <v>8.08</v>
       </c>
+      <c r="AD328" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>-6.47</v>
+      </c>
       <c r="AG328" t="b">
         <v>1</v>
       </c>
@@ -37107,7 +37341,7 @@
       </c>
       <c r="AI328" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -37208,11 +37442,11 @@
       </c>
       <c r="Y329" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z329" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA329" t="n">
         <v>-5.73</v>
@@ -37223,6 +37457,15 @@
       <c r="AC329" t="n">
         <v>-13.1</v>
       </c>
+      <c r="AD329" t="n">
+        <v>-11.93</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>-23.74</v>
+      </c>
       <c r="AG329" t="b">
         <v>0</v>
       </c>
@@ -37231,7 +37474,7 @@
       </c>
       <c r="AI329" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -37554,11 +37797,11 @@
       </c>
       <c r="Y332" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z332" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA332" t="n">
         <v>-16.33</v>
@@ -37569,6 +37812,15 @@
       <c r="AC332" t="n">
         <v>-4.9</v>
       </c>
+      <c r="AD332" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>-17.55</v>
+      </c>
       <c r="AG332" t="b">
         <v>0</v>
       </c>
@@ -37577,7 +37829,7 @@
       </c>
       <c r="AI332" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -37682,7 +37934,7 @@
         </is>
       </c>
       <c r="Z333" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA333" t="n">
         <v>-0.15</v>
@@ -37806,7 +38058,7 @@
         </is>
       </c>
       <c r="Z334" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA334" t="n">
         <v>-0.42</v>
@@ -37930,7 +38182,7 @@
         </is>
       </c>
       <c r="Z335" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA335" t="n">
         <v>-1.37</v>
@@ -38054,7 +38306,7 @@
         </is>
       </c>
       <c r="Z336" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA336" t="n">
         <v>-0.8100000000000001</v>
@@ -38178,7 +38430,7 @@
         </is>
       </c>
       <c r="Z337" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA337" t="n">
         <v>-7.14</v>
@@ -38302,7 +38554,7 @@
         </is>
       </c>
       <c r="Z338" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA338" t="n">
         <v>-3.07</v>
@@ -38426,7 +38678,7 @@
         </is>
       </c>
       <c r="Z339" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA339" t="n">
         <v>-3.32</v>
@@ -38550,7 +38802,7 @@
         </is>
       </c>
       <c r="Z340" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA340" t="n">
         <v>1.48</v>
@@ -38674,7 +38926,7 @@
         </is>
       </c>
       <c r="Z341" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA341" t="n">
         <v>0.97</v>
@@ -38798,7 +39050,7 @@
         </is>
       </c>
       <c r="Z342" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA342" t="n">
         <v>3.57</v>
@@ -38922,7 +39174,7 @@
         </is>
       </c>
       <c r="Z343" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA343" t="n">
         <v>2.44</v>
@@ -39046,7 +39298,7 @@
         </is>
       </c>
       <c r="Z344" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA344" t="n">
         <v>1.38</v>
@@ -39170,7 +39422,7 @@
         </is>
       </c>
       <c r="Z345" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA345" t="n">
         <v>3.52</v>
@@ -39294,7 +39546,7 @@
         </is>
       </c>
       <c r="Z346" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA346" t="n">
         <v>9.26</v>
@@ -39418,7 +39670,7 @@
         </is>
       </c>
       <c r="Z347" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA347" t="n">
         <v>2.91</v>
@@ -39542,7 +39794,7 @@
         </is>
       </c>
       <c r="Z348" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA348" t="n">
         <v>2.49</v>
@@ -39666,7 +39918,7 @@
         </is>
       </c>
       <c r="Z349" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA349" t="n">
         <v>4.28</v>
@@ -39790,7 +40042,7 @@
         </is>
       </c>
       <c r="Z350" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA350" t="n">
         <v>8.880000000000001</v>
@@ -39914,7 +40166,7 @@
         </is>
       </c>
       <c r="Z351" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA351" t="n">
         <v>-12.04</v>
@@ -40038,7 +40290,7 @@
         </is>
       </c>
       <c r="Z352" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA352" t="n">
         <v>-4.34</v>
@@ -40162,7 +40414,7 @@
         </is>
       </c>
       <c r="Z353" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA353" t="n">
         <v>1.39</v>
@@ -40730,7 +40982,7 @@
         </is>
       </c>
       <c r="Z358" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA358" t="n">
         <v>-7.02</v>
@@ -40854,7 +41106,7 @@
         </is>
       </c>
       <c r="Z359" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA359" t="n">
         <v>-10.92</v>
@@ -40978,7 +41230,7 @@
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -41102,7 +41354,7 @@
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -41226,7 +41478,7 @@
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -41350,7 +41602,7 @@
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -41474,7 +41726,7 @@
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -41598,7 +41850,7 @@
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -41722,7 +41974,7 @@
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -41846,7 +42098,7 @@
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -41970,7 +42222,7 @@
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -42094,7 +42346,7 @@
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -42218,7 +42470,7 @@
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -42342,7 +42594,7 @@
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -42466,7 +42718,7 @@
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -42590,7 +42842,7 @@
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -42714,7 +42966,7 @@
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -42838,7 +43090,7 @@
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -42962,7 +43214,7 @@
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -43086,7 +43338,7 @@
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -43432,7 +43684,7 @@
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -43556,7 +43808,7 @@
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -43791,7 +44043,7 @@
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -43915,7 +44167,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -44039,7 +44291,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -44163,7 +44415,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -44287,7 +44539,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -44411,7 +44663,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -44535,7 +44787,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -44656,7 +44908,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -44780,7 +45032,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -44904,7 +45156,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -45028,7 +45280,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -45152,7 +45404,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -45276,7 +45528,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -45400,7 +45652,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -45524,7 +45776,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -45648,7 +45900,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -45772,7 +46024,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -45896,7 +46148,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -46020,7 +46272,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -46144,7 +46396,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -46268,7 +46520,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -46392,7 +46644,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -46516,7 +46768,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -46640,7 +46892,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -46764,7 +47016,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -46888,7 +47140,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -47012,7 +47264,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -47469,7 +47721,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -47593,7 +47845,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -47717,7 +47969,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -47841,7 +48093,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -47965,7 +48217,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -48089,7 +48341,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -48213,7 +48465,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -48337,7 +48589,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -48461,7 +48713,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -48585,7 +48837,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -48709,7 +48961,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -48833,7 +49085,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -48957,7 +49209,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -49081,7 +49333,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -49205,7 +49457,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -49329,7 +49581,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -49453,7 +49705,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -49577,7 +49829,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -49701,7 +49953,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -49825,7 +50077,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -49949,7 +50201,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -50073,7 +50325,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -50419,7 +50671,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -50654,13 +50906,16 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
       </c>
       <c r="AB439" t="n">
         <v>0.71</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>1.28</v>
       </c>
       <c r="AG439" t="b">
         <v>0</v>
@@ -50775,13 +51030,16 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
       </c>
       <c r="AB440" t="n">
         <v>-0.77</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>2.61</v>
       </c>
       <c r="AG440" t="b">
         <v>0</v>
@@ -50896,13 +51154,16 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
       </c>
       <c r="AB441" t="n">
         <v>-1.49</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>8.09</v>
       </c>
       <c r="AG441" t="b">
         <v>0</v>
@@ -51017,13 +51278,16 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
       </c>
       <c r="AB442" t="n">
         <v>-5.81</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>-4.11</v>
       </c>
       <c r="AG442" t="b">
         <v>0</v>
@@ -51138,13 +51402,16 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
       </c>
       <c r="AB443" t="n">
         <v>16.79</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>17.88</v>
       </c>
       <c r="AG443" t="b">
         <v>1</v>
@@ -51259,13 +51526,16 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
       </c>
       <c r="AB444" t="n">
         <v>-3.9</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>-2.81</v>
       </c>
       <c r="AG444" t="b">
         <v>0</v>
@@ -51380,13 +51650,16 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
       </c>
       <c r="AB445" t="n">
         <v>7.73</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>-8.17</v>
       </c>
       <c r="AG445" t="b">
         <v>0</v>
@@ -51501,13 +51774,16 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
       </c>
       <c r="AB446" t="n">
         <v>9.98</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>5.73</v>
       </c>
       <c r="AG446" t="b">
         <v>0</v>
@@ -51622,13 +51898,16 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
       </c>
       <c r="AB447" t="n">
         <v>4.02</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>0.45</v>
       </c>
       <c r="AG447" t="b">
         <v>0</v>
@@ -51743,13 +52022,16 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
       </c>
       <c r="AB448" t="n">
         <v>3.11</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>-1.13</v>
       </c>
       <c r="AG448" t="b">
         <v>0</v>
@@ -51864,13 +52146,16 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
       </c>
       <c r="AB449" t="n">
         <v>3.69</v>
+      </c>
+      <c r="AC449" t="n">
+        <v>1.01</v>
       </c>
       <c r="AG449" t="b">
         <v>0</v>
@@ -51985,13 +52270,16 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
       </c>
       <c r="AB450" t="n">
         <v>-1.32</v>
+      </c>
+      <c r="AC450" t="n">
+        <v>-2.64</v>
       </c>
       <c r="AG450" t="b">
         <v>0</v>
@@ -52106,13 +52394,16 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
       </c>
       <c r="AB451" t="n">
         <v>5.36</v>
+      </c>
+      <c r="AC451" t="n">
+        <v>-1.07</v>
       </c>
       <c r="AG451" t="b">
         <v>0</v>
@@ -52227,13 +52518,16 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
       </c>
       <c r="AB452" t="n">
         <v>1.1</v>
+      </c>
+      <c r="AC452" t="n">
+        <v>-0.44</v>
       </c>
       <c r="AG452" t="b">
         <v>0</v>
@@ -52348,13 +52642,16 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
       </c>
       <c r="AB453" t="n">
         <v>0.23</v>
+      </c>
+      <c r="AC453" t="n">
+        <v>-3.62</v>
       </c>
       <c r="AG453" t="b">
         <v>0</v>
@@ -52469,13 +52766,16 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
       </c>
       <c r="AB454" t="n">
         <v>4.49</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>0.46</v>
       </c>
       <c r="AG454" t="b">
         <v>0</v>
@@ -52590,13 +52890,16 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
       </c>
       <c r="AB455" t="n">
         <v>5.42</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>2.25</v>
       </c>
       <c r="AG455" t="b">
         <v>0</v>
@@ -52711,13 +53014,16 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
       </c>
       <c r="AB456" t="n">
         <v>-6.7</v>
+      </c>
+      <c r="AC456" t="n">
+        <v>-5.86</v>
       </c>
       <c r="AG456" t="b">
         <v>0</v>
@@ -52832,13 +53138,16 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
       </c>
       <c r="AB457" t="n">
         <v>3.2</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>6.85</v>
       </c>
       <c r="AG457" t="b">
         <v>0</v>
@@ -52953,13 +53262,16 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
       </c>
       <c r="AB458" t="n">
         <v>4.24</v>
+      </c>
+      <c r="AC458" t="n">
+        <v>3.39</v>
       </c>
       <c r="AG458" t="b">
         <v>0</v>
@@ -53296,13 +53608,16 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
       </c>
       <c r="AB461" t="n">
         <v>40.52</v>
+      </c>
+      <c r="AC461" t="n">
+        <v>32.55</v>
       </c>
       <c r="AG461" t="b">
         <v>1</v>
@@ -53417,13 +53732,16 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AB462" t="n">
         <v>0.74</v>
+      </c>
+      <c r="AC462" t="n">
+        <v>-3.17</v>
       </c>
       <c r="AG462" t="b">
         <v>0</v>
@@ -53538,7 +53856,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -53659,7 +53977,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -53780,7 +54098,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -53901,7 +54219,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -54022,7 +54340,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -54143,7 +54461,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -54264,7 +54582,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -54385,7 +54703,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -54506,7 +54824,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -54627,7 +54945,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -54748,7 +55066,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -54869,7 +55187,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -54990,7 +55308,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -55111,7 +55429,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -55232,7 +55550,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -55353,7 +55671,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -55807,7 +56125,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -55928,7 +56246,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -55937,7 +56255,7 @@
         <v>10.37</v>
       </c>
       <c r="AG483" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH483" t="b">
         <v>0</v>
@@ -56049,7 +56367,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -56170,7 +56488,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -56291,7 +56609,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -56412,7 +56730,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -56533,7 +56851,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -56654,7 +56972,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -56775,7 +57093,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -56896,7 +57214,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -57017,7 +57335,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -57138,7 +57456,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -57259,7 +57577,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -57380,7 +57698,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -57501,7 +57819,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -57622,7 +57940,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -57743,7 +58061,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -57864,7 +58182,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -57985,7 +58303,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -58106,7 +58424,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -58227,7 +58545,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -58348,7 +58666,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -58469,7 +58787,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -58590,7 +58908,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -58711,7 +59029,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -58832,7 +59150,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -58953,7 +59271,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -59074,7 +59392,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -59195,7 +59513,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -59316,7 +59634,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -59328,7 +59646,7 @@
         <v>0</v>
       </c>
       <c r="AH511" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI511" t="inlineStr">
         <is>
@@ -59437,7 +59755,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -59449,7 +59767,7 @@
         <v>0</v>
       </c>
       <c r="AH512" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI512" t="inlineStr">
         <is>
@@ -59558,7 +59876,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -59679,7 +59997,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -59800,7 +60118,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -59921,7 +60239,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -60042,7 +60360,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -60163,7 +60481,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -60284,7 +60602,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -60405,7 +60723,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -60526,7 +60844,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -60647,10 +60965,13 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
+      </c>
+      <c r="AB522" t="n">
+        <v>-2.78</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -60765,10 +61086,13 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
+      </c>
+      <c r="AB523" t="n">
+        <v>-3.52</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -60883,10 +61207,13 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
+      </c>
+      <c r="AB524" t="n">
+        <v>-0.33</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -61001,10 +61328,13 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
+      </c>
+      <c r="AB525" t="n">
+        <v>-3.28</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -61119,10 +61449,13 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
+      </c>
+      <c r="AB526" t="n">
+        <v>-0.66</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -61237,10 +61570,13 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
+      </c>
+      <c r="AB527" t="n">
+        <v>-5.69</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -61355,16 +61691,19 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
       </c>
+      <c r="AB528" t="n">
+        <v>-4.95</v>
+      </c>
       <c r="AG528" t="b">
         <v>0</v>
       </c>
       <c r="AH528" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI528" t="inlineStr">
         <is>
@@ -61473,10 +61812,13 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
+      </c>
+      <c r="AB529" t="n">
+        <v>-2.02</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -61591,10 +61933,13 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
+      </c>
+      <c r="AB530" t="n">
+        <v>-2.58</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -61709,10 +62054,13 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
+      </c>
+      <c r="AB531" t="n">
+        <v>-2.15</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -61827,10 +62175,13 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+      <c r="AB532" t="n">
+        <v>-1.61</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -61945,10 +62296,13 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
+      </c>
+      <c r="AB533" t="n">
+        <v>30.9</v>
       </c>
       <c r="AG533" t="b">
         <v>1</v>
@@ -62063,10 +62417,13 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
+      </c>
+      <c r="AB534" t="n">
+        <v>16.46</v>
       </c>
       <c r="AG534" t="b">
         <v>1</v>
@@ -62181,10 +62538,13 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+      <c r="AB535" t="n">
+        <v>-1.41</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -62299,10 +62659,13 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
+      </c>
+      <c r="AB536" t="n">
+        <v>-3.7</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -62417,7 +62780,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
@@ -62535,7 +62898,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -62653,7 +63016,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
@@ -62771,7 +63134,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
@@ -62780,7 +63143,7 @@
         <v>0</v>
       </c>
       <c r="AH540" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI540" t="inlineStr">
         <is>
@@ -62889,7 +63252,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
@@ -63007,7 +63370,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
@@ -63125,7 +63488,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
@@ -63134,7 +63497,7 @@
         <v>0</v>
       </c>
       <c r="AH543" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI543" t="inlineStr">
         <is>
@@ -63243,7 +63606,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
@@ -63361,7 +63724,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
@@ -63479,7 +63842,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
@@ -63488,7 +63851,7 @@
         <v>0</v>
       </c>
       <c r="AH546" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI546" t="inlineStr">
         <is>
@@ -63597,7 +63960,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
@@ -63715,7 +64078,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
@@ -63833,7 +64196,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
@@ -63951,7 +64314,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
@@ -64291,7 +64654,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
@@ -64409,7 +64772,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
@@ -64527,7 +64890,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
@@ -64756,7 +65119,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA557" t="n">
         <v>-0.77</v>
@@ -64874,7 +65237,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA558" t="n">
         <v>0.85</v>
@@ -64992,7 +65355,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA559" t="n">
         <v>-2.33</v>
@@ -65110,7 +65473,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA560" t="n">
         <v>4.41</v>
@@ -65228,7 +65591,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA561" t="n">
         <v>-1.6</v>
@@ -65346,7 +65709,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA562" t="n">
         <v>14</v>
@@ -65461,7 +65824,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA563" t="n">
         <v>-4.15</v>
@@ -65579,7 +65942,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA564" t="n">
         <v>-4.8</v>
@@ -65588,7 +65951,7 @@
         <v>0</v>
       </c>
       <c r="AH564" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI564" t="inlineStr">
         <is>
@@ -65697,7 +66060,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA565" t="n">
         <v>-4.49</v>
@@ -65706,7 +66069,7 @@
         <v>0</v>
       </c>
       <c r="AH565" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI565" t="inlineStr">
         <is>
@@ -65815,7 +66178,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA566" t="n">
         <v>-0.99</v>
@@ -65933,7 +66296,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA567" t="n">
         <v>-1.34</v>
@@ -66051,7 +66414,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA568" t="n">
         <v>-1.77</v>
@@ -66060,7 +66423,7 @@
         <v>0</v>
       </c>
       <c r="AH568" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI568" t="inlineStr">
         <is>
@@ -66169,7 +66532,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA569" t="n">
         <v>-3.59</v>
@@ -66287,7 +66650,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA570" t="n">
         <v>0.29</v>
@@ -66296,7 +66659,7 @@
         <v>0</v>
       </c>
       <c r="AH570" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI570" t="inlineStr">
         <is>
@@ -66405,7 +66768,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA571" t="n">
         <v>-4.43</v>
@@ -66523,7 +66886,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA572" t="n">
         <v>-3.52</v>
@@ -66532,7 +66895,7 @@
         <v>0</v>
       </c>
       <c r="AH572" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI572" t="inlineStr">
         <is>
@@ -66641,7 +67004,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA573" t="n">
         <v>-1.74</v>
@@ -66759,7 +67122,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA574" t="n">
         <v>-3.79</v>
@@ -66877,7 +67240,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA575" t="n">
         <v>-3.07</v>
@@ -66995,7 +67358,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA576" t="n">
         <v>-1.21</v>
@@ -67446,7 +67809,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA580" t="n">
         <v>31.15</v>
@@ -67564,7 +67927,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA581" t="n">
         <v>2.49</v>
@@ -67682,7 +68045,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA582" t="n">
         <v>-0.9399999999999999</v>
@@ -67800,7 +68163,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA583" t="n">
         <v>-3.99</v>
@@ -68029,7 +68392,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA585" t="n">
         <v>3.78</v>
@@ -68147,7 +68510,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA586" t="n">
         <v>-0.88</v>
@@ -68265,7 +68628,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA587" t="n">
         <v>-1.6</v>
@@ -68383,7 +68746,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA588" t="n">
         <v>4.07</v>
@@ -68501,7 +68864,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA589" t="n">
         <v>-1.9</v>
@@ -68619,7 +68982,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA590" t="n">
         <v>15.49</v>
@@ -68737,7 +69100,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA591" t="n">
         <v>4.25</v>
@@ -68855,7 +69218,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA592" t="n">
         <v>-4.09</v>
@@ -68973,7 +69336,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA593" t="n">
         <v>-5.77</v>
@@ -68982,7 +69345,7 @@
         <v>0</v>
       </c>
       <c r="AH593" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI593" t="inlineStr">
         <is>
@@ -69088,7 +69451,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA594" t="n">
         <v>0.66</v>
@@ -69206,7 +69569,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA595" t="n">
         <v>0.9</v>
@@ -69324,7 +69687,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA596" t="n">
         <v>-0.89</v>
@@ -69333,7 +69696,7 @@
         <v>0</v>
       </c>
       <c r="AH596" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI596" t="inlineStr">
         <is>
@@ -69442,7 +69805,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA597" t="n">
         <v>-3.23</v>
@@ -69560,7 +69923,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA598" t="n">
         <v>-1.86</v>
@@ -69569,7 +69932,7 @@
         <v>0</v>
       </c>
       <c r="AH598" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI598" t="inlineStr">
         <is>
@@ -69678,7 +70041,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA599" t="n">
         <v>-3.91</v>
@@ -69796,7 +70159,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA600" t="n">
         <v>-5.86</v>
@@ -69805,7 +70168,7 @@
         <v>0</v>
       </c>
       <c r="AH600" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI600" t="inlineStr">
         <is>
@@ -69914,7 +70277,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA601" t="n">
         <v>-2.98</v>
@@ -70032,7 +70395,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA602" t="n">
         <v>-3.02</v>
@@ -70150,7 +70513,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA603" t="n">
         <v>-2.06</v>
@@ -70268,7 +70631,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA604" t="n">
         <v>-0.87</v>
@@ -70386,7 +70749,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA605" t="n">
         <v>0.58</v>
@@ -70501,7 +70864,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA606" t="n">
         <v>-2.42</v>
@@ -71063,7 +71426,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA611" t="n">
         <v>1.45</v>
@@ -71178,7 +71541,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA612" t="n">
         <v>-2.34</v>
@@ -71407,7 +71770,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA614" t="n">
         <v>-4.58</v>
@@ -71525,7 +71888,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA615" t="n">
         <v>6.68</v>
@@ -71643,7 +72006,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA616" t="n">
         <v>-1.59</v>
@@ -71761,7 +72124,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA617" t="n">
         <v>-10.11</v>
@@ -71879,7 +72242,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA618" t="n">
         <v>-2.58</v>
@@ -71997,7 +72360,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA619" t="n">
         <v>-1.8</v>
@@ -72115,7 +72478,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA620" t="n">
         <v>-3.27</v>
@@ -72230,7 +72593,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA621" t="n">
         <v>-2.27</v>
@@ -72348,7 +72711,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA622" t="n">
         <v>-1.77</v>
@@ -72466,7 +72829,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA623" t="n">
         <v>-3.96</v>
@@ -72475,7 +72838,7 @@
         <v>0</v>
       </c>
       <c r="AH623" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI623" t="inlineStr">
         <is>
@@ -72584,7 +72947,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA624" t="n">
         <v>-2.7</v>
@@ -72593,7 +72956,7 @@
         <v>0</v>
       </c>
       <c r="AH624" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI624" t="inlineStr">
         <is>
@@ -72702,7 +73065,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA625" t="n">
         <v>-3.17</v>
@@ -72820,7 +73183,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA626" t="n">
         <v>-2.84</v>
@@ -72938,7 +73301,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA627" t="n">
         <v>0.59</v>
@@ -73056,7 +73419,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA628" t="n">
         <v>0.19</v>
@@ -73171,7 +73534,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA629" t="n">
         <v>-4.02</v>
@@ -73622,7 +73985,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA633" t="n">
         <v>5.58</v>
@@ -73740,7 +74103,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA634" t="n">
         <v>8.529999999999999</v>
@@ -73969,7 +74332,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA636" t="n">
         <v>7.05</v>
@@ -74198,7 +74561,10 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA638" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="AG638" t="b">
         <v>0</v>
@@ -74313,7 +74679,10 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA639" t="n">
+        <v>-14.75</v>
       </c>
       <c r="AG639" t="b">
         <v>0</v>
@@ -74428,7 +74797,10 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA640" t="n">
+        <v>-3.86</v>
       </c>
       <c r="AG640" t="b">
         <v>0</v>
@@ -74543,13 +74915,16 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA641" t="n">
+        <v>-4.11</v>
       </c>
       <c r="AG641" t="b">
         <v>0</v>
       </c>
       <c r="AH641" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI641" t="inlineStr">
         <is>
@@ -74655,7 +75030,10 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA642" t="n">
+        <v>-2.59</v>
       </c>
       <c r="AG642" t="b">
         <v>0</v>
@@ -74770,13 +75148,16 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA643" t="n">
+        <v>-6.11</v>
       </c>
       <c r="AG643" t="b">
         <v>0</v>
       </c>
       <c r="AH643" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI643" t="inlineStr">
         <is>
@@ -74885,7 +75266,10 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA644" t="n">
+        <v>-1.52</v>
       </c>
       <c r="AG644" t="b">
         <v>0</v>
@@ -75000,13 +75384,16 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA645" t="n">
+        <v>-4.53</v>
       </c>
       <c r="AG645" t="b">
         <v>0</v>
       </c>
       <c r="AH645" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI645" t="inlineStr">
         <is>
@@ -75115,13 +75502,16 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA646" t="n">
+        <v>-3.85</v>
       </c>
       <c r="AG646" t="b">
         <v>0</v>
       </c>
       <c r="AH646" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI646" t="inlineStr">
         <is>
@@ -75230,7 +75620,10 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA647" t="n">
+        <v>-3.85</v>
       </c>
       <c r="AG647" t="b">
         <v>0</v>
@@ -75345,7 +75738,10 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA648" t="n">
+        <v>-3.01</v>
       </c>
       <c r="AG648" t="b">
         <v>0</v>
@@ -75460,7 +75856,10 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA649" t="n">
+        <v>3.54</v>
       </c>
       <c r="AG649" t="b">
         <v>0</v>
@@ -75575,7 +75974,10 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA650" t="n">
+        <v>-1.86</v>
       </c>
       <c r="AG650" t="b">
         <v>0</v>
@@ -76023,7 +76425,10 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA654" t="n">
+        <v>9.09</v>
       </c>
       <c r="AG654" t="b">
         <v>0</v>
@@ -76360,7 +76765,7 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG657" t="b">
         <v>0</v>
@@ -76475,7 +76880,7 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG658" t="b">
         <v>0</v>
@@ -76590,7 +76995,7 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG659" t="b">
         <v>0</v>
@@ -76705,7 +77110,7 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG660" t="b">
         <v>0</v>
@@ -76820,7 +77225,7 @@
         </is>
       </c>
       <c r="Z661" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG661" t="b">
         <v>0</v>
@@ -76935,7 +77340,7 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG662" t="b">
         <v>0</v>
@@ -77050,7 +77455,7 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG663" t="b">
         <v>0</v>
@@ -77165,7 +77570,7 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG664" t="b">
         <v>0</v>
@@ -77277,7 +77682,7 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG665" t="b">
         <v>0</v>
@@ -77392,13 +77797,13 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG666" t="b">
         <v>0</v>
       </c>
       <c r="AH666" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI666" t="inlineStr">
         <is>
@@ -77507,7 +77912,7 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG667" t="b">
         <v>0</v>
@@ -77622,13 +78027,13 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG668" t="b">
         <v>0</v>
       </c>
       <c r="AH668" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI668" t="inlineStr">
         <is>
@@ -77737,13 +78142,13 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG669" t="b">
         <v>0</v>
       </c>
       <c r="AH669" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI669" t="inlineStr">
         <is>
@@ -77852,7 +78257,7 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG670" t="b">
         <v>0</v>
@@ -77967,7 +78372,7 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG671" t="b">
         <v>0</v>
@@ -78082,7 +78487,7 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG672" t="b">
         <v>0</v>
@@ -78197,7 +78602,7 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG673" t="b">
         <v>0</v>
@@ -78534,13 +78939,13 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG676" t="b">
         <v>0</v>
       </c>
       <c r="AH676" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI676" t="inlineStr">
         <is>
@@ -78760,7 +79165,7 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG678" t="b">
         <v>0</v>
@@ -78875,7 +79280,7 @@
         </is>
       </c>
       <c r="Z679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG679" t="b">
         <v>0</v>
@@ -78990,7 +79395,7 @@
         </is>
       </c>
       <c r="Z680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG680" t="b">
         <v>0</v>
@@ -79105,7 +79510,7 @@
         </is>
       </c>
       <c r="Z681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG681" t="b">
         <v>0</v>
@@ -79220,7 +79625,7 @@
         </is>
       </c>
       <c r="Z682" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG682" t="b">
         <v>0</v>
@@ -79335,7 +79740,7 @@
         </is>
       </c>
       <c r="Z683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG683" t="b">
         <v>0</v>
@@ -79450,7 +79855,7 @@
         </is>
       </c>
       <c r="Z684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG684" t="b">
         <v>0</v>
@@ -79565,7 +79970,7 @@
         </is>
       </c>
       <c r="Z685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG685" t="b">
         <v>0</v>
@@ -79680,7 +80085,7 @@
         </is>
       </c>
       <c r="Z686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG686" t="b">
         <v>0</v>
@@ -79795,7 +80200,7 @@
         </is>
       </c>
       <c r="Z687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG687" t="b">
         <v>0</v>
@@ -79910,7 +80315,7 @@
         </is>
       </c>
       <c r="Z688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG688" t="b">
         <v>0</v>
@@ -80358,7 +80763,7 @@
         </is>
       </c>
       <c r="Z692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG692" t="b">
         <v>0</v>
@@ -80584,7 +80989,7 @@
         </is>
       </c>
       <c r="Z694" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG694" t="b">
         <v>0</v>
@@ -80699,7 +81104,7 @@
         </is>
       </c>
       <c r="Z695" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG695" t="b">
         <v>0</v>
@@ -81036,7 +81441,7 @@
         </is>
       </c>
       <c r="Z698" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG698" t="b">
         <v>0</v>
@@ -81151,7 +81556,7 @@
         </is>
       </c>
       <c r="Z699" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG699" t="b">
         <v>0</v>
@@ -81266,7 +81671,7 @@
         </is>
       </c>
       <c r="Z700" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG700" t="b">
         <v>0</v>
@@ -81381,7 +81786,7 @@
         </is>
       </c>
       <c r="Z701" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG701" t="b">
         <v>0</v>
@@ -81496,7 +81901,7 @@
         </is>
       </c>
       <c r="Z702" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG702" t="b">
         <v>0</v>
@@ -81611,7 +82016,7 @@
         </is>
       </c>
       <c r="Z703" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG703" t="b">
         <v>0</v>
@@ -82059,7 +82464,7 @@
         </is>
       </c>
       <c r="Z707" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG707" t="b">
         <v>0</v>
@@ -82285,7 +82690,7 @@
         </is>
       </c>
       <c r="Z709" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG709" t="b">
         <v>0</v>
@@ -82400,7 +82805,7 @@
         </is>
       </c>
       <c r="Z710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG710" t="b">
         <v>0</v>
@@ -82515,7 +82920,7 @@
         </is>
       </c>
       <c r="Z711" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG711" t="b">
         <v>0</v>
@@ -82852,7 +83257,7 @@
         </is>
       </c>
       <c r="Z714" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG714" t="b">
         <v>0</v>
@@ -82967,7 +83372,7 @@
         </is>
       </c>
       <c r="Z715" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG715" t="b">
         <v>0</v>
@@ -83082,7 +83487,7 @@
         </is>
       </c>
       <c r="Z716" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG716" t="b">
         <v>0</v>
@@ -83197,7 +83602,7 @@
         </is>
       </c>
       <c r="Z717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG717" t="b">
         <v>0</v>
@@ -83312,7 +83717,7 @@
         </is>
       </c>
       <c r="Z718" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG718" t="b">
         <v>0</v>
@@ -83427,7 +83832,7 @@
         </is>
       </c>
       <c r="Z719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG719" t="b">
         <v>0</v>
@@ -83542,13 +83947,13 @@
         </is>
       </c>
       <c r="Z720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG720" t="b">
         <v>0</v>
       </c>
       <c r="AH720" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI720" t="inlineStr">
         <is>
@@ -83657,7 +84062,7 @@
         </is>
       </c>
       <c r="Z721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG721" t="b">
         <v>0</v>
@@ -83772,7 +84177,7 @@
         </is>
       </c>
       <c r="Z722" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG722" t="b">
         <v>0</v>
@@ -83887,7 +84292,7 @@
         </is>
       </c>
       <c r="Z723" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG723" t="b">
         <v>0</v>
@@ -84113,7 +84518,7 @@
         </is>
       </c>
       <c r="Z725" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG725" t="b">
         <v>0</v>
@@ -84339,7 +84744,7 @@
         </is>
       </c>
       <c r="Z727" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG727" t="b">
         <v>0</v>
@@ -84454,7 +84859,7 @@
         </is>
       </c>
       <c r="Z728" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG728" t="b">
         <v>0</v>
@@ -84680,7 +85085,7 @@
         </is>
       </c>
       <c r="Z730" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG730" t="b">
         <v>0</v>
@@ -84689,13 +85094,2408 @@
         <v>0</v>
       </c>
       <c r="AI730" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>70.38</v>
+      </c>
+      <c r="F731" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I731" t="b">
+        <v>0</v>
+      </c>
+      <c r="J731" t="n">
+        <v>10</v>
+      </c>
+      <c r="K731" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M731" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N731" t="n">
+        <v>5</v>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P731" t="n">
+        <v>242.75</v>
+      </c>
+      <c r="Q731" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S731" t="n">
+        <v>7</v>
+      </c>
+      <c r="T731" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U731" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V731" t="n">
+        <v>254</v>
+      </c>
+      <c r="W731" t="n">
+        <v>304.8</v>
+      </c>
+      <c r="X731" t="n">
+        <v>236.22</v>
+      </c>
+      <c r="Y731" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z731" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG731" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH731" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI731" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="F732" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I732" t="b">
+        <v>0</v>
+      </c>
+      <c r="J732" t="n">
+        <v>10</v>
+      </c>
+      <c r="K732" t="n">
+        <v>177.65</v>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M732" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N732" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P732" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="Q732" t="n">
+        <v>62</v>
+      </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S732" t="n">
+        <v>7</v>
+      </c>
+      <c r="T732" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U732" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V732" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="W732" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="X732" t="n">
+        <v>150.195</v>
+      </c>
+      <c r="Y732" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z732" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG732" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH732" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI732" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="F733" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I733" t="b">
+        <v>0</v>
+      </c>
+      <c r="J733" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="K733" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M733" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N733" t="n">
+        <v>7</v>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P733" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="Q733" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S733" t="n">
+        <v>7</v>
+      </c>
+      <c r="T733" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U733" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V733" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="W733" t="n">
+        <v>110.4762</v>
+      </c>
+      <c r="X733" t="n">
+        <v>88.72199999999999</v>
+      </c>
+      <c r="Y733" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z733" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG733" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH733" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI733" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>瑞昱</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="F734" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I734" t="b">
+        <v>0</v>
+      </c>
+      <c r="J734" t="n">
+        <v>10</v>
+      </c>
+      <c r="K734" t="n">
+        <v>838.2</v>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M734" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N734" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P734" t="n">
+        <v>740</v>
+      </c>
+      <c r="Q734" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S734" t="n">
+        <v>7</v>
+      </c>
+      <c r="T734" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U734" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V734" t="n">
+        <v>762</v>
+      </c>
+      <c r="W734" t="n">
+        <v>880.0452</v>
+      </c>
+      <c r="X734" t="n">
+        <v>708.66</v>
+      </c>
+      <c r="Y734" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z734" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG734" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH734" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI734" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>78.95999999999999</v>
+      </c>
+      <c r="F735" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I735" t="b">
+        <v>0</v>
+      </c>
+      <c r="J735" t="n">
+        <v>10</v>
+      </c>
+      <c r="K735" t="n">
+        <v>42.13</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M735" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N735" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P735" t="n">
+        <v>33.88</v>
+      </c>
+      <c r="Q735" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S735" t="n">
+        <v>7</v>
+      </c>
+      <c r="T735" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U735" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V735" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W735" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="X735" t="n">
+        <v>35.619</v>
+      </c>
+      <c r="Y735" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z735" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG735" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH735" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI735" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="F736" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I736" t="b">
+        <v>0</v>
+      </c>
+      <c r="J736" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K736" t="n">
+        <v>154</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>gap_MM_Target_Up</t>
+        </is>
+      </c>
+      <c r="M736" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N736" t="n">
+        <v>10</v>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P736" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="Q736" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S736" t="n">
+        <v>2.8935</v>
+      </c>
+      <c r="T736" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U736" t="inlineStr">
+        <is>
+          <t>telecom</t>
+        </is>
+      </c>
+      <c r="V736" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="W736" t="n">
+        <v>156.791</v>
+      </c>
+      <c r="X736" t="n">
+        <v>141.29</v>
+      </c>
+      <c r="Y736" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z736" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG736" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH736" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI736" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="F737" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I737" t="b">
+        <v>0</v>
+      </c>
+      <c r="J737" t="n">
+        <v>10</v>
+      </c>
+      <c r="K737" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M737" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N737" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P737" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="Q737" t="n">
+        <v>46.74</v>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S737" t="n">
+        <v>7</v>
+      </c>
+      <c r="T737" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U737" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V737" t="n">
+        <v>296</v>
+      </c>
+      <c r="W737" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="X737" t="n">
+        <v>275.28</v>
+      </c>
+      <c r="Y737" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z737" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG737" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH737" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI737" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="F738" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I738" t="b">
+        <v>0</v>
+      </c>
+      <c r="J738" t="n">
+        <v>10</v>
+      </c>
+      <c r="K738" t="n">
+        <v>5478</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M738" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N738" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P738" t="n">
+        <v>4955</v>
+      </c>
+      <c r="Q738" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S738" t="n">
+        <v>7</v>
+      </c>
+      <c r="T738" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U738" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V738" t="n">
+        <v>4980</v>
+      </c>
+      <c r="W738" t="n">
+        <v>5976</v>
+      </c>
+      <c r="X738" t="n">
+        <v>4631.4</v>
+      </c>
+      <c r="Y738" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z738" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG738" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH738" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI738" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="F739" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I739" t="b">
+        <v>0</v>
+      </c>
+      <c r="J739" t="n">
+        <v>10</v>
+      </c>
+      <c r="K739" t="n">
+        <v>3861</v>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M739" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N739" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P739" t="n">
+        <v>3350</v>
+      </c>
+      <c r="Q739" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="R739" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S739" t="n">
+        <v>7</v>
+      </c>
+      <c r="T739" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U739" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V739" t="n">
+        <v>3510</v>
+      </c>
+      <c r="W739" t="n">
+        <v>4212</v>
+      </c>
+      <c r="X739" t="n">
+        <v>3264.3</v>
+      </c>
+      <c r="Y739" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z739" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG739" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH739" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI739" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>77.62</v>
+      </c>
+      <c r="F740" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I740" t="b">
+        <v>0</v>
+      </c>
+      <c r="J740" t="n">
+        <v>10</v>
+      </c>
+      <c r="K740" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M740" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N740" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P740" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q740" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S740" t="n">
+        <v>7</v>
+      </c>
+      <c r="T740" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U740" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V740" t="n">
+        <v>213</v>
+      </c>
+      <c r="W740" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="X740" t="n">
+        <v>198.09</v>
+      </c>
+      <c r="Y740" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z740" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG740" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH740" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI740" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="F741" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I741" t="b">
+        <v>0</v>
+      </c>
+      <c r="J741" t="n">
+        <v>10</v>
+      </c>
+      <c r="K741" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M741" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N741" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P741" t="n">
+        <v>1081</v>
+      </c>
+      <c r="Q741" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S741" t="n">
+        <v>7</v>
+      </c>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U741" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V741" t="n">
+        <v>1215</v>
+      </c>
+      <c r="W741" t="n">
+        <v>1458</v>
+      </c>
+      <c r="X741" t="n">
+        <v>1129.95</v>
+      </c>
+      <c r="Y741" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z741" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG741" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH741" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI741" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>76.68000000000001</v>
+      </c>
+      <c r="F742" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I742" t="b">
+        <v>0</v>
+      </c>
+      <c r="J742" t="n">
+        <v>10</v>
+      </c>
+      <c r="K742" t="n">
+        <v>591.8</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M742" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N742" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P742" t="n">
+        <v>483</v>
+      </c>
+      <c r="Q742" t="n">
+        <v>61.59</v>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S742" t="n">
+        <v>7</v>
+      </c>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U742" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V742" t="n">
+        <v>538</v>
+      </c>
+      <c r="W742" t="n">
+        <v>645.6</v>
+      </c>
+      <c r="X742" t="n">
+        <v>500.34</v>
+      </c>
+      <c r="Y742" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI742" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ742" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>81.20999999999999</v>
+      </c>
+      <c r="F743" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I743" t="b">
+        <v>0</v>
+      </c>
+      <c r="J743" t="n">
+        <v>10</v>
+      </c>
+      <c r="K743" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M743" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N743" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P743" t="n">
+        <v>902</v>
+      </c>
+      <c r="Q743" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S743" t="n">
+        <v>7</v>
+      </c>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U743" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V743" t="n">
+        <v>1010</v>
+      </c>
+      <c r="W743" t="n">
+        <v>1212</v>
+      </c>
+      <c r="X743" t="n">
+        <v>939.3</v>
+      </c>
+      <c r="Y743" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z743" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG743" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH743" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI743" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>73.48999999999999</v>
+      </c>
+      <c r="F744" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I744" t="b">
+        <v>0</v>
+      </c>
+      <c r="J744" t="n">
+        <v>10</v>
+      </c>
+      <c r="K744" t="n">
+        <v>8690</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M744" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N744" t="n">
+        <v>3</v>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P744" t="n">
+        <v>7197.5</v>
+      </c>
+      <c r="Q744" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S744" t="n">
+        <v>7</v>
+      </c>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U744" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V744" t="n">
+        <v>7900</v>
+      </c>
+      <c r="W744" t="n">
+        <v>9480</v>
+      </c>
+      <c r="X744" t="n">
+        <v>7347</v>
+      </c>
+      <c r="Y744" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z744" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG744" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH744" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI744" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="F745" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I745" t="b">
+        <v>0</v>
+      </c>
+      <c r="J745" t="n">
+        <v>10</v>
+      </c>
+      <c r="K745" t="n">
+        <v>3569.5</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M745" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N745" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P745" t="n">
+        <v>3082.5</v>
+      </c>
+      <c r="Q745" t="n">
+        <v>53.76</v>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S745" t="n">
+        <v>7</v>
+      </c>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V745" t="n">
+        <v>3245</v>
+      </c>
+      <c r="W745" t="n">
+        <v>3894</v>
+      </c>
+      <c r="X745" t="n">
+        <v>3017.85</v>
+      </c>
+      <c r="Y745" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI745" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ745" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>74.84999999999999</v>
+      </c>
+      <c r="F746" t="n">
+        <v>49.79</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I746" t="b">
+        <v>0</v>
+      </c>
+      <c r="J746" t="n">
+        <v>10</v>
+      </c>
+      <c r="K746" t="n">
+        <v>521.4</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M746" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N746" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P746" t="n">
+        <v>448.75</v>
+      </c>
+      <c r="Q746" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S746" t="n">
+        <v>7</v>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V746" t="n">
+        <v>474</v>
+      </c>
+      <c r="W746" t="n">
+        <v>568.8</v>
+      </c>
+      <c r="X746" t="n">
+        <v>440.82</v>
+      </c>
+      <c r="Y746" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z746" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG746" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH746" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI746" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="F747" t="n">
+        <v>52.88</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I747" t="b">
+        <v>0</v>
+      </c>
+      <c r="J747" t="n">
+        <v>10</v>
+      </c>
+      <c r="K747" t="n">
+        <v>781</v>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M747" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N747" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P747" t="n">
+        <v>657.5</v>
+      </c>
+      <c r="Q747" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S747" t="n">
+        <v>7</v>
+      </c>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U747" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V747" t="n">
+        <v>710</v>
+      </c>
+      <c r="W747" t="n">
+        <v>852</v>
+      </c>
+      <c r="X747" t="n">
+        <v>660.3</v>
+      </c>
+      <c r="Y747" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z747" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG747" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH747" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI747" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="F748" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I748" t="b">
+        <v>0</v>
+      </c>
+      <c r="J748" t="n">
+        <v>10</v>
+      </c>
+      <c r="K748" t="n">
+        <v>202.95</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M748" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N748" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P748" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="Q748" t="n">
+        <v>65.98</v>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S748" t="n">
+        <v>7</v>
+      </c>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V748" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="W748" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="X748" t="n">
+        <v>171.585</v>
+      </c>
+      <c r="Y748" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI748" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ748" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="F749" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I749" t="b">
+        <v>0</v>
+      </c>
+      <c r="J749" t="n">
+        <v>10</v>
+      </c>
+      <c r="K749" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M749" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N749" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P749" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="Q749" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S749" t="n">
+        <v>7</v>
+      </c>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U749" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V749" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="W749" t="n">
+        <v>111.657</v>
+      </c>
+      <c r="X749" t="n">
+        <v>90.675</v>
+      </c>
+      <c r="Y749" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI749" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ749" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="F750" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I750" t="b">
+        <v>0</v>
+      </c>
+      <c r="J750" t="n">
+        <v>10</v>
+      </c>
+      <c r="K750" t="n">
+        <v>248.05</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M750" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N750" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P750" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q750" t="n">
+        <v>64</v>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S750" t="n">
+        <v>7</v>
+      </c>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U750" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V750" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="W750" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="X750" t="n">
+        <v>209.715</v>
+      </c>
+      <c r="Y750" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI750" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ750" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>73.98999999999999</v>
+      </c>
+      <c r="F751" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I751" t="b">
+        <v>0</v>
+      </c>
+      <c r="J751" t="n">
+        <v>10</v>
+      </c>
+      <c r="K751" t="n">
+        <v>1562</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M751" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N751" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P751" t="n">
+        <v>1237.5</v>
+      </c>
+      <c r="Q751" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S751" t="n">
+        <v>7</v>
+      </c>
+      <c r="T751" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U751" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V751" t="n">
+        <v>1420</v>
+      </c>
+      <c r="W751" t="n">
+        <v>1704</v>
+      </c>
+      <c r="X751" t="n">
+        <v>1320.6</v>
+      </c>
+      <c r="Y751" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z751" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG751" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH751" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI751" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ730"/>
+  <autoFilter ref="A1:AJ751"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -84768,25 +87568,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C2" t="n">
-        <v>0.374</v>
+        <v>0.3856</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.71</v>
+        <v>-2.89</v>
       </c>
       <c r="E2" t="n">
-        <v>8.15</v>
+        <v>8.42</v>
       </c>
       <c r="F2" t="n">
-        <v>-13.12</v>
+        <v>-12.76</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1832</v>
+        <v>0.1699</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="3">
@@ -84796,25 +87596,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5652</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>1.74</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7</v>
+        <v>7.84</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.85</v>
+        <v>-4.54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1304</v>
+        <v>0.1034</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1739</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="4">
@@ -84918,25 +87718,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.43</v>
+        <v>-5.95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.44</v>
+        <v>11.94</v>
       </c>
       <c r="F2" t="n">
-        <v>-16.69</v>
+        <v>-13.59</v>
       </c>
       <c r="G2" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -84946,25 +87746,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3571</v>
+        <v>0.3678</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.74</v>
+        <v>-3.69</v>
       </c>
       <c r="E3" t="n">
-        <v>5.99</v>
+        <v>6.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.89</v>
+        <v>-12.43</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1571</v>
+        <v>0.1379</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5571</v>
+        <v>0.5862000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -84974,25 +87774,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4324</v>
+        <v>0.439</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.72</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.62</v>
+        <v>-10.35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1757</v>
+        <v>0.1707</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5946</v>
+        <v>0.5732</v>
       </c>
     </row>
     <row r="5">
@@ -85002,25 +87802,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="D5" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="E5" t="n">
-        <v>8.300000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.48</v>
+        <v>-6.08</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="6">
@@ -85089,7 +87889,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-30 14:24:01</t>
+          <t>2026-10-01 14:26:53</t>
         </is>
       </c>
     </row>
@@ -85136,7 +87936,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>729</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -85146,7 +87946,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>276</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8">
@@ -85156,7 +87956,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$769</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$795</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ769"/>
+  <dimension ref="A1:AJ795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41433,11 +41433,11 @@
       </c>
       <c r="Y360" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z360" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA360" t="n">
         <v>0.71</v>
@@ -41448,6 +41448,15 @@
       <c r="AC360" t="n">
         <v>1.42</v>
       </c>
+      <c r="AD360" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>-1.7</v>
+      </c>
       <c r="AG360" t="b">
         <v>0</v>
       </c>
@@ -41456,7 +41465,7 @@
       </c>
       <c r="AI360" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -41557,11 +41566,11 @@
       </c>
       <c r="Y361" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z361" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA361" t="n">
         <v>-0.15</v>
@@ -41572,6 +41581,15 @@
       <c r="AC361" t="n">
         <v>-2.44</v>
       </c>
+      <c r="AD361" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>-6.85</v>
+      </c>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -41580,7 +41598,7 @@
       </c>
       <c r="AI361" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -41681,11 +41699,11 @@
       </c>
       <c r="Y362" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z362" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA362" t="n">
         <v>10.41</v>
@@ -41696,15 +41714,24 @@
       <c r="AC362" t="n">
         <v>7.69</v>
       </c>
+      <c r="AD362" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="AG362" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH362" t="b">
         <v>0</v>
       </c>
       <c r="AI362" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -41805,11 +41832,11 @@
       </c>
       <c r="Y363" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z363" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA363" t="n">
         <v>-2.68</v>
@@ -41820,6 +41847,15 @@
       <c r="AC363" t="n">
         <v>-4.01</v>
       </c>
+      <c r="AD363" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>-9.359999999999999</v>
+      </c>
       <c r="AG363" t="b">
         <v>0</v>
       </c>
@@ -41828,7 +41864,7 @@
       </c>
       <c r="AI363" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -41929,11 +41965,11 @@
       </c>
       <c r="Y364" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z364" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA364" t="n">
         <v>1.85</v>
@@ -41944,6 +41980,15 @@
       <c r="AC364" t="n">
         <v>-1.85</v>
       </c>
+      <c r="AD364" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>-7.31</v>
+      </c>
       <c r="AG364" t="b">
         <v>0</v>
       </c>
@@ -41952,7 +41997,7 @@
       </c>
       <c r="AI364" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -42053,11 +42098,11 @@
       </c>
       <c r="Y365" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z365" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA365" t="n">
         <v>0.3</v>
@@ -42068,6 +42113,15 @@
       <c r="AC365" t="n">
         <v>1.04</v>
       </c>
+      <c r="AD365" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>-2.09</v>
+      </c>
       <c r="AG365" t="b">
         <v>0</v>
       </c>
@@ -42076,7 +42130,7 @@
       </c>
       <c r="AI365" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -42177,11 +42231,11 @@
       </c>
       <c r="Y366" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z366" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA366" t="n">
         <v>8.76</v>
@@ -42192,6 +42246,15 @@
       <c r="AC366" t="n">
         <v>21.77</v>
       </c>
+      <c r="AD366" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="AF366" t="n">
+        <v>0</v>
+      </c>
       <c r="AG366" t="b">
         <v>1</v>
       </c>
@@ -42200,7 +42263,7 @@
       </c>
       <c r="AI366" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -42301,11 +42364,11 @@
       </c>
       <c r="Y367" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z367" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA367" t="n">
         <v>-4.33</v>
@@ -42316,6 +42379,15 @@
       <c r="AC367" t="n">
         <v>0</v>
       </c>
+      <c r="AD367" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="AF367" t="n">
+        <v>-7.79</v>
+      </c>
       <c r="AG367" t="b">
         <v>0</v>
       </c>
@@ -42324,7 +42396,7 @@
       </c>
       <c r="AI367" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -42425,11 +42497,11 @@
       </c>
       <c r="Y368" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z368" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA368" t="n">
         <v>1.02</v>
@@ -42440,6 +42512,15 @@
       <c r="AC368" t="n">
         <v>2.04</v>
       </c>
+      <c r="AD368" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AF368" t="n">
+        <v>-2.04</v>
+      </c>
       <c r="AG368" t="b">
         <v>0</v>
       </c>
@@ -42448,7 +42529,7 @@
       </c>
       <c r="AI368" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -42549,11 +42630,11 @@
       </c>
       <c r="Y369" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z369" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA369" t="n">
         <v>-1.78</v>
@@ -42564,6 +42645,15 @@
       <c r="AC369" t="n">
         <v>-1.78</v>
       </c>
+      <c r="AD369" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF369" t="n">
+        <v>-4</v>
+      </c>
       <c r="AG369" t="b">
         <v>0</v>
       </c>
@@ -42572,7 +42662,7 @@
       </c>
       <c r="AI369" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -42673,11 +42763,11 @@
       </c>
       <c r="Y370" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z370" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA370" t="n">
         <v>3.62</v>
@@ -42688,6 +42778,15 @@
       <c r="AC370" t="n">
         <v>8.5</v>
       </c>
+      <c r="AD370" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="AF370" t="n">
+        <v>0</v>
+      </c>
       <c r="AG370" t="b">
         <v>0</v>
       </c>
@@ -42696,7 +42795,7 @@
       </c>
       <c r="AI370" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -42797,11 +42896,11 @@
       </c>
       <c r="Y371" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z371" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA371" t="n">
         <v>4.05</v>
@@ -42812,6 +42911,15 @@
       <c r="AC371" t="n">
         <v>5.56</v>
       </c>
+      <c r="AD371" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE371" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="AF371" t="n">
+        <v>-0.93</v>
+      </c>
       <c r="AG371" t="b">
         <v>0</v>
       </c>
@@ -42820,7 +42928,7 @@
       </c>
       <c r="AI371" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -42921,11 +43029,11 @@
       </c>
       <c r="Y372" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z372" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA372" t="n">
         <v>1.75</v>
@@ -42936,6 +43044,15 @@
       <c r="AC372" t="n">
         <v>1.02</v>
       </c>
+      <c r="AD372" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>-2.92</v>
+      </c>
       <c r="AG372" t="b">
         <v>0</v>
       </c>
@@ -42944,7 +43061,7 @@
       </c>
       <c r="AI372" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -43045,11 +43162,11 @@
       </c>
       <c r="Y373" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z373" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA373" t="n">
         <v>1.69</v>
@@ -43060,6 +43177,15 @@
       <c r="AC373" t="n">
         <v>2.53</v>
       </c>
+      <c r="AD373" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="AE373" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AF373" t="n">
+        <v>-3.26</v>
+      </c>
       <c r="AG373" t="b">
         <v>0</v>
       </c>
@@ -43068,7 +43194,7 @@
       </c>
       <c r="AI373" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -43169,11 +43295,11 @@
       </c>
       <c r="Y374" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z374" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA374" t="n">
         <v>0.7</v>
@@ -43184,6 +43310,15 @@
       <c r="AC374" t="n">
         <v>5.99</v>
       </c>
+      <c r="AD374" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE374" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AF374" t="n">
+        <v>-1.06</v>
+      </c>
       <c r="AG374" t="b">
         <v>0</v>
       </c>
@@ -43192,7 +43327,7 @@
       </c>
       <c r="AI374" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -43293,11 +43428,11 @@
       </c>
       <c r="Y375" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z375" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA375" t="n">
         <v>3.12</v>
@@ -43308,6 +43443,15 @@
       <c r="AC375" t="n">
         <v>7.19</v>
       </c>
+      <c r="AD375" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="AF375" t="n">
+        <v>-1.22</v>
+      </c>
       <c r="AG375" t="b">
         <v>0</v>
       </c>
@@ -43316,7 +43460,7 @@
       </c>
       <c r="AI375" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -43417,11 +43561,11 @@
       </c>
       <c r="Y376" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z376" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA376" t="n">
         <v>-6.01</v>
@@ -43432,6 +43576,15 @@
       <c r="AC376" t="n">
         <v>-12.66</v>
       </c>
+      <c r="AD376" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="AE376" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF376" t="n">
+        <v>-19.72</v>
+      </c>
       <c r="AG376" t="b">
         <v>0</v>
       </c>
@@ -43440,7 +43593,7 @@
       </c>
       <c r="AI376" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -43541,11 +43694,11 @@
       </c>
       <c r="Y377" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z377" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA377" t="n">
         <v>1.69</v>
@@ -43556,6 +43709,15 @@
       <c r="AC377" t="n">
         <v>3.81</v>
       </c>
+      <c r="AD377" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AE377" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AF377" t="n">
+        <v>-1.27</v>
+      </c>
       <c r="AG377" t="b">
         <v>0</v>
       </c>
@@ -43564,7 +43726,7 @@
       </c>
       <c r="AI377" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -43887,11 +44049,11 @@
       </c>
       <c r="Y380" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z380" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA380" t="n">
         <v>0.12</v>
@@ -43902,6 +44064,15 @@
       <c r="AC380" t="n">
         <v>-6.91</v>
       </c>
+      <c r="AD380" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="AE380" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AF380" t="n">
+        <v>-19.51</v>
+      </c>
       <c r="AG380" t="b">
         <v>0</v>
       </c>
@@ -43910,7 +44081,7 @@
       </c>
       <c r="AI380" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -44011,11 +44182,11 @@
       </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z381" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA381" t="n">
         <v>0.5600000000000001</v>
@@ -44026,6 +44197,15 @@
       <c r="AC381" t="n">
         <v>-0.9399999999999999</v>
       </c>
+      <c r="AD381" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AF381" t="n">
+        <v>-3.93</v>
+      </c>
       <c r="AG381" t="b">
         <v>0</v>
       </c>
@@ -44034,7 +44214,7 @@
       </c>
       <c r="AI381" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -44246,11 +44426,11 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z383" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA383" t="n">
         <v>-5.25</v>
@@ -44261,6 +44441,15 @@
       <c r="AC383" t="n">
         <v>-14.55</v>
       </c>
+      <c r="AD383" t="n">
+        <v>-13.13</v>
+      </c>
+      <c r="AE383" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AF383" t="n">
+        <v>-16.16</v>
+      </c>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
@@ -44269,7 +44458,7 @@
       </c>
       <c r="AI383" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -44374,7 +44563,7 @@
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -44498,7 +44687,7 @@
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -44510,7 +44699,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AG385" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH385" t="b">
         <v>0</v>
@@ -44622,7 +44811,7 @@
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -44746,7 +44935,7 @@
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -44870,7 +45059,7 @@
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -44994,7 +45183,7 @@
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -45115,7 +45304,7 @@
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -45239,7 +45428,7 @@
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -45363,7 +45552,7 @@
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -45487,7 +45676,7 @@
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -45611,7 +45800,7 @@
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -45735,7 +45924,7 @@
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -45859,7 +46048,7 @@
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -45983,7 +46172,7 @@
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -46107,7 +46296,7 @@
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -46231,7 +46420,7 @@
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -46355,7 +46544,7 @@
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -46479,7 +46668,7 @@
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -46603,7 +46792,7 @@
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -46727,7 +46916,7 @@
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -46851,7 +47040,7 @@
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -46975,7 +47164,7 @@
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -47099,7 +47288,7 @@
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -47223,7 +47412,7 @@
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -47347,7 +47536,7 @@
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -47471,7 +47660,7 @@
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -47928,7 +48117,7 @@
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -48052,7 +48241,7 @@
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -48176,7 +48365,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -48300,7 +48489,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -48312,7 +48501,7 @@
         <v>10.85</v>
       </c>
       <c r="AG416" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH416" t="b">
         <v>0</v>
@@ -48424,7 +48613,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -48548,7 +48737,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -48672,7 +48861,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -48796,7 +48985,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -48920,7 +49109,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -49044,7 +49233,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -49168,7 +49357,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -49292,7 +49481,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -49416,7 +49605,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -49540,7 +49729,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -49664,7 +49853,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -49788,7 +49977,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -49912,7 +50101,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -50036,7 +50225,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -50160,7 +50349,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -50284,7 +50473,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -50408,7 +50597,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -50532,7 +50721,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -50878,7 +51067,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -51113,7 +51302,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -51237,7 +51426,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -51361,7 +51550,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -51373,7 +51562,7 @@
         <v>8.09</v>
       </c>
       <c r="AG441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH441" t="b">
         <v>0</v>
@@ -51485,7 +51674,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -51609,7 +51798,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -51733,7 +51922,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -51857,7 +52046,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -51981,7 +52170,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -52105,7 +52294,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -52229,7 +52418,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -52353,7 +52542,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -52477,7 +52666,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -52601,7 +52790,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -52725,7 +52914,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -52849,7 +53038,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -52973,7 +53162,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -53097,7 +53286,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -53221,7 +53410,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -53345,7 +53534,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -53469,7 +53658,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -53815,7 +54004,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -53939,7 +54128,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -54063,13 +54252,16 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
       </c>
       <c r="AB463" t="n">
         <v>0.71</v>
+      </c>
+      <c r="AC463" t="n">
+        <v>-0.85</v>
       </c>
       <c r="AG463" t="b">
         <v>0</v>
@@ -54184,13 +54376,16 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
       </c>
       <c r="AB464" t="n">
         <v>-2.29</v>
+      </c>
+      <c r="AC464" t="n">
+        <v>4.42</v>
       </c>
       <c r="AG464" t="b">
         <v>0</v>
@@ -54305,13 +54500,16 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
       </c>
       <c r="AB465" t="n">
         <v>-2.46</v>
+      </c>
+      <c r="AC465" t="n">
+        <v>17.21</v>
       </c>
       <c r="AG465" t="b">
         <v>0</v>
@@ -54426,13 +54624,16 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
       </c>
       <c r="AB466" t="n">
         <v>-6.03</v>
+      </c>
+      <c r="AC466" t="n">
+        <v>0.42</v>
       </c>
       <c r="AG466" t="b">
         <v>0</v>
@@ -54547,13 +54748,16 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
       </c>
       <c r="AB467" t="n">
         <v>8.07</v>
+      </c>
+      <c r="AC467" t="n">
+        <v>7.02</v>
       </c>
       <c r="AG467" t="b">
         <v>0</v>
@@ -54668,13 +54872,16 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
       </c>
       <c r="AB468" t="n">
         <v>-3.64</v>
+      </c>
+      <c r="AC468" t="n">
+        <v>0.61</v>
       </c>
       <c r="AG468" t="b">
         <v>0</v>
@@ -54789,13 +54996,16 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
       </c>
       <c r="AB469" t="n">
         <v>9.619999999999999</v>
+      </c>
+      <c r="AC469" t="n">
+        <v>25.16</v>
       </c>
       <c r="AG469" t="b">
         <v>1</v>
@@ -54910,13 +55120,16 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
       </c>
       <c r="AB470" t="n">
         <v>11.97</v>
+      </c>
+      <c r="AC470" t="n">
+        <v>9.43</v>
       </c>
       <c r="AG470" t="b">
         <v>0</v>
@@ -55031,13 +55244,16 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
       </c>
       <c r="AB471" t="n">
         <v>-0.28</v>
+      </c>
+      <c r="AC471" t="n">
+        <v>-3.35</v>
       </c>
       <c r="AG471" t="b">
         <v>0</v>
@@ -55152,13 +55368,16 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
       </c>
       <c r="AB472" t="n">
         <v>2.12</v>
+      </c>
+      <c r="AC472" t="n">
+        <v>-0.45</v>
       </c>
       <c r="AG472" t="b">
         <v>0</v>
@@ -55273,13 +55492,16 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
       </c>
       <c r="AB473" t="n">
         <v>4.7</v>
+      </c>
+      <c r="AC473" t="n">
+        <v>0.27</v>
       </c>
       <c r="AG473" t="b">
         <v>0</v>
@@ -55394,13 +55616,16 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
       </c>
       <c r="AB474" t="n">
         <v>1.45</v>
+      </c>
+      <c r="AC474" t="n">
+        <v>-0.33</v>
       </c>
       <c r="AG474" t="b">
         <v>0</v>
@@ -55515,13 +55740,16 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
       </c>
       <c r="AB475" t="n">
         <v>3.95</v>
+      </c>
+      <c r="AC475" t="n">
+        <v>0.13</v>
       </c>
       <c r="AG475" t="b">
         <v>0</v>
@@ -55636,13 +55864,16 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
       </c>
       <c r="AB476" t="n">
         <v>-11.86</v>
+      </c>
+      <c r="AC476" t="n">
+        <v>-9.619999999999999</v>
       </c>
       <c r="AG476" t="b">
         <v>0</v>
@@ -55757,13 +55988,16 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
       </c>
       <c r="AB477" t="n">
         <v>2.75</v>
+      </c>
+      <c r="AC477" t="n">
+        <v>3.61</v>
       </c>
       <c r="AG477" t="b">
         <v>0</v>
@@ -55878,12 +56112,15 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
       </c>
       <c r="AB478" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC478" t="n">
         <v>2.08</v>
       </c>
       <c r="AG478" t="b">
@@ -56332,13 +56569,16 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
       </c>
       <c r="AB482" t="n">
         <v>36.95</v>
+      </c>
+      <c r="AC482" t="n">
+        <v>38.15</v>
       </c>
       <c r="AG482" t="b">
         <v>1</v>
@@ -56453,13 +56693,16 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
       </c>
       <c r="AB483" t="n">
         <v>10.37</v>
+      </c>
+      <c r="AC483" t="n">
+        <v>14.51</v>
       </c>
       <c r="AG483" t="b">
         <v>1</v>
@@ -56574,13 +56817,16 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
       </c>
       <c r="AB484" t="n">
         <v>-1.49</v>
+      </c>
+      <c r="AC484" t="n">
+        <v>-3.54</v>
       </c>
       <c r="AG484" t="b">
         <v>0</v>
@@ -56695,7 +56941,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -56816,7 +57062,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -56825,7 +57071,7 @@
         <v>5.33</v>
       </c>
       <c r="AG486" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH486" t="b">
         <v>0</v>
@@ -56937,7 +57183,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -57058,7 +57304,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -57179,7 +57425,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -57300,7 +57546,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -57421,7 +57667,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -57542,7 +57788,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -57663,7 +57909,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -57784,7 +58030,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -57905,7 +58151,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -58026,7 +58272,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -58147,7 +58393,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -58268,7 +58514,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -58389,7 +58635,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -58510,7 +58756,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -58631,7 +58877,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -58752,7 +58998,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -58873,7 +59119,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -58994,7 +59240,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -59115,7 +59361,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -59236,7 +59482,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -59357,7 +59603,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -59478,7 +59724,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -59599,7 +59845,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -59720,7 +59966,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -59841,7 +60087,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -59962,7 +60208,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -60083,7 +60329,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -60204,7 +60450,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -60325,7 +60571,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -60446,7 +60692,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -60567,7 +60813,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -60688,7 +60934,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -60809,7 +61055,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -60930,7 +61176,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -61051,7 +61297,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -61172,7 +61418,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
@@ -61293,7 +61539,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
@@ -61414,7 +61660,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
@@ -61535,7 +61781,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
@@ -61656,7 +61902,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
@@ -61777,7 +62023,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
@@ -61898,7 +62144,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
@@ -62019,7 +62265,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
@@ -62140,7 +62386,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
@@ -62261,7 +62507,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
@@ -62382,7 +62628,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
@@ -62503,7 +62749,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
@@ -62624,7 +62870,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
@@ -62745,7 +62991,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
@@ -62866,7 +63112,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
@@ -62987,7 +63233,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
@@ -63108,7 +63354,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -63229,7 +63475,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
@@ -63350,7 +63596,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
@@ -63471,7 +63717,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
@@ -63592,7 +63838,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
@@ -63713,7 +63959,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
@@ -63834,7 +64080,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
@@ -63955,7 +64201,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
@@ -64076,7 +64322,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
@@ -64197,7 +64443,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
@@ -64318,7 +64564,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
@@ -64439,7 +64685,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
@@ -64560,7 +64806,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
@@ -64903,7 +65149,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
@@ -65024,7 +65270,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
@@ -65145,7 +65391,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
@@ -65377,10 +65623,13 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA557" t="n">
         <v>-0.77</v>
+      </c>
+      <c r="AB557" t="n">
+        <v>6.04</v>
       </c>
       <c r="AG557" t="b">
         <v>0</v>
@@ -65495,13 +65744,16 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA558" t="n">
         <v>0.85</v>
       </c>
+      <c r="AB558" t="n">
+        <v>21.19</v>
+      </c>
       <c r="AG558" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH558" t="b">
         <v>0</v>
@@ -65613,10 +65865,13 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA559" t="n">
         <v>-2.33</v>
+      </c>
+      <c r="AB559" t="n">
+        <v>4.37</v>
       </c>
       <c r="AG559" t="b">
         <v>0</v>
@@ -65731,10 +65986,13 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA560" t="n">
         <v>4.41</v>
+      </c>
+      <c r="AB560" t="n">
+        <v>3.39</v>
       </c>
       <c r="AG560" t="b">
         <v>0</v>
@@ -65849,10 +66107,13 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA561" t="n">
         <v>-1.6</v>
+      </c>
+      <c r="AB561" t="n">
+        <v>-3.78</v>
       </c>
       <c r="AG561" t="b">
         <v>0</v>
@@ -65967,10 +66228,13 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA562" t="n">
         <v>14</v>
+      </c>
+      <c r="AB562" t="n">
+        <v>30.17</v>
       </c>
       <c r="AG562" t="b">
         <v>1</v>
@@ -66082,10 +66346,13 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA563" t="n">
         <v>-4.15</v>
+      </c>
+      <c r="AB563" t="n">
+        <v>-8.300000000000001</v>
       </c>
       <c r="AG563" t="b">
         <v>0</v>
@@ -66200,10 +66467,13 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA564" t="n">
         <v>-4.8</v>
+      </c>
+      <c r="AB564" t="n">
+        <v>-7.73</v>
       </c>
       <c r="AG564" t="b">
         <v>0</v>
@@ -66318,10 +66588,13 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA565" t="n">
         <v>-4.49</v>
+      </c>
+      <c r="AB565" t="n">
+        <v>-6.89</v>
       </c>
       <c r="AG565" t="b">
         <v>0</v>
@@ -66436,10 +66709,13 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA566" t="n">
         <v>-0.99</v>
+      </c>
+      <c r="AB566" t="n">
+        <v>0.33</v>
       </c>
       <c r="AG566" t="b">
         <v>0</v>
@@ -66554,10 +66830,13 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA567" t="n">
         <v>-1.34</v>
+      </c>
+      <c r="AB567" t="n">
+        <v>-0.45</v>
       </c>
       <c r="AG567" t="b">
         <v>0</v>
@@ -66672,10 +66951,13 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA568" t="n">
         <v>-1.77</v>
+      </c>
+      <c r="AB568" t="n">
+        <v>-5.93</v>
       </c>
       <c r="AG568" t="b">
         <v>0</v>
@@ -66790,10 +67072,13 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA569" t="n">
         <v>-3.59</v>
+      </c>
+      <c r="AB569" t="n">
+        <v>-5.29</v>
       </c>
       <c r="AG569" t="b">
         <v>0</v>
@@ -66908,10 +67193,13 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA570" t="n">
         <v>0.29</v>
+      </c>
+      <c r="AB570" t="n">
+        <v>-1.16</v>
       </c>
       <c r="AG570" t="b">
         <v>0</v>
@@ -67026,10 +67314,13 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA571" t="n">
         <v>-4.43</v>
+      </c>
+      <c r="AB571" t="n">
+        <v>-6.45</v>
       </c>
       <c r="AG571" t="b">
         <v>0</v>
@@ -67144,10 +67435,13 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA572" t="n">
         <v>-3.52</v>
+      </c>
+      <c r="AB572" t="n">
+        <v>-7.26</v>
       </c>
       <c r="AG572" t="b">
         <v>0</v>
@@ -67262,10 +67556,13 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA573" t="n">
         <v>-1.74</v>
+      </c>
+      <c r="AB573" t="n">
+        <v>-4.13</v>
       </c>
       <c r="AG573" t="b">
         <v>0</v>
@@ -67380,10 +67677,13 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA574" t="n">
         <v>-3.79</v>
+      </c>
+      <c r="AB574" t="n">
+        <v>-5.34</v>
       </c>
       <c r="AG574" t="b">
         <v>0</v>
@@ -67498,10 +67798,13 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA575" t="n">
         <v>-3.07</v>
+      </c>
+      <c r="AB575" t="n">
+        <v>-6.63</v>
       </c>
       <c r="AG575" t="b">
         <v>0</v>
@@ -67616,9 +67919,12 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA576" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="AB576" t="n">
         <v>-1.21</v>
       </c>
       <c r="AG576" t="b">
@@ -68067,10 +68373,13 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA580" t="n">
         <v>31.15</v>
+      </c>
+      <c r="AB580" t="n">
+        <v>32.31</v>
       </c>
       <c r="AG580" t="b">
         <v>1</v>
@@ -68185,10 +68494,13 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA581" t="n">
         <v>2.49</v>
+      </c>
+      <c r="AB581" t="n">
+        <v>6.34</v>
       </c>
       <c r="AG581" t="b">
         <v>0</v>
@@ -68303,9 +68615,12 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA582" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AB582" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="AG582" t="b">
@@ -68421,10 +68736,13 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA583" t="n">
         <v>-3.99</v>
+      </c>
+      <c r="AB583" t="n">
+        <v>-5.99</v>
       </c>
       <c r="AG583" t="b">
         <v>0</v>
@@ -68650,13 +68968,13 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA585" t="n">
         <v>3.78</v>
       </c>
       <c r="AG585" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH585" t="b">
         <v>0</v>
@@ -68768,7 +69086,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA586" t="n">
         <v>-0.88</v>
@@ -68886,7 +69204,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA587" t="n">
         <v>-1.6</v>
@@ -69004,7 +69322,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA588" t="n">
         <v>4.07</v>
@@ -69122,7 +69440,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA589" t="n">
         <v>-1.9</v>
@@ -69240,7 +69558,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA590" t="n">
         <v>15.49</v>
@@ -69358,7 +69676,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA591" t="n">
         <v>4.25</v>
@@ -69476,7 +69794,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA592" t="n">
         <v>-4.09</v>
@@ -69594,7 +69912,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA593" t="n">
         <v>-5.77</v>
@@ -69709,7 +70027,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA594" t="n">
         <v>0.66</v>
@@ -69827,7 +70145,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA595" t="n">
         <v>0.9</v>
@@ -69945,7 +70263,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA596" t="n">
         <v>-0.89</v>
@@ -70063,7 +70381,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA597" t="n">
         <v>-3.23</v>
@@ -70181,7 +70499,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA598" t="n">
         <v>-1.86</v>
@@ -70299,7 +70617,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA599" t="n">
         <v>-3.91</v>
@@ -70417,7 +70735,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA600" t="n">
         <v>-5.86</v>
@@ -70535,7 +70853,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA601" t="n">
         <v>-2.98</v>
@@ -70653,7 +70971,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA602" t="n">
         <v>-3.02</v>
@@ -70771,7 +71089,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA603" t="n">
         <v>-2.06</v>
@@ -70889,7 +71207,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA604" t="n">
         <v>-0.87</v>
@@ -71007,7 +71325,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA605" t="n">
         <v>0.58</v>
@@ -71122,7 +71440,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA606" t="n">
         <v>-2.42</v>
@@ -71684,7 +72002,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA611" t="n">
         <v>1.45</v>
@@ -71799,7 +72117,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA612" t="n">
         <v>-2.34</v>
@@ -72028,7 +72346,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA614" t="n">
         <v>-4.58</v>
@@ -72146,7 +72464,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA615" t="n">
         <v>6.68</v>
@@ -72264,7 +72582,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA616" t="n">
         <v>-1.59</v>
@@ -72382,7 +72700,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA617" t="n">
         <v>-10.11</v>
@@ -72500,7 +72818,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA618" t="n">
         <v>-2.58</v>
@@ -72618,7 +72936,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA619" t="n">
         <v>-1.8</v>
@@ -72736,7 +73054,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA620" t="n">
         <v>-3.27</v>
@@ -72851,7 +73169,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA621" t="n">
         <v>-2.27</v>
@@ -72969,7 +73287,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA622" t="n">
         <v>-1.77</v>
@@ -73087,7 +73405,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA623" t="n">
         <v>-3.96</v>
@@ -73205,7 +73523,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA624" t="n">
         <v>-2.7</v>
@@ -73323,7 +73641,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA625" t="n">
         <v>-3.17</v>
@@ -73441,7 +73759,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA626" t="n">
         <v>-2.84</v>
@@ -73559,7 +73877,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA627" t="n">
         <v>0.59</v>
@@ -73677,7 +73995,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA628" t="n">
         <v>0.19</v>
@@ -73792,7 +74110,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA629" t="n">
         <v>-4.02</v>
@@ -74243,7 +74561,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA633" t="n">
         <v>5.58</v>
@@ -74361,7 +74679,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA634" t="n">
         <v>8.529999999999999</v>
@@ -74590,7 +74908,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA636" t="n">
         <v>7.05</v>
@@ -74819,7 +75137,7 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA638" t="n">
         <v>0.9399999999999999</v>
@@ -74937,7 +75255,7 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA639" t="n">
         <v>-14.75</v>
@@ -75055,7 +75373,7 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA640" t="n">
         <v>-3.86</v>
@@ -75173,7 +75491,7 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA641" t="n">
         <v>-4.11</v>
@@ -75288,7 +75606,7 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA642" t="n">
         <v>-2.59</v>
@@ -75406,7 +75724,7 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA643" t="n">
         <v>-6.11</v>
@@ -75524,7 +75842,7 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA644" t="n">
         <v>-1.52</v>
@@ -75642,7 +75960,7 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA645" t="n">
         <v>-4.53</v>
@@ -75760,7 +76078,7 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA646" t="n">
         <v>-3.85</v>
@@ -75878,7 +76196,7 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA647" t="n">
         <v>-3.85</v>
@@ -75996,7 +76314,7 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA648" t="n">
         <v>-3.01</v>
@@ -76114,7 +76432,7 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA649" t="n">
         <v>3.54</v>
@@ -76232,7 +76550,7 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA650" t="n">
         <v>-1.86</v>
@@ -76683,7 +77001,7 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA654" t="n">
         <v>9.09</v>
@@ -77023,7 +77341,7 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA657" t="n">
         <v>-0.97</v>
@@ -77141,7 +77459,7 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA658" t="n">
         <v>0.9399999999999999</v>
@@ -77259,7 +77577,7 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA659" t="n">
         <v>-1.95</v>
@@ -77377,7 +77695,7 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA660" t="n">
         <v>2.75</v>
@@ -77495,7 +77813,7 @@
         </is>
       </c>
       <c r="Z661" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA661" t="n">
         <v>-5.81</v>
@@ -77613,7 +77931,7 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA662" t="n">
         <v>0.34</v>
@@ -77731,7 +78049,7 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA663" t="n">
         <v>-2.8</v>
@@ -77849,7 +78167,7 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA664" t="n">
         <v>-4.53</v>
@@ -77964,7 +78282,7 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA665" t="n">
         <v>-1.63</v>
@@ -78082,7 +78400,7 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA666" t="n">
         <v>-5.08</v>
@@ -78200,7 +78518,7 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA667" t="n">
         <v>-0.55</v>
@@ -78318,7 +78636,7 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA668" t="n">
         <v>-4.02</v>
@@ -78436,7 +78754,7 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA669" t="n">
         <v>-5.59</v>
@@ -78554,7 +78872,7 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA670" t="n">
         <v>-2.22</v>
@@ -78672,7 +78990,7 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA671" t="n">
         <v>-3.26</v>
@@ -78790,7 +79108,7 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA672" t="n">
         <v>-0.86</v>
@@ -78908,7 +79226,7 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA673" t="n">
         <v>-0.18</v>
@@ -79248,7 +79566,7 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA676" t="n">
         <v>-5.78</v>
@@ -79477,7 +79795,7 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA678" t="n">
         <v>6.85</v>
@@ -79595,7 +79913,10 @@
         </is>
       </c>
       <c r="Z679" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA679" t="n">
+        <v>2.65</v>
       </c>
       <c r="AG679" t="b">
         <v>0</v>
@@ -79710,7 +80031,10 @@
         </is>
       </c>
       <c r="Z680" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA680" t="n">
+        <v>2.49</v>
       </c>
       <c r="AG680" t="b">
         <v>0</v>
@@ -79825,10 +80149,13 @@
         </is>
       </c>
       <c r="Z681" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA681" t="n">
+        <v>14.18</v>
       </c>
       <c r="AG681" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH681" t="b">
         <v>0</v>
@@ -79940,7 +80267,10 @@
         </is>
       </c>
       <c r="Z682" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA682" t="n">
+        <v>-5.47</v>
       </c>
       <c r="AG682" t="b">
         <v>0</v>
@@ -80055,7 +80385,10 @@
         </is>
       </c>
       <c r="Z683" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA683" t="n">
+        <v>-2.27</v>
       </c>
       <c r="AG683" t="b">
         <v>0</v>
@@ -80170,7 +80503,10 @@
         </is>
       </c>
       <c r="Z684" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA684" t="n">
+        <v>-1.75</v>
       </c>
       <c r="AG684" t="b">
         <v>0</v>
@@ -80285,7 +80621,10 @@
         </is>
       </c>
       <c r="Z685" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA685" t="n">
+        <v>-2.44</v>
       </c>
       <c r="AG685" t="b">
         <v>0</v>
@@ -80400,7 +80739,10 @@
         </is>
       </c>
       <c r="Z686" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA686" t="n">
+        <v>0.84</v>
       </c>
       <c r="AG686" t="b">
         <v>0</v>
@@ -80515,7 +80857,10 @@
         </is>
       </c>
       <c r="Z687" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA687" t="n">
+        <v>4.6</v>
       </c>
       <c r="AG687" t="b">
         <v>0</v>
@@ -80630,7 +80975,10 @@
         </is>
       </c>
       <c r="Z688" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA688" t="n">
+        <v>3.53</v>
       </c>
       <c r="AG688" t="b">
         <v>0</v>
@@ -81078,7 +81426,10 @@
         </is>
       </c>
       <c r="Z692" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA692" t="n">
+        <v>0.88</v>
       </c>
       <c r="AG692" t="b">
         <v>0</v>
@@ -81304,7 +81655,10 @@
         </is>
       </c>
       <c r="Z694" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA694" t="n">
+        <v>3.76</v>
       </c>
       <c r="AG694" t="b">
         <v>0</v>
@@ -81419,7 +81773,10 @@
         </is>
       </c>
       <c r="Z695" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA695" t="n">
+        <v>6.15</v>
       </c>
       <c r="AG695" t="b">
         <v>0</v>
@@ -81756,7 +82113,7 @@
         </is>
       </c>
       <c r="Z698" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG698" t="b">
         <v>0</v>
@@ -81871,7 +82228,7 @@
         </is>
       </c>
       <c r="Z699" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG699" t="b">
         <v>0</v>
@@ -81986,7 +82343,7 @@
         </is>
       </c>
       <c r="Z700" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG700" t="b">
         <v>0</v>
@@ -82101,10 +82458,10 @@
         </is>
       </c>
       <c r="Z701" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG701" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH701" t="b">
         <v>0</v>
@@ -82216,7 +82573,7 @@
         </is>
       </c>
       <c r="Z702" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG702" t="b">
         <v>0</v>
@@ -82331,7 +82688,7 @@
         </is>
       </c>
       <c r="Z703" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG703" t="b">
         <v>0</v>
@@ -82779,7 +83136,7 @@
         </is>
       </c>
       <c r="Z707" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG707" t="b">
         <v>0</v>
@@ -83005,7 +83362,7 @@
         </is>
       </c>
       <c r="Z709" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG709" t="b">
         <v>0</v>
@@ -83120,7 +83477,7 @@
         </is>
       </c>
       <c r="Z710" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG710" t="b">
         <v>0</v>
@@ -83235,10 +83592,10 @@
         </is>
       </c>
       <c r="Z711" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG711" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH711" t="b">
         <v>0</v>
@@ -83572,7 +83929,7 @@
         </is>
       </c>
       <c r="Z714" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG714" t="b">
         <v>0</v>
@@ -83687,7 +84044,7 @@
         </is>
       </c>
       <c r="Z715" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG715" t="b">
         <v>0</v>
@@ -83802,7 +84159,7 @@
         </is>
       </c>
       <c r="Z716" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG716" t="b">
         <v>0</v>
@@ -83917,7 +84274,7 @@
         </is>
       </c>
       <c r="Z717" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG717" t="b">
         <v>0</v>
@@ -84032,7 +84389,7 @@
         </is>
       </c>
       <c r="Z718" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG718" t="b">
         <v>0</v>
@@ -84147,7 +84504,7 @@
         </is>
       </c>
       <c r="Z719" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG719" t="b">
         <v>0</v>
@@ -84262,7 +84619,7 @@
         </is>
       </c>
       <c r="Z720" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG720" t="b">
         <v>0</v>
@@ -84377,7 +84734,7 @@
         </is>
       </c>
       <c r="Z721" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG721" t="b">
         <v>0</v>
@@ -84492,10 +84849,10 @@
         </is>
       </c>
       <c r="Z722" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG722" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH722" t="b">
         <v>0</v>
@@ -84607,7 +84964,7 @@
         </is>
       </c>
       <c r="Z723" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG723" t="b">
         <v>0</v>
@@ -84833,7 +85190,7 @@
         </is>
       </c>
       <c r="Z725" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG725" t="b">
         <v>0</v>
@@ -85059,7 +85416,7 @@
         </is>
       </c>
       <c r="Z727" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG727" t="b">
         <v>0</v>
@@ -85174,7 +85531,7 @@
         </is>
       </c>
       <c r="Z728" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG728" t="b">
         <v>0</v>
@@ -85400,7 +85757,7 @@
         </is>
       </c>
       <c r="Z730" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG730" t="b">
         <v>0</v>
@@ -85515,7 +85872,7 @@
         </is>
       </c>
       <c r="Z731" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG731" t="b">
         <v>0</v>
@@ -85630,7 +85987,7 @@
         </is>
       </c>
       <c r="Z732" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG732" t="b">
         <v>0</v>
@@ -85745,7 +86102,7 @@
         </is>
       </c>
       <c r="Z733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG733" t="b">
         <v>0</v>
@@ -85860,7 +86217,7 @@
         </is>
       </c>
       <c r="Z734" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG734" t="b">
         <v>0</v>
@@ -85975,7 +86332,7 @@
         </is>
       </c>
       <c r="Z735" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG735" t="b">
         <v>0</v>
@@ -86090,7 +86447,7 @@
         </is>
       </c>
       <c r="Z736" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG736" t="b">
         <v>0</v>
@@ -86205,7 +86562,7 @@
         </is>
       </c>
       <c r="Z737" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG737" t="b">
         <v>0</v>
@@ -86320,7 +86677,7 @@
         </is>
       </c>
       <c r="Z738" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG738" t="b">
         <v>0</v>
@@ -86435,7 +86792,7 @@
         </is>
       </c>
       <c r="Z739" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG739" t="b">
         <v>0</v>
@@ -86550,7 +86907,7 @@
         </is>
       </c>
       <c r="Z740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG740" t="b">
         <v>0</v>
@@ -86665,7 +87022,7 @@
         </is>
       </c>
       <c r="Z741" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG741" t="b">
         <v>0</v>
@@ -86891,7 +87248,7 @@
         </is>
       </c>
       <c r="Z743" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG743" t="b">
         <v>0</v>
@@ -87006,7 +87363,7 @@
         </is>
       </c>
       <c r="Z744" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG744" t="b">
         <v>0</v>
@@ -87232,7 +87589,7 @@
         </is>
       </c>
       <c r="Z746" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG746" t="b">
         <v>0</v>
@@ -87347,7 +87704,7 @@
         </is>
       </c>
       <c r="Z747" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG747" t="b">
         <v>0</v>
@@ -87795,7 +88152,7 @@
         </is>
       </c>
       <c r="Z751" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG751" t="b">
         <v>0</v>
@@ -87910,7 +88267,7 @@
         </is>
       </c>
       <c r="Z752" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG752" t="b">
         <v>0</v>
@@ -88025,7 +88382,7 @@
         </is>
       </c>
       <c r="Z753" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG753" t="b">
         <v>0</v>
@@ -88140,7 +88497,7 @@
         </is>
       </c>
       <c r="Z754" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG754" t="b">
         <v>0</v>
@@ -88255,7 +88612,7 @@
         </is>
       </c>
       <c r="Z755" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG755" t="b">
         <v>0</v>
@@ -88370,7 +88727,7 @@
         </is>
       </c>
       <c r="Z756" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG756" t="b">
         <v>0</v>
@@ -88485,7 +88842,7 @@
         </is>
       </c>
       <c r="Z757" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG757" t="b">
         <v>0</v>
@@ -88600,7 +88957,7 @@
         </is>
       </c>
       <c r="Z758" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG758" t="b">
         <v>0</v>
@@ -88715,7 +89072,7 @@
         </is>
       </c>
       <c r="Z759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG759" t="b">
         <v>0</v>
@@ -88830,7 +89187,7 @@
         </is>
       </c>
       <c r="Z760" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG760" t="b">
         <v>0</v>
@@ -88945,7 +89302,7 @@
         </is>
       </c>
       <c r="Z761" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG761" t="b">
         <v>0</v>
@@ -89060,7 +89417,7 @@
         </is>
       </c>
       <c r="Z762" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG762" t="b">
         <v>0</v>
@@ -89175,7 +89532,7 @@
         </is>
       </c>
       <c r="Z763" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG763" t="b">
         <v>0</v>
@@ -89845,7 +90202,7 @@
         </is>
       </c>
       <c r="Z769" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG769" t="b">
         <v>0</v>
@@ -89854,13 +90211,2971 @@
         <v>0</v>
       </c>
       <c r="AI769" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="F770" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I770" t="b">
+        <v>0</v>
+      </c>
+      <c r="J770" t="n">
+        <v>10</v>
+      </c>
+      <c r="K770" t="n">
+        <v>167.75</v>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M770" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="N770" t="n">
+        <v>8</v>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P770" t="n">
+        <v>153.25</v>
+      </c>
+      <c r="Q770" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S770" t="n">
+        <v>1.1525</v>
+      </c>
+      <c r="T770" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U770" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V770" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="W770" t="n">
+        <v>183</v>
+      </c>
+      <c r="X770" t="n">
+        <v>150.7425</v>
+      </c>
+      <c r="Y770" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z770" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG770" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH770" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI770" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>75.87</v>
+      </c>
+      <c r="F771" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I771" t="b">
+        <v>0</v>
+      </c>
+      <c r="J771" t="n">
+        <v>10</v>
+      </c>
+      <c r="K771" t="n">
+        <v>2205.5</v>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M771" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N771" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P771" t="n">
+        <v>1832.5</v>
+      </c>
+      <c r="Q771" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="R771" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S771" t="n">
+        <v>7</v>
+      </c>
+      <c r="T771" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U771" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V771" t="n">
+        <v>2005</v>
+      </c>
+      <c r="W771" t="n">
+        <v>2406</v>
+      </c>
+      <c r="X771" t="n">
+        <v>1864.65</v>
+      </c>
+      <c r="Y771" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z771" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG771" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH771" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI771" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F772" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I772" t="b">
+        <v>0</v>
+      </c>
+      <c r="J772" t="n">
+        <v>10</v>
+      </c>
+      <c r="K772" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M772" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N772" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P772" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="Q772" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S772" t="n">
+        <v>7</v>
+      </c>
+      <c r="T772" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U772" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V772" t="n">
+        <v>97</v>
+      </c>
+      <c r="W772" t="n">
+        <v>112.4054</v>
+      </c>
+      <c r="X772" t="n">
+        <v>90.20999999999999</v>
+      </c>
+      <c r="Y772" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z772" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG772" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH772" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI772" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="F773" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I773" t="b">
+        <v>0</v>
+      </c>
+      <c r="J773" t="n">
+        <v>10</v>
+      </c>
+      <c r="K773" t="n">
+        <v>2557.5</v>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M773" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N773" t="n">
+        <v>5</v>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P773" t="n">
+        <v>2282.5</v>
+      </c>
+      <c r="Q773" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="R773" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S773" t="n">
+        <v>7</v>
+      </c>
+      <c r="T773" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U773" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V773" t="n">
+        <v>2325</v>
+      </c>
+      <c r="W773" t="n">
+        <v>2790</v>
+      </c>
+      <c r="X773" t="n">
+        <v>2162.25</v>
+      </c>
+      <c r="Y773" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z773" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG773" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH773" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI773" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="F774" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I774" t="b">
+        <v>0</v>
+      </c>
+      <c r="J774" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K774" t="n">
+        <v>411</v>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M774" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N774" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P774" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="Q774" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S774" t="n">
+        <v>7</v>
+      </c>
+      <c r="T774" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U774" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V774" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="W774" t="n">
+        <v>460.4457</v>
+      </c>
+      <c r="X774" t="n">
+        <v>361.305</v>
+      </c>
+      <c r="Y774" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z774" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG774" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH774" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI774" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="F775" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I775" t="b">
+        <v>0</v>
+      </c>
+      <c r="J775" t="n">
+        <v>10</v>
+      </c>
+      <c r="K775" t="n">
+        <v>814</v>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M775" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N775" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P775" t="n">
+        <v>715</v>
+      </c>
+      <c r="Q775" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S775" t="n">
+        <v>7</v>
+      </c>
+      <c r="T775" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U775" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V775" t="n">
+        <v>740</v>
+      </c>
+      <c r="W775" t="n">
+        <v>869.0132</v>
+      </c>
+      <c r="X775" t="n">
+        <v>688.2</v>
+      </c>
+      <c r="Y775" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z775" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG775" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH775" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI775" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="F776" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I776" t="b">
+        <v>0</v>
+      </c>
+      <c r="J776" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K776" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M776" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N776" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P776" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="Q776" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S776" t="n">
+        <v>7</v>
+      </c>
+      <c r="T776" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U776" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V776" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="W776" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="X776" t="n">
+        <v>36.3165</v>
+      </c>
+      <c r="Y776" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z776" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG776" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH776" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI776" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="F777" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I777" t="b">
+        <v>0</v>
+      </c>
+      <c r="J777" t="n">
+        <v>10</v>
+      </c>
+      <c r="K777" t="n">
+        <v>5681.5</v>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M777" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N777" t="n">
+        <v>5</v>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P777" t="n">
+        <v>4957.5</v>
+      </c>
+      <c r="Q777" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="R777" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S777" t="n">
+        <v>7</v>
+      </c>
+      <c r="T777" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U777" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V777" t="n">
+        <v>5165</v>
+      </c>
+      <c r="W777" t="n">
+        <v>6198</v>
+      </c>
+      <c r="X777" t="n">
+        <v>4803.45</v>
+      </c>
+      <c r="Y777" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z777" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG777" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH777" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI777" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="F778" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I778" t="b">
+        <v>0</v>
+      </c>
+      <c r="J778" t="n">
+        <v>10</v>
+      </c>
+      <c r="K778" t="n">
+        <v>3943.5</v>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M778" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N778" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P778" t="n">
+        <v>3395</v>
+      </c>
+      <c r="Q778" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="R778" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S778" t="n">
+        <v>7</v>
+      </c>
+      <c r="T778" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U778" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V778" t="n">
+        <v>3585</v>
+      </c>
+      <c r="W778" t="n">
+        <v>4302</v>
+      </c>
+      <c r="X778" t="n">
+        <v>3334.05</v>
+      </c>
+      <c r="Y778" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z778" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG778" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH778" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI778" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="F779" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I779" t="b">
+        <v>0</v>
+      </c>
+      <c r="J779" t="n">
+        <v>10</v>
+      </c>
+      <c r="K779" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M779" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N779" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P779" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q779" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="R779" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S779" t="n">
+        <v>7</v>
+      </c>
+      <c r="T779" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U779" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V779" t="n">
+        <v>216</v>
+      </c>
+      <c r="W779" t="n">
+        <v>259.2</v>
+      </c>
+      <c r="X779" t="n">
+        <v>200.88</v>
+      </c>
+      <c r="Y779" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z779" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG779" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH779" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI779" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="F780" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I780" t="b">
+        <v>0</v>
+      </c>
+      <c r="J780" t="n">
+        <v>10</v>
+      </c>
+      <c r="K780" t="n">
+        <v>1457.5</v>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M780" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N780" t="n">
+        <v>3</v>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P780" t="n">
+        <v>1180</v>
+      </c>
+      <c r="Q780" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="R780" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S780" t="n">
+        <v>7</v>
+      </c>
+      <c r="T780" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U780" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V780" t="n">
+        <v>1325</v>
+      </c>
+      <c r="W780" t="n">
+        <v>1590</v>
+      </c>
+      <c r="X780" t="n">
+        <v>1232.25</v>
+      </c>
+      <c r="Y780" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z780" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG780" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH780" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI780" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>75.34</v>
+      </c>
+      <c r="F781" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I781" t="b">
+        <v>0</v>
+      </c>
+      <c r="J781" t="n">
+        <v>10</v>
+      </c>
+      <c r="K781" t="n">
+        <v>612.7</v>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M781" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N781" t="n">
+        <v>5</v>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P781" t="n">
+        <v>525.75</v>
+      </c>
+      <c r="Q781" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="R781" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S781" t="n">
+        <v>7</v>
+      </c>
+      <c r="T781" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U781" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V781" t="n">
+        <v>557</v>
+      </c>
+      <c r="W781" t="n">
+        <v>668.4</v>
+      </c>
+      <c r="X781" t="n">
+        <v>518.01</v>
+      </c>
+      <c r="Y781" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z781" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG781" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH781" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI781" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="F782" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I782" t="b">
+        <v>0</v>
+      </c>
+      <c r="J782" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="K782" t="n">
+        <v>664</v>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M782" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N782" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P782" t="n">
+        <v>542</v>
+      </c>
+      <c r="Q782" t="n">
+        <v>69.34</v>
+      </c>
+      <c r="R782" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S782" t="n">
+        <v>7</v>
+      </c>
+      <c r="T782" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U782" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V782" t="n">
+        <v>615</v>
+      </c>
+      <c r="W782" t="n">
+        <v>738</v>
+      </c>
+      <c r="X782" t="n">
+        <v>571.95</v>
+      </c>
+      <c r="Y782" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI782" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ782" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>82.02</v>
+      </c>
+      <c r="F783" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I783" t="b">
+        <v>0</v>
+      </c>
+      <c r="J783" t="n">
+        <v>10</v>
+      </c>
+      <c r="K783" t="n">
+        <v>1204.5</v>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M783" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N783" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P783" t="n">
+        <v>967.5</v>
+      </c>
+      <c r="Q783" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="R783" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S783" t="n">
+        <v>7</v>
+      </c>
+      <c r="T783" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U783" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V783" t="n">
+        <v>1095</v>
+      </c>
+      <c r="W783" t="n">
+        <v>1314</v>
+      </c>
+      <c r="X783" t="n">
+        <v>1018.35</v>
+      </c>
+      <c r="Y783" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z783" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG783" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH783" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI783" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="F784" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I784" t="b">
+        <v>0</v>
+      </c>
+      <c r="J784" t="n">
+        <v>10</v>
+      </c>
+      <c r="K784" t="n">
+        <v>873.4</v>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M784" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N784" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P784" t="n">
+        <v>758.5</v>
+      </c>
+      <c r="Q784" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S784" t="n">
+        <v>7</v>
+      </c>
+      <c r="T784" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U784" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V784" t="n">
+        <v>794</v>
+      </c>
+      <c r="W784" t="n">
+        <v>930.2428</v>
+      </c>
+      <c r="X784" t="n">
+        <v>738.42</v>
+      </c>
+      <c r="Y784" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI784" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ784" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="F785" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I785" t="b">
+        <v>0</v>
+      </c>
+      <c r="J785" t="n">
+        <v>10</v>
+      </c>
+      <c r="K785" t="n">
+        <v>548.35</v>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M785" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N785" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P785" t="n">
+        <v>457.75</v>
+      </c>
+      <c r="Q785" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S785" t="n">
+        <v>7</v>
+      </c>
+      <c r="T785" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U785" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V785" t="n">
+        <v>498.5</v>
+      </c>
+      <c r="W785" t="n">
+        <v>598.2</v>
+      </c>
+      <c r="X785" t="n">
+        <v>463.605</v>
+      </c>
+      <c r="Y785" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI785" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ785" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="F786" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I786" t="b">
+        <v>0</v>
+      </c>
+      <c r="J786" t="n">
+        <v>10</v>
+      </c>
+      <c r="K786" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M786" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N786" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P786" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="Q786" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S786" t="n">
+        <v>7</v>
+      </c>
+      <c r="T786" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U786" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V786" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="W786" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="X786" t="n">
+        <v>48.639</v>
+      </c>
+      <c r="Y786" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z786" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG786" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH786" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI786" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="F787" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I787" t="b">
+        <v>0</v>
+      </c>
+      <c r="J787" t="n">
+        <v>10</v>
+      </c>
+      <c r="K787" t="n">
+        <v>3470.5</v>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M787" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N787" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P787" t="n">
+        <v>3130</v>
+      </c>
+      <c r="Q787" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S787" t="n">
+        <v>7</v>
+      </c>
+      <c r="T787" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U787" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V787" t="n">
+        <v>3155</v>
+      </c>
+      <c r="W787" t="n">
+        <v>3786</v>
+      </c>
+      <c r="X787" t="n">
+        <v>2934.15</v>
+      </c>
+      <c r="Y787" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI787" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ787" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="F788" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I788" t="b">
+        <v>0</v>
+      </c>
+      <c r="J788" t="n">
+        <v>10</v>
+      </c>
+      <c r="K788" t="n">
+        <v>516.45</v>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M788" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N788" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P788" t="n">
+        <v>453.25</v>
+      </c>
+      <c r="Q788" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S788" t="n">
+        <v>7</v>
+      </c>
+      <c r="T788" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U788" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V788" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="W788" t="n">
+        <v>563.4</v>
+      </c>
+      <c r="X788" t="n">
+        <v>436.635</v>
+      </c>
+      <c r="Y788" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z788" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG788" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH788" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI788" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="F789" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I789" t="b">
+        <v>0</v>
+      </c>
+      <c r="J789" t="n">
+        <v>10</v>
+      </c>
+      <c r="K789" t="n">
+        <v>816.2</v>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M789" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N789" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P789" t="n">
+        <v>677.5</v>
+      </c>
+      <c r="Q789" t="n">
+        <v>68.48999999999999</v>
+      </c>
+      <c r="R789" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S789" t="n">
+        <v>7</v>
+      </c>
+      <c r="T789" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U789" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V789" t="n">
+        <v>742</v>
+      </c>
+      <c r="W789" t="n">
+        <v>890.4</v>
+      </c>
+      <c r="X789" t="n">
+        <v>690.0599999999999</v>
+      </c>
+      <c r="Y789" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z789" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG789" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH789" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI789" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="F790" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I790" t="b">
+        <v>0</v>
+      </c>
+      <c r="J790" t="n">
+        <v>10</v>
+      </c>
+      <c r="K790" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M790" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N790" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P790" t="n">
+        <v>526.75</v>
+      </c>
+      <c r="Q790" t="n">
+        <v>66.44</v>
+      </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S790" t="n">
+        <v>7</v>
+      </c>
+      <c r="T790" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U790" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V790" t="n">
+        <v>576</v>
+      </c>
+      <c r="W790" t="n">
+        <v>691.2</v>
+      </c>
+      <c r="X790" t="n">
+        <v>535.6799999999999</v>
+      </c>
+      <c r="Y790" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z790" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG790" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH790" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI790" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>77.67</v>
+      </c>
+      <c r="F791" t="n">
+        <v>54.47</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I791" t="b">
+        <v>0</v>
+      </c>
+      <c r="J791" t="n">
+        <v>10</v>
+      </c>
+      <c r="K791" t="n">
+        <v>202.4</v>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M791" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N791" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P791" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q791" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S791" t="n">
+        <v>7</v>
+      </c>
+      <c r="T791" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U791" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V791" t="n">
+        <v>184</v>
+      </c>
+      <c r="W791" t="n">
+        <v>220.8</v>
+      </c>
+      <c r="X791" t="n">
+        <v>171.12</v>
+      </c>
+      <c r="Y791" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI791" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ791" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>中美晶</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="F792" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I792" t="b">
+        <v>0</v>
+      </c>
+      <c r="J792" t="n">
+        <v>10</v>
+      </c>
+      <c r="K792" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M792" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N792" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P792" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="Q792" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="R792" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S792" t="n">
+        <v>7</v>
+      </c>
+      <c r="T792" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U792" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V792" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="W792" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="X792" t="n">
+        <v>199.485</v>
+      </c>
+      <c r="Y792" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI792" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ792" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>合晶</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F793" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I793" t="b">
+        <v>0</v>
+      </c>
+      <c r="J793" t="n">
+        <v>10</v>
+      </c>
+      <c r="K793" t="n">
+        <v>144.65</v>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M793" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N793" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P793" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="Q793" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S793" t="n">
+        <v>7</v>
+      </c>
+      <c r="T793" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U793" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V793" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="W793" t="n">
+        <v>157.8</v>
+      </c>
+      <c r="X793" t="n">
+        <v>122.295</v>
+      </c>
+      <c r="Y793" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI793" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ793" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="F794" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I794" t="b">
+        <v>0</v>
+      </c>
+      <c r="J794" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K794" t="n">
+        <v>1198</v>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M794" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N794" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P794" t="n">
+        <v>1068</v>
+      </c>
+      <c r="Q794" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S794" t="n">
+        <v>7</v>
+      </c>
+      <c r="T794" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U794" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V794" t="n">
+        <v>1180</v>
+      </c>
+      <c r="W794" t="n">
+        <v>1416</v>
+      </c>
+      <c r="X794" t="n">
+        <v>1097.4</v>
+      </c>
+      <c r="Y794" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI794" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ794" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="F795" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I795" t="b">
+        <v>0</v>
+      </c>
+      <c r="J795" t="n">
+        <v>10</v>
+      </c>
+      <c r="K795" t="n">
+        <v>1644.5</v>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M795" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N795" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P795" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q795" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S795" t="n">
+        <v>7</v>
+      </c>
+      <c r="T795" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U795" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V795" t="n">
+        <v>1495</v>
+      </c>
+      <c r="W795" t="n">
+        <v>1794</v>
+      </c>
+      <c r="X795" t="n">
+        <v>1390.35</v>
+      </c>
+      <c r="Y795" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z795" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG795" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH795" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI795" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ769"/>
+  <autoFilter ref="A1:AJ795"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -89933,25 +93248,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4036</v>
+        <v>0.4101</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.77</v>
+        <v>-2.38</v>
       </c>
       <c r="E2" t="n">
-        <v>8.32</v>
+        <v>8.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.65</v>
+        <v>-12.33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1566</v>
+        <v>0.1573</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6446</v>
+        <v>0.6348</v>
       </c>
     </row>
     <row r="3">
@@ -89961,25 +93276,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5897</v>
+        <v>0.5625</v>
       </c>
       <c r="D3" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="E3" t="n">
-        <v>8.26</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.23</v>
+        <v>-3.82</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1282</v>
+        <v>0.1042</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1795</v>
+        <v>0.1458</v>
       </c>
     </row>
     <row r="4">
@@ -90083,25 +93398,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>0.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.49</v>
+        <v>-4.65</v>
       </c>
       <c r="E2" t="n">
-        <v>10.77</v>
+        <v>10.78</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.67</v>
+        <v>-11.29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2143</v>
+        <v>0.1875</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4286</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="3">
@@ -90111,25 +93426,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.404</v>
+        <v>0.4286</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.26</v>
+        <v>-2.43</v>
       </c>
       <c r="E3" t="n">
-        <v>6.85</v>
+        <v>7.18</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.86</v>
+        <v>-11.03</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1414</v>
+        <v>0.1429</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5758</v>
+        <v>0.5268</v>
       </c>
     </row>
     <row r="4">
@@ -90139,25 +93454,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4607</v>
+        <v>0.4421</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>9.56</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.07</v>
+        <v>-9.94</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1573</v>
+        <v>0.1474</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5618</v>
+        <v>0.5684</v>
       </c>
     </row>
     <row r="5">
@@ -90254,7 +93569,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-02 14:25:13</t>
+          <t>2026-10-05 14:24:45</t>
         </is>
       </c>
     </row>
@@ -90301,7 +93616,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>768</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -90311,7 +93626,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>327</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8">
@@ -90321,7 +93636,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$795</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$820</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ795"/>
+  <dimension ref="A1:AJ820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -44559,11 +44559,11 @@
       </c>
       <c r="Y384" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z384" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA384" t="n">
         <v>-2.12</v>
@@ -44574,6 +44574,15 @@
       <c r="AC384" t="n">
         <v>-2.12</v>
       </c>
+      <c r="AD384" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE384" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AF384" t="n">
+        <v>-7.27</v>
+      </c>
       <c r="AG384" t="b">
         <v>0</v>
       </c>
@@ -44582,7 +44591,7 @@
       </c>
       <c r="AI384" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -44683,11 +44692,11 @@
       </c>
       <c r="Y385" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z385" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA385" t="n">
         <v>3.99</v>
@@ -44698,6 +44707,15 @@
       <c r="AC385" t="n">
         <v>9.529999999999999</v>
       </c>
+      <c r="AD385" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AE385" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="AF385" t="n">
+        <v>-2.22</v>
+      </c>
       <c r="AG385" t="b">
         <v>1</v>
       </c>
@@ -44706,7 +44724,7 @@
       </c>
       <c r="AI385" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -44807,11 +44825,11 @@
       </c>
       <c r="Y386" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z386" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA386" t="n">
         <v>-3.74</v>
@@ -44822,6 +44840,15 @@
       <c r="AC386" t="n">
         <v>-5.12</v>
       </c>
+      <c r="AD386" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AE386" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AF386" t="n">
+        <v>-6.37</v>
+      </c>
       <c r="AG386" t="b">
         <v>0</v>
       </c>
@@ -44830,7 +44857,7 @@
       </c>
       <c r="AI386" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -44931,11 +44958,11 @@
       </c>
       <c r="Y387" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z387" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA387" t="n">
         <v>-4.56</v>
@@ -44946,6 +44973,15 @@
       <c r="AC387" t="n">
         <v>-7.77</v>
       </c>
+      <c r="AD387" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="AE387" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AF387" t="n">
+        <v>-8.710000000000001</v>
+      </c>
       <c r="AG387" t="b">
         <v>0</v>
       </c>
@@ -44954,7 +44990,7 @@
       </c>
       <c r="AI387" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -45055,11 +45091,11 @@
       </c>
       <c r="Y388" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z388" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA388" t="n">
         <v>-10.06</v>
@@ -45070,6 +45106,15 @@
       <c r="AC388" t="n">
         <v>-8.77</v>
       </c>
+      <c r="AD388" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="AE388" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF388" t="n">
+        <v>-12.01</v>
+      </c>
       <c r="AG388" t="b">
         <v>0</v>
       </c>
@@ -45078,7 +45123,7 @@
       </c>
       <c r="AI388" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -45179,11 +45224,11 @@
       </c>
       <c r="Y389" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z389" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA389" t="n">
         <v>-9.130000000000001</v>
@@ -45194,6 +45239,15 @@
       <c r="AC389" t="n">
         <v>-13.34</v>
       </c>
+      <c r="AD389" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF389" t="n">
+        <v>-14.18</v>
+      </c>
       <c r="AG389" t="b">
         <v>0</v>
       </c>
@@ -45202,7 +45256,7 @@
       </c>
       <c r="AI389" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -45300,11 +45354,11 @@
       </c>
       <c r="Y390" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z390" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA390" t="n">
         <v>-4.89</v>
@@ -45315,6 +45369,15 @@
       <c r="AC390" t="n">
         <v>-3.98</v>
       </c>
+      <c r="AD390" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="AE390" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF390" t="n">
+        <v>-5.96</v>
+      </c>
       <c r="AG390" t="b">
         <v>0</v>
       </c>
@@ -45323,7 +45386,7 @@
       </c>
       <c r="AI390" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -45424,11 +45487,11 @@
       </c>
       <c r="Y391" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z391" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA391" t="n">
         <v>-9.85</v>
@@ -45439,6 +45502,15 @@
       <c r="AC391" t="n">
         <v>-6.05</v>
       </c>
+      <c r="AD391" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="AE391" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF391" t="n">
+        <v>-12.2</v>
+      </c>
       <c r="AG391" t="b">
         <v>0</v>
       </c>
@@ -45447,7 +45519,7 @@
       </c>
       <c r="AI391" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -45548,11 +45620,11 @@
       </c>
       <c r="Y392" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z392" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA392" t="n">
         <v>-7.74</v>
@@ -45563,6 +45635,15 @@
       <c r="AC392" t="n">
         <v>-6.5</v>
       </c>
+      <c r="AD392" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF392" t="n">
+        <v>-10.53</v>
+      </c>
       <c r="AG392" t="b">
         <v>0</v>
       </c>
@@ -45571,7 +45652,7 @@
       </c>
       <c r="AI392" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -45672,11 +45753,11 @@
       </c>
       <c r="Y393" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z393" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA393" t="n">
         <v>-2.46</v>
@@ -45687,6 +45768,15 @@
       <c r="AC393" t="n">
         <v>-2.46</v>
       </c>
+      <c r="AD393" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="AE393" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF393" t="n">
+        <v>-4.93</v>
+      </c>
       <c r="AG393" t="b">
         <v>0</v>
       </c>
@@ -45695,7 +45785,7 @@
       </c>
       <c r="AI393" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -45796,11 +45886,11 @@
       </c>
       <c r="Y394" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z394" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA394" t="n">
         <v>-4.98</v>
@@ -45811,6 +45901,15 @@
       <c r="AC394" t="n">
         <v>-5.43</v>
       </c>
+      <c r="AD394" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AF394" t="n">
+        <v>-7.69</v>
+      </c>
       <c r="AG394" t="b">
         <v>0</v>
       </c>
@@ -45819,7 +45918,7 @@
       </c>
       <c r="AI394" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -45920,11 +46019,11 @@
       </c>
       <c r="Y395" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z395" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA395" t="n">
         <v>-5.2</v>
@@ -45935,6 +46034,15 @@
       <c r="AC395" t="n">
         <v>2.67</v>
       </c>
+      <c r="AD395" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AF395" t="n">
+        <v>-9.279999999999999</v>
+      </c>
       <c r="AG395" t="b">
         <v>0</v>
       </c>
@@ -45943,7 +46051,7 @@
       </c>
       <c r="AI395" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -46044,11 +46152,11 @@
       </c>
       <c r="Y396" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z396" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA396" t="n">
         <v>3.85</v>
@@ -46059,6 +46167,15 @@
       <c r="AC396" t="n">
         <v>11.21</v>
       </c>
+      <c r="AD396" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="AF396" t="n">
+        <v>0</v>
+      </c>
       <c r="AG396" t="b">
         <v>1</v>
       </c>
@@ -46067,7 +46184,7 @@
       </c>
       <c r="AI396" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -46168,11 +46285,11 @@
       </c>
       <c r="Y397" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z397" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA397" t="n">
         <v>2.06</v>
@@ -46183,6 +46300,15 @@
       <c r="AC397" t="n">
         <v>0.34</v>
       </c>
+      <c r="AD397" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AF397" t="n">
+        <v>-2.92</v>
+      </c>
       <c r="AG397" t="b">
         <v>0</v>
       </c>
@@ -46191,7 +46317,7 @@
       </c>
       <c r="AI397" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -46292,11 +46418,11 @@
       </c>
       <c r="Y398" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z398" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA398" t="n">
         <v>-2.61</v>
@@ -46307,6 +46433,15 @@
       <c r="AC398" t="n">
         <v>-3.48</v>
       </c>
+      <c r="AD398" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AF398" t="n">
+        <v>-7.39</v>
+      </c>
       <c r="AG398" t="b">
         <v>0</v>
       </c>
@@ -46315,7 +46450,7 @@
       </c>
       <c r="AI398" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -46416,11 +46551,11 @@
       </c>
       <c r="Y399" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z399" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA399" t="n">
         <v>-1.33</v>
@@ -46431,6 +46566,15 @@
       <c r="AC399" t="n">
         <v>0.66</v>
       </c>
+      <c r="AD399" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AF399" t="n">
+        <v>-4.32</v>
+      </c>
       <c r="AG399" t="b">
         <v>0</v>
       </c>
@@ -46439,7 +46583,7 @@
       </c>
       <c r="AI399" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -46540,11 +46684,11 @@
       </c>
       <c r="Y400" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z400" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA400" t="n">
         <v>-3.91</v>
@@ -46555,6 +46699,15 @@
       <c r="AC400" t="n">
         <v>-3.04</v>
       </c>
+      <c r="AD400" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF400" t="n">
+        <v>-6.09</v>
+      </c>
       <c r="AG400" t="b">
         <v>0</v>
       </c>
@@ -46563,7 +46716,7 @@
       </c>
       <c r="AI400" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -46664,11 +46817,11 @@
       </c>
       <c r="Y401" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z401" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA401" t="n">
         <v>3.13</v>
@@ -46679,6 +46832,15 @@
       <c r="AC401" t="n">
         <v>6.13</v>
       </c>
+      <c r="AD401" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="AF401" t="n">
+        <v>-1.91</v>
+      </c>
       <c r="AG401" t="b">
         <v>0</v>
       </c>
@@ -46687,7 +46849,7 @@
       </c>
       <c r="AI401" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -46788,11 +46950,11 @@
       </c>
       <c r="Y402" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z402" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA402" t="n">
         <v>6.31</v>
@@ -46803,6 +46965,15 @@
       <c r="AC402" t="n">
         <v>3.1</v>
       </c>
+      <c r="AD402" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AE402" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AF402" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
       <c r="AG402" t="b">
         <v>0</v>
       </c>
@@ -46811,7 +46982,7 @@
       </c>
       <c r="AI402" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -46912,11 +47083,11 @@
       </c>
       <c r="Y403" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z403" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA403" t="n">
         <v>2.77</v>
@@ -46927,6 +47098,15 @@
       <c r="AC403" t="n">
         <v>0.72</v>
       </c>
+      <c r="AD403" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AF403" t="n">
+        <v>-3.37</v>
+      </c>
       <c r="AG403" t="b">
         <v>0</v>
       </c>
@@ -46935,7 +47115,7 @@
       </c>
       <c r="AI403" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -47036,11 +47216,11 @@
       </c>
       <c r="Y404" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z404" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA404" t="n">
         <v>1.98</v>
@@ -47051,6 +47231,15 @@
       <c r="AC404" t="n">
         <v>2.45</v>
       </c>
+      <c r="AD404" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="AF404" t="n">
+        <v>-1.63</v>
+      </c>
       <c r="AG404" t="b">
         <v>0</v>
       </c>
@@ -47059,7 +47248,7 @@
       </c>
       <c r="AI404" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -47160,11 +47349,11 @@
       </c>
       <c r="Y405" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z405" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA405" t="n">
         <v>4.29</v>
@@ -47175,6 +47364,15 @@
       <c r="AC405" t="n">
         <v>3.49</v>
       </c>
+      <c r="AD405" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="AF405" t="n">
+        <v>-1.21</v>
+      </c>
       <c r="AG405" t="b">
         <v>0</v>
       </c>
@@ -47183,7 +47381,7 @@
       </c>
       <c r="AI405" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -47284,11 +47482,11 @@
       </c>
       <c r="Y406" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z406" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA406" t="n">
         <v>4.31</v>
@@ -47299,6 +47497,15 @@
       <c r="AC406" t="n">
         <v>2.33</v>
       </c>
+      <c r="AD406" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AF406" t="n">
+        <v>-5.57</v>
+      </c>
       <c r="AG406" t="b">
         <v>0</v>
       </c>
@@ -47307,7 +47514,7 @@
       </c>
       <c r="AI406" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -47408,11 +47615,11 @@
       </c>
       <c r="Y407" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z407" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA407" t="n">
         <v>-10</v>
@@ -47423,6 +47630,15 @@
       <c r="AC407" t="n">
         <v>-18.65</v>
       </c>
+      <c r="AD407" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="AF407" t="n">
+        <v>-22.43</v>
+      </c>
       <c r="AG407" t="b">
         <v>0</v>
       </c>
@@ -47431,7 +47647,7 @@
       </c>
       <c r="AI407" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -47532,11 +47748,11 @@
       </c>
       <c r="Y408" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z408" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA408" t="n">
         <v>-5.6</v>
@@ -47547,6 +47763,15 @@
       <c r="AC408" t="n">
         <v>-4.76</v>
       </c>
+      <c r="AD408" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AF408" t="n">
+        <v>-13.17</v>
+      </c>
       <c r="AG408" t="b">
         <v>0</v>
       </c>
@@ -47555,7 +47780,7 @@
       </c>
       <c r="AI408" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -47656,11 +47881,11 @@
       </c>
       <c r="Y409" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z409" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA409" t="n">
         <v>2.54</v>
@@ -47671,6 +47896,15 @@
       <c r="AC409" t="n">
         <v>2.54</v>
       </c>
+      <c r="AD409" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AE409" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AF409" t="n">
+        <v>-1.27</v>
+      </c>
       <c r="AG409" t="b">
         <v>0</v>
       </c>
@@ -47679,7 +47913,7 @@
       </c>
       <c r="AI409" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -48113,11 +48347,11 @@
       </c>
       <c r="Y413" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z413" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA413" t="n">
         <v>-13.51</v>
@@ -48128,6 +48362,15 @@
       <c r="AC413" t="n">
         <v>-12.68</v>
       </c>
+      <c r="AD413" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AE413" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AF413" t="n">
+        <v>-22.75</v>
+      </c>
       <c r="AG413" t="b">
         <v>0</v>
       </c>
@@ -48136,7 +48379,7 @@
       </c>
       <c r="AI413" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -48237,11 +48480,11 @@
       </c>
       <c r="Y414" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z414" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA414" t="n">
         <v>2.06</v>
@@ -48252,6 +48495,15 @@
       <c r="AC414" t="n">
         <v>-2.25</v>
       </c>
+      <c r="AD414" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="AE414" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AF414" t="n">
+        <v>-3.75</v>
+      </c>
       <c r="AG414" t="b">
         <v>0</v>
       </c>
@@ -48260,7 +48512,7 @@
       </c>
       <c r="AI414" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -48365,7 +48617,7 @@
         </is>
       </c>
       <c r="Z415" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA415" t="n">
         <v>-5.56</v>
@@ -48489,7 +48741,7 @@
         </is>
       </c>
       <c r="Z416" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA416" t="n">
         <v>1.52</v>
@@ -48613,7 +48865,7 @@
         </is>
       </c>
       <c r="Z417" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA417" t="n">
         <v>-5.98</v>
@@ -48737,7 +48989,7 @@
         </is>
       </c>
       <c r="Z418" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA418" t="n">
         <v>-5.68</v>
@@ -48861,7 +49113,7 @@
         </is>
       </c>
       <c r="Z419" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA419" t="n">
         <v>-7.92</v>
@@ -48985,7 +49237,7 @@
         </is>
       </c>
       <c r="Z420" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA420" t="n">
         <v>-6.51</v>
@@ -49109,7 +49361,7 @@
         </is>
       </c>
       <c r="Z421" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA421" t="n">
         <v>-4.32</v>
@@ -49233,7 +49485,7 @@
         </is>
       </c>
       <c r="Z422" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA422" t="n">
         <v>-4.21</v>
@@ -49357,7 +49609,7 @@
         </is>
       </c>
       <c r="Z423" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA423" t="n">
         <v>-4.2</v>
@@ -49481,7 +49733,7 @@
         </is>
       </c>
       <c r="Z424" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA424" t="n">
         <v>-1.31</v>
@@ -49605,7 +49857,7 @@
         </is>
       </c>
       <c r="Z425" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA425" t="n">
         <v>3.01</v>
@@ -49729,7 +49981,7 @@
         </is>
       </c>
       <c r="Z426" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA426" t="n">
         <v>-1.75</v>
@@ -49853,7 +50105,7 @@
         </is>
       </c>
       <c r="Z427" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA427" t="n">
         <v>5.01</v>
@@ -49977,7 +50229,7 @@
         </is>
       </c>
       <c r="Z428" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA428" t="n">
         <v>6.43</v>
@@ -50101,7 +50353,7 @@
         </is>
       </c>
       <c r="Z429" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA429" t="n">
         <v>5.96</v>
@@ -50225,7 +50477,7 @@
         </is>
       </c>
       <c r="Z430" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA430" t="n">
         <v>5.16</v>
@@ -50349,7 +50601,7 @@
         </is>
       </c>
       <c r="Z431" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA431" t="n">
         <v>6.84</v>
@@ -50473,7 +50725,7 @@
         </is>
       </c>
       <c r="Z432" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA432" t="n">
         <v>-3.22</v>
@@ -50597,7 +50849,7 @@
         </is>
       </c>
       <c r="Z433" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA433" t="n">
         <v>3.45</v>
@@ -50721,7 +50973,7 @@
         </is>
       </c>
       <c r="Z434" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA434" t="n">
         <v>3.85</v>
@@ -51067,7 +51319,7 @@
         </is>
       </c>
       <c r="Z437" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA437" t="n">
         <v>7.83</v>
@@ -51302,7 +51554,7 @@
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -51426,7 +51678,7 @@
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -51550,7 +51802,7 @@
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -51674,7 +51926,7 @@
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -51798,7 +52050,7 @@
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -51922,7 +52174,7 @@
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -52046,7 +52298,7 @@
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -52170,7 +52422,7 @@
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -52294,7 +52546,7 @@
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -52418,7 +52670,7 @@
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -52542,7 +52794,7 @@
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -52666,7 +52918,7 @@
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -52790,7 +53042,7 @@
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -52914,7 +53166,7 @@
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -53038,7 +53290,7 @@
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -53162,7 +53414,7 @@
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -53286,7 +53538,7 @@
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -53410,7 +53662,7 @@
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -53534,7 +53786,7 @@
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -53658,7 +53910,7 @@
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -54004,7 +54256,7 @@
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -54128,7 +54380,7 @@
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -54252,7 +54504,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -54376,7 +54628,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -54500,7 +54752,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -54512,7 +54764,7 @@
         <v>17.21</v>
       </c>
       <c r="AG465" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH465" t="b">
         <v>1</v>
@@ -54624,7 +54876,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -54748,7 +55000,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -54872,7 +55124,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -54996,7 +55248,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -55120,7 +55372,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -55244,7 +55496,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -55368,7 +55620,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -55492,7 +55744,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -55616,7 +55868,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -55740,7 +55992,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -55864,7 +56116,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -55988,7 +56240,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -56112,7 +56364,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -56569,7 +56821,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -56693,7 +56945,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -56817,7 +57069,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -56941,13 +57193,16 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
       </c>
       <c r="AB485" t="n">
         <v>-0</v>
+      </c>
+      <c r="AC485" t="n">
+        <v>0.42</v>
       </c>
       <c r="AG485" t="b">
         <v>0</v>
@@ -57062,13 +57317,16 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
       </c>
       <c r="AB486" t="n">
         <v>5.33</v>
+      </c>
+      <c r="AC486" t="n">
+        <v>24.95</v>
       </c>
       <c r="AG486" t="b">
         <v>1</v>
@@ -57183,13 +57441,16 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
       </c>
       <c r="AB487" t="n">
         <v>16.06</v>
+      </c>
+      <c r="AC487" t="n">
+        <v>24.01</v>
       </c>
       <c r="AG487" t="b">
         <v>1</v>
@@ -57304,13 +57565,16 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
       </c>
       <c r="AB488" t="n">
         <v>2.49</v>
+      </c>
+      <c r="AC488" t="n">
+        <v>3.56</v>
       </c>
       <c r="AG488" t="b">
         <v>0</v>
@@ -57425,13 +57689,16 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
       </c>
       <c r="AB489" t="n">
         <v>7.09</v>
+      </c>
+      <c r="AC489" t="n">
+        <v>7.31</v>
       </c>
       <c r="AG489" t="b">
         <v>0</v>
@@ -57546,13 +57813,16 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
       </c>
       <c r="AB490" t="n">
         <v>-2.22</v>
+      </c>
+      <c r="AC490" t="n">
+        <v>-3.61</v>
       </c>
       <c r="AG490" t="b">
         <v>0</v>
@@ -57667,13 +57937,16 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
       </c>
       <c r="AB491" t="n">
         <v>-2.07</v>
+      </c>
+      <c r="AC491" t="n">
+        <v>-0.87</v>
       </c>
       <c r="AG491" t="b">
         <v>0</v>
@@ -57788,13 +58061,16 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
       </c>
       <c r="AB492" t="n">
         <v>2.91</v>
+      </c>
+      <c r="AC492" t="n">
+        <v>-0.53</v>
       </c>
       <c r="AG492" t="b">
         <v>0</v>
@@ -57909,13 +58185,16 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
       </c>
       <c r="AB493" t="n">
         <v>-3.02</v>
+      </c>
+      <c r="AC493" t="n">
+        <v>-1.84</v>
       </c>
       <c r="AG493" t="b">
         <v>0</v>
@@ -58030,13 +58309,16 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
       </c>
       <c r="AB494" t="n">
         <v>-5.03</v>
+      </c>
+      <c r="AC494" t="n">
+        <v>-4.64</v>
       </c>
       <c r="AG494" t="b">
         <v>0</v>
@@ -58151,13 +58433,16 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
       </c>
       <c r="AB495" t="n">
         <v>-1.99</v>
+      </c>
+      <c r="AC495" t="n">
+        <v>-2.81</v>
       </c>
       <c r="AG495" t="b">
         <v>0</v>
@@ -58272,13 +58557,16 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
       </c>
       <c r="AB496" t="n">
         <v>0.46</v>
+      </c>
+      <c r="AC496" t="n">
+        <v>3.89</v>
       </c>
       <c r="AG496" t="b">
         <v>0</v>
@@ -58393,13 +58681,16 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
       </c>
       <c r="AB497" t="n">
         <v>-0.77</v>
+      </c>
+      <c r="AC497" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AG497" t="b">
         <v>0</v>
@@ -58514,13 +58805,16 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
       </c>
       <c r="AB498" t="n">
         <v>-1.28</v>
+      </c>
+      <c r="AC498" t="n">
+        <v>-1.83</v>
       </c>
       <c r="AG498" t="b">
         <v>0</v>
@@ -58635,7 +58929,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -58643,8 +58937,11 @@
       <c r="AB499" t="n">
         <v>2.56</v>
       </c>
+      <c r="AC499" t="n">
+        <v>13.98</v>
+      </c>
       <c r="AG499" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH499" t="b">
         <v>0</v>
@@ -58756,13 +59053,16 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
       </c>
       <c r="AB500" t="n">
         <v>0</v>
+      </c>
+      <c r="AC500" t="n">
+        <v>1.65</v>
       </c>
       <c r="AG500" t="b">
         <v>0</v>
@@ -58877,13 +59177,16 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
       </c>
       <c r="AB501" t="n">
         <v>29.49</v>
+      </c>
+      <c r="AC501" t="n">
+        <v>36.85</v>
       </c>
       <c r="AG501" t="b">
         <v>1</v>
@@ -58998,13 +59301,16 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
       </c>
       <c r="AB502" t="n">
         <v>7.33</v>
+      </c>
+      <c r="AC502" t="n">
+        <v>10.4</v>
       </c>
       <c r="AG502" t="b">
         <v>0</v>
@@ -59119,12 +59425,15 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
       </c>
       <c r="AB503" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AC503" t="n">
         <v>-0.95</v>
       </c>
       <c r="AG503" t="b">
@@ -59240,13 +59549,16 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
       </c>
       <c r="AB504" t="n">
         <v>-4.23</v>
+      </c>
+      <c r="AC504" t="n">
+        <v>-4.6</v>
       </c>
       <c r="AG504" t="b">
         <v>0</v>
@@ -59361,7 +59673,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -59482,7 +59794,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -59603,7 +59915,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -59724,7 +60036,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -59845,7 +60157,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -59966,7 +60278,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -60087,7 +60399,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -60208,7 +60520,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -60329,7 +60641,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -60450,7 +60762,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -60571,7 +60883,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -60692,7 +61004,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -60701,7 +61013,7 @@
         <v>2.94</v>
       </c>
       <c r="AG516" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH516" t="b">
         <v>0</v>
@@ -60813,7 +61125,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -60934,7 +61246,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -61055,7 +61367,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -61176,7 +61488,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -61297,7 +61609,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -61418,7 +61730,7 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
@@ -61539,7 +61851,7 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
@@ -61660,7 +61972,7 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
@@ -61781,7 +62093,7 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
@@ -61902,7 +62214,7 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
@@ -62023,7 +62335,7 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
@@ -62144,7 +62456,7 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
@@ -62265,7 +62577,7 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
@@ -62386,7 +62698,7 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
@@ -62507,7 +62819,7 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
@@ -62628,7 +62940,7 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
@@ -62749,7 +63061,7 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
@@ -62870,7 +63182,7 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
@@ -62991,7 +63303,7 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
@@ -63112,7 +63424,7 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
@@ -63233,7 +63545,7 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
@@ -63354,7 +63666,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -63475,7 +63787,7 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
@@ -63596,7 +63908,7 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
@@ -63717,7 +64029,7 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
@@ -63838,7 +64150,7 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
@@ -63959,7 +64271,7 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
@@ -64080,7 +64392,7 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
@@ -64201,7 +64513,7 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
@@ -64322,7 +64634,7 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
@@ -64443,7 +64755,7 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
@@ -64564,7 +64876,7 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
@@ -64685,7 +64997,7 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
@@ -64806,7 +65118,7 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
@@ -65149,7 +65461,7 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
@@ -65270,7 +65582,7 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
@@ -65391,7 +65703,7 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
@@ -65623,7 +65935,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA557" t="n">
         <v>-0.77</v>
@@ -65744,7 +66056,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA558" t="n">
         <v>0.85</v>
@@ -65865,7 +66177,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA559" t="n">
         <v>-2.33</v>
@@ -65986,7 +66298,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA560" t="n">
         <v>4.41</v>
@@ -66107,7 +66419,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA561" t="n">
         <v>-1.6</v>
@@ -66228,7 +66540,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA562" t="n">
         <v>14</v>
@@ -66346,7 +66658,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA563" t="n">
         <v>-4.15</v>
@@ -66467,7 +66779,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA564" t="n">
         <v>-4.8</v>
@@ -66588,7 +66900,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA565" t="n">
         <v>-4.49</v>
@@ -66709,7 +67021,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA566" t="n">
         <v>-0.99</v>
@@ -66830,7 +67142,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA567" t="n">
         <v>-1.34</v>
@@ -66951,7 +67263,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA568" t="n">
         <v>-1.77</v>
@@ -67072,7 +67384,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA569" t="n">
         <v>-3.59</v>
@@ -67193,7 +67505,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA570" t="n">
         <v>0.29</v>
@@ -67314,7 +67626,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA571" t="n">
         <v>-4.43</v>
@@ -67435,7 +67747,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA572" t="n">
         <v>-3.52</v>
@@ -67556,7 +67868,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA573" t="n">
         <v>-1.74</v>
@@ -67677,7 +67989,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA574" t="n">
         <v>-3.79</v>
@@ -67798,7 +68110,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA575" t="n">
         <v>-3.07</v>
@@ -67919,7 +68231,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA576" t="n">
         <v>-1.21</v>
@@ -68373,7 +68685,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA580" t="n">
         <v>31.15</v>
@@ -68494,7 +68806,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA581" t="n">
         <v>2.49</v>
@@ -68615,7 +68927,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA582" t="n">
         <v>-0.9399999999999999</v>
@@ -68736,7 +69048,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA583" t="n">
         <v>-3.99</v>
@@ -68968,10 +69280,13 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA585" t="n">
         <v>3.78</v>
+      </c>
+      <c r="AB585" t="n">
+        <v>23.11</v>
       </c>
       <c r="AG585" t="b">
         <v>1</v>
@@ -69086,10 +69401,13 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA586" t="n">
         <v>-0.88</v>
+      </c>
+      <c r="AB586" t="n">
+        <v>7.2</v>
       </c>
       <c r="AG586" t="b">
         <v>0</v>
@@ -69204,10 +69522,13 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA587" t="n">
         <v>-1.6</v>
+      </c>
+      <c r="AB587" t="n">
+        <v>-5.45</v>
       </c>
       <c r="AG587" t="b">
         <v>0</v>
@@ -69322,10 +69643,13 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA588" t="n">
         <v>4.07</v>
+      </c>
+      <c r="AB588" t="n">
+        <v>5.51</v>
       </c>
       <c r="AG588" t="b">
         <v>1</v>
@@ -69440,10 +69764,13 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA589" t="n">
         <v>-1.9</v>
+      </c>
+      <c r="AB589" t="n">
+        <v>-2.77</v>
       </c>
       <c r="AG589" t="b">
         <v>0</v>
@@ -69558,10 +69885,13 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA590" t="n">
         <v>15.49</v>
+      </c>
+      <c r="AB590" t="n">
+        <v>23.39</v>
       </c>
       <c r="AG590" t="b">
         <v>1</v>
@@ -69676,10 +70006,13 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA591" t="n">
         <v>4.25</v>
+      </c>
+      <c r="AB591" t="n">
+        <v>4.46</v>
       </c>
       <c r="AG591" t="b">
         <v>0</v>
@@ -69794,10 +70127,13 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA592" t="n">
         <v>-4.09</v>
+      </c>
+      <c r="AB592" t="n">
+        <v>-5.45</v>
       </c>
       <c r="AG592" t="b">
         <v>0</v>
@@ -69912,10 +70248,13 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA593" t="n">
         <v>-5.77</v>
+      </c>
+      <c r="AB593" t="n">
+        <v>-4.62</v>
       </c>
       <c r="AG593" t="b">
         <v>0</v>
@@ -70027,10 +70366,13 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA594" t="n">
         <v>0.66</v>
+      </c>
+      <c r="AB594" t="n">
+        <v>2.66</v>
       </c>
       <c r="AG594" t="b">
         <v>0</v>
@@ -70145,10 +70487,13 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA595" t="n">
         <v>0.9</v>
+      </c>
+      <c r="AB595" t="n">
+        <v>1.36</v>
       </c>
       <c r="AG595" t="b">
         <v>0</v>
@@ -70263,10 +70608,13 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA596" t="n">
         <v>-0.89</v>
+      </c>
+      <c r="AB596" t="n">
+        <v>-4.2</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -70381,10 +70729,13 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA597" t="n">
         <v>-3.23</v>
+      </c>
+      <c r="AB597" t="n">
+        <v>-2.05</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -70499,10 +70850,13 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA598" t="n">
         <v>-1.86</v>
+      </c>
+      <c r="AB598" t="n">
+        <v>-1</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -70617,10 +70971,13 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA599" t="n">
         <v>-3.91</v>
+      </c>
+      <c r="AB599" t="n">
+        <v>-3.52</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -70735,10 +71092,13 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA600" t="n">
         <v>-5.86</v>
+      </c>
+      <c r="AB600" t="n">
+        <v>-6.64</v>
       </c>
       <c r="AG600" t="b">
         <v>0</v>
@@ -70853,10 +71213,13 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA601" t="n">
         <v>-2.98</v>
+      </c>
+      <c r="AB601" t="n">
+        <v>0.33</v>
       </c>
       <c r="AG601" t="b">
         <v>0</v>
@@ -70971,10 +71334,13 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA602" t="n">
         <v>-3.02</v>
+      </c>
+      <c r="AB602" t="n">
+        <v>-3.14</v>
       </c>
       <c r="AG602" t="b">
         <v>0</v>
@@ -71089,10 +71455,13 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA603" t="n">
         <v>-2.06</v>
+      </c>
+      <c r="AB603" t="n">
+        <v>-6.01</v>
       </c>
       <c r="AG603" t="b">
         <v>0</v>
@@ -71207,10 +71576,13 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA604" t="n">
         <v>-0.87</v>
+      </c>
+      <c r="AB604" t="n">
+        <v>7.43</v>
       </c>
       <c r="AG604" t="b">
         <v>0</v>
@@ -71325,10 +71697,13 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA605" t="n">
         <v>0.58</v>
+      </c>
+      <c r="AB605" t="n">
+        <v>11.78</v>
       </c>
       <c r="AG605" t="b">
         <v>0</v>
@@ -71440,10 +71815,13 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA606" t="n">
         <v>-2.42</v>
+      </c>
+      <c r="AB606" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AG606" t="b">
         <v>0</v>
@@ -72002,10 +72380,13 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA611" t="n">
         <v>1.45</v>
+      </c>
+      <c r="AB611" t="n">
+        <v>4.36</v>
       </c>
       <c r="AG611" t="b">
         <v>0</v>
@@ -72117,9 +72498,12 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA612" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="AB612" t="n">
         <v>-2.34</v>
       </c>
       <c r="AG612" t="b">
@@ -72346,10 +72730,13 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA614" t="n">
         <v>-4.58</v>
+      </c>
+      <c r="AB614" t="n">
+        <v>-4.95</v>
       </c>
       <c r="AG614" t="b">
         <v>0</v>
@@ -72464,13 +72851,13 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA615" t="n">
         <v>6.68</v>
       </c>
       <c r="AG615" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH615" t="b">
         <v>0</v>
@@ -72582,7 +72969,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA616" t="n">
         <v>-1.59</v>
@@ -72591,7 +72978,7 @@
         <v>0</v>
       </c>
       <c r="AH616" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI616" t="inlineStr">
         <is>
@@ -72700,7 +73087,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA617" t="n">
         <v>-10.11</v>
@@ -72818,7 +73205,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA618" t="n">
         <v>-2.58</v>
@@ -72936,7 +73323,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA619" t="n">
         <v>-1.8</v>
@@ -73054,7 +73441,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA620" t="n">
         <v>-3.27</v>
@@ -73169,7 +73556,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA621" t="n">
         <v>-2.27</v>
@@ -73287,7 +73674,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA622" t="n">
         <v>-1.77</v>
@@ -73405,7 +73792,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA623" t="n">
         <v>-3.96</v>
@@ -73523,7 +73910,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA624" t="n">
         <v>-2.7</v>
@@ -73641,7 +74028,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA625" t="n">
         <v>-3.17</v>
@@ -73759,7 +74146,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA626" t="n">
         <v>-2.84</v>
@@ -73877,7 +74264,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA627" t="n">
         <v>0.59</v>
@@ -73995,7 +74382,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA628" t="n">
         <v>0.19</v>
@@ -74110,7 +74497,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA629" t="n">
         <v>-4.02</v>
@@ -74561,7 +74948,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA633" t="n">
         <v>5.58</v>
@@ -74679,7 +75066,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA634" t="n">
         <v>8.529999999999999</v>
@@ -74908,7 +75295,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA636" t="n">
         <v>7.05</v>
@@ -75137,7 +75524,7 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA638" t="n">
         <v>0.9399999999999999</v>
@@ -75146,7 +75533,7 @@
         <v>0</v>
       </c>
       <c r="AH638" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI638" t="inlineStr">
         <is>
@@ -75255,7 +75642,7 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA639" t="n">
         <v>-14.75</v>
@@ -75373,7 +75760,7 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA640" t="n">
         <v>-3.86</v>
@@ -75491,7 +75878,7 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA641" t="n">
         <v>-4.11</v>
@@ -75606,7 +75993,7 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA642" t="n">
         <v>-2.59</v>
@@ -75724,7 +76111,7 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA643" t="n">
         <v>-6.11</v>
@@ -75842,7 +76229,7 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA644" t="n">
         <v>-1.52</v>
@@ -75960,7 +76347,7 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA645" t="n">
         <v>-4.53</v>
@@ -76078,7 +76465,7 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA646" t="n">
         <v>-3.85</v>
@@ -76196,7 +76583,7 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA647" t="n">
         <v>-3.85</v>
@@ -76314,7 +76701,7 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA648" t="n">
         <v>-3.01</v>
@@ -76432,7 +76819,7 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA649" t="n">
         <v>3.54</v>
@@ -76550,7 +76937,7 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA650" t="n">
         <v>-1.86</v>
@@ -77001,7 +77388,7 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA654" t="n">
         <v>9.09</v>
@@ -77341,7 +77728,7 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA657" t="n">
         <v>-0.97</v>
@@ -77459,7 +77846,7 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA658" t="n">
         <v>0.9399999999999999</v>
@@ -77468,7 +77855,7 @@
         <v>0</v>
       </c>
       <c r="AH658" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI658" t="inlineStr">
         <is>
@@ -77577,7 +77964,7 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA659" t="n">
         <v>-1.95</v>
@@ -77695,7 +78082,7 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA660" t="n">
         <v>2.75</v>
@@ -77813,7 +78200,7 @@
         </is>
       </c>
       <c r="Z661" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA661" t="n">
         <v>-5.81</v>
@@ -77931,7 +78318,7 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA662" t="n">
         <v>0.34</v>
@@ -78049,7 +78436,7 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA663" t="n">
         <v>-2.8</v>
@@ -78167,7 +78554,7 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA664" t="n">
         <v>-4.53</v>
@@ -78282,7 +78669,7 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA665" t="n">
         <v>-1.63</v>
@@ -78400,7 +78787,7 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA666" t="n">
         <v>-5.08</v>
@@ -78518,7 +78905,7 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA667" t="n">
         <v>-0.55</v>
@@ -78636,7 +79023,7 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA668" t="n">
         <v>-4.02</v>
@@ -78754,7 +79141,7 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA669" t="n">
         <v>-5.59</v>
@@ -78872,7 +79259,7 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA670" t="n">
         <v>-2.22</v>
@@ -78990,7 +79377,7 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA671" t="n">
         <v>-3.26</v>
@@ -79108,7 +79495,7 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA672" t="n">
         <v>-0.86</v>
@@ -79226,7 +79613,7 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA673" t="n">
         <v>-0.18</v>
@@ -79566,7 +79953,7 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA676" t="n">
         <v>-5.78</v>
@@ -79795,7 +80182,7 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA678" t="n">
         <v>6.85</v>
@@ -79913,7 +80300,7 @@
         </is>
       </c>
       <c r="Z679" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA679" t="n">
         <v>2.65</v>
@@ -80031,7 +80418,7 @@
         </is>
       </c>
       <c r="Z680" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA680" t="n">
         <v>2.49</v>
@@ -80149,7 +80536,7 @@
         </is>
       </c>
       <c r="Z681" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA681" t="n">
         <v>14.18</v>
@@ -80267,7 +80654,7 @@
         </is>
       </c>
       <c r="Z682" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA682" t="n">
         <v>-5.47</v>
@@ -80276,7 +80663,7 @@
         <v>0</v>
       </c>
       <c r="AH682" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI682" t="inlineStr">
         <is>
@@ -80385,7 +80772,7 @@
         </is>
       </c>
       <c r="Z683" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA683" t="n">
         <v>-2.27</v>
@@ -80503,7 +80890,7 @@
         </is>
       </c>
       <c r="Z684" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA684" t="n">
         <v>-1.75</v>
@@ -80621,7 +81008,7 @@
         </is>
       </c>
       <c r="Z685" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA685" t="n">
         <v>-2.44</v>
@@ -80739,7 +81126,7 @@
         </is>
       </c>
       <c r="Z686" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA686" t="n">
         <v>0.84</v>
@@ -80857,7 +81244,7 @@
         </is>
       </c>
       <c r="Z687" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA687" t="n">
         <v>4.6</v>
@@ -80975,7 +81362,7 @@
         </is>
       </c>
       <c r="Z688" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA688" t="n">
         <v>3.53</v>
@@ -81426,7 +81813,7 @@
         </is>
       </c>
       <c r="Z692" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA692" t="n">
         <v>0.88</v>
@@ -81655,7 +82042,7 @@
         </is>
       </c>
       <c r="Z694" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA694" t="n">
         <v>3.76</v>
@@ -81773,7 +82160,7 @@
         </is>
       </c>
       <c r="Z695" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA695" t="n">
         <v>6.15</v>
@@ -82113,10 +82500,13 @@
         </is>
       </c>
       <c r="Z698" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA698" t="n">
+        <v>18.62</v>
       </c>
       <c r="AG698" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH698" t="b">
         <v>0</v>
@@ -82228,7 +82618,10 @@
         </is>
       </c>
       <c r="Z699" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA699" t="n">
+        <v>1.38</v>
       </c>
       <c r="AG699" t="b">
         <v>0</v>
@@ -82343,7 +82736,10 @@
         </is>
       </c>
       <c r="Z700" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA700" t="n">
+        <v>1.1</v>
       </c>
       <c r="AG700" t="b">
         <v>0</v>
@@ -82458,7 +82854,10 @@
         </is>
       </c>
       <c r="Z701" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA701" t="n">
+        <v>6.85</v>
       </c>
       <c r="AG701" t="b">
         <v>1</v>
@@ -82573,7 +82972,10 @@
         </is>
       </c>
       <c r="Z702" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA702" t="n">
+        <v>0.2</v>
       </c>
       <c r="AG702" t="b">
         <v>0</v>
@@ -82688,7 +83090,10 @@
         </is>
       </c>
       <c r="Z703" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA703" t="n">
+        <v>0.24</v>
       </c>
       <c r="AG703" t="b">
         <v>0</v>
@@ -83136,7 +83541,10 @@
         </is>
       </c>
       <c r="Z707" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA707" t="n">
+        <v>5.68</v>
       </c>
       <c r="AG707" t="b">
         <v>0</v>
@@ -83362,7 +83770,10 @@
         </is>
       </c>
       <c r="Z709" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA709" t="n">
+        <v>2.86</v>
       </c>
       <c r="AG709" t="b">
         <v>0</v>
@@ -83477,7 +83888,10 @@
         </is>
       </c>
       <c r="Z710" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA710" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="AG710" t="b">
         <v>0</v>
@@ -83592,7 +84006,10 @@
         </is>
       </c>
       <c r="Z711" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="AA711" t="n">
+        <v>15.15</v>
       </c>
       <c r="AG711" t="b">
         <v>1</v>
@@ -83929,7 +84346,7 @@
         </is>
       </c>
       <c r="Z714" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG714" t="b">
         <v>0</v>
@@ -84044,7 +84461,7 @@
         </is>
       </c>
       <c r="Z715" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG715" t="b">
         <v>0</v>
@@ -84159,7 +84576,7 @@
         </is>
       </c>
       <c r="Z716" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG716" t="b">
         <v>0</v>
@@ -84274,7 +84691,7 @@
         </is>
       </c>
       <c r="Z717" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG717" t="b">
         <v>0</v>
@@ -84389,7 +84806,7 @@
         </is>
       </c>
       <c r="Z718" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG718" t="b">
         <v>0</v>
@@ -84504,7 +84921,7 @@
         </is>
       </c>
       <c r="Z719" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG719" t="b">
         <v>0</v>
@@ -84619,7 +85036,7 @@
         </is>
       </c>
       <c r="Z720" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG720" t="b">
         <v>0</v>
@@ -84734,7 +85151,7 @@
         </is>
       </c>
       <c r="Z721" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG721" t="b">
         <v>0</v>
@@ -84849,7 +85266,7 @@
         </is>
       </c>
       <c r="Z722" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG722" t="b">
         <v>1</v>
@@ -84964,7 +85381,7 @@
         </is>
       </c>
       <c r="Z723" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG723" t="b">
         <v>0</v>
@@ -85190,7 +85607,7 @@
         </is>
       </c>
       <c r="Z725" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG725" t="b">
         <v>0</v>
@@ -85416,7 +85833,7 @@
         </is>
       </c>
       <c r="Z727" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG727" t="b">
         <v>0</v>
@@ -85531,7 +85948,7 @@
         </is>
       </c>
       <c r="Z728" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG728" t="b">
         <v>0</v>
@@ -85757,7 +86174,7 @@
         </is>
       </c>
       <c r="Z730" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG730" t="b">
         <v>0</v>
@@ -85872,7 +86289,7 @@
         </is>
       </c>
       <c r="Z731" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG731" t="b">
         <v>0</v>
@@ -85987,13 +86404,13 @@
         </is>
       </c>
       <c r="Z732" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG732" t="b">
         <v>0</v>
       </c>
       <c r="AH732" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI732" t="inlineStr">
         <is>
@@ -86102,7 +86519,7 @@
         </is>
       </c>
       <c r="Z733" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG733" t="b">
         <v>0</v>
@@ -86217,7 +86634,7 @@
         </is>
       </c>
       <c r="Z734" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG734" t="b">
         <v>0</v>
@@ -86332,7 +86749,7 @@
         </is>
       </c>
       <c r="Z735" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG735" t="b">
         <v>0</v>
@@ -86447,7 +86864,7 @@
         </is>
       </c>
       <c r="Z736" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG736" t="b">
         <v>0</v>
@@ -86562,7 +86979,7 @@
         </is>
       </c>
       <c r="Z737" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG737" t="b">
         <v>0</v>
@@ -86677,7 +87094,7 @@
         </is>
       </c>
       <c r="Z738" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG738" t="b">
         <v>0</v>
@@ -86792,7 +87209,7 @@
         </is>
       </c>
       <c r="Z739" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG739" t="b">
         <v>0</v>
@@ -86907,7 +87324,7 @@
         </is>
       </c>
       <c r="Z740" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG740" t="b">
         <v>0</v>
@@ -87022,7 +87439,7 @@
         </is>
       </c>
       <c r="Z741" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG741" t="b">
         <v>0</v>
@@ -87248,7 +87665,7 @@
         </is>
       </c>
       <c r="Z743" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG743" t="b">
         <v>0</v>
@@ -87363,7 +87780,7 @@
         </is>
       </c>
       <c r="Z744" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG744" t="b">
         <v>0</v>
@@ -87589,7 +88006,7 @@
         </is>
       </c>
       <c r="Z746" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG746" t="b">
         <v>0</v>
@@ -87704,7 +88121,7 @@
         </is>
       </c>
       <c r="Z747" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG747" t="b">
         <v>0</v>
@@ -88152,7 +88569,7 @@
         </is>
       </c>
       <c r="Z751" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG751" t="b">
         <v>0</v>
@@ -88267,7 +88684,7 @@
         </is>
       </c>
       <c r="Z752" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG752" t="b">
         <v>0</v>
@@ -88382,13 +88799,13 @@
         </is>
       </c>
       <c r="Z753" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG753" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH753" t="b">
         <v>1</v>
-      </c>
-      <c r="AG753" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH753" t="b">
-        <v>0</v>
       </c>
       <c r="AI753" t="inlineStr">
         <is>
@@ -88497,7 +88914,7 @@
         </is>
       </c>
       <c r="Z754" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG754" t="b">
         <v>0</v>
@@ -88612,13 +89029,13 @@
         </is>
       </c>
       <c r="Z755" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG755" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH755" t="b">
         <v>1</v>
-      </c>
-      <c r="AG755" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH755" t="b">
-        <v>0</v>
       </c>
       <c r="AI755" t="inlineStr">
         <is>
@@ -88727,7 +89144,7 @@
         </is>
       </c>
       <c r="Z756" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG756" t="b">
         <v>0</v>
@@ -88842,7 +89259,7 @@
         </is>
       </c>
       <c r="Z757" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG757" t="b">
         <v>0</v>
@@ -88957,7 +89374,7 @@
         </is>
       </c>
       <c r="Z758" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG758" t="b">
         <v>0</v>
@@ -89072,7 +89489,7 @@
         </is>
       </c>
       <c r="Z759" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG759" t="b">
         <v>0</v>
@@ -89187,7 +89604,7 @@
         </is>
       </c>
       <c r="Z760" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG760" t="b">
         <v>0</v>
@@ -89302,7 +89719,7 @@
         </is>
       </c>
       <c r="Z761" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG761" t="b">
         <v>0</v>
@@ -89417,7 +89834,7 @@
         </is>
       </c>
       <c r="Z762" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG762" t="b">
         <v>0</v>
@@ -89532,7 +89949,7 @@
         </is>
       </c>
       <c r="Z763" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG763" t="b">
         <v>0</v>
@@ -90202,7 +90619,7 @@
         </is>
       </c>
       <c r="Z769" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG769" t="b">
         <v>0</v>
@@ -90317,13 +90734,13 @@
         </is>
       </c>
       <c r="Z770" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG770" t="b">
         <v>0</v>
       </c>
       <c r="AH770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI770" t="inlineStr">
         <is>
@@ -90432,7 +90849,7 @@
         </is>
       </c>
       <c r="Z771" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG771" t="b">
         <v>0</v>
@@ -90547,7 +90964,7 @@
         </is>
       </c>
       <c r="Z772" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG772" t="b">
         <v>0</v>
@@ -90662,7 +91079,7 @@
         </is>
       </c>
       <c r="Z773" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG773" t="b">
         <v>0</v>
@@ -90777,7 +91194,7 @@
         </is>
       </c>
       <c r="Z774" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG774" t="b">
         <v>0</v>
@@ -90892,7 +91309,7 @@
         </is>
       </c>
       <c r="Z775" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG775" t="b">
         <v>0</v>
@@ -91007,7 +91424,7 @@
         </is>
       </c>
       <c r="Z776" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG776" t="b">
         <v>0</v>
@@ -91122,7 +91539,7 @@
         </is>
       </c>
       <c r="Z777" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG777" t="b">
         <v>0</v>
@@ -91237,7 +91654,7 @@
         </is>
       </c>
       <c r="Z778" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG778" t="b">
         <v>0</v>
@@ -91352,7 +91769,7 @@
         </is>
       </c>
       <c r="Z779" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG779" t="b">
         <v>0</v>
@@ -91467,7 +91884,7 @@
         </is>
       </c>
       <c r="Z780" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG780" t="b">
         <v>0</v>
@@ -91582,7 +91999,7 @@
         </is>
       </c>
       <c r="Z781" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG781" t="b">
         <v>0</v>
@@ -91808,7 +92225,7 @@
         </is>
       </c>
       <c r="Z783" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG783" t="b">
         <v>0</v>
@@ -92145,7 +92562,7 @@
         </is>
       </c>
       <c r="Z786" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG786" t="b">
         <v>0</v>
@@ -92371,7 +92788,7 @@
         </is>
       </c>
       <c r="Z788" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG788" t="b">
         <v>0</v>
@@ -92486,7 +92903,7 @@
         </is>
       </c>
       <c r="Z789" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG789" t="b">
         <v>0</v>
@@ -92601,7 +93018,7 @@
         </is>
       </c>
       <c r="Z790" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG790" t="b">
         <v>0</v>
@@ -93160,7 +93577,7 @@
         </is>
       </c>
       <c r="Z795" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG795" t="b">
         <v>0</v>
@@ -93169,13 +93586,2852 @@
         <v>0</v>
       </c>
       <c r="AI795" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>90.45999999999999</v>
+      </c>
+      <c r="F796" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I796" t="b">
+        <v>0</v>
+      </c>
+      <c r="J796" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="K796" t="n">
+        <v>312</v>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M796" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N796" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P796" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="Q796" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="S796" t="n">
+        <v>7</v>
+      </c>
+      <c r="T796" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U796" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="V796" t="n">
+        <v>293</v>
+      </c>
+      <c r="W796" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="X796" t="n">
+        <v>272.49</v>
+      </c>
+      <c r="Y796" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z796" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG796" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH796" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI796" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="F797" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I797" t="b">
+        <v>0</v>
+      </c>
+      <c r="J797" t="n">
+        <v>10</v>
+      </c>
+      <c r="K797" t="n">
+        <v>2255</v>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M797" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N797" t="n">
+        <v>3</v>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P797" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Q797" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="R797" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S797" t="n">
+        <v>7</v>
+      </c>
+      <c r="T797" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U797" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V797" t="n">
+        <v>2050</v>
+      </c>
+      <c r="W797" t="n">
+        <v>2460</v>
+      </c>
+      <c r="X797" t="n">
+        <v>1906.5</v>
+      </c>
+      <c r="Y797" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z797" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG797" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH797" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI797" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>swing_buy_confirmed</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="F798" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I798" t="b">
+        <v>0</v>
+      </c>
+      <c r="J798" t="n">
+        <v>10</v>
+      </c>
+      <c r="K798" t="n">
+        <v>2585</v>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M798" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N798" t="n">
+        <v>7</v>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P798" t="n">
+        <v>2282.5</v>
+      </c>
+      <c r="Q798" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S798" t="n">
+        <v>7</v>
+      </c>
+      <c r="T798" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U798" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V798" t="n">
+        <v>2350</v>
+      </c>
+      <c r="W798" t="n">
+        <v>2820</v>
+      </c>
+      <c r="X798" t="n">
+        <v>2185.5</v>
+      </c>
+      <c r="Y798" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z798" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG798" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH798" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI798" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="F799" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I799" t="b">
+        <v>0</v>
+      </c>
+      <c r="J799" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="K799" t="n">
+        <v>411</v>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M799" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N799" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P799" t="n">
+        <v>374</v>
+      </c>
+      <c r="Q799" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S799" t="n">
+        <v>7</v>
+      </c>
+      <c r="T799" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U799" t="inlineStr">
+        <is>
+          <t>ai_hardware</t>
+        </is>
+      </c>
+      <c r="V799" t="n">
+        <v>380</v>
+      </c>
+      <c r="W799" t="n">
+        <v>437.5292</v>
+      </c>
+      <c r="X799" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="Y799" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z799" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG799" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH799" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI799" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>友達</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="F800" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I800" t="b">
+        <v>0</v>
+      </c>
+      <c r="J800" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K800" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M800" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N800" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P800" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="Q800" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="R800" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S800" t="n">
+        <v>7</v>
+      </c>
+      <c r="T800" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U800" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V800" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="W800" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="X800" t="n">
+        <v>34.8285</v>
+      </c>
+      <c r="Y800" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z800" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG800" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH800" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI800" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="F801" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I801" t="b">
+        <v>0</v>
+      </c>
+      <c r="J801" t="n">
+        <v>10</v>
+      </c>
+      <c r="K801" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M801" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N801" t="n">
+        <v>10</v>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P801" t="n">
+        <v>297.25</v>
+      </c>
+      <c r="Q801" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S801" t="n">
+        <v>3.672</v>
+      </c>
+      <c r="T801" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U801" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V801" t="n">
+        <v>298</v>
+      </c>
+      <c r="W801" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="X801" t="n">
+        <v>287.0575</v>
+      </c>
+      <c r="Y801" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z801" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG801" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH801" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI801" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="F802" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I802" t="b">
+        <v>0</v>
+      </c>
+      <c r="J802" t="n">
+        <v>10</v>
+      </c>
+      <c r="K802" t="n">
+        <v>5412</v>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M802" t="n">
+        <v>3</v>
+      </c>
+      <c r="N802" t="n">
+        <v>8</v>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P802" t="n">
+        <v>4990</v>
+      </c>
+      <c r="Q802" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S802" t="n">
+        <v>3.3313</v>
+      </c>
+      <c r="T802" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V802" t="n">
+        <v>4920</v>
+      </c>
+      <c r="W802" t="n">
+        <v>5904</v>
+      </c>
+      <c r="X802" t="n">
+        <v>4756.1</v>
+      </c>
+      <c r="Y802" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z802" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG802" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH802" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI802" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>智原</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="F803" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I803" t="b">
+        <v>0</v>
+      </c>
+      <c r="J803" t="n">
+        <v>10</v>
+      </c>
+      <c r="K803" t="n">
+        <v>231.55</v>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M803" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N803" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P803" t="n">
+        <v>199.25</v>
+      </c>
+      <c r="Q803" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="R803" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S803" t="n">
+        <v>7</v>
+      </c>
+      <c r="T803" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U803" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V803" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="W803" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="X803" t="n">
+        <v>195.765</v>
+      </c>
+      <c r="Y803" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z803" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG803" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH803" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI803" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="F804" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I804" t="b">
+        <v>0</v>
+      </c>
+      <c r="J804" t="n">
+        <v>10</v>
+      </c>
+      <c r="K804" t="n">
+        <v>1441</v>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M804" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N804" t="n">
+        <v>3</v>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P804" t="n">
+        <v>1180</v>
+      </c>
+      <c r="Q804" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S804" t="n">
+        <v>7</v>
+      </c>
+      <c r="T804" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U804" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V804" t="n">
+        <v>1310</v>
+      </c>
+      <c r="W804" t="n">
+        <v>1572</v>
+      </c>
+      <c r="X804" t="n">
+        <v>1218.3</v>
+      </c>
+      <c r="Y804" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z804" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG804" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH804" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI804" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="F805" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I805" t="b">
+        <v>0</v>
+      </c>
+      <c r="J805" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="K805" t="n">
+        <v>619</v>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M805" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N805" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P805" t="n">
+        <v>542.75</v>
+      </c>
+      <c r="Q805" t="n">
+        <v>70.29000000000001</v>
+      </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S805" t="n">
+        <v>7</v>
+      </c>
+      <c r="T805" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U805" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V805" t="n">
+        <v>579</v>
+      </c>
+      <c r="W805" t="n">
+        <v>694.8</v>
+      </c>
+      <c r="X805" t="n">
+        <v>538.47</v>
+      </c>
+      <c r="Y805" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z805" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG805" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH805" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI805" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>穩懋</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="F806" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I806" t="b">
+        <v>0</v>
+      </c>
+      <c r="J806" t="n">
+        <v>10</v>
+      </c>
+      <c r="K806" t="n">
+        <v>651.2</v>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M806" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N806" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P806" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="Q806" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S806" t="n">
+        <v>7</v>
+      </c>
+      <c r="T806" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U806" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V806" t="n">
+        <v>592</v>
+      </c>
+      <c r="W806" t="n">
+        <v>710.4</v>
+      </c>
+      <c r="X806" t="n">
+        <v>550.5599999999999</v>
+      </c>
+      <c r="Y806" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI806" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ806" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>72.73999999999999</v>
+      </c>
+      <c r="F807" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I807" t="b">
+        <v>0</v>
+      </c>
+      <c r="J807" t="n">
+        <v>10</v>
+      </c>
+      <c r="K807" t="n">
+        <v>1177</v>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M807" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N807" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P807" t="n">
+        <v>967.5</v>
+      </c>
+      <c r="Q807" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S807" t="n">
+        <v>7</v>
+      </c>
+      <c r="T807" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U807" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V807" t="n">
+        <v>1070</v>
+      </c>
+      <c r="W807" t="n">
+        <v>1284</v>
+      </c>
+      <c r="X807" t="n">
+        <v>995.1</v>
+      </c>
+      <c r="Y807" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z807" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG807" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH807" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI807" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>72.81</v>
+      </c>
+      <c r="F808" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I808" t="b">
+        <v>0</v>
+      </c>
+      <c r="J808" t="n">
+        <v>10</v>
+      </c>
+      <c r="K808" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M808" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N808" t="n">
+        <v>5</v>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P808" t="n">
+        <v>474.25</v>
+      </c>
+      <c r="Q808" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="R808" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S808" t="n">
+        <v>7</v>
+      </c>
+      <c r="T808" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U808" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V808" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="W808" t="n">
+        <v>585</v>
+      </c>
+      <c r="X808" t="n">
+        <v>453.375</v>
+      </c>
+      <c r="Y808" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI808" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ808" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="F809" t="n">
+        <v>48.78</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I809" t="b">
+        <v>0</v>
+      </c>
+      <c r="J809" t="n">
+        <v>10</v>
+      </c>
+      <c r="K809" t="n">
+        <v>9212.5</v>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M809" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N809" t="n">
+        <v>1</v>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P809" t="n">
+        <v>7457.5</v>
+      </c>
+      <c r="Q809" t="n">
+        <v>65.19</v>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S809" t="n">
+        <v>7</v>
+      </c>
+      <c r="T809" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U809" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V809" t="n">
+        <v>8375</v>
+      </c>
+      <c r="W809" t="n">
+        <v>10050</v>
+      </c>
+      <c r="X809" t="n">
+        <v>7788.75</v>
+      </c>
+      <c r="Y809" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z809" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG809" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH809" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI809" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="F810" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I810" t="b">
+        <v>0</v>
+      </c>
+      <c r="J810" t="n">
+        <v>10</v>
+      </c>
+      <c r="K810" t="n">
+        <v>3426.5</v>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M810" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N810" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P810" t="n">
+        <v>3147.5</v>
+      </c>
+      <c r="Q810" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S810" t="n">
+        <v>7</v>
+      </c>
+      <c r="T810" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U810" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V810" t="n">
+        <v>3115</v>
+      </c>
+      <c r="W810" t="n">
+        <v>3738</v>
+      </c>
+      <c r="X810" t="n">
+        <v>2896.95</v>
+      </c>
+      <c r="Y810" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI810" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ810" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="F811" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I811" t="b">
+        <v>0</v>
+      </c>
+      <c r="J811" t="n">
+        <v>10</v>
+      </c>
+      <c r="K811" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M811" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N811" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P811" t="n">
+        <v>464</v>
+      </c>
+      <c r="Q811" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S811" t="n">
+        <v>7</v>
+      </c>
+      <c r="T811" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U811" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V811" t="n">
+        <v>467</v>
+      </c>
+      <c r="W811" t="n">
+        <v>560.4</v>
+      </c>
+      <c r="X811" t="n">
+        <v>434.31</v>
+      </c>
+      <c r="Y811" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z811" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG811" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH811" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI811" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="F812" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I812" t="b">
+        <v>0</v>
+      </c>
+      <c r="J812" t="n">
+        <v>10</v>
+      </c>
+      <c r="K812" t="n">
+        <v>818.4</v>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M812" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N812" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P812" t="n">
+        <v>685</v>
+      </c>
+      <c r="Q812" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S812" t="n">
+        <v>7</v>
+      </c>
+      <c r="T812" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U812" t="inlineStr">
+        <is>
+          <t>semiconductor</t>
+        </is>
+      </c>
+      <c r="V812" t="n">
+        <v>744</v>
+      </c>
+      <c r="W812" t="n">
+        <v>892.8</v>
+      </c>
+      <c r="X812" t="n">
+        <v>691.92</v>
+      </c>
+      <c r="Y812" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z812" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG812" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH812" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI812" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="F813" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I813" t="b">
+        <v>0</v>
+      </c>
+      <c r="J813" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="K813" t="n">
+        <v>615.5</v>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M813" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N813" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P813" t="n">
+        <v>533.75</v>
+      </c>
+      <c r="Q813" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S813" t="n">
+        <v>7</v>
+      </c>
+      <c r="T813" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U813" t="inlineStr">
+        <is>
+          <t>electronic_components</t>
+        </is>
+      </c>
+      <c r="V813" t="n">
+        <v>574</v>
+      </c>
+      <c r="W813" t="n">
+        <v>688.8</v>
+      </c>
+      <c r="X813" t="n">
+        <v>533.8200000000001</v>
+      </c>
+      <c r="Y813" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z813" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG813" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH813" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI813" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>世界</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="F814" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I814" t="b">
+        <v>0</v>
+      </c>
+      <c r="J814" t="n">
+        <v>10</v>
+      </c>
+      <c r="K814" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M814" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N814" t="n">
+        <v>3</v>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P814" t="n">
+        <v>177.25</v>
+      </c>
+      <c r="Q814" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S814" t="n">
+        <v>7</v>
+      </c>
+      <c r="T814" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U814" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V814" t="n">
+        <v>191</v>
+      </c>
+      <c r="W814" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="X814" t="n">
+        <v>177.63</v>
+      </c>
+      <c r="Y814" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI814" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ814" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="F815" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I815" t="b">
+        <v>0</v>
+      </c>
+      <c r="J815" t="n">
+        <v>10</v>
+      </c>
+      <c r="K815" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M815" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N815" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P815" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="Q815" t="n">
+        <v>60.64</v>
+      </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S815" t="n">
+        <v>7</v>
+      </c>
+      <c r="T815" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U815" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V815" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="W815" t="n">
+        <v>119.7118</v>
+      </c>
+      <c r="X815" t="n">
+        <v>93.465</v>
+      </c>
+      <c r="Y815" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI815" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ815" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="F816" t="n">
+        <v>73.66</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I816" t="b">
+        <v>0</v>
+      </c>
+      <c r="J816" t="n">
+        <v>10</v>
+      </c>
+      <c r="K816" t="n">
+        <v>238.15</v>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M816" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N816" t="n">
+        <v>10</v>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P816" t="n">
+        <v>219.5</v>
+      </c>
+      <c r="Q816" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="R816" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S816" t="n">
+        <v>4.4065</v>
+      </c>
+      <c r="T816" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U816" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V816" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="W816" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="X816" t="n">
+        <v>206.96</v>
+      </c>
+      <c r="Y816" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI816" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ816" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>6182</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>合晶</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E817" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="F817" t="n">
+        <v>54</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I817" t="b">
+        <v>0</v>
+      </c>
+      <c r="J817" t="n">
+        <v>10</v>
+      </c>
+      <c r="K817" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M817" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N817" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="P817" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q817" t="n">
+        <v>63.32</v>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S817" t="n">
+        <v>7</v>
+      </c>
+      <c r="T817" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U817" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V817" t="n">
+        <v>128</v>
+      </c>
+      <c r="W817" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="X817" t="n">
+        <v>119.04</v>
+      </c>
+      <c r="Y817" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI817" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ817" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E818" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F818" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="I818" t="b">
+        <v>0</v>
+      </c>
+      <c r="J818" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K818" t="n">
+        <v>1825</v>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M818" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N818" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P818" t="n">
+        <v>1527.5</v>
+      </c>
+      <c r="Q818" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S818" t="n">
+        <v>7</v>
+      </c>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V818" t="n">
+        <v>1755</v>
+      </c>
+      <c r="W818" t="n">
+        <v>2106</v>
+      </c>
+      <c r="X818" t="n">
+        <v>1632.15</v>
+      </c>
+      <c r="Y818" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI818" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ818" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="F819" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I819" t="b">
+        <v>0</v>
+      </c>
+      <c r="J819" t="n">
+        <v>10</v>
+      </c>
+      <c r="K819" t="n">
+        <v>1325.5</v>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M819" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N819" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P819" t="n">
+        <v>1080.5</v>
+      </c>
+      <c r="Q819" t="n">
+        <v>66.20999999999999</v>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="S819" t="n">
+        <v>7</v>
+      </c>
+      <c r="T819" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V819" t="n">
+        <v>1205</v>
+      </c>
+      <c r="W819" t="n">
+        <v>1446</v>
+      </c>
+      <c r="X819" t="n">
+        <v>1120.65</v>
+      </c>
+      <c r="Y819" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="AI819" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AJ819" t="inlineStr">
+        <is>
+          <t>market_data_temporarily_unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>swing_accumulation_ready</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="F820" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>WaitPullback</t>
+        </is>
+      </c>
+      <c r="I820" t="b">
+        <v>0</v>
+      </c>
+      <c r="J820" t="n">
+        <v>10</v>
+      </c>
+      <c r="K820" t="n">
+        <v>1655.5</v>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>measured_move_target_up</t>
+        </is>
+      </c>
+      <c r="M820" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N820" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P820" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q820" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="S820" t="n">
+        <v>7</v>
+      </c>
+      <c r="T820" t="inlineStr">
+        <is>
+          <t>BullTrend</t>
+        </is>
+      </c>
+      <c r="U820" t="inlineStr">
+        <is>
+          <t>unclassified</t>
+        </is>
+      </c>
+      <c r="V820" t="n">
+        <v>1505</v>
+      </c>
+      <c r="W820" t="n">
+        <v>1806</v>
+      </c>
+      <c r="X820" t="n">
+        <v>1399.65</v>
+      </c>
+      <c r="Y820" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="Z820" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG820" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH820" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI820" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ795"/>
+  <autoFilter ref="A1:AJ820"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -93248,25 +96504,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4101</v>
+        <v>0.4192</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.38</v>
+        <v>-1.95</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4</v>
+        <v>8.31</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.33</v>
+        <v>-11.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1573</v>
+        <v>0.1515</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6348</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="3">
@@ -93276,25 +96532,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5625</v>
+        <v>0.5179</v>
       </c>
       <c r="D3" t="n">
-        <v>1.63</v>
+        <v>0.98</v>
       </c>
       <c r="E3" t="n">
-        <v>8.039999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.82</v>
+        <v>-4.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1042</v>
+        <v>0.0893</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1458</v>
+        <v>0.1964</v>
       </c>
     </row>
     <row r="4">
@@ -93398,25 +96654,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.5556</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.65</v>
+        <v>-3.75</v>
       </c>
       <c r="E2" t="n">
-        <v>10.78</v>
+        <v>10.69</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.29</v>
+        <v>-10.18</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1875</v>
+        <v>0.1667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.375</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="3">
@@ -93426,25 +96682,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4286</v>
+        <v>0.4419</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.43</v>
+        <v>-1.76</v>
       </c>
       <c r="E3" t="n">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.03</v>
+        <v>-10.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1429</v>
+        <v>0.1395</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5268</v>
+        <v>0.5116000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -93454,25 +96710,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4421</v>
+        <v>0.4175</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06</v>
+        <v>-0.29</v>
       </c>
       <c r="E4" t="n">
-        <v>9.289999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.94</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1474</v>
+        <v>0.1359</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5684</v>
+        <v>0.5728</v>
       </c>
     </row>
     <row r="5">
@@ -93482,25 +96738,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6667</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.51</v>
+        <v>-1.54</v>
       </c>
       <c r="E5" t="n">
-        <v>7.55</v>
+        <v>5.67</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.08</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -93569,7 +96825,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:24:45</t>
+          <t>2026-10-06 14:24:32</t>
         </is>
       </c>
     </row>
@@ -93616,7 +96872,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>794</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
@@ -93626,7 +96882,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>348</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8">
@@ -93636,7 +96892,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">

--- a/data/swing_performance_analysis.xlsx
+++ b/data/swing_performance_analysis.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$847</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'T20_Tracking'!$A$1:$AJ$866</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ847"/>
+  <dimension ref="A1:AJ866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -51739,11 +51739,11 @@
       </c>
       <c r="Y439" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z439" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA439" t="n">
         <v>0</v>
@@ -51754,6 +51754,15 @@
       <c r="AC439" t="n">
         <v>1.28</v>
       </c>
+      <c r="AD439" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>-1.14</v>
+      </c>
       <c r="AG439" t="b">
         <v>0</v>
       </c>
@@ -51762,7 +51771,7 @@
       </c>
       <c r="AI439" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -51863,11 +51872,11 @@
       </c>
       <c r="Y440" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z440" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA440" t="n">
         <v>-4.76</v>
@@ -51878,15 +51887,24 @@
       <c r="AC440" t="n">
         <v>2.61</v>
       </c>
+      <c r="AD440" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>-5.99</v>
+      </c>
       <c r="AG440" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH440" t="b">
         <v>0</v>
       </c>
       <c r="AI440" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -51987,11 +52005,11 @@
       </c>
       <c r="Y441" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z441" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA441" t="n">
         <v>-5.74</v>
@@ -52002,6 +52020,15 @@
       <c r="AC441" t="n">
         <v>8.09</v>
       </c>
+      <c r="AD441" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>-6.17</v>
+      </c>
       <c r="AG441" t="b">
         <v>1</v>
       </c>
@@ -52010,7 +52037,7 @@
       </c>
       <c r="AI441" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -52111,11 +52138,11 @@
       </c>
       <c r="Y442" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z442" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA442" t="n">
         <v>-6.8</v>
@@ -52126,6 +52153,15 @@
       <c r="AC442" t="n">
         <v>-4.11</v>
       </c>
+      <c r="AD442" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>-9.630000000000001</v>
+      </c>
       <c r="AG442" t="b">
         <v>0</v>
       </c>
@@ -52134,7 +52170,7 @@
       </c>
       <c r="AI442" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -52235,11 +52271,11 @@
       </c>
       <c r="Y443" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z443" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA443" t="n">
         <v>1.09</v>
@@ -52250,6 +52286,15 @@
       <c r="AC443" t="n">
         <v>17.88</v>
       </c>
+      <c r="AD443" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>-1.46</v>
+      </c>
       <c r="AG443" t="b">
         <v>1</v>
       </c>
@@ -52258,7 +52303,7 @@
       </c>
       <c r="AI443" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -52359,11 +52404,11 @@
       </c>
       <c r="Y444" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z444" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA444" t="n">
         <v>-5.41</v>
@@ -52374,6 +52419,15 @@
       <c r="AC444" t="n">
         <v>-2.81</v>
       </c>
+      <c r="AD444" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>-7.79</v>
+      </c>
       <c r="AG444" t="b">
         <v>0</v>
       </c>
@@ -52382,7 +52436,7 @@
       </c>
       <c r="AI444" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -52483,11 +52537,11 @@
       </c>
       <c r="Y445" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z445" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA445" t="n">
         <v>-8.17</v>
@@ -52498,6 +52552,15 @@
       <c r="AC445" t="n">
         <v>-8.17</v>
       </c>
+      <c r="AD445" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>-10.6</v>
+      </c>
       <c r="AG445" t="b">
         <v>0</v>
       </c>
@@ -52506,7 +52569,7 @@
       </c>
       <c r="AI445" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -52607,11 +52670,11 @@
       </c>
       <c r="Y446" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z446" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA446" t="n">
         <v>-5.94</v>
@@ -52622,6 +52685,15 @@
       <c r="AC446" t="n">
         <v>5.73</v>
       </c>
+      <c r="AD446" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>-5.94</v>
+      </c>
       <c r="AG446" t="b">
         <v>0</v>
       </c>
@@ -52630,7 +52702,7 @@
       </c>
       <c r="AI446" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FLAT</t>
         </is>
       </c>
     </row>
@@ -52731,11 +52803,11 @@
       </c>
       <c r="Y447" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z447" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA447" t="n">
         <v>0</v>
@@ -52746,6 +52818,15 @@
       <c r="AC447" t="n">
         <v>0.45</v>
       </c>
+      <c r="AD447" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>-4.91</v>
+      </c>
       <c r="AG447" t="b">
         <v>0</v>
       </c>
@@ -52754,7 +52835,7 @@
       </c>
       <c r="AI447" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -52855,11 +52936,11 @@
       </c>
       <c r="Y448" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z448" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA448" t="n">
         <v>1.69</v>
@@ -52870,6 +52951,15 @@
       <c r="AC448" t="n">
         <v>-1.13</v>
       </c>
+      <c r="AD448" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>-2.54</v>
+      </c>
       <c r="AG448" t="b">
         <v>0</v>
       </c>
@@ -52878,7 +52968,7 @@
       </c>
       <c r="AI448" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -52979,11 +53069,11 @@
       </c>
       <c r="Y449" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z449" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA449" t="n">
         <v>1.34</v>
@@ -52994,6 +53084,15 @@
       <c r="AC449" t="n">
         <v>1.01</v>
       </c>
+      <c r="AD449" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>-3.36</v>
+      </c>
       <c r="AG449" t="b">
         <v>0</v>
       </c>
@@ -53002,7 +53101,7 @@
       </c>
       <c r="AI449" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -53103,11 +53202,11 @@
       </c>
       <c r="Y450" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z450" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA450" t="n">
         <v>-3.08</v>
@@ -53118,6 +53217,15 @@
       <c r="AC450" t="n">
         <v>-2.64</v>
       </c>
+      <c r="AD450" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AF450" t="n">
+        <v>-4.85</v>
+      </c>
       <c r="AG450" t="b">
         <v>0</v>
       </c>
@@ -53126,7 +53234,7 @@
       </c>
       <c r="AI450" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -53227,11 +53335,11 @@
       </c>
       <c r="Y451" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z451" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA451" t="n">
         <v>2.28</v>
@@ -53242,6 +53350,15 @@
       <c r="AC451" t="n">
         <v>-1.07</v>
       </c>
+      <c r="AD451" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AE451" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AF451" t="n">
+        <v>-3.49</v>
+      </c>
       <c r="AG451" t="b">
         <v>0</v>
       </c>
@@ -53250,7 +53367,7 @@
       </c>
       <c r="AI451" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -53351,11 +53468,11 @@
       </c>
       <c r="Y452" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z452" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA452" t="n">
         <v>0.22</v>
@@ -53366,6 +53483,15 @@
       <c r="AC452" t="n">
         <v>-0.44</v>
       </c>
+      <c r="AD452" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="AE452" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AF452" t="n">
+        <v>-3.84</v>
+      </c>
       <c r="AG452" t="b">
         <v>0</v>
       </c>
@@ -53374,7 +53500,7 @@
       </c>
       <c r="AI452" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -53475,11 +53601,11 @@
       </c>
       <c r="Y453" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z453" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA453" t="n">
         <v>1.4</v>
@@ -53490,6 +53616,15 @@
       <c r="AC453" t="n">
         <v>-3.62</v>
       </c>
+      <c r="AD453" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="AE453" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AF453" t="n">
+        <v>-6.31</v>
+      </c>
       <c r="AG453" t="b">
         <v>0</v>
       </c>
@@ -53498,7 +53633,7 @@
       </c>
       <c r="AI453" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -53599,11 +53734,11 @@
       </c>
       <c r="Y454" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z454" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA454" t="n">
         <v>2.53</v>
@@ -53614,6 +53749,15 @@
       <c r="AC454" t="n">
         <v>-0.3</v>
       </c>
+      <c r="AD454" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>-2.07</v>
+      </c>
       <c r="AG454" t="b">
         <v>0</v>
       </c>
@@ -53622,7 +53766,7 @@
       </c>
       <c r="AI454" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -53723,11 +53867,11 @@
       </c>
       <c r="Y455" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z455" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA455" t="n">
         <v>4.49</v>
@@ -53738,6 +53882,15 @@
       <c r="AC455" t="n">
         <v>2.25</v>
       </c>
+      <c r="AD455" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AF455" t="n">
+        <v>-1.85</v>
+      </c>
       <c r="AG455" t="b">
         <v>0</v>
       </c>
@@ -53746,7 +53899,7 @@
       </c>
       <c r="AI455" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -53847,11 +54000,11 @@
       </c>
       <c r="Y456" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z456" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA456" t="n">
         <v>-11.56</v>
@@ -53862,6 +54015,15 @@
       <c r="AC456" t="n">
         <v>-5.86</v>
       </c>
+      <c r="AD456" t="n">
+        <v>-10.55</v>
+      </c>
+      <c r="AE456" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="AF456" t="n">
+        <v>-11.89</v>
+      </c>
       <c r="AG456" t="b">
         <v>0</v>
       </c>
@@ -53870,7 +54032,7 @@
       </c>
       <c r="AI456" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>STOP_FIRST</t>
         </is>
       </c>
     </row>
@@ -53971,11 +54133,11 @@
       </c>
       <c r="Y457" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z457" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA457" t="n">
         <v>-5.18</v>
@@ -53986,6 +54148,15 @@
       <c r="AC457" t="n">
         <v>6.85</v>
       </c>
+      <c r="AD457" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>-5.63</v>
+      </c>
       <c r="AG457" t="b">
         <v>0</v>
       </c>
@@ -53994,7 +54165,7 @@
       </c>
       <c r="AI457" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -54095,11 +54266,11 @@
       </c>
       <c r="Y458" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z458" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA458" t="n">
         <v>5.08</v>
@@ -54110,6 +54281,15 @@
       <c r="AC458" t="n">
         <v>3.39</v>
       </c>
+      <c r="AD458" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AE458" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AF458" t="n">
+        <v>-0.85</v>
+      </c>
       <c r="AG458" t="b">
         <v>0</v>
       </c>
@@ -54118,7 +54298,7 @@
       </c>
       <c r="AI458" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -54441,11 +54621,11 @@
       </c>
       <c r="Y461" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z461" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA461" t="n">
         <v>1.26</v>
@@ -54456,6 +54636,15 @@
       <c r="AC461" t="n">
         <v>32.55</v>
       </c>
+      <c r="AD461" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="AE461" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="AF461" t="n">
+        <v>-1.85</v>
+      </c>
       <c r="AG461" t="b">
         <v>1</v>
       </c>
@@ -54464,7 +54653,7 @@
       </c>
       <c r="AI461" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>TARGET_HIT</t>
         </is>
       </c>
     </row>
@@ -54565,11 +54754,11 @@
       </c>
       <c r="Y462" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="Z462" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA462" t="n">
         <v>0.5600000000000001</v>
@@ -54580,6 +54769,15 @@
       <c r="AC462" t="n">
         <v>-3.17</v>
       </c>
+      <c r="AD462" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="AE462" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AF462" t="n">
+        <v>-4.47</v>
+      </c>
       <c r="AG462" t="b">
         <v>0</v>
       </c>
@@ -54588,7 +54786,7 @@
       </c>
       <c r="AI462" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -54693,7 +54891,7 @@
         </is>
       </c>
       <c r="Z463" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA463" t="n">
         <v>-0.42</v>
@@ -54817,7 +55015,7 @@
         </is>
       </c>
       <c r="Z464" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA464" t="n">
         <v>-1.52</v>
@@ -54829,7 +55027,7 @@
         <v>4.42</v>
       </c>
       <c r="AG464" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH464" t="b">
         <v>1</v>
@@ -54941,7 +55139,7 @@
         </is>
       </c>
       <c r="Z465" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA465" t="n">
         <v>-3.28</v>
@@ -55065,7 +55263,7 @@
         </is>
       </c>
       <c r="Z466" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA466" t="n">
         <v>-3.79</v>
@@ -55189,7 +55387,7 @@
         </is>
       </c>
       <c r="Z467" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA467" t="n">
         <v>3.51</v>
@@ -55313,7 +55511,7 @@
         </is>
       </c>
       <c r="Z468" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA468" t="n">
         <v>-4.15</v>
@@ -55437,7 +55635,7 @@
         </is>
       </c>
       <c r="Z469" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA469" t="n">
         <v>-3.85</v>
@@ -55561,7 +55759,7 @@
         </is>
       </c>
       <c r="Z470" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA470" t="n">
         <v>-4.66</v>
@@ -55685,7 +55883,7 @@
         </is>
       </c>
       <c r="Z471" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA471" t="n">
         <v>4.75</v>
@@ -55809,7 +56007,7 @@
         </is>
       </c>
       <c r="Z472" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA472" t="n">
         <v>6.92</v>
@@ -55933,7 +56131,7 @@
         </is>
       </c>
       <c r="Z473" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA473" t="n">
         <v>6.59</v>
@@ -56057,7 +56255,7 @@
         </is>
       </c>
       <c r="Z474" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA474" t="n">
         <v>5.23</v>
@@ -56181,7 +56379,7 @@
         </is>
       </c>
       <c r="Z475" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA475" t="n">
         <v>7.24</v>
@@ -56305,7 +56503,7 @@
         </is>
       </c>
       <c r="Z476" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA476" t="n">
         <v>-10.74</v>
@@ -56429,7 +56627,7 @@
         </is>
       </c>
       <c r="Z477" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA477" t="n">
         <v>-7.95</v>
@@ -56553,7 +56751,7 @@
         </is>
       </c>
       <c r="Z478" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA478" t="n">
         <v>3.33</v>
@@ -57010,7 +57208,7 @@
         </is>
       </c>
       <c r="Z482" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA482" t="n">
         <v>4.42</v>
@@ -57134,7 +57332,7 @@
         </is>
       </c>
       <c r="Z483" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA483" t="n">
         <v>7.68</v>
@@ -57258,7 +57456,7 @@
         </is>
       </c>
       <c r="Z484" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA484" t="n">
         <v>2.61</v>
@@ -57382,7 +57580,7 @@
         </is>
       </c>
       <c r="Z485" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA485" t="n">
         <v>-0.42</v>
@@ -57506,7 +57704,7 @@
         </is>
       </c>
       <c r="Z486" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA486" t="n">
         <v>1.49</v>
@@ -57630,7 +57828,7 @@
         </is>
       </c>
       <c r="Z487" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA487" t="n">
         <v>0.5</v>
@@ -57754,7 +57952,7 @@
         </is>
       </c>
       <c r="Z488" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA488" t="n">
         <v>3.56</v>
@@ -57878,7 +58076,7 @@
         </is>
       </c>
       <c r="Z489" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA489" t="n">
         <v>2.73</v>
@@ -58002,7 +58200,7 @@
         </is>
       </c>
       <c r="Z490" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA490" t="n">
         <v>1.94</v>
@@ -58126,7 +58324,7 @@
         </is>
       </c>
       <c r="Z491" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA491" t="n">
         <v>3.93</v>
@@ -58250,7 +58448,7 @@
         </is>
       </c>
       <c r="Z492" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA492" t="n">
         <v>3.83</v>
@@ -58374,7 +58572,7 @@
         </is>
       </c>
       <c r="Z493" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA493" t="n">
         <v>0.22</v>
@@ -58498,7 +58696,7 @@
         </is>
       </c>
       <c r="Z494" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA494" t="n">
         <v>-1.16</v>
@@ -58622,7 +58820,7 @@
         </is>
       </c>
       <c r="Z495" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA495" t="n">
         <v>4.1</v>
@@ -58746,7 +58944,7 @@
         </is>
       </c>
       <c r="Z496" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA496" t="n">
         <v>3.55</v>
@@ -58870,7 +59068,7 @@
         </is>
       </c>
       <c r="Z497" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA497" t="n">
         <v>2.31</v>
@@ -58994,7 +59192,7 @@
         </is>
       </c>
       <c r="Z498" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA498" t="n">
         <v>2.01</v>
@@ -59118,7 +59316,7 @@
         </is>
       </c>
       <c r="Z499" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA499" t="n">
         <v>1.97</v>
@@ -59242,7 +59440,7 @@
         </is>
       </c>
       <c r="Z500" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA500" t="n">
         <v>2.48</v>
@@ -59366,7 +59564,7 @@
         </is>
       </c>
       <c r="Z501" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA501" t="n">
         <v>16.83</v>
@@ -59490,7 +59688,7 @@
         </is>
       </c>
       <c r="Z502" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA502" t="n">
         <v>5.79</v>
@@ -59614,7 +59812,7 @@
         </is>
       </c>
       <c r="Z503" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA503" t="n">
         <v>1.42</v>
@@ -59738,7 +59936,7 @@
         </is>
       </c>
       <c r="Z504" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA504" t="n">
         <v>0.37</v>
@@ -59862,7 +60060,7 @@
         </is>
       </c>
       <c r="Z505" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA505" t="n">
         <v>10.18</v>
@@ -59986,7 +60184,7 @@
         </is>
       </c>
       <c r="Z506" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA506" t="n">
         <v>0</v>
@@ -60110,7 +60308,7 @@
         </is>
       </c>
       <c r="Z507" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA507" t="n">
         <v>0.76</v>
@@ -60234,7 +60432,7 @@
         </is>
       </c>
       <c r="Z508" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA508" t="n">
         <v>0.32</v>
@@ -60358,7 +60556,7 @@
         </is>
       </c>
       <c r="Z509" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA509" t="n">
         <v>4.25</v>
@@ -60482,7 +60680,7 @@
         </is>
       </c>
       <c r="Z510" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA510" t="n">
         <v>-0.32</v>
@@ -60606,7 +60804,7 @@
         </is>
       </c>
       <c r="Z511" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA511" t="n">
         <v>-2.67</v>
@@ -60730,7 +60928,7 @@
         </is>
       </c>
       <c r="Z512" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA512" t="n">
         <v>0.57</v>
@@ -60854,7 +61052,7 @@
         </is>
       </c>
       <c r="Z513" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA513" t="n">
         <v>2.01</v>
@@ -60978,7 +61176,7 @@
         </is>
       </c>
       <c r="Z514" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA514" t="n">
         <v>-0.25</v>
@@ -61102,7 +61300,7 @@
         </is>
       </c>
       <c r="Z515" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA515" t="n">
         <v>-1.44</v>
@@ -61226,7 +61424,7 @@
         </is>
       </c>
       <c r="Z516" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA516" t="n">
         <v>2.75</v>
@@ -61350,7 +61548,7 @@
         </is>
       </c>
       <c r="Z517" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA517" t="n">
         <v>2.47</v>
@@ -61474,7 +61672,7 @@
         </is>
       </c>
       <c r="Z518" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA518" t="n">
         <v>18.98</v>
@@ -61598,7 +61796,7 @@
         </is>
       </c>
       <c r="Z519" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA519" t="n">
         <v>5.77</v>
@@ -61722,7 +61920,7 @@
         </is>
       </c>
       <c r="Z520" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA520" t="n">
         <v>0</v>
@@ -61846,7 +62044,7 @@
         </is>
       </c>
       <c r="Z521" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA521" t="n">
         <v>-0.91</v>
@@ -61970,13 +62168,16 @@
         </is>
       </c>
       <c r="Z522" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA522" t="n">
         <v>1.39</v>
       </c>
       <c r="AB522" t="n">
         <v>-2.78</v>
+      </c>
+      <c r="AC522" t="n">
+        <v>-3.06</v>
       </c>
       <c r="AG522" t="b">
         <v>0</v>
@@ -62091,13 +62292,16 @@
         </is>
       </c>
       <c r="Z523" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA523" t="n">
         <v>-0.75</v>
       </c>
       <c r="AB523" t="n">
         <v>-3.52</v>
+      </c>
+      <c r="AC523" t="n">
+        <v>-2.35</v>
       </c>
       <c r="AG523" t="b">
         <v>0</v>
@@ -62212,13 +62416,16 @@
         </is>
       </c>
       <c r="Z524" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA524" t="n">
         <v>2.32</v>
       </c>
       <c r="AB524" t="n">
         <v>-0.33</v>
+      </c>
+      <c r="AC524" t="n">
+        <v>1.32</v>
       </c>
       <c r="AG524" t="b">
         <v>0</v>
@@ -62333,13 +62540,16 @@
         </is>
       </c>
       <c r="Z525" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA525" t="n">
         <v>3.01</v>
       </c>
       <c r="AB525" t="n">
         <v>-3.28</v>
+      </c>
+      <c r="AC525" t="n">
+        <v>-1.57</v>
       </c>
       <c r="AG525" t="b">
         <v>0</v>
@@ -62454,13 +62664,16 @@
         </is>
       </c>
       <c r="Z526" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA526" t="n">
         <v>0.88</v>
       </c>
       <c r="AB526" t="n">
         <v>-0.66</v>
+      </c>
+      <c r="AC526" t="n">
+        <v>-1.42</v>
       </c>
       <c r="AG526" t="b">
         <v>0</v>
@@ -62575,13 +62788,16 @@
         </is>
       </c>
       <c r="Z527" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA527" t="n">
         <v>-2.51</v>
       </c>
       <c r="AB527" t="n">
         <v>-5.69</v>
+      </c>
+      <c r="AC527" t="n">
+        <v>-4.83</v>
       </c>
       <c r="AG527" t="b">
         <v>0</v>
@@ -62696,13 +62912,16 @@
         </is>
       </c>
       <c r="Z528" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA528" t="n">
         <v>-1.15</v>
       </c>
       <c r="AB528" t="n">
         <v>-4.95</v>
+      </c>
+      <c r="AC528" t="n">
+        <v>-5.53</v>
       </c>
       <c r="AG528" t="b">
         <v>0</v>
@@ -62817,13 +63036,16 @@
         </is>
       </c>
       <c r="Z529" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA529" t="n">
         <v>1.91</v>
       </c>
       <c r="AB529" t="n">
         <v>-2.76</v>
+      </c>
+      <c r="AC529" t="n">
+        <v>-1.12</v>
       </c>
       <c r="AG529" t="b">
         <v>0</v>
@@ -62938,13 +63160,16 @@
         </is>
       </c>
       <c r="Z530" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA530" t="n">
         <v>-0.14</v>
       </c>
       <c r="AB530" t="n">
         <v>-2.58</v>
+      </c>
+      <c r="AC530" t="n">
+        <v>-3.44</v>
       </c>
       <c r="AG530" t="b">
         <v>0</v>
@@ -63059,13 +63284,16 @@
         </is>
       </c>
       <c r="Z531" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA531" t="n">
         <v>0.88</v>
       </c>
       <c r="AB531" t="n">
         <v>-2.15</v>
+      </c>
+      <c r="AC531" t="n">
+        <v>-2.28</v>
       </c>
       <c r="AG531" t="b">
         <v>0</v>
@@ -63180,13 +63408,16 @@
         </is>
       </c>
       <c r="Z532" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA532" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="AB532" t="n">
         <v>-1.61</v>
+      </c>
+      <c r="AC532" t="n">
+        <v>0</v>
       </c>
       <c r="AG532" t="b">
         <v>0</v>
@@ -63301,13 +63532,16 @@
         </is>
       </c>
       <c r="Z533" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA533" t="n">
         <v>38.77</v>
       </c>
       <c r="AB533" t="n">
         <v>30.9</v>
+      </c>
+      <c r="AC533" t="n">
+        <v>38.53</v>
       </c>
       <c r="AG533" t="b">
         <v>1</v>
@@ -63422,13 +63656,16 @@
         </is>
       </c>
       <c r="Z534" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA534" t="n">
         <v>6.76</v>
       </c>
       <c r="AB534" t="n">
         <v>16.46</v>
+      </c>
+      <c r="AC534" t="n">
+        <v>25.06</v>
       </c>
       <c r="AG534" t="b">
         <v>1</v>
@@ -63543,13 +63780,16 @@
         </is>
       </c>
       <c r="Z535" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA535" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="AB535" t="n">
         <v>-1.41</v>
+      </c>
+      <c r="AC535" t="n">
+        <v>-0.47</v>
       </c>
       <c r="AG535" t="b">
         <v>0</v>
@@ -63664,13 +63904,16 @@
         </is>
       </c>
       <c r="Z536" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA536" t="n">
         <v>0.19</v>
       </c>
       <c r="AB536" t="n">
         <v>-3.7</v>
+      </c>
+      <c r="AC536" t="n">
+        <v>-2.04</v>
       </c>
       <c r="AG536" t="b">
         <v>0</v>
@@ -63785,13 +64028,16 @@
         </is>
       </c>
       <c r="Z537" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA537" t="n">
         <v>12.68</v>
       </c>
       <c r="AB537" t="n">
         <v>13.73</v>
+      </c>
+      <c r="AC537" t="n">
+        <v>2.46</v>
       </c>
       <c r="AG537" t="b">
         <v>0</v>
@@ -63906,7 +64152,7 @@
         </is>
       </c>
       <c r="Z538" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA538" t="n">
         <v>0.29</v>
@@ -63914,11 +64160,14 @@
       <c r="AB538" t="n">
         <v>-2.5</v>
       </c>
+      <c r="AC538" t="n">
+        <v>-5.43</v>
+      </c>
       <c r="AG538" t="b">
         <v>0</v>
       </c>
       <c r="AH538" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI538" t="inlineStr">
         <is>
@@ -64027,13 +64276,16 @@
         </is>
       </c>
       <c r="Z539" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA539" t="n">
         <v>-1.65</v>
       </c>
       <c r="AB539" t="n">
         <v>-4.12</v>
+      </c>
+      <c r="AC539" t="n">
+        <v>-2.47</v>
       </c>
       <c r="AG539" t="b">
         <v>0</v>
@@ -64148,13 +64400,16 @@
         </is>
       </c>
       <c r="Z540" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA540" t="n">
         <v>-3.27</v>
       </c>
       <c r="AB540" t="n">
         <v>-5.28</v>
+      </c>
+      <c r="AC540" t="n">
+        <v>0.63</v>
       </c>
       <c r="AG540" t="b">
         <v>0</v>
@@ -64269,13 +64524,16 @@
         </is>
       </c>
       <c r="Z541" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA541" t="n">
         <v>0</v>
       </c>
       <c r="AB541" t="n">
         <v>-1.63</v>
+      </c>
+      <c r="AC541" t="n">
+        <v>3.59</v>
       </c>
       <c r="AG541" t="b">
         <v>0</v>
@@ -64390,13 +64648,16 @@
         </is>
       </c>
       <c r="Z542" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA542" t="n">
         <v>-0.89</v>
       </c>
       <c r="AB542" t="n">
         <v>-0.89</v>
+      </c>
+      <c r="AC542" t="n">
+        <v>0.44</v>
       </c>
       <c r="AG542" t="b">
         <v>0</v>
@@ -64511,13 +64772,16 @@
         </is>
       </c>
       <c r="Z543" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA543" t="n">
         <v>0.51</v>
       </c>
       <c r="AB543" t="n">
         <v>-4.6</v>
+      </c>
+      <c r="AC543" t="n">
+        <v>-0.89</v>
       </c>
       <c r="AG543" t="b">
         <v>0</v>
@@ -64632,13 +64896,16 @@
         </is>
       </c>
       <c r="Z544" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA544" t="n">
         <v>-1.83</v>
       </c>
       <c r="AB544" t="n">
         <v>-2.37</v>
+      </c>
+      <c r="AC544" t="n">
+        <v>-0.97</v>
       </c>
       <c r="AG544" t="b">
         <v>0</v>
@@ -64753,13 +65020,16 @@
         </is>
       </c>
       <c r="Z545" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA545" t="n">
         <v>0.29</v>
       </c>
       <c r="AB545" t="n">
         <v>-3.75</v>
+      </c>
+      <c r="AC545" t="n">
+        <v>1.01</v>
       </c>
       <c r="AG545" t="b">
         <v>0</v>
@@ -64874,13 +65144,16 @@
         </is>
       </c>
       <c r="Z546" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA546" t="n">
         <v>-3.27</v>
       </c>
       <c r="AB546" t="n">
         <v>-8.67</v>
+      </c>
+      <c r="AC546" t="n">
+        <v>-3.15</v>
       </c>
       <c r="AG546" t="b">
         <v>0</v>
@@ -64995,13 +65268,16 @@
         </is>
       </c>
       <c r="Z547" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA547" t="n">
         <v>-0.55</v>
       </c>
       <c r="AB547" t="n">
         <v>-3.49</v>
+      </c>
+      <c r="AC547" t="n">
+        <v>-0.22</v>
       </c>
       <c r="AG547" t="b">
         <v>0</v>
@@ -65116,13 +65392,16 @@
         </is>
       </c>
       <c r="Z548" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA548" t="n">
         <v>-2.68</v>
       </c>
       <c r="AB548" t="n">
         <v>-4.94</v>
+      </c>
+      <c r="AC548" t="n">
+        <v>-1.41</v>
       </c>
       <c r="AG548" t="b">
         <v>0</v>
@@ -65237,13 +65516,16 @@
         </is>
       </c>
       <c r="Z549" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA549" t="n">
         <v>-0.38</v>
       </c>
       <c r="AB549" t="n">
         <v>-3.63</v>
+      </c>
+      <c r="AC549" t="n">
+        <v>-0.75</v>
       </c>
       <c r="AG549" t="b">
         <v>0</v>
@@ -65358,13 +65640,16 @@
         </is>
       </c>
       <c r="Z550" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA550" t="n">
         <v>-1.2</v>
       </c>
       <c r="AB550" t="n">
         <v>-2.01</v>
+      </c>
+      <c r="AC550" t="n">
+        <v>-2.41</v>
       </c>
       <c r="AG550" t="b">
         <v>0</v>
@@ -65701,13 +65986,16 @@
         </is>
       </c>
       <c r="Z553" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA553" t="n">
         <v>35.9</v>
       </c>
       <c r="AB553" t="n">
         <v>28.04</v>
+      </c>
+      <c r="AC553" t="n">
+        <v>31.28</v>
       </c>
       <c r="AG553" t="b">
         <v>1</v>
@@ -65822,13 +66110,16 @@
         </is>
       </c>
       <c r="Z554" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA554" t="n">
         <v>1.14</v>
       </c>
       <c r="AB554" t="n">
         <v>8.07</v>
+      </c>
+      <c r="AC554" t="n">
+        <v>10.34</v>
       </c>
       <c r="AG554" t="b">
         <v>0</v>
@@ -65943,13 +66234,16 @@
         </is>
       </c>
       <c r="Z555" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA555" t="n">
         <v>-2.19</v>
       </c>
       <c r="AB555" t="n">
         <v>-4.39</v>
+      </c>
+      <c r="AC555" t="n">
+        <v>-2.01</v>
       </c>
       <c r="AG555" t="b">
         <v>0</v>
@@ -66175,7 +66469,7 @@
         </is>
       </c>
       <c r="Z557" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA557" t="n">
         <v>-0.77</v>
@@ -66184,7 +66478,7 @@
         <v>6.04</v>
       </c>
       <c r="AG557" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH557" t="b">
         <v>0</v>
@@ -66296,7 +66590,7 @@
         </is>
       </c>
       <c r="Z558" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA558" t="n">
         <v>0.85</v>
@@ -66417,7 +66711,7 @@
         </is>
       </c>
       <c r="Z559" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA559" t="n">
         <v>-2.33</v>
@@ -66538,7 +66832,7 @@
         </is>
       </c>
       <c r="Z560" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA560" t="n">
         <v>4.41</v>
@@ -66659,7 +66953,7 @@
         </is>
       </c>
       <c r="Z561" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA561" t="n">
         <v>-1.6</v>
@@ -66671,7 +66965,7 @@
         <v>0</v>
       </c>
       <c r="AH561" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI561" t="inlineStr">
         <is>
@@ -66780,7 +67074,7 @@
         </is>
       </c>
       <c r="Z562" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA562" t="n">
         <v>14</v>
@@ -66898,7 +67192,7 @@
         </is>
       </c>
       <c r="Z563" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA563" t="n">
         <v>-4.15</v>
@@ -67019,7 +67313,7 @@
         </is>
       </c>
       <c r="Z564" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA564" t="n">
         <v>-4.8</v>
@@ -67140,7 +67434,7 @@
         </is>
       </c>
       <c r="Z565" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA565" t="n">
         <v>-4.49</v>
@@ -67261,7 +67555,7 @@
         </is>
       </c>
       <c r="Z566" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA566" t="n">
         <v>-0.99</v>
@@ -67382,7 +67676,7 @@
         </is>
       </c>
       <c r="Z567" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA567" t="n">
         <v>-1.34</v>
@@ -67503,7 +67797,7 @@
         </is>
       </c>
       <c r="Z568" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA568" t="n">
         <v>-1.77</v>
@@ -67624,7 +67918,7 @@
         </is>
       </c>
       <c r="Z569" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA569" t="n">
         <v>-3.59</v>
@@ -67745,7 +68039,7 @@
         </is>
       </c>
       <c r="Z570" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA570" t="n">
         <v>0.29</v>
@@ -67866,7 +68160,7 @@
         </is>
       </c>
       <c r="Z571" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA571" t="n">
         <v>-4.43</v>
@@ -67987,7 +68281,7 @@
         </is>
       </c>
       <c r="Z572" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA572" t="n">
         <v>-3.52</v>
@@ -68108,7 +68402,7 @@
         </is>
       </c>
       <c r="Z573" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA573" t="n">
         <v>-1.74</v>
@@ -68229,7 +68523,7 @@
         </is>
       </c>
       <c r="Z574" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA574" t="n">
         <v>-3.79</v>
@@ -68350,7 +68644,7 @@
         </is>
       </c>
       <c r="Z575" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA575" t="n">
         <v>-3.07</v>
@@ -68471,7 +68765,7 @@
         </is>
       </c>
       <c r="Z576" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA576" t="n">
         <v>-1.21</v>
@@ -68925,7 +69219,7 @@
         </is>
       </c>
       <c r="Z580" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA580" t="n">
         <v>31.15</v>
@@ -69046,7 +69340,7 @@
         </is>
       </c>
       <c r="Z581" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA581" t="n">
         <v>2.49</v>
@@ -69167,7 +69461,7 @@
         </is>
       </c>
       <c r="Z582" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA582" t="n">
         <v>-0.9399999999999999</v>
@@ -69288,7 +69582,7 @@
         </is>
       </c>
       <c r="Z583" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA583" t="n">
         <v>-3.99</v>
@@ -69520,7 +69814,7 @@
         </is>
       </c>
       <c r="Z585" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA585" t="n">
         <v>3.78</v>
@@ -69641,7 +69935,7 @@
         </is>
       </c>
       <c r="Z586" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA586" t="n">
         <v>-0.88</v>
@@ -69762,7 +70056,7 @@
         </is>
       </c>
       <c r="Z587" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA587" t="n">
         <v>-1.6</v>
@@ -69774,7 +70068,7 @@
         <v>0</v>
       </c>
       <c r="AH587" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI587" t="inlineStr">
         <is>
@@ -69883,7 +70177,7 @@
         </is>
       </c>
       <c r="Z588" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA588" t="n">
         <v>4.07</v>
@@ -70004,7 +70298,7 @@
         </is>
       </c>
       <c r="Z589" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA589" t="n">
         <v>-1.9</v>
@@ -70016,7 +70310,7 @@
         <v>0</v>
       </c>
       <c r="AH589" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI589" t="inlineStr">
         <is>
@@ -70125,7 +70419,7 @@
         </is>
       </c>
       <c r="Z590" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA590" t="n">
         <v>15.49</v>
@@ -70246,7 +70540,7 @@
         </is>
       </c>
       <c r="Z591" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA591" t="n">
         <v>4.25</v>
@@ -70367,7 +70661,7 @@
         </is>
       </c>
       <c r="Z592" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA592" t="n">
         <v>-4.09</v>
@@ -70488,7 +70782,7 @@
         </is>
       </c>
       <c r="Z593" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA593" t="n">
         <v>-5.77</v>
@@ -70606,7 +70900,7 @@
         </is>
       </c>
       <c r="Z594" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA594" t="n">
         <v>0.66</v>
@@ -70727,7 +71021,7 @@
         </is>
       </c>
       <c r="Z595" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA595" t="n">
         <v>0.9</v>
@@ -70848,7 +71142,7 @@
         </is>
       </c>
       <c r="Z596" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA596" t="n">
         <v>-0.89</v>
@@ -70969,7 +71263,7 @@
         </is>
       </c>
       <c r="Z597" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA597" t="n">
         <v>-3.23</v>
@@ -71090,7 +71384,7 @@
         </is>
       </c>
       <c r="Z598" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA598" t="n">
         <v>-1.86</v>
@@ -71211,7 +71505,7 @@
         </is>
       </c>
       <c r="Z599" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA599" t="n">
         <v>-3.91</v>
@@ -71332,7 +71626,7 @@
         </is>
       </c>
       <c r="Z600" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA600" t="n">
         <v>-5.86</v>
@@ -71453,7 +71747,7 @@
         </is>
       </c>
       <c r="Z601" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA601" t="n">
         <v>-3.72</v>
@@ -71574,7 +71868,7 @@
         </is>
       </c>
       <c r="Z602" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA602" t="n">
         <v>-3.02</v>
@@ -71695,7 +71989,7 @@
         </is>
       </c>
       <c r="Z603" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA603" t="n">
         <v>-2.06</v>
@@ -71816,7 +72110,7 @@
         </is>
       </c>
       <c r="Z604" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA604" t="n">
         <v>-0.87</v>
@@ -71937,7 +72231,7 @@
         </is>
       </c>
       <c r="Z605" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA605" t="n">
         <v>0.58</v>
@@ -72055,7 +72349,7 @@
         </is>
       </c>
       <c r="Z606" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA606" t="n">
         <v>-2.42</v>
@@ -72620,7 +72914,7 @@
         </is>
       </c>
       <c r="Z611" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA611" t="n">
         <v>1.45</v>
@@ -72738,7 +73032,7 @@
         </is>
       </c>
       <c r="Z612" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA612" t="n">
         <v>-2.34</v>
@@ -72970,7 +73264,7 @@
         </is>
       </c>
       <c r="Z614" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA614" t="n">
         <v>-4.58</v>
@@ -73091,7 +73385,7 @@
         </is>
       </c>
       <c r="Z615" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA615" t="n">
         <v>6.68</v>
@@ -73212,7 +73506,7 @@
         </is>
       </c>
       <c r="Z616" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA616" t="n">
         <v>-1.59</v>
@@ -73333,7 +73627,7 @@
         </is>
       </c>
       <c r="Z617" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA617" t="n">
         <v>-10.11</v>
@@ -73454,7 +73748,7 @@
         </is>
       </c>
       <c r="Z618" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA618" t="n">
         <v>-2.58</v>
@@ -73575,7 +73869,7 @@
         </is>
       </c>
       <c r="Z619" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA619" t="n">
         <v>-1.8</v>
@@ -73587,7 +73881,7 @@
         <v>0</v>
       </c>
       <c r="AH619" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI619" t="inlineStr">
         <is>
@@ -73696,7 +73990,7 @@
         </is>
       </c>
       <c r="Z620" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA620" t="n">
         <v>-3.27</v>
@@ -73814,7 +74108,7 @@
         </is>
       </c>
       <c r="Z621" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA621" t="n">
         <v>-2.27</v>
@@ -73935,7 +74229,7 @@
         </is>
       </c>
       <c r="Z622" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA622" t="n">
         <v>-1.77</v>
@@ -74056,7 +74350,7 @@
         </is>
       </c>
       <c r="Z623" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA623" t="n">
         <v>-3.96</v>
@@ -74177,7 +74471,7 @@
         </is>
       </c>
       <c r="Z624" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA624" t="n">
         <v>-2.7</v>
@@ -74298,7 +74592,7 @@
         </is>
       </c>
       <c r="Z625" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA625" t="n">
         <v>-3.9</v>
@@ -74419,7 +74713,7 @@
         </is>
       </c>
       <c r="Z626" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA626" t="n">
         <v>-2.84</v>
@@ -74540,7 +74834,7 @@
         </is>
       </c>
       <c r="Z627" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA627" t="n">
         <v>0.59</v>
@@ -74661,7 +74955,7 @@
         </is>
       </c>
       <c r="Z628" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA628" t="n">
         <v>0.19</v>
@@ -74779,7 +75073,7 @@
         </is>
       </c>
       <c r="Z629" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA629" t="n">
         <v>-4.02</v>
@@ -75233,7 +75527,7 @@
         </is>
       </c>
       <c r="Z633" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA633" t="n">
         <v>5.58</v>
@@ -75354,7 +75648,7 @@
         </is>
       </c>
       <c r="Z634" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA634" t="n">
         <v>8.529999999999999</v>
@@ -75586,7 +75880,7 @@
         </is>
       </c>
       <c r="Z636" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA636" t="n">
         <v>7.05</v>
@@ -75818,10 +76112,13 @@
         </is>
       </c>
       <c r="Z638" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA638" t="n">
         <v>0.9399999999999999</v>
+      </c>
+      <c r="AB638" t="n">
+        <v>-7.81</v>
       </c>
       <c r="AG638" t="b">
         <v>0</v>
@@ -75936,10 +76233,13 @@
         </is>
       </c>
       <c r="Z639" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA639" t="n">
         <v>-14.75</v>
+      </c>
+      <c r="AB639" t="n">
+        <v>-4.51</v>
       </c>
       <c r="AG639" t="b">
         <v>0</v>
@@ -76054,16 +76354,19 @@
         </is>
       </c>
       <c r="Z640" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA640" t="n">
         <v>-3.86</v>
       </c>
+      <c r="AB640" t="n">
+        <v>-9.460000000000001</v>
+      </c>
       <c r="AG640" t="b">
         <v>0</v>
       </c>
       <c r="AH640" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI640" t="inlineStr">
         <is>
@@ -76172,10 +76475,13 @@
         </is>
       </c>
       <c r="Z641" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA641" t="n">
         <v>-4.11</v>
+      </c>
+      <c r="AB641" t="n">
+        <v>-4.38</v>
       </c>
       <c r="AG641" t="b">
         <v>0</v>
@@ -76287,10 +76593,13 @@
         </is>
       </c>
       <c r="Z642" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA642" t="n">
         <v>-2.59</v>
+      </c>
+      <c r="AB642" t="n">
+        <v>-0.97</v>
       </c>
       <c r="AG642" t="b">
         <v>0</v>
@@ -76405,10 +76714,13 @@
         </is>
       </c>
       <c r="Z643" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA643" t="n">
         <v>-6.11</v>
+      </c>
+      <c r="AB643" t="n">
+        <v>-4.45</v>
       </c>
       <c r="AG643" t="b">
         <v>0</v>
@@ -76523,10 +76835,13 @@
         </is>
       </c>
       <c r="Z644" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA644" t="n">
         <v>-1.52</v>
+      </c>
+      <c r="AB644" t="n">
+        <v>-2.28</v>
       </c>
       <c r="AG644" t="b">
         <v>0</v>
@@ -76641,10 +76956,13 @@
         </is>
       </c>
       <c r="Z645" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA645" t="n">
         <v>-4.53</v>
+      </c>
+      <c r="AB645" t="n">
+        <v>-3.26</v>
       </c>
       <c r="AG645" t="b">
         <v>0</v>
@@ -76759,10 +77077,13 @@
         </is>
       </c>
       <c r="Z646" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA646" t="n">
         <v>-3.85</v>
+      </c>
+      <c r="AB646" t="n">
+        <v>-4.43</v>
       </c>
       <c r="AG646" t="b">
         <v>0</v>
@@ -76877,10 +77198,13 @@
         </is>
       </c>
       <c r="Z647" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA647" t="n">
         <v>-4.58</v>
+      </c>
+      <c r="AB647" t="n">
+        <v>-2.97</v>
       </c>
       <c r="AG647" t="b">
         <v>0</v>
@@ -76995,10 +77319,13 @@
         </is>
       </c>
       <c r="Z648" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA648" t="n">
         <v>-3.01</v>
+      </c>
+      <c r="AB648" t="n">
+        <v>-3.13</v>
       </c>
       <c r="AG648" t="b">
         <v>0</v>
@@ -77113,10 +77440,13 @@
         </is>
       </c>
       <c r="Z649" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA649" t="n">
         <v>3.54</v>
+      </c>
+      <c r="AB649" t="n">
+        <v>1.47</v>
       </c>
       <c r="AG649" t="b">
         <v>0</v>
@@ -77231,10 +77561,13 @@
         </is>
       </c>
       <c r="Z650" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA650" t="n">
         <v>-1.86</v>
+      </c>
+      <c r="AB650" t="n">
+        <v>7.98</v>
       </c>
       <c r="AG650" t="b">
         <v>0</v>
@@ -77682,10 +78015,13 @@
         </is>
       </c>
       <c r="Z654" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA654" t="n">
         <v>9.09</v>
+      </c>
+      <c r="AB654" t="n">
+        <v>17.15</v>
       </c>
       <c r="AG654" t="b">
         <v>0</v>
@@ -78022,10 +78358,13 @@
         </is>
       </c>
       <c r="Z657" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA657" t="n">
         <v>-0.97</v>
+      </c>
+      <c r="AB657" t="n">
+        <v>1.95</v>
       </c>
       <c r="AG657" t="b">
         <v>0</v>
@@ -78140,10 +78479,13 @@
         </is>
       </c>
       <c r="Z658" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA658" t="n">
         <v>0.9399999999999999</v>
+      </c>
+      <c r="AB658" t="n">
+        <v>-9.06</v>
       </c>
       <c r="AG658" t="b">
         <v>0</v>
@@ -78258,16 +78600,19 @@
         </is>
       </c>
       <c r="Z659" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA659" t="n">
         <v>-1.95</v>
       </c>
+      <c r="AB659" t="n">
+        <v>-4.49</v>
+      </c>
       <c r="AG659" t="b">
         <v>0</v>
       </c>
       <c r="AH659" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI659" t="inlineStr">
         <is>
@@ -78376,10 +78721,13 @@
         </is>
       </c>
       <c r="Z660" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA660" t="n">
         <v>2.75</v>
+      </c>
+      <c r="AB660" t="n">
+        <v>4.66</v>
       </c>
       <c r="AG660" t="b">
         <v>0</v>
@@ -78494,10 +78842,13 @@
         </is>
       </c>
       <c r="Z661" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA661" t="n">
         <v>-5.81</v>
+      </c>
+      <c r="AB661" t="n">
+        <v>1.72</v>
       </c>
       <c r="AG661" t="b">
         <v>0</v>
@@ -78612,10 +78963,13 @@
         </is>
       </c>
       <c r="Z662" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA662" t="n">
         <v>0.34</v>
+      </c>
+      <c r="AB662" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AG662" t="b">
         <v>0</v>
@@ -78730,10 +79084,13 @@
         </is>
       </c>
       <c r="Z663" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA663" t="n">
         <v>-2.8</v>
+      </c>
+      <c r="AB663" t="n">
+        <v>-1.32</v>
       </c>
       <c r="AG663" t="b">
         <v>0</v>
@@ -78848,16 +79205,19 @@
         </is>
       </c>
       <c r="Z664" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA664" t="n">
         <v>-4.53</v>
       </c>
+      <c r="AB664" t="n">
+        <v>-10.8</v>
+      </c>
       <c r="AG664" t="b">
         <v>0</v>
       </c>
       <c r="AH664" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI664" t="inlineStr">
         <is>
@@ -78963,10 +79323,13 @@
         </is>
       </c>
       <c r="Z665" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA665" t="n">
         <v>-1.63</v>
+      </c>
+      <c r="AB665" t="n">
+        <v>3.59</v>
       </c>
       <c r="AG665" t="b">
         <v>0</v>
@@ -79081,10 +79444,13 @@
         </is>
       </c>
       <c r="Z666" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA666" t="n">
         <v>-5.08</v>
+      </c>
+      <c r="AB666" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AG666" t="b">
         <v>0</v>
@@ -79199,10 +79565,13 @@
         </is>
       </c>
       <c r="Z667" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA667" t="n">
         <v>-0.55</v>
+      </c>
+      <c r="AB667" t="n">
+        <v>0.88</v>
       </c>
       <c r="AG667" t="b">
         <v>0</v>
@@ -79317,10 +79686,13 @@
         </is>
       </c>
       <c r="Z668" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA668" t="n">
         <v>-4.02</v>
+      </c>
+      <c r="AB668" t="n">
+        <v>0.72</v>
       </c>
       <c r="AG668" t="b">
         <v>0</v>
@@ -79435,10 +79807,13 @@
         </is>
       </c>
       <c r="Z669" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA669" t="n">
         <v>-5.59</v>
+      </c>
+      <c r="AB669" t="n">
+        <v>0.12</v>
       </c>
       <c r="AG669" t="b">
         <v>0</v>
@@ -79553,10 +79928,13 @@
         </is>
       </c>
       <c r="Z670" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA670" t="n">
         <v>-2.96</v>
+      </c>
+      <c r="AB670" t="n">
+        <v>0.33</v>
       </c>
       <c r="AG670" t="b">
         <v>0</v>
@@ -79671,10 +80049,13 @@
         </is>
       </c>
       <c r="Z671" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA671" t="n">
         <v>-3.26</v>
+      </c>
+      <c r="AB671" t="n">
+        <v>-0.38</v>
       </c>
       <c r="AG671" t="b">
         <v>0</v>
@@ -79789,10 +80170,13 @@
         </is>
       </c>
       <c r="Z672" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA672" t="n">
         <v>-0.86</v>
+      </c>
+      <c r="AB672" t="n">
+        <v>-2.45</v>
       </c>
       <c r="AG672" t="b">
         <v>0</v>
@@ -79907,10 +80291,13 @@
         </is>
       </c>
       <c r="Z673" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA673" t="n">
         <v>-0.18</v>
+      </c>
+      <c r="AB673" t="n">
+        <v>6.63</v>
       </c>
       <c r="AG673" t="b">
         <v>0</v>
@@ -80247,10 +80634,13 @@
         </is>
       </c>
       <c r="Z676" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA676" t="n">
         <v>-5.78</v>
+      </c>
+      <c r="AB676" t="n">
+        <v>-3.4</v>
       </c>
       <c r="AG676" t="b">
         <v>0</v>
@@ -80476,10 +80866,13 @@
         </is>
       </c>
       <c r="Z678" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA678" t="n">
         <v>6.85</v>
+      </c>
+      <c r="AB678" t